--- a/docs/GameBalance.xlsx
+++ b/docs/GameBalance.xlsx
@@ -79,9 +79,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ArtifactsTable" displayName="ArtifactsTable" ref="A3:M26" headerRowCount="1">
-  <x:autoFilter ref="A3:M26"/>
-  <x:tableColumns count="13">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ArtifactsTable" displayName="ArtifactsTable" ref="A3:AA32" headerRowCount="1">
+  <x:autoFilter ref="A3:AA32"/>
+  <x:tableColumns count="27">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="名称"/>
     <x:tableColumn id="3" name="体系"/>
@@ -95,14 +95,28 @@
     <x:tableColumn id="11" name="星级3效果"/>
     <x:tableColumn id="12" name="当前状态（测试中/完成）"/>
     <x:tableColumn id="13" name="备注"/>
+    <x:tableColumn id="14" name="summon_base_count"/>
+    <x:tableColumn id="15" name="summon_hp"/>
+    <x:tableColumn id="16" name="summon_attack"/>
+    <x:tableColumn id="17" name="summon_attack_speed"/>
+    <x:tableColumn id="18" name="summon_move_speed"/>
+    <x:tableColumn id="19" name="summon_combat_radius"/>
+    <x:tableColumn id="20" name="summon_return_radius"/>
+    <x:tableColumn id="21" name="summon_respawn_time"/>
+    <x:tableColumn id="22" name="summon_behavior_type"/>
+    <x:tableColumn id="23" name="summon_special_effect"/>
+    <x:tableColumn id="24" name="tier / 品阶"/>
+    <x:tableColumn id="25" name="cost / 价格"/>
+    <x:tableColumn id="26" name="cultivation_requirement"/>
+    <x:tableColumn id="27" name="shop_weight"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SynergiesTable" displayName="SynergiesTable" ref="A3:H18" headerRowCount="1">
-  <x:autoFilter ref="A3:H18"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SynergiesTable" displayName="SynergiesTable" ref="A3:H16" headerRowCount="1">
+  <x:autoFilter ref="A3:H16"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="名称"/>
@@ -312,22 +326,32 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.75" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="11.25" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="8.75" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="8.75" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16.8799991607666" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="9.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="9.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="9.38" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9.38" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="22.5" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="41.25" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="21.25" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="32.5" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="34" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="32.5" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="12" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="12" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="14" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="14" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="16" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="16" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="16" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="18" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="46" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22.5" customHeight="1">
@@ -380,6 +404,56 @@
       <x:c r="M3" s="6" t="str">
         <x:v>备注</x:v>
       </x:c>
+      <x:c r="N3" s="6" t="str">
+        <x:v>summon_base_count</x:v>
+      </x:c>
+      <x:c r="O3" s="6" t="str">
+        <x:v>summon_hp</x:v>
+      </x:c>
+      <x:c r="P3" s="6" t="str">
+        <x:v>summon_attack</x:v>
+      </x:c>
+      <x:c r="Q3" s="6" t="str">
+        <x:v>summon_attack_speed</x:v>
+      </x:c>
+      <x:c r="R3" s="6" t="str">
+        <x:v>summon_move_speed</x:v>
+      </x:c>
+      <x:c r="S3" s="6" t="str">
+        <x:v>summon_combat_radius</x:v>
+      </x:c>
+      <x:c r="T3" s="6" t="str">
+        <x:v>summon_return_radius</x:v>
+      </x:c>
+      <x:c r="U3" s="6" t="str">
+        <x:v>summon_respawn_time</x:v>
+      </x:c>
+      <x:c r="V3" s="6" t="str">
+        <x:v>summon_behavior_type</x:v>
+      </x:c>
+      <x:c r="W3" s="6" t="str">
+        <x:v>summon_special_effect</x:v>
+      </x:c>
+      <x:c r="X3" t="inlineStr">
+        <x:is>
+          <x:t>tier / 品阶</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y3" t="inlineStr">
+        <x:is>
+          <x:t>cost / 价格</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z3" t="inlineStr">
+        <x:is>
+          <x:t>cultivation_requirement</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AA3" t="inlineStr">
+        <x:is>
+          <x:t>shop_weight</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="4" ht="36" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -392,12 +466,12 @@
         <x:v>阵法</x:v>
       </x:c>
       <x:c r="D4" s="6" t="str">
-        <x:v>风</x:v>
+        <x:v>雷</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
         <x:v>formation / aura / attack_speed</x:v>
       </x:c>
-      <x:c r="F4" s="6" t="n">
+      <x:c r="F4" s="6" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G4" s="6" t="str"/>
@@ -405,7 +479,7 @@
         <x:v>半径 125</x:v>
       </x:c>
       <x:c r="I4" s="6" t="str">
-        <x:v>持续提高玩家法宝攻击速度，并周期性释放小范围风刃脉冲。</x:v>
+        <x:v>持续提高玩家法宝攻击速度，并周期性释放小范围灵刃脉冲。</x:v>
       </x:c>
       <x:c r="J4" s="6" t="str">
         <x:v>伤害 x1.8；冷却 x0.85</x:v>
@@ -418,6 +492,36 @@
       </x:c>
       <x:c r="M4" s="6" t="str">
         <x:v>攻速 +25%</x:v>
+      </x:c>
+      <x:c r="N4" s="6" t="str"/>
+      <x:c r="O4" s="6" t="str"/>
+      <x:c r="P4" s="6" t="str"/>
+      <x:c r="Q4" s="6" t="str"/>
+      <x:c r="R4" s="6" t="str"/>
+      <x:c r="S4" s="6" t="str"/>
+      <x:c r="T4" s="6" t="str"/>
+      <x:c r="U4" s="6" t="str"/>
+      <x:c r="V4" s="6" t="str"/>
+      <x:c r="W4" s="6" t="str"/>
+      <x:c r="X4" t="inlineStr">
+        <x:is>
+          <x:t>通天灵宝</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y4" t="inlineStr">
+        <x:is>
+          <x:t>5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z4" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA4" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="5" ht="36" customHeight="1">
@@ -436,10 +540,10 @@
       <x:c r="E5" s="6" t="str">
         <x:v>projectile / projectile</x:v>
       </x:c>
-      <x:c r="F5" s="6" t="n">
+      <x:c r="F5" s="6" t="str">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="G5" s="6" t="n">
+      <x:c r="G5" s="6" t="str">
         <x:v>1.35</x:v>
       </x:c>
       <x:c r="H5" s="6" t="str">
@@ -459,6 +563,36 @@
       </x:c>
       <x:c r="M5" s="6" t="str">
         <x:v>穿透 +1；攻击扣血 3，低于 30% 不扣；击杀回复 5</x:v>
+      </x:c>
+      <x:c r="N5" s="6" t="str"/>
+      <x:c r="O5" s="6" t="str"/>
+      <x:c r="P5" s="6" t="str"/>
+      <x:c r="Q5" s="6" t="str"/>
+      <x:c r="R5" s="6" t="str"/>
+      <x:c r="S5" s="6" t="str"/>
+      <x:c r="T5" s="6" t="str"/>
+      <x:c r="U5" s="6" t="str"/>
+      <x:c r="V5" s="6" t="str"/>
+      <x:c r="W5" s="6" t="str"/>
+      <x:c r="X5" t="inlineStr">
+        <x:is>
+          <x:t>通天灵宝</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y5" t="inlineStr">
+        <x:is>
+          <x:t>5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z5" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA5" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="6" ht="36" customHeight="1">
@@ -477,10 +611,10 @@
       <x:c r="E6" s="6" t="str">
         <x:v>melee / slash</x:v>
       </x:c>
-      <x:c r="F6" s="6" t="n">
+      <x:c r="F6" s="6" t="str">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G6" s="6" t="n">
+      <x:c r="G6" s="6" t="str">
         <x:v>1.2</x:v>
       </x:c>
       <x:c r="H6" s="6" t="str">
@@ -500,6 +634,36 @@
       </x:c>
       <x:c r="M6" s="6" t="str">
         <x:v>击退 140；攻击扣血 3，低于 30% 不扣；击杀回复 5</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="str"/>
+      <x:c r="O6" s="6" t="str"/>
+      <x:c r="P6" s="6" t="str"/>
+      <x:c r="Q6" s="6" t="str"/>
+      <x:c r="R6" s="6" t="str"/>
+      <x:c r="S6" s="6" t="str"/>
+      <x:c r="T6" s="6" t="str"/>
+      <x:c r="U6" s="6" t="str"/>
+      <x:c r="V6" s="6" t="str"/>
+      <x:c r="W6" s="6" t="str"/>
+      <x:c r="X6" t="inlineStr">
+        <x:is>
+          <x:t>古宝</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y6" t="inlineStr">
+        <x:is>
+          <x:t>4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z6" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA6" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="7" ht="36" customHeight="1">
@@ -518,10 +682,10 @@
       <x:c r="E7" s="6" t="str">
         <x:v>line_delayed / line</x:v>
       </x:c>
-      <x:c r="F7" s="6" t="n">
+      <x:c r="F7" s="6" t="str">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="G7" s="6" t="n">
+      <x:c r="G7" s="6" t="str">
         <x:v>1.7</x:v>
       </x:c>
       <x:c r="H7" s="6" t="str">
@@ -540,6 +704,36 @@
         <x:v>测试中</x:v>
       </x:c>
       <x:c r="M7" s="6" t="str"/>
+      <x:c r="N7" s="6" t="str"/>
+      <x:c r="O7" s="6" t="str"/>
+      <x:c r="P7" s="6" t="str"/>
+      <x:c r="Q7" s="6" t="str"/>
+      <x:c r="R7" s="6" t="str"/>
+      <x:c r="S7" s="6" t="str"/>
+      <x:c r="T7" s="6" t="str"/>
+      <x:c r="U7" s="6" t="str"/>
+      <x:c r="V7" s="6" t="str"/>
+      <x:c r="W7" s="6" t="str"/>
+      <x:c r="X7" t="inlineStr">
+        <x:is>
+          <x:t>灵器</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y7" t="inlineStr">
+        <x:is>
+          <x:t>3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z7" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA7" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="8" ht="36" customHeight="1">
       <x:c r="A8" s="6" t="str">
@@ -557,10 +751,10 @@
       <x:c r="E8" s="6" t="str">
         <x:v>projectile / circle</x:v>
       </x:c>
-      <x:c r="F8" s="6" t="n">
+      <x:c r="F8" s="6" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G8" s="6" t="n">
+      <x:c r="G8" s="6" t="str">
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="H8" s="6" t="str">
@@ -580,6 +774,36 @@
       </x:c>
       <x:c r="M8" s="6" t="str">
         <x:v>弹射 2</x:v>
+      </x:c>
+      <x:c r="N8" s="6" t="str"/>
+      <x:c r="O8" s="6" t="str"/>
+      <x:c r="P8" s="6" t="str"/>
+      <x:c r="Q8" s="6" t="str"/>
+      <x:c r="R8" s="6" t="str"/>
+      <x:c r="S8" s="6" t="str"/>
+      <x:c r="T8" s="6" t="str"/>
+      <x:c r="U8" s="6" t="str"/>
+      <x:c r="V8" s="6" t="str"/>
+      <x:c r="W8" s="6" t="str"/>
+      <x:c r="X8" t="inlineStr">
+        <x:is>
+          <x:t>法器</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y8" t="inlineStr">
+        <x:is>
+          <x:t>2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z8" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA8" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="9" ht="36" customHeight="1">
@@ -598,10 +822,10 @@
       <x:c r="E9" s="6" t="str">
         <x:v>melee / stab</x:v>
       </x:c>
-      <x:c r="F9" s="6" t="n">
+      <x:c r="F9" s="6" t="str">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G9" s="6" t="n">
+      <x:c r="G9" s="6" t="str">
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="H9" s="6" t="str">
@@ -620,6 +844,36 @@
         <x:v>测试中</x:v>
       </x:c>
       <x:c r="M9" s="6" t="str"/>
+      <x:c r="N9" s="6" t="str"/>
+      <x:c r="O9" s="6" t="str"/>
+      <x:c r="P9" s="6" t="str"/>
+      <x:c r="Q9" s="6" t="str"/>
+      <x:c r="R9" s="6" t="str"/>
+      <x:c r="S9" s="6" t="str"/>
+      <x:c r="T9" s="6" t="str"/>
+      <x:c r="U9" s="6" t="str"/>
+      <x:c r="V9" s="6" t="str"/>
+      <x:c r="W9" s="6" t="str"/>
+      <x:c r="X9" t="inlineStr">
+        <x:is>
+          <x:t>凡品</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y9" t="inlineStr">
+        <x:is>
+          <x:t>1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z9" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA9" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="10" ht="36" customHeight="1">
       <x:c r="A10" s="6" t="str">
@@ -637,7 +891,7 @@
       <x:c r="E10" s="6" t="str">
         <x:v>formation / aura / damage</x:v>
       </x:c>
-      <x:c r="F10" s="6" t="n">
+      <x:c r="F10" s="6" t="str">
         <x:v>7</x:v>
       </x:c>
       <x:c r="G10" s="6" t="str"/>
@@ -657,6 +911,36 @@
         <x:v>测试中</x:v>
       </x:c>
       <x:c r="M10" s="6" t="str"/>
+      <x:c r="N10" s="6" t="str"/>
+      <x:c r="O10" s="6" t="str"/>
+      <x:c r="P10" s="6" t="str"/>
+      <x:c r="Q10" s="6" t="str"/>
+      <x:c r="R10" s="6" t="str"/>
+      <x:c r="S10" s="6" t="str"/>
+      <x:c r="T10" s="6" t="str"/>
+      <x:c r="U10" s="6" t="str"/>
+      <x:c r="V10" s="6" t="str"/>
+      <x:c r="W10" s="6" t="str"/>
+      <x:c r="X10" t="inlineStr">
+        <x:is>
+          <x:t>灵器</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y10" t="inlineStr">
+        <x:is>
+          <x:t>3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z10" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA10" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="11" ht="36" customHeight="1">
       <x:c r="A11" s="6" t="str">
@@ -674,10 +958,10 @@
       <x:c r="E11" s="6" t="str">
         <x:v>projectile / circle</x:v>
       </x:c>
-      <x:c r="F11" s="6" t="n">
+      <x:c r="F11" s="6" t="str">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G11" s="6" t="n">
+      <x:c r="G11" s="6" t="str">
         <x:v>1.35</x:v>
       </x:c>
       <x:c r="H11" s="6" t="str">
@@ -697,6 +981,36 @@
       </x:c>
       <x:c r="M11" s="6" t="str">
         <x:v>爆炸半径 60</x:v>
+      </x:c>
+      <x:c r="N11" s="6" t="str"/>
+      <x:c r="O11" s="6" t="str"/>
+      <x:c r="P11" s="6" t="str"/>
+      <x:c r="Q11" s="6" t="str"/>
+      <x:c r="R11" s="6" t="str"/>
+      <x:c r="S11" s="6" t="str"/>
+      <x:c r="T11" s="6" t="str"/>
+      <x:c r="U11" s="6" t="str"/>
+      <x:c r="V11" s="6" t="str"/>
+      <x:c r="W11" s="6" t="str"/>
+      <x:c r="X11" t="inlineStr">
+        <x:is>
+          <x:t>凡品</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y11" t="inlineStr">
+        <x:is>
+          <x:t>1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z11" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA11" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="12" ht="36" customHeight="1">
@@ -715,17 +1029,17 @@
       <x:c r="E12" s="6" t="str">
         <x:v>melee / stab</x:v>
       </x:c>
-      <x:c r="F12" s="6" t="n">
+      <x:c r="F12" s="6" t="str">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G12" s="6" t="n">
+      <x:c r="G12" s="6" t="str">
         <x:v>0.38</x:v>
       </x:c>
       <x:c r="H12" s="6" t="str">
         <x:v>长度 76 / 宽度 32</x:v>
       </x:c>
       <x:c r="I12" s="6" t="str">
-        <x:v>快速近身拳风打击最近敌人，伤害高于远程法宝。</x:v>
+        <x:v>快速近身拳劲打击最近敌人，伤害高于远程法宝。</x:v>
       </x:c>
       <x:c r="J12" s="6" t="str">
         <x:v>伤害 x1.8；冷却 x0.85</x:v>
@@ -738,6 +1052,36 @@
       </x:c>
       <x:c r="M12" s="6" t="str">
         <x:v>击退 120</x:v>
+      </x:c>
+      <x:c r="N12" s="6" t="str"/>
+      <x:c r="O12" s="6" t="str"/>
+      <x:c r="P12" s="6" t="str"/>
+      <x:c r="Q12" s="6" t="str"/>
+      <x:c r="R12" s="6" t="str"/>
+      <x:c r="S12" s="6" t="str"/>
+      <x:c r="T12" s="6" t="str"/>
+      <x:c r="U12" s="6" t="str"/>
+      <x:c r="V12" s="6" t="str"/>
+      <x:c r="W12" s="6" t="str"/>
+      <x:c r="X12" t="inlineStr">
+        <x:is>
+          <x:t>凡品</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y12" t="inlineStr">
+        <x:is>
+          <x:t>1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z12" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA12" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="13" ht="36" customHeight="1">
@@ -756,7 +1100,7 @@
       <x:c r="E13" s="6" t="str">
         <x:v>formation / aura / damage</x:v>
       </x:c>
-      <x:c r="F13" s="6" t="n">
+      <x:c r="F13" s="6" t="str">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G13" s="6" t="str"/>
@@ -776,6 +1120,36 @@
         <x:v>测试中</x:v>
       </x:c>
       <x:c r="M13" s="6" t="str"/>
+      <x:c r="N13" s="6" t="str"/>
+      <x:c r="O13" s="6" t="str"/>
+      <x:c r="P13" s="6" t="str"/>
+      <x:c r="Q13" s="6" t="str"/>
+      <x:c r="R13" s="6" t="str"/>
+      <x:c r="S13" s="6" t="str"/>
+      <x:c r="T13" s="6" t="str"/>
+      <x:c r="U13" s="6" t="str"/>
+      <x:c r="V13" s="6" t="str"/>
+      <x:c r="W13" s="6" t="str"/>
+      <x:c r="X13" t="inlineStr">
+        <x:is>
+          <x:t>古宝</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y13" t="inlineStr">
+        <x:is>
+          <x:t>4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z13" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA13" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="14" ht="36" customHeight="1">
       <x:c r="A14" s="6" t="str">
@@ -793,10 +1167,10 @@
       <x:c r="E14" s="6" t="str">
         <x:v>projectile / projectile</x:v>
       </x:c>
-      <x:c r="F14" s="6" t="n">
+      <x:c r="F14" s="6" t="str">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G14" s="6" t="n">
+      <x:c r="G14" s="6" t="str">
         <x:v>0.95</x:v>
       </x:c>
       <x:c r="H14" s="6" t="str">
@@ -816,6 +1190,36 @@
       </x:c>
       <x:c r="M14" s="6" t="str">
         <x:v>穿透 +1</x:v>
+      </x:c>
+      <x:c r="N14" s="6" t="str"/>
+      <x:c r="O14" s="6" t="str"/>
+      <x:c r="P14" s="6" t="str"/>
+      <x:c r="Q14" s="6" t="str"/>
+      <x:c r="R14" s="6" t="str"/>
+      <x:c r="S14" s="6" t="str"/>
+      <x:c r="T14" s="6" t="str"/>
+      <x:c r="U14" s="6" t="str"/>
+      <x:c r="V14" s="6" t="str"/>
+      <x:c r="W14" s="6" t="str"/>
+      <x:c r="X14" t="inlineStr">
+        <x:is>
+          <x:t>法器</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y14" t="inlineStr">
+        <x:is>
+          <x:t>2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z14" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA14" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="15" ht="36" customHeight="1">
@@ -854,6 +1258,36 @@
       <x:c r="M15" s="6" t="str">
         <x:v>护盾 12，上限 36</x:v>
       </x:c>
+      <x:c r="N15" s="6" t="str"/>
+      <x:c r="O15" s="6" t="str"/>
+      <x:c r="P15" s="6" t="str"/>
+      <x:c r="Q15" s="6" t="str"/>
+      <x:c r="R15" s="6" t="str"/>
+      <x:c r="S15" s="6" t="str"/>
+      <x:c r="T15" s="6" t="str"/>
+      <x:c r="U15" s="6" t="str"/>
+      <x:c r="V15" s="6" t="str"/>
+      <x:c r="W15" s="6" t="str"/>
+      <x:c r="X15" t="inlineStr">
+        <x:is>
+          <x:t>灵器</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y15" t="inlineStr">
+        <x:is>
+          <x:t>3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z15" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA15" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="16" ht="36" customHeight="1">
       <x:c r="A16" s="6" t="str">
@@ -871,10 +1305,10 @@
       <x:c r="E16" s="6" t="str">
         <x:v>orbit</x:v>
       </x:c>
-      <x:c r="F16" s="6" t="n">
+      <x:c r="F16" s="6" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G16" s="6" t="n">
+      <x:c r="G16" s="6" t="str">
         <x:v>0.85</x:v>
       </x:c>
       <x:c r="H16" s="6" t="str">
@@ -893,6 +1327,36 @@
         <x:v>测试中</x:v>
       </x:c>
       <x:c r="M16" s="6" t="str"/>
+      <x:c r="N16" s="6" t="str"/>
+      <x:c r="O16" s="6" t="str"/>
+      <x:c r="P16" s="6" t="str"/>
+      <x:c r="Q16" s="6" t="str"/>
+      <x:c r="R16" s="6" t="str"/>
+      <x:c r="S16" s="6" t="str"/>
+      <x:c r="T16" s="6" t="str"/>
+      <x:c r="U16" s="6" t="str"/>
+      <x:c r="V16" s="6" t="str"/>
+      <x:c r="W16" s="6" t="str"/>
+      <x:c r="X16" t="inlineStr">
+        <x:is>
+          <x:t>古宝</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y16" t="inlineStr">
+        <x:is>
+          <x:t>4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z16" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA16" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="17" ht="36" customHeight="1">
       <x:c r="A17" s="6" t="str">
@@ -905,15 +1369,15 @@
         <x:v>法修</x:v>
       </x:c>
       <x:c r="D17" s="6" t="str">
-        <x:v>风</x:v>
+        <x:v>木</x:v>
       </x:c>
       <x:c r="E17" s="6" t="str">
         <x:v>projectile / circle</x:v>
       </x:c>
-      <x:c r="F17" s="6" t="n">
+      <x:c r="F17" s="6" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G17" s="6" t="n">
+      <x:c r="G17" s="6" t="str">
         <x:v>1.15</x:v>
       </x:c>
       <x:c r="H17" s="6" t="str">
@@ -932,6 +1396,36 @@
         <x:v>测试中</x:v>
       </x:c>
       <x:c r="M17" s="6" t="str"/>
+      <x:c r="N17" s="6" t="str"/>
+      <x:c r="O17" s="6" t="str"/>
+      <x:c r="P17" s="6" t="str"/>
+      <x:c r="Q17" s="6" t="str"/>
+      <x:c r="R17" s="6" t="str"/>
+      <x:c r="S17" s="6" t="str"/>
+      <x:c r="T17" s="6" t="str"/>
+      <x:c r="U17" s="6" t="str"/>
+      <x:c r="V17" s="6" t="str"/>
+      <x:c r="W17" s="6" t="str"/>
+      <x:c r="X17" t="inlineStr">
+        <x:is>
+          <x:t>法器</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y17" t="inlineStr">
+        <x:is>
+          <x:t>2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z17" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA17" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="18" ht="36" customHeight="1">
       <x:c r="A18" s="6" t="str">
@@ -949,7 +1443,7 @@
       <x:c r="E18" s="6" t="str">
         <x:v>formation / aura / heal</x:v>
       </x:c>
-      <x:c r="F18" s="6" t="n">
+      <x:c r="F18" s="6" t="str">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G18" s="6" t="str"/>
@@ -971,6 +1465,36 @@
       <x:c r="M18" s="6" t="str">
         <x:v>治疗 3</x:v>
       </x:c>
+      <x:c r="N18" s="6" t="str"/>
+      <x:c r="O18" s="6" t="str"/>
+      <x:c r="P18" s="6" t="str"/>
+      <x:c r="Q18" s="6" t="str"/>
+      <x:c r="R18" s="6" t="str"/>
+      <x:c r="S18" s="6" t="str"/>
+      <x:c r="T18" s="6" t="str"/>
+      <x:c r="U18" s="6" t="str"/>
+      <x:c r="V18" s="6" t="str"/>
+      <x:c r="W18" s="6" t="str"/>
+      <x:c r="X18" t="inlineStr">
+        <x:is>
+          <x:t>法器</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y18" t="inlineStr">
+        <x:is>
+          <x:t>2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z18" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA18" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="19" ht="36" customHeight="1">
       <x:c r="A19" s="6" t="str">
@@ -988,10 +1512,10 @@
       <x:c r="E19" s="6" t="str">
         <x:v>beam / beam</x:v>
       </x:c>
-      <x:c r="F19" s="6" t="n">
+      <x:c r="F19" s="6" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G19" s="6" t="n">
+      <x:c r="G19" s="6" t="str">
         <x:v>3</x:v>
       </x:c>
       <x:c r="H19" s="6" t="str">
@@ -1010,6 +1534,36 @@
         <x:v>测试中</x:v>
       </x:c>
       <x:c r="M19" s="6" t="str"/>
+      <x:c r="N19" s="6" t="str"/>
+      <x:c r="O19" s="6" t="str"/>
+      <x:c r="P19" s="6" t="str"/>
+      <x:c r="Q19" s="6" t="str"/>
+      <x:c r="R19" s="6" t="str"/>
+      <x:c r="S19" s="6" t="str"/>
+      <x:c r="T19" s="6" t="str"/>
+      <x:c r="U19" s="6" t="str"/>
+      <x:c r="V19" s="6" t="str"/>
+      <x:c r="W19" s="6" t="str"/>
+      <x:c r="X19" t="inlineStr">
+        <x:is>
+          <x:t>通天灵宝</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y19" t="inlineStr">
+        <x:is>
+          <x:t>5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z19" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA19" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="20" ht="36" customHeight="1">
       <x:c r="A20" s="6" t="str">
@@ -1027,29 +1581,59 @@
       <x:c r="E20" s="6" t="str">
         <x:v>melee / circle</x:v>
       </x:c>
-      <x:c r="F20" s="6" t="n">
+      <x:c r="F20" s="6" t="str">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G20" s="6" t="n">
+      <x:c r="G20" s="6" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H20" s="6" t="str">
         <x:v>半径 98</x:v>
       </x:c>
       <x:c r="I20" s="6" t="str">
-        <x:v>贴身旋风扫腿，对周围一圈敌人造成较高伤害并轻微击退。</x:v>
+        <x:v>贴身旋身扫腿，对周围一圈敌人造成较高伤害并轻微击退。</x:v>
       </x:c>
       <x:c r="J20" s="6" t="str">
         <x:v>伤害 x1.8；冷却 x0.85</x:v>
       </x:c>
       <x:c r="K20" s="6" t="str">
-        <x:v>伤害 x3.0；冷却 x0.7；旋风腿范围 +50%</x:v>
+        <x:v>伤害 x3.0；冷却 x0.7；旋身腿范围 +50%</x:v>
       </x:c>
       <x:c r="L20" s="6" t="str">
         <x:v>测试中</x:v>
       </x:c>
       <x:c r="M20" s="6" t="str">
         <x:v>击退 90</x:v>
+      </x:c>
+      <x:c r="N20" s="6" t="str"/>
+      <x:c r="O20" s="6" t="str"/>
+      <x:c r="P20" s="6" t="str"/>
+      <x:c r="Q20" s="6" t="str"/>
+      <x:c r="R20" s="6" t="str"/>
+      <x:c r="S20" s="6" t="str"/>
+      <x:c r="T20" s="6" t="str"/>
+      <x:c r="U20" s="6" t="str"/>
+      <x:c r="V20" s="6" t="str"/>
+      <x:c r="W20" s="6" t="str"/>
+      <x:c r="X20" t="inlineStr">
+        <x:is>
+          <x:t>法器</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y20" t="inlineStr">
+        <x:is>
+          <x:t>2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z20" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA20" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="21" ht="36" customHeight="1">
@@ -1063,15 +1647,15 @@
         <x:v>剑修</x:v>
       </x:c>
       <x:c r="D21" s="6" t="str">
-        <x:v>风</x:v>
+        <x:v>金</x:v>
       </x:c>
       <x:c r="E21" s="6" t="str">
         <x:v>melee / stab</x:v>
       </x:c>
-      <x:c r="F21" s="6" t="n">
+      <x:c r="F21" s="6" t="str">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G21" s="6" t="n">
+      <x:c r="G21" s="6" t="str">
         <x:v>1.05</x:v>
       </x:c>
       <x:c r="H21" s="6" t="str">
@@ -1090,6 +1674,36 @@
         <x:v>测试中</x:v>
       </x:c>
       <x:c r="M21" s="6" t="str"/>
+      <x:c r="N21" s="6" t="str"/>
+      <x:c r="O21" s="6" t="str"/>
+      <x:c r="P21" s="6" t="str"/>
+      <x:c r="Q21" s="6" t="str"/>
+      <x:c r="R21" s="6" t="str"/>
+      <x:c r="S21" s="6" t="str"/>
+      <x:c r="T21" s="6" t="str"/>
+      <x:c r="U21" s="6" t="str"/>
+      <x:c r="V21" s="6" t="str"/>
+      <x:c r="W21" s="6" t="str"/>
+      <x:c r="X21" t="inlineStr">
+        <x:is>
+          <x:t>灵器</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y21" t="inlineStr">
+        <x:is>
+          <x:t>3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z21" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA21" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="22" ht="36" customHeight="1">
       <x:c r="A22" s="6" t="str">
@@ -1107,10 +1721,10 @@
       <x:c r="E22" s="6" t="str">
         <x:v>projectile / circle</x:v>
       </x:c>
-      <x:c r="F22" s="6" t="n">
+      <x:c r="F22" s="6" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G22" s="6" t="n">
+      <x:c r="G22" s="6" t="str">
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="H22" s="6" t="str">
@@ -1130,6 +1744,36 @@
       </x:c>
       <x:c r="M22" s="6" t="str">
         <x:v>穿透 +3</x:v>
+      </x:c>
+      <x:c r="N22" s="6" t="str"/>
+      <x:c r="O22" s="6" t="str"/>
+      <x:c r="P22" s="6" t="str"/>
+      <x:c r="Q22" s="6" t="str"/>
+      <x:c r="R22" s="6" t="str"/>
+      <x:c r="S22" s="6" t="str"/>
+      <x:c r="T22" s="6" t="str"/>
+      <x:c r="U22" s="6" t="str"/>
+      <x:c r="V22" s="6" t="str"/>
+      <x:c r="W22" s="6" t="str"/>
+      <x:c r="X22" t="inlineStr">
+        <x:is>
+          <x:t>灵器</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y22" t="inlineStr">
+        <x:is>
+          <x:t>3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z22" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA22" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="23" ht="36" customHeight="1">
@@ -1148,10 +1792,10 @@
       <x:c r="E23" s="6" t="str">
         <x:v>melee / slash</x:v>
       </x:c>
-      <x:c r="F23" s="6" t="n">
+      <x:c r="F23" s="6" t="str">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="G23" s="6" t="n">
+      <x:c r="G23" s="6" t="str">
         <x:v>0.75</x:v>
       </x:c>
       <x:c r="H23" s="6" t="str">
@@ -1170,6 +1814,36 @@
         <x:v>测试中</x:v>
       </x:c>
       <x:c r="M23" s="6" t="str"/>
+      <x:c r="N23" s="6" t="str"/>
+      <x:c r="O23" s="6" t="str"/>
+      <x:c r="P23" s="6" t="str"/>
+      <x:c r="Q23" s="6" t="str"/>
+      <x:c r="R23" s="6" t="str"/>
+      <x:c r="S23" s="6" t="str"/>
+      <x:c r="T23" s="6" t="str"/>
+      <x:c r="U23" s="6" t="str"/>
+      <x:c r="V23" s="6" t="str"/>
+      <x:c r="W23" s="6" t="str"/>
+      <x:c r="X23" t="inlineStr">
+        <x:is>
+          <x:t>凡品</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y23" t="inlineStr">
+        <x:is>
+          <x:t>1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z23" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA23" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="24" ht="36" customHeight="1">
       <x:c r="A24" s="6" t="str">
@@ -1187,29 +1861,59 @@
       <x:c r="E24" s="6" t="str">
         <x:v>melee / slash</x:v>
       </x:c>
-      <x:c r="F24" s="6" t="n">
+      <x:c r="F24" s="6" t="str">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G24" s="6" t="n">
+      <x:c r="G24" s="6" t="str">
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="H24" s="6" t="str">
         <x:v>长度 112 / 宽度 110</x:v>
       </x:c>
       <x:c r="I24" s="6" t="str">
-        <x:v>挥出爆发掌风打击前方扇形敌人，并将敌人击退。</x:v>
+        <x:v>挥出爆发掌劲打击前方扇形敌人，并将敌人击退。</x:v>
       </x:c>
       <x:c r="J24" s="6" t="str">
         <x:v>伤害 x1.8；冷却 x0.85</x:v>
       </x:c>
       <x:c r="K24" s="6" t="str">
-        <x:v>伤害 x3.0；冷却 x0.7；掌风角度 +50%</x:v>
+        <x:v>伤害 x3.0；冷却 x0.7；掌劲角度 +50%</x:v>
       </x:c>
       <x:c r="L24" s="6" t="str">
         <x:v>测试中</x:v>
       </x:c>
       <x:c r="M24" s="6" t="str">
         <x:v>击退 360</x:v>
+      </x:c>
+      <x:c r="N24" s="6" t="str"/>
+      <x:c r="O24" s="6" t="str"/>
+      <x:c r="P24" s="6" t="str"/>
+      <x:c r="Q24" s="6" t="str"/>
+      <x:c r="R24" s="6" t="str"/>
+      <x:c r="S24" s="6" t="str"/>
+      <x:c r="T24" s="6" t="str"/>
+      <x:c r="U24" s="6" t="str"/>
+      <x:c r="V24" s="6" t="str"/>
+      <x:c r="W24" s="6" t="str"/>
+      <x:c r="X24" t="inlineStr">
+        <x:is>
+          <x:t>法器</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y24" t="inlineStr">
+        <x:is>
+          <x:t>2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z24" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA24" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="25" ht="36" customHeight="1">
@@ -1228,10 +1932,10 @@
       <x:c r="E25" s="6" t="str">
         <x:v>projectile / projectile</x:v>
       </x:c>
-      <x:c r="F25" s="6" t="n">
+      <x:c r="F25" s="6" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G25" s="6" t="n">
+      <x:c r="G25" s="6" t="str">
         <x:v>0.65</x:v>
       </x:c>
       <x:c r="H25" s="6" t="str">
@@ -1251,6 +1955,36 @@
       </x:c>
       <x:c r="M25" s="6" t="str">
         <x:v>中毒 3/秒，3秒</x:v>
+      </x:c>
+      <x:c r="N25" s="6" t="str"/>
+      <x:c r="O25" s="6" t="str"/>
+      <x:c r="P25" s="6" t="str"/>
+      <x:c r="Q25" s="6" t="str"/>
+      <x:c r="R25" s="6" t="str"/>
+      <x:c r="S25" s="6" t="str"/>
+      <x:c r="T25" s="6" t="str"/>
+      <x:c r="U25" s="6" t="str"/>
+      <x:c r="V25" s="6" t="str"/>
+      <x:c r="W25" s="6" t="str"/>
+      <x:c r="X25" t="inlineStr">
+        <x:is>
+          <x:t>古宝</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y25" t="inlineStr">
+        <x:is>
+          <x:t>4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z25" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA25" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="26" ht="36" customHeight="1">
@@ -1269,7 +2003,7 @@
       <x:c r="E26" s="6" t="str">
         <x:v>formation / aura / slow</x:v>
       </x:c>
-      <x:c r="F26" s="6" t="n">
+      <x:c r="F26" s="6" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G26" s="6" t="str"/>
@@ -1291,15 +2025,591 @@
       <x:c r="M26" s="6" t="str">
         <x:v>减速 35%</x:v>
       </x:c>
+      <x:c r="N26" s="6" t="str"/>
+      <x:c r="O26" s="6" t="str"/>
+      <x:c r="P26" s="6" t="str"/>
+      <x:c r="Q26" s="6" t="str"/>
+      <x:c r="R26" s="6" t="str"/>
+      <x:c r="S26" s="6" t="str"/>
+      <x:c r="T26" s="6" t="str"/>
+      <x:c r="U26" s="6" t="str"/>
+      <x:c r="V26" s="6" t="str"/>
+      <x:c r="W26" s="6" t="str"/>
+      <x:c r="X26" t="inlineStr">
+        <x:is>
+          <x:t>凡品</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y26" t="inlineStr">
+        <x:is>
+          <x:t>1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z26" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA26" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="36" customHeight="1">
+      <x:c r="A27" s="6" t="str">
+        <x:v>sword_puppet</x:v>
+      </x:c>
+      <x:c r="B27" s="6" t="str">
+        <x:v>剑傀儡</x:v>
+      </x:c>
+      <x:c r="C27" s="6" t="str">
+        <x:v>召唤</x:v>
+      </x:c>
+      <x:c r="D27" s="6" t="str">
+        <x:v>金</x:v>
+      </x:c>
+      <x:c r="E27" s="6" t="str">
+        <x:v>summon / slash / melee</x:v>
+      </x:c>
+      <x:c r="F27" s="6" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G27" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H27" s="6" t="str">
+        <x:v>combat 500 / return 700</x:v>
+      </x:c>
+      <x:c r="I27" s="6" t="str">
+        <x:v>基础数量1；生命100；攻击15；攻速1.0；近战扇形挥砍；6秒重生</x:v>
+      </x:c>
+      <x:c r="J27" s="6" t="str">
+        <x:v>生命+50%；攻击+50%</x:v>
+      </x:c>
+      <x:c r="K27" s="6" t="str">
+        <x:v>攻击范围+30%；每第三次攻击造成200%伤害</x:v>
+      </x:c>
+      <x:c r="L27" s="6" t="str">
+        <x:v>测试中</x:v>
+      </x:c>
+      <x:c r="M27" s="6" t="str">
+        <x:v>近战主力输出</x:v>
+      </x:c>
+      <x:c r="N27" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O27" s="6" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="P27" s="6" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q27" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R27" s="6" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="S27" s="6" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="T27" s="6" t="n">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="U27" s="6" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="V27" s="6" t="str">
+        <x:v>melee</x:v>
+      </x:c>
+      <x:c r="W27" s="6" t="str">
+        <x:v>追击最近敌人，近战扇形挥砍</x:v>
+      </x:c>
+      <x:c r="X27" t="inlineStr">
+        <x:is>
+          <x:t>凡品</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y27" t="inlineStr">
+        <x:is>
+          <x:t>1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z27" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA27" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="36" customHeight="1">
+      <x:c r="A28" s="6" t="str">
+        <x:v>crossbow_puppet</x:v>
+      </x:c>
+      <x:c r="B28" s="6" t="str">
+        <x:v>弩傀儡</x:v>
+      </x:c>
+      <x:c r="C28" s="6" t="str">
+        <x:v>召唤</x:v>
+      </x:c>
+      <x:c r="D28" s="6" t="str">
+        <x:v>雷</x:v>
+      </x:c>
+      <x:c r="E28" s="6" t="str">
+        <x:v>summon / projectile / ranged</x:v>
+      </x:c>
+      <x:c r="F28" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G28" s="6" t="n">
+        <x:v>0.67</x:v>
+      </x:c>
+      <x:c r="H28" s="6" t="str">
+        <x:v>combat 600 / return 700</x:v>
+      </x:c>
+      <x:c r="I28" s="6" t="str">
+        <x:v>基础数量1；生命70；攻击10；攻速1.5；保持距离发射灵能箭；6秒重生</x:v>
+      </x:c>
+      <x:c r="J28" s="6" t="str">
+        <x:v>攻击+50%；攻速+30%</x:v>
+      </x:c>
+      <x:c r="K28" s="6" t="str">
+        <x:v>灵能箭弹射1次</x:v>
+      </x:c>
+      <x:c r="L28" s="6" t="str">
+        <x:v>测试中</x:v>
+      </x:c>
+      <x:c r="M28" s="6" t="str">
+        <x:v>后排持续输出</x:v>
+      </x:c>
+      <x:c r="N28" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O28" s="6" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="P28" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q28" s="6" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="R28" s="6" t="n">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="S28" s="6" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="T28" s="6" t="n">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="U28" s="6" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="V28" s="6" t="str">
+        <x:v>ranged</x:v>
+      </x:c>
+      <x:c r="W28" s="6" t="str">
+        <x:v>保持距离，优先攻击最近敌人</x:v>
+      </x:c>
+      <x:c r="X28" t="inlineStr">
+        <x:is>
+          <x:t>灵器</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y28" t="inlineStr">
+        <x:is>
+          <x:t>3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z28" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA28" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="36" customHeight="1">
+      <x:c r="A29" s="6" t="str">
+        <x:v>iron_guard_puppet</x:v>
+      </x:c>
+      <x:c r="B29" s="6" t="str">
+        <x:v>铁卫傀儡</x:v>
+      </x:c>
+      <x:c r="C29" s="6" t="str">
+        <x:v>召唤</x:v>
+      </x:c>
+      <x:c r="D29" s="6" t="str">
+        <x:v>土</x:v>
+      </x:c>
+      <x:c r="E29" s="6" t="str">
+        <x:v>summon / melee / tank</x:v>
+      </x:c>
+      <x:c r="F29" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G29" s="6" t="n">
+        <x:v>1.43</x:v>
+      </x:c>
+      <x:c r="H29" s="6" t="str">
+        <x:v>combat 450 / return 600</x:v>
+      </x:c>
+      <x:c r="I29" s="6" t="str">
+        <x:v>基础数量1；生命300；攻击8；攻速0.7；每5秒嘲讽半径300内敌人2秒；8秒重生</x:v>
+      </x:c>
+      <x:c r="J29" s="6" t="str">
+        <x:v>生命+80%</x:v>
+      </x:c>
+      <x:c r="K29" s="6" t="str">
+        <x:v>嘲讽范围+50%；受到攻击时释放震荡波</x:v>
+      </x:c>
+      <x:c r="L29" s="6" t="str">
+        <x:v>测试中</x:v>
+      </x:c>
+      <x:c r="M29" s="6" t="str">
+        <x:v>尽量站在玩家与怪群之间</x:v>
+      </x:c>
+      <x:c r="N29" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O29" s="6" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="P29" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="Q29" s="6" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="R29" s="6" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="S29" s="6" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="T29" s="6" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="U29" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="V29" s="6" t="str">
+        <x:v>tank</x:v>
+      </x:c>
+      <x:c r="W29" s="6" t="str">
+        <x:v>5秒嘲讽；阻挡怪群</x:v>
+      </x:c>
+      <x:c r="X29" t="inlineStr">
+        <x:is>
+          <x:t>古宝</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y29" t="inlineStr">
+        <x:is>
+          <x:t>4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z29" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA29" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="36" customHeight="1">
+      <x:c r="A30" s="6" t="str">
+        <x:v>turret</x:v>
+      </x:c>
+      <x:c r="B30" s="6" t="str">
+        <x:v>炮台</x:v>
+      </x:c>
+      <x:c r="C30" s="6" t="str">
+        <x:v>召唤</x:v>
+      </x:c>
+      <x:c r="D30" s="6" t="str">
+        <x:v>火</x:v>
+      </x:c>
+      <x:c r="E30" s="6" t="str">
+        <x:v>summon / projectile / turret</x:v>
+      </x:c>
+      <x:c r="F30" s="6" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G30" s="6" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="H30" s="6" t="str">
+        <x:v>combat 700 / redeploy 900</x:v>
+      </x:c>
+      <x:c r="I30" s="6" t="str">
+        <x:v>基础数量1；生命120；攻击18；攻速0.8；固定炮台发射小范围爆炸炮弹；10秒重生</x:v>
+      </x:c>
+      <x:c r="J30" s="6" t="str">
+        <x:v>攻击+50%</x:v>
+      </x:c>
+      <x:c r="K30" s="6" t="str">
+        <x:v>爆炸范围+50%</x:v>
+      </x:c>
+      <x:c r="L30" s="6" t="str">
+        <x:v>测试中</x:v>
+      </x:c>
+      <x:c r="M30" s="6" t="str">
+        <x:v>玩家距离超过900时，2秒后在玩家附近重新建造</x:v>
+      </x:c>
+      <x:c r="N30" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O30" s="6" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="P30" s="6" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="Q30" s="6" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="R30" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S30" s="6" t="n">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="T30" s="6" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="U30" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="V30" s="6" t="str">
+        <x:v>turret</x:v>
+      </x:c>
+      <x:c r="W30" s="6" t="str">
+        <x:v>固定不移动，超距重新部署</x:v>
+      </x:c>
+      <x:c r="X30" t="inlineStr">
+        <x:is>
+          <x:t>法器</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y30" t="inlineStr">
+        <x:is>
+          <x:t>2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z30" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA30" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="36" customHeight="1">
+      <x:c r="A31" s="6" t="str">
+        <x:v>ghost</x:v>
+      </x:c>
+      <x:c r="B31" s="6" t="str">
+        <x:v>幽魂</x:v>
+      </x:c>
+      <x:c r="C31" s="6" t="str">
+        <x:v>召唤</x:v>
+      </x:c>
+      <x:c r="D31" s="6" t="str">
+        <x:v>水</x:v>
+      </x:c>
+      <x:c r="E31" s="6" t="str">
+        <x:v>summon / line / ghost</x:v>
+      </x:c>
+      <x:c r="F31" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G31" s="6" t="n">
+        <x:v>0.83</x:v>
+      </x:c>
+      <x:c r="H31" s="6" t="str">
+        <x:v>combat 700 / return 900</x:v>
+      </x:c>
+      <x:c r="I31" s="6" t="str">
+        <x:v>基础数量2；生命60；攻击8；攻速1.2；穿过敌人造成伤害并回复玩家生命；4秒重生</x:v>
+      </x:c>
+      <x:c r="J31" s="6" t="str">
+        <x:v>攻击+50%；回复量+50%</x:v>
+      </x:c>
+      <x:c r="K31" s="6" t="str">
+        <x:v>命中触发灵魂冲击</x:v>
+      </x:c>
+      <x:c r="L31" s="6" t="str">
+        <x:v>测试中</x:v>
+      </x:c>
+      <x:c r="M31" s="6" t="str">
+        <x:v>机动骚扰，无实体阻挡</x:v>
+      </x:c>
+      <x:c r="N31" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O31" s="6" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="P31" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="Q31" s="6" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="R31" s="6" t="n">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="S31" s="6" t="n">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="T31" s="6" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="U31" s="6" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="V31" s="6" t="str">
+        <x:v>ghost</x:v>
+      </x:c>
+      <x:c r="W31" s="6" t="str">
+        <x:v>穿透冲刺，命中回血</x:v>
+      </x:c>
+      <x:c r="X31" t="inlineStr">
+        <x:is>
+          <x:t>灵器</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y31" t="inlineStr">
+        <x:is>
+          <x:t>3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z31" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA31" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="36" customHeight="1">
+      <x:c r="A32" s="6" t="str">
+        <x:v>poison_bug</x:v>
+      </x:c>
+      <x:c r="B32" s="6" t="str">
+        <x:v>毒虫</x:v>
+      </x:c>
+      <x:c r="C32" s="6" t="str">
+        <x:v>召唤</x:v>
+      </x:c>
+      <x:c r="D32" s="6" t="str">
+        <x:v>毒</x:v>
+      </x:c>
+      <x:c r="E32" s="6" t="str">
+        <x:v>summon / melee / swarm</x:v>
+      </x:c>
+      <x:c r="F32" s="6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G32" s="6" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="H32" s="6" t="str">
+        <x:v>combat 450 / return 650</x:v>
+      </x:c>
+      <x:c r="I32" s="6" t="str">
+        <x:v>基础数量3；生命30；攻击5；攻速2.0；近战撕咬附加中毒；3秒重生</x:v>
+      </x:c>
+      <x:c r="J32" s="6" t="str">
+        <x:v>数量+1；攻击+50%</x:v>
+      </x:c>
+      <x:c r="K32" s="6" t="str">
+        <x:v>中毒伤害翻倍</x:v>
+      </x:c>
+      <x:c r="L32" s="6" t="str">
+        <x:v>测试中</x:v>
+      </x:c>
+      <x:c r="M32" s="6" t="str">
+        <x:v>敌人死亡20%概率补充毒虫，总数不超过上限</x:v>
+      </x:c>
+      <x:c r="N32" s="6" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O32" s="6" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="P32" s="6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="Q32" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="R32" s="6" t="n">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="S32" s="6" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="T32" s="6" t="n">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="U32" s="6" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="V32" s="6" t="str">
+        <x:v>swarm</x:v>
+      </x:c>
+      <x:c r="W32" s="6" t="str">
+        <x:v>轻量寻路，过远回防或瞬移</x:v>
+      </x:c>
+      <x:c r="X32" t="inlineStr">
+        <x:is>
+          <x:t>通天灵宝</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y32" t="inlineStr">
+        <x:is>
+          <x:t>5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z32" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="AA32" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:M1"/>
-    <x:mergeCell ref="A2:M2"/>
+    <x:mergeCell ref="A1:W1"/>
+    <x:mergeCell ref="A2:W2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra36a99d7160a4039"/>
+    <x:tablePart ns1:id="Ra36a99d7160a4039"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1308,14 +2618,14 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="13.75" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="38.75" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="38.75" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="31.25" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="12.5" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="37.5" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11.25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="8.75" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8.75" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="9.38" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9.38" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22.5" customHeight="1">
@@ -1465,15 +2775,19 @@
         <x:v>体系</x:v>
       </x:c>
       <x:c r="D8" s="6" t="str">
-        <x:v>召唤流预留羁绊</x:v>
-      </x:c>
-      <x:c r="E8" s="6" t="str"/>
-      <x:c r="F8" s="6" t="str"/>
+        <x:v>所有召唤法宝：数量上限 +1</x:v>
+      </x:c>
+      <x:c r="E8" s="6" t="str">
+        <x:v>所有召唤法宝：数量上限额外 +1；重生时间 -50%</x:v>
+      </x:c>
+      <x:c r="F8" s="6" t="str">
+        <x:v>所有召唤法宝：数量上限额外 +2；召唤物死亡释放灵力冲击</x:v>
+      </x:c>
       <x:c r="G8" s="6" t="str">
         <x:v>测试中</x:v>
       </x:c>
       <x:c r="H8" s="6" t="str">
-        <x:v>UI 已显示；召唤玩法仍为验证/预留方向</x:v>
+        <x:v>已实现：summon_extra_count / summon_respawn_time_multiplier / summon_death_burst_enabled</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="36" customHeight="1">
@@ -1524,16 +2838,16 @@
     </x:row>
     <x:row r="11" ht="36" customHeight="1">
       <x:c r="A11" s="6" t="str">
-        <x:v>wind</x:v>
+        <x:v>poison</x:v>
       </x:c>
       <x:c r="B11" s="6" t="str">
-        <x:v>风</x:v>
+        <x:v>毒</x:v>
       </x:c>
       <x:c r="C11" s="6" t="str">
         <x:v>属性</x:v>
       </x:c>
       <x:c r="D11" s="6" t="str">
-        <x:v>阈值3：属性羁绊预留：风属性 Build 方向</x:v>
+        <x:v>阈值3：属性羁绊预留：毒属性 Build 方向</x:v>
       </x:c>
       <x:c r="E11" s="6" t="str"/>
       <x:c r="F11" s="6" t="str"/>
@@ -1546,16 +2860,16 @@
     </x:row>
     <x:row r="12" ht="36" customHeight="1">
       <x:c r="A12" s="6" t="str">
-        <x:v>poison</x:v>
+        <x:v>thunder</x:v>
       </x:c>
       <x:c r="B12" s="6" t="str">
-        <x:v>毒</x:v>
+        <x:v>雷</x:v>
       </x:c>
       <x:c r="C12" s="6" t="str">
         <x:v>属性</x:v>
       </x:c>
       <x:c r="D12" s="6" t="str">
-        <x:v>阈值3：属性羁绊预留：毒属性 Build 方向</x:v>
+        <x:v>阈值2：属性羁绊预留：雷属性 Build 方向</x:v>
       </x:c>
       <x:c r="E12" s="6" t="str"/>
       <x:c r="F12" s="6" t="str"/>
@@ -1568,16 +2882,16 @@
     </x:row>
     <x:row r="13" ht="36" customHeight="1">
       <x:c r="A13" s="6" t="str">
-        <x:v>thunder</x:v>
+        <x:v>water</x:v>
       </x:c>
       <x:c r="B13" s="6" t="str">
-        <x:v>雷</x:v>
+        <x:v>水</x:v>
       </x:c>
       <x:c r="C13" s="6" t="str">
         <x:v>属性</x:v>
       </x:c>
       <x:c r="D13" s="6" t="str">
-        <x:v>阈值2：属性羁绊预留：雷属性 Build 方向</x:v>
+        <x:v>阈值2：属性羁绊预留：水属性 Build 方向</x:v>
       </x:c>
       <x:c r="E13" s="6" t="str"/>
       <x:c r="F13" s="6" t="str"/>
@@ -1590,16 +2904,16 @@
     </x:row>
     <x:row r="14" ht="36" customHeight="1">
       <x:c r="A14" s="6" t="str">
-        <x:v>water</x:v>
+        <x:v>earth</x:v>
       </x:c>
       <x:c r="B14" s="6" t="str">
-        <x:v>水</x:v>
+        <x:v>土</x:v>
       </x:c>
       <x:c r="C14" s="6" t="str">
         <x:v>属性</x:v>
       </x:c>
       <x:c r="D14" s="6" t="str">
-        <x:v>阈值2：属性羁绊预留：水属性 Build 方向</x:v>
+        <x:v>阈值2：属性羁绊预留：土属性 Build 方向</x:v>
       </x:c>
       <x:c r="E14" s="6" t="str"/>
       <x:c r="F14" s="6" t="str"/>
@@ -1612,16 +2926,16 @@
     </x:row>
     <x:row r="15" ht="36" customHeight="1">
       <x:c r="A15" s="6" t="str">
-        <x:v>earth</x:v>
+        <x:v>metal</x:v>
       </x:c>
       <x:c r="B15" s="6" t="str">
-        <x:v>土</x:v>
+        <x:v>金</x:v>
       </x:c>
       <x:c r="C15" s="6" t="str">
         <x:v>属性</x:v>
       </x:c>
       <x:c r="D15" s="6" t="str">
-        <x:v>阈值2：属性羁绊预留：土属性 Build 方向</x:v>
+        <x:v>阈值2：属性羁绊预留：金属性 Build 方向</x:v>
       </x:c>
       <x:c r="E15" s="6" t="str"/>
       <x:c r="F15" s="6" t="str"/>
@@ -1634,16 +2948,16 @@
     </x:row>
     <x:row r="16" ht="36" customHeight="1">
       <x:c r="A16" s="6" t="str">
-        <x:v>metal</x:v>
+        <x:v>wood</x:v>
       </x:c>
       <x:c r="B16" s="6" t="str">
-        <x:v>金</x:v>
+        <x:v>木</x:v>
       </x:c>
       <x:c r="C16" s="6" t="str">
         <x:v>属性</x:v>
       </x:c>
       <x:c r="D16" s="6" t="str">
-        <x:v>阈值2：属性羁绊预留：金属性 Build 方向</x:v>
+        <x:v>阈值2：属性羁绊预留：木属性 Build 方向</x:v>
       </x:c>
       <x:c r="E16" s="6" t="str"/>
       <x:c r="F16" s="6" t="str"/>
@@ -1651,50 +2965,6 @@
         <x:v>测试中</x:v>
       </x:c>
       <x:c r="H16" s="6" t="str">
-        <x:v>当前仅显示进度与提示，未实现战斗效果</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="36" customHeight="1">
-      <x:c r="A17" s="6" t="str">
-        <x:v>wood</x:v>
-      </x:c>
-      <x:c r="B17" s="6" t="str">
-        <x:v>木</x:v>
-      </x:c>
-      <x:c r="C17" s="6" t="str">
-        <x:v>属性</x:v>
-      </x:c>
-      <x:c r="D17" s="6" t="str">
-        <x:v>阈值2：属性羁绊预留：木属性 Build 方向</x:v>
-      </x:c>
-      <x:c r="E17" s="6" t="str"/>
-      <x:c r="F17" s="6" t="str"/>
-      <x:c r="G17" s="6" t="str">
-        <x:v>测试中</x:v>
-      </x:c>
-      <x:c r="H17" s="6" t="str">
-        <x:v>当前仅显示进度与提示，未实现战斗效果</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="36" customHeight="1">
-      <x:c r="A18" s="6" t="str">
-        <x:v>dark</x:v>
-      </x:c>
-      <x:c r="B18" s="6" t="str">
-        <x:v>暗</x:v>
-      </x:c>
-      <x:c r="C18" s="6" t="str">
-        <x:v>属性</x:v>
-      </x:c>
-      <x:c r="D18" s="6" t="str">
-        <x:v>阈值2：属性羁绊预留：暗属性 Build 方向</x:v>
-      </x:c>
-      <x:c r="E18" s="6" t="str"/>
-      <x:c r="F18" s="6" t="str"/>
-      <x:c r="G18" s="6" t="str">
-        <x:v>测试中</x:v>
-      </x:c>
-      <x:c r="H18" s="6" t="str">
         <x:v>当前仅显示进度与提示，未实现战斗效果</x:v>
       </x:c>
     </x:row>
@@ -1705,7 +2975,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfda46139e4094005"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafa84f5115a14823"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/docs/GameBalance.xlsx
+++ b/docs/GameBalance.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Playtest" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artifacts'!$A$1:$AT$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artifacts'!$A$1:$AT$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Synergies'!$A$1:$J$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT32"/>
+  <dimension ref="A1:AT34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1086,11 +1087,11 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>灵器</t>
+          <t>法器</t>
         </is>
       </c>
       <c r="AK5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
@@ -1192,11 +1193,11 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>法器</t>
+          <t>凡器</t>
         </is>
       </c>
       <c r="AK6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="n">
@@ -1509,17 +1510,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fire_orb</t>
+          <t>divine_thunder</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>法球</t>
+          <t>神雷术</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>向最近敌人发射火焰法球，直伤较低，命中后造成小范围爆炸。</t>
+          <t>锁定一名敌人降下神雷，以该敌人为中心造成范围伤害。三星时神雷范围大幅增加。</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1529,12 +1530,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>雷</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>projectile</t>
+          <t>target_aoe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1544,37 +1545,31 @@
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="J10" t="n">
-        <v>1.35</v>
+        <v>2.8</v>
       </c>
       <c r="K10" t="n">
-        <v>500</v>
+        <v>760</v>
       </c>
       <c r="L10" t="n">
-        <v>10</v>
-      </c>
-      <c r="M10" t="n">
-        <v>20</v>
-      </c>
-      <c r="N10" t="n">
-        <v>20</v>
-      </c>
-      <c r="O10" t="n">
-        <v>360</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>0.22</v>
+      </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
-      <c r="X10" t="n">
-        <v>60</v>
-      </c>
+      <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
@@ -1587,25 +1582,33 @@
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Color(1, 0.32, 0.08, 1)</t>
+          <t>Color(0.58, 0.9, 1.0, 0.86)</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>凡器</t>
+          <t>仙宝</t>
         </is>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="n">
         <v>1</v>
       </c>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
+      <c r="AN10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.85</v>
+      </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr"/>
@@ -1613,22 +1616,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fist</t>
+          <t>fire_gourd</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>拳</t>
+          <t>火葫芦</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>快速近身拳劲打击最近敌人，伤害高于远程法宝。</t>
+          <t>向目标方向喷出锥形火焰，对范围内敌人造成伤害。</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>体修</t>
+          <t>法修</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1643,23 +1646,27 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stab</t>
+          <t>cone</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="J11" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+        <v>1.65</v>
+      </c>
+      <c r="K11" t="n">
+        <v>230</v>
+      </c>
+      <c r="L11" t="n">
+        <v>42</v>
+      </c>
       <c r="M11" t="n">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="N11" t="n">
-        <v>76</v>
+        <v>230</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -1667,7 +1674,7 @@
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="n">
-        <v>0.1</v>
+        <v>0.24</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
@@ -1679,24 +1686,22 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="n">
-        <v>120</v>
-      </c>
+      <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Color(1, 0.42, 0.12, 0.65)</t>
+          <t>Color(1.0, 0.32, 0.05, 0.56)</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>凡器</t>
+          <t>灵宝</t>
         </is>
       </c>
       <c r="AK11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="n">
@@ -1713,22 +1718,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>flame_robe</t>
+          <t>fire_orb</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>衣</t>
+          <t>法球</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>贴身火焰光环持续伤害周围敌人。</t>
+          <t>向最近敌人发射火焰法球，直伤较低，命中后造成小范围爆炸。</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>体修</t>
+          <t>法修</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1738,41 +1743,47 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>formation</t>
+          <t>projectile</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>aura</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>damage</t>
-        </is>
-      </c>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K12" t="n">
+        <v>500</v>
+      </c>
       <c r="L12" t="n">
-        <v>62</v>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20</v>
+      </c>
+      <c r="O12" t="n">
+        <v>360</v>
+      </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="n">
-        <v>0.45</v>
-      </c>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="n">
+        <v>60</v>
+      </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
@@ -1785,16 +1796,16 @@
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Color(1, 0.2, 0.04, 0.1)</t>
+          <t>Color(1, 0.32, 0.08, 1)</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>灵宝</t>
+          <t>凡器</t>
         </is>
       </c>
       <c r="AK12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="n">
@@ -1811,68 +1822,62 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>flying_sword</t>
+          <t>fist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>飞剑</t>
+          <t>拳</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>向最近敌人发射一柄可穿透的飞剑，安全稳定但直伤偏低。</t>
+          <t>快速近身拳劲打击最近敌人，伤害高于远程法宝。</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>剑修</t>
+          <t>体修</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>雷</t>
+          <t>火</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>projectile</t>
+          <t>melee</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>projectile</t>
+          <t>stab</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="K13" t="n">
-        <v>560</v>
-      </c>
-      <c r="L13" t="n">
-        <v>6</v>
-      </c>
+        <v>0.38</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
-      </c>
-      <c r="O13" t="n">
-        <v>520</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
+      <c r="T13" t="n">
+        <v>0.1</v>
+      </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
@@ -1883,22 +1888,24 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
+      <c r="AE13" t="n">
+        <v>120</v>
+      </c>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Color(0.55, 0.85, 1, 1)</t>
+          <t>Color(1, 0.42, 0.12, 0.65)</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>法器</t>
+          <t>凡器</t>
         </is>
       </c>
       <c r="AK13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="n">
@@ -1915,50 +1922,52 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ghost</t>
+          <t>flame_robe</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>幽魂</t>
+          <t>衣</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>召唤高速幽魂穿过敌人造成伤害，命中时回复玩家生命。幽魂无复杂碰撞体积，死亡后快速重生。</t>
+          <t>贴身火焰光环持续伤害周围敌人。</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>召唤</t>
+          <t>体修</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>summon</t>
+          <t>formation</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>line</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>aura</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="K14" t="n">
-        <v>700</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>62</v>
+      </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1967,7 +1976,9 @@
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+      <c r="U14" t="n">
+        <v>0.45</v>
+      </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
@@ -1978,23 +1989,21 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="n">
-        <v>2</v>
-      </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Color(0.50, 0.78, 1, 0.72)</t>
+          <t>Color(1, 0.2, 0.04, 0.1)</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>灵器</t>
+          <t>灵宝</t>
         </is>
       </c>
       <c r="AK14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="n">
@@ -2011,17 +2020,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>giant_sword_art</t>
+          <t>flying_sword</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>巨剑术</t>
+          <t>飞剑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>在角色身后凝聚巨剑，朝敌人发射，在较宽的直线范围内造成伤害。三星时以角色为中心横扫一整圈。</t>
+          <t>向最近敌人发射一柄可穿透的飞剑，安全稳定但直伤偏低。</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2031,7 +2040,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>雷</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2041,40 +2050,38 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>projectile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="J15" t="n">
-        <v>2.35</v>
+        <v>0.95</v>
       </c>
       <c r="K15" t="n">
-        <v>760</v>
+        <v>560</v>
       </c>
       <c r="L15" t="n">
-        <v>680</v>
+        <v>6</v>
       </c>
       <c r="M15" t="n">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="N15" t="n">
-        <v>185</v>
+        <v>26</v>
       </c>
       <c r="O15" t="n">
         <v>520</v>
       </c>
       <c r="P15" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
-      <c r="T15" t="n">
-        <v>0.42</v>
-      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
@@ -2091,33 +2098,25 @@
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Color(1, 0.82, 0.24, 0.86)</t>
+          <t>Color(0.55, 0.85, 1, 1)</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>仙宝</t>
+          <t>法器</t>
         </is>
       </c>
       <c r="AK15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="n">
         <v>1</v>
       </c>
-      <c r="AN15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0.85</v>
-      </c>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
       <c r="AR15" t="inlineStr"/>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr"/>
@@ -2125,50 +2124,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>golden_shield</t>
+          <t>ghost</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>罩</t>
+          <t>幽魂</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>周期性为玩家补充护盾。</t>
+          <t>召唤高速幽魂穿过敌人造成伤害，命中时回复玩家生命。幽魂无复杂碰撞体积，死亡后快速重生。</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>体修</t>
+          <t>召唤</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>formation</t>
+          <t>summon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>aura</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>shield</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
-        <v>48</v>
-      </c>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K16" t="n">
+        <v>700</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -2177,9 +2176,7 @@
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="n">
-        <v>4</v>
-      </c>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
@@ -2190,16 +2187,14 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>36</v>
-      </c>
+      <c r="AF16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Color(1, 0.85, 0.25, 0.06)</t>
+          <t>Color(0.50, 0.78, 1, 0.72)</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2225,17 +2220,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>guardian_flying_sword</t>
+          <t>giant_sword_art</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>护体飞剑</t>
+          <t>巨剑术</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>飞剑常驻环绕护身，敌人靠近时会自动刺出反击后返回。</t>
+          <t>在角色身后凝聚巨剑，朝敌人发射，在较宽的直线范围内造成伤害。三星时以角色为中心横扫一整圈。</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2245,38 +2240,52 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>orbit</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>projectile</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="J17" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K17" t="inlineStr"/>
+        <v>2.35</v>
+      </c>
+      <c r="K17" t="n">
+        <v>760</v>
+      </c>
       <c r="L17" t="n">
-        <v>62</v>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+        <v>680</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86</v>
+      </c>
+      <c r="N17" t="n">
+        <v>185</v>
+      </c>
+      <c r="O17" t="n">
+        <v>520</v>
+      </c>
+      <c r="P17" t="n">
+        <v>99</v>
+      </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
+      <c r="T17" t="n">
+        <v>0.42</v>
+      </c>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="n">
-        <v>2</v>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
@@ -2291,25 +2300,33 @@
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Color(0.82, 0.72, 0.36, 1)</t>
+          <t>Color(1, 0.82, 0.24, 0.86)</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>灵宝</t>
+          <t>仙宝</t>
         </is>
       </c>
       <c r="AK17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="n">
         <v>1</v>
       </c>
-      <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="inlineStr"/>
-      <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="inlineStr"/>
+      <c r="AN17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0.85</v>
+      </c>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr"/>
@@ -2317,94 +2334,90 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>guqin</t>
+          <t>golden_shield</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>古琴</t>
+          <t>罩</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>音符命中后短暂降低敌人伤害，直伤较低。</t>
+          <t>周期性为玩家补充护盾。</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>法修</t>
+          <t>体修</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>projectile</t>
+          <t>formation</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>circle</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
-        <v>5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="K18" t="n">
-        <v>480</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="n">
-        <v>16</v>
-      </c>
-      <c r="N18" t="n">
-        <v>16</v>
-      </c>
-      <c r="O18" t="n">
-        <v>320</v>
-      </c>
+          <t>aura</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>48</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+      <c r="U18" t="n">
+        <v>4</v>
+      </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0.3</v>
-      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
+      <c r="AG18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>36</v>
+      </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Color(0.65, 1, 0.8, 1)</t>
+          <t>Color(1, 0.85, 0.25, 0.06)</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>法器</t>
+          <t>灵器</t>
         </is>
       </c>
       <c r="AK18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="n">
@@ -2421,51 +2434,45 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>healing_formation</t>
+          <t>guardian_flying_sword</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>回血阵</t>
+          <t>护体飞剑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>领域周期性恢复玩家生命，并对阵内敌人造成少量水属性伤害。</t>
+          <t>飞剑常驻环绕护身，敌人靠近时会自动刺出反击后返回。</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>阵法</t>
+          <t>剑修</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>土</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>formation</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>aura</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>heal</t>
-        </is>
-      </c>
+          <t>orbit</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.85</v>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2475,10 +2482,10 @@
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="n">
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
         <v>2</v>
       </c>
-      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
@@ -2488,23 +2495,21 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="n">
-        <v>3</v>
-      </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Color(0.2, 0.65, 1, 0.06)</t>
+          <t>Color(0.82, 0.72, 0.36, 1)</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>法器</t>
+          <t>灵宝</t>
         </is>
       </c>
       <c r="AK19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL19" t="inlineStr"/>
       <c r="AM19" t="n">
@@ -2521,22 +2526,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>heaven_eye</t>
+          <t>guqin</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>天眼</t>
+          <t>古琴</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>短时间锁定最近敌人并持续发射光束，持续稳定但单体效率降低。</t>
+          <t>音符命中后短暂降低敌人伤害，直伤较低。</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>魔修</t>
+          <t>法修</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2546,43 +2551,49 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>beam</t>
+          <t>projectile</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>beam</t>
+          <t>circle</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+        <v>1.15</v>
+      </c>
+      <c r="K20" t="n">
+        <v>480</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>16</v>
+      </c>
+      <c r="N20" t="n">
+        <v>16</v>
+      </c>
+      <c r="O20" t="n">
+        <v>320</v>
+      </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
-      <c r="T20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+      <c r="Y20" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.3</v>
+      </c>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
@@ -2593,16 +2604,16 @@
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Color(0.35, 0.8, 1, 0.82)</t>
+          <t>Color(0.65, 1, 0.8, 1)</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>仙宝</t>
+          <t>灵器</t>
         </is>
       </c>
       <c r="AK20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="n">
@@ -2619,63 +2630,63 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>iron_guard_puppet</t>
+          <t>healing_formation</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>铁卫傀儡</t>
+          <t>回血阵</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>召唤高生命铁卫傀儡，尽量挡在玩家与怪群之间，并周期性嘲讽附近敌人。死亡后会重生。</t>
+          <t>领域周期性恢复玩家生命，并对阵内敌人造成少量水属性伤害。</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>召唤</t>
+          <t>阵法</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>水</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>summon</t>
+          <t>formation</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stab</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>aura</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>heal</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>8</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="K21" t="n">
-        <v>450</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>300</v>
+        <v>125</v>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="n">
-        <v>46</v>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
@@ -2686,21 +2697,23 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
+      <c r="AF21" t="n">
+        <v>3</v>
+      </c>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Color(0.72, 0.60, 0.42, 1)</t>
+          <t>Color(0.2, 0.65, 1, 0.06)</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>灵宝</t>
+          <t>法器</t>
         </is>
       </c>
       <c r="AK21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AL21" t="inlineStr"/>
       <c r="AM21" t="n">
@@ -2717,49 +2730,49 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kick</t>
+          <t>heaven_eye</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>腿</t>
+          <t>天眼</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>贴身旋身扫腿，对周围一圈敌人造成较高伤害并轻微击退。</t>
+          <t>短时间锁定最近敌人并持续发射光束，持续稳定但单体效率降低。</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>体修</t>
+          <t>魔修</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>雷</t>
+          <t>水</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>melee</t>
+          <t>beam</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>circle</t>
+          <t>beam</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>98</v>
+        <v>5</v>
       </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -2769,9 +2782,11 @@
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="U22" t="inlineStr"/>
+        <v>1.2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.2</v>
+      </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
@@ -2781,24 +2796,22 @@
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="n">
-        <v>90</v>
-      </c>
+      <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Color(0.65, 0.82, 1, 0.38)</t>
+          <t>Color(0.35, 0.8, 1, 0.82)</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>法器</t>
+          <t>仙宝</t>
         </is>
       </c>
       <c r="AK22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AL22" t="inlineStr"/>
       <c r="AM22" t="n">
@@ -2815,32 +2828,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>long_spear</t>
+          <t>iron_guard_puppet</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>长枪</t>
+          <t>铁卫傀儡</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>向最近敌人方向刺出长距离贯穿枪影，适合安全地穿透成排敌人。</t>
+          <t>召唤高生命铁卫傀儡，尽量挡在玩家与怪群之间，并周期性嘲讽附近敌人。死亡后会重生。</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>剑修</t>
+          <t>召唤</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>土</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>melee</t>
+          <t>summon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2850,27 +2863,27 @@
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="n">
-        <v>24</v>
-      </c>
+        <v>1.43</v>
+      </c>
+      <c r="K23" t="n">
+        <v>450</v>
+      </c>
+      <c r="L23" t="n">
+        <v>300</v>
+      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>220</v>
+        <v>46</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
-      <c r="T23" t="n">
-        <v>0.18</v>
-      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
@@ -2887,16 +2900,16 @@
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Color(0.65, 1, 0.82, 0.65)</t>
+          <t>Color(0.72, 0.60, 0.42, 1)</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>灵器</t>
+          <t>灵宝</t>
         </is>
       </c>
       <c r="AK23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL23" t="inlineStr"/>
       <c r="AM23" t="n">
@@ -2913,32 +2926,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>magic_ring</t>
+          <t>kick</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>法环</t>
+          <t>腿</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>宽大的法环沿直线缓慢穿透敌人，清线稳定但直伤偏低。</t>
+          <t>贴身旋身扫腿，对周围一圈敌人造成较高伤害并轻微击退。</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>法修</t>
+          <t>体修</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>雷</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>projectile</t>
+          <t>melee</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2948,31 +2961,25 @@
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K24" t="n">
-        <v>520</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="n">
-        <v>34</v>
-      </c>
-      <c r="N24" t="n">
-        <v>34</v>
-      </c>
-      <c r="O24" t="n">
-        <v>280</v>
-      </c>
-      <c r="P24" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>98</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
+      <c r="T24" t="n">
+        <v>0.22</v>
+      </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
@@ -2983,22 +2990,24 @@
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
+      <c r="AE24" t="n">
+        <v>90</v>
+      </c>
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Color(0.25, 0.7, 1, 0.8)</t>
+          <t>Color(0.65, 0.82, 1, 0.38)</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>灵器</t>
+          <t>法器</t>
         </is>
       </c>
       <c r="AK24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL24" t="inlineStr"/>
       <c r="AM24" t="n">
@@ -3015,17 +3024,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>one_handed_sword</t>
+          <t>long_spear</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>单手剑</t>
+          <t>长枪</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>向最近敌人方向挥出近战剑光，伤害和范围都较稳定。</t>
+          <t>向最近敌人方向刺出长距离贯穿枪影，适合安全地穿透成排敌人。</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3045,27 +3054,23 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>slash</t>
+          <t>stab</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K25" t="n">
-        <v>86</v>
-      </c>
-      <c r="L25" t="n">
-        <v>25</v>
-      </c>
+        <v>1.05</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="N25" t="n">
-        <v>108</v>
+        <v>220</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
@@ -3073,7 +3078,7 @@
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
@@ -3091,16 +3096,16 @@
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Color(0.75, 0.92, 1, 0.72)</t>
+          <t>Color(0.65, 1, 0.82, 0.65)</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>凡器</t>
+          <t>灵器</t>
         </is>
       </c>
       <c r="AK25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL25" t="inlineStr"/>
       <c r="AM25" t="n">
@@ -3117,22 +3122,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>palm</t>
+          <t>magic_ring</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>掌</t>
+          <t>法环</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>挥出爆发掌劲打击前方扇形敌人，并将敌人击退。</t>
+          <t>宽大的法环沿直线缓慢穿透敌人，清线稳定但直伤偏低。</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>体修</t>
+          <t>法修</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3142,37 +3147,41 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>melee</t>
+          <t>projectile</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>slash</t>
+          <t>circle</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J26" t="n">
         <v>1.25</v>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="n">
+        <v>520</v>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="N26" t="n">
-        <v>112</v>
-      </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="O26" t="n">
+        <v>280</v>
+      </c>
+      <c r="P26" t="n">
+        <v>3</v>
+      </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
-      <c r="T26" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
@@ -3183,15 +3192,13 @@
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="n">
-        <v>360</v>
-      </c>
+      <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Color(0.35, 0.78, 1, 0.5)</t>
+          <t>Color(0.25, 0.7, 1, 0.8)</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3217,60 +3224,66 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>poison_bug</t>
+          <t>one_handed_sword</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>毒虫</t>
+          <t>单手剑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>召唤轻量虫群近战撕咬并附加中毒。敌人死亡时有概率补充毒虫，但总数不会超过上限。</t>
+          <t>向最近敌人方向挥出近战剑光，伤害和范围都较稳定。</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>召唤</t>
+          <t>剑修</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>毒</t>
+          <t>金</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>summon</t>
+          <t>melee</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stab</t>
+          <t>slash</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="K27" t="n">
-        <v>450</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+        <v>86</v>
+      </c>
+      <c r="L27" t="n">
+        <v>25</v>
+      </c>
+      <c r="M27" t="n">
+        <v>55</v>
+      </c>
       <c r="N27" t="n">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
+      <c r="T27" t="n">
+        <v>0.14</v>
+      </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
@@ -3279,28 +3292,24 @@
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>3</v>
-      </c>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Color(0.42, 1, 0.22, 1)</t>
+          <t>Color(0.75, 0.92, 1, 0.72)</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>仙宝</t>
+          <t>凡器</t>
         </is>
       </c>
       <c r="AK27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="n">
@@ -3317,64 +3326,62 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>poison_needle</t>
+          <t>palm</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>毒针</t>
+          <t>掌</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>高速发射毒针，直接伤害较低，但会让敌人持续中毒。</t>
+          <t>挥出爆发掌劲打击前方扇形敌人，并将敌人击退。</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>魔修</t>
+          <t>体修</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>毒</t>
+          <t>水</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>projectile</t>
+          <t>melee</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>projectile</t>
+          <t>slash</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="K28" t="n">
-        <v>500</v>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="N28" t="n">
-        <v>22</v>
-      </c>
-      <c r="O28" t="n">
-        <v>620</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
+      <c r="T28" t="n">
+        <v>0.2</v>
+      </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
@@ -3383,28 +3390,26 @@
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="n">
+        <v>360</v>
+      </c>
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Color(0.35, 1, 0.2, 1)</t>
+          <t>Color(0.35, 0.78, 1, 0.5)</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>灵宝</t>
+          <t>法器</t>
         </is>
       </c>
       <c r="AK28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AL28" t="inlineStr"/>
       <c r="AM28" t="n">
@@ -3421,90 +3426,90 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>slow_formation</t>
+          <t>poison_bug</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>减速阵</t>
+          <t>毒虫</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>领域内敌人移动速度降低，并持续受到少量木属性伤害。</t>
+          <t>召唤轻量虫群近战撕咬并附加中毒。敌人死亡时有概率补充毒虫，但总数不会超过上限。</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>阵法</t>
+          <t>召唤</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>毒</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>formation</t>
+          <t>summon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>aura</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>slow</t>
-        </is>
-      </c>
+          <t>stab</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="n">
-        <v>125</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>450</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>32</v>
+      </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="n">
-        <v>0.35</v>
-      </c>
+      <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
+      <c r="AC29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3</v>
+      </c>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Color(0.25, 0.85, 0.35, 0.08)</t>
+          <t>Color(0.42, 1, 0.22, 1)</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>凡器</t>
+          <t>仙宝</t>
         </is>
       </c>
       <c r="AK29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AL29" t="inlineStr"/>
       <c r="AM29" t="n">
@@ -3521,57 +3526,59 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>sword_puppet</t>
+          <t>poison_needle</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>剑傀儡</t>
+          <t>毒针</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>召唤持续存在的剑傀儡，追击最近敌人并用近战扇形挥砍。死亡后会在短时间后重生。</t>
+          <t>高速发射毒针，直接伤害较低，但会让敌人持续中毒。</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>召唤</t>
+          <t>魔修</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>毒</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>summon</t>
+          <t>projectile</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>slash</t>
+          <t>projectile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="K30" t="n">
         <v>500</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="N30" t="n">
-        <v>58</v>
-      </c>
-      <c r="O30" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="O30" t="n">
+        <v>620</v>
+      </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
@@ -3585,24 +3592,28 @@
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
+      <c r="AC30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>3</v>
+      </c>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Color(0.95, 0.86, 0.45, 1)</t>
+          <t>Color(0.35, 1, 0.2, 1)</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>凡器</t>
+          <t>灵宝</t>
         </is>
       </c>
       <c r="AK30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL30" t="inlineStr"/>
       <c r="AM30" t="n">
@@ -3619,69 +3630,71 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>turret</t>
+          <t>slow_formation</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>炮台</t>
+          <t>减速阵</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>召唤固定炮台自动索敌并发射爆炸炮弹。玩家离开过远时，炮台会延迟重新部署到玩家附近。</t>
+          <t>领域内敌人移动速度降低，并持续受到少量木属性伤害。</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>召唤</t>
+          <t>阵法</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>summon</t>
+          <t>formation</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>projectile</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>aura</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>slow</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>18</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K31" t="n">
-        <v>700</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>125</v>
+      </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="n">
-        <v>420</v>
-      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
+      <c r="U31" t="n">
+        <v>0.5</v>
+      </c>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
-      <c r="X31" t="n">
-        <v>58</v>
-      </c>
+      <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
+      <c r="AA31" t="n">
+        <v>0.35</v>
+      </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr"/>
@@ -3691,16 +3704,16 @@
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Color(1, 0.32, 0.10, 1)</t>
+          <t>Color(0.25, 0.85, 0.35, 0.08)</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>法器</t>
+          <t>凡器</t>
         </is>
       </c>
       <c r="AK31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL31" t="inlineStr"/>
       <c r="AM31" t="n">
@@ -3717,32 +3730,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>two_handed_sword</t>
+          <t>sword_puppet</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>双手剑</t>
+          <t>剑傀儡</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>以较慢节奏挥出沉重剑光，造成高伤害的大范围扇形斩击。</t>
+          <t>召唤持续存在的剑傀儡，追击最近敌人并用近战扇形挥砍。死亡后会在短时间后重生。</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>剑修</t>
+          <t>召唤</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>melee</t>
+          <t>summon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3752,31 +3765,27 @@
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
+        <v>15</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>500</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="n">
         <v>52</v>
       </c>
-      <c r="J32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="K32" t="n">
-        <v>145</v>
-      </c>
-      <c r="L32" t="n">
-        <v>38</v>
-      </c>
-      <c r="M32" t="n">
-        <v>96</v>
-      </c>
       <c r="N32" t="n">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
-      <c r="T32" t="n">
-        <v>0.22</v>
-      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
@@ -3787,24 +3796,22 @@
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="n">
-        <v>90</v>
-      </c>
+      <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Color(0.86, 0.68, 0.34, 0.72)</t>
+          <t>Color(0.95, 0.86, 0.45, 1)</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>法器</t>
+          <t>凡器</t>
         </is>
       </c>
       <c r="AK32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL32" t="inlineStr"/>
       <c r="AM32" t="n">
@@ -3818,8 +3825,210 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>turret</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>炮台</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>召唤固定炮台自动索敌并发射爆炸炮弹。玩家离开过远时，炮台会延迟重新部署到玩家附近。</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>召唤</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>summon</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>projectile</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>18</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K33" t="n">
+        <v>700</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="n">
+        <v>420</v>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="n">
+        <v>58</v>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Color(1, 0.32, 0.10, 1)</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>法器</t>
+        </is>
+      </c>
+      <c r="AK33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>two_handed_sword</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>双手剑</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>以较慢节奏挥出沉重剑光，造成高伤害的大范围扇形斩击。</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>剑修</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>melee</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>slash</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>52</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K34" t="n">
+        <v>145</v>
+      </c>
+      <c r="L34" t="n">
+        <v>38</v>
+      </c>
+      <c r="M34" t="n">
+        <v>96</v>
+      </c>
+      <c r="N34" t="n">
+        <v>165</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Color(0.86, 0.68, 0.34, 0.72)</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>法器</t>
+        </is>
+      </c>
+      <c r="AK34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AT32"/>
+  <autoFilter ref="A1:AT34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3830,17 +4039,207 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Synergies</t>
+          <t>synergy_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>threshold</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>affected</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>attack_speed_per_stack</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>max_stacks</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>max_attack_speed_bonus</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>reset_timing</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>剑修</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>剑修法宝每次造成伤害</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>所有剑修法宝</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>每场战斗开始/结束</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>机制简单，不新增专属名词</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>剑修</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>剑修法宝每次造成伤害</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>所有剑修法宝</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>每场战斗开始/结束</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>达到上限后不再增加</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>剑修</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>剑修法宝每次造成伤害</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>所有剑修法宝</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G4" t="n">
+        <v>60</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>每场战斗开始/结束</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>未来新增剑修法宝同样适用</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/GameBalance.xlsx
+++ b/docs/GameBalance.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,13 +32,21 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -53,8 +61,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,348 +431,556 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT34"/>
+  <dimension ref="A1:CB34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="15" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="18" customWidth="1" min="24" max="24"/>
-    <col width="17" customWidth="1" min="25" max="25"/>
-    <col width="26" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="20" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="17" customWidth="1" min="30" max="30"/>
-    <col width="17" customWidth="1" min="31" max="31"/>
-    <col width="13" customWidth="1" min="32" max="32"/>
-    <col width="15" customWidth="1" min="33" max="33"/>
-    <col width="12" customWidth="1" min="34" max="34"/>
-    <col width="32" customWidth="1" min="35" max="35"/>
-    <col width="10" customWidth="1" min="36" max="36"/>
-    <col width="10" customWidth="1" min="37" max="37"/>
-    <col width="25" customWidth="1" min="38" max="38"/>
-    <col width="13" customWidth="1" min="39" max="39"/>
-    <col width="19" customWidth="1" min="40" max="40"/>
-    <col width="21" customWidth="1" min="41" max="41"/>
-    <col width="19" customWidth="1" min="42" max="42"/>
-    <col width="21" customWidth="1" min="43" max="43"/>
-    <col width="30" customWidth="1" min="44" max="44"/>
-    <col width="25" customWidth="1" min="45" max="45"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="19" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="18" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="14" customWidth="1" min="34" max="34"/>
+    <col width="20" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="17" customWidth="1" min="37" max="37"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="17" customWidth="1" min="39" max="39"/>
+    <col width="15" customWidth="1" min="40" max="40"/>
+    <col width="15" customWidth="1" min="41" max="41"/>
+    <col width="13" customWidth="1" min="42" max="42"/>
+    <col width="15" customWidth="1" min="43" max="43"/>
+    <col width="12" customWidth="1" min="44" max="44"/>
+    <col width="22" customWidth="1" min="45" max="45"/>
     <col width="22" customWidth="1" min="46" max="46"/>
+    <col width="25" customWidth="1" min="47" max="47"/>
+    <col width="32" customWidth="1" min="48" max="48"/>
+    <col width="10" customWidth="1" min="49" max="49"/>
+    <col width="10" customWidth="1" min="50" max="50"/>
+    <col width="25" customWidth="1" min="51" max="51"/>
+    <col width="13" customWidth="1" min="52" max="52"/>
+    <col width="19" customWidth="1" min="53" max="53"/>
+    <col width="11" customWidth="1" min="54" max="54"/>
+    <col width="15" customWidth="1" min="55" max="55"/>
+    <col width="21" customWidth="1" min="56" max="56"/>
+    <col width="19" customWidth="1" min="57" max="57"/>
+    <col width="22" customWidth="1" min="58" max="58"/>
+    <col width="22" customWidth="1" min="59" max="59"/>
+    <col width="21" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="26" customWidth="1" min="62" max="62"/>
+    <col width="20" customWidth="1" min="63" max="63"/>
+    <col width="19" customWidth="1" min="64" max="64"/>
+    <col width="21" customWidth="1" min="65" max="65"/>
+    <col width="19" customWidth="1" min="66" max="66"/>
+    <col width="21" customWidth="1" min="67" max="67"/>
+    <col width="13" customWidth="1" min="68" max="68"/>
+    <col width="18" customWidth="1" min="69" max="69"/>
+    <col width="30" customWidth="1" min="70" max="70"/>
+    <col width="24" customWidth="1" min="71" max="71"/>
+    <col width="24" customWidth="1" min="72" max="72"/>
+    <col width="25" customWidth="1" min="73" max="73"/>
+    <col width="25" customWidth="1" min="74" max="74"/>
+    <col width="30" customWidth="1" min="75" max="75"/>
+    <col width="24" customWidth="1" min="76" max="76"/>
+    <col width="22" customWidth="1" min="77" max="77"/>
+    <col width="22" customWidth="1" min="78" max="78"/>
+    <col width="14" customWidth="1" min="79" max="79"/>
+    <col width="28" customWidth="1" min="80" max="80"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>display_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>system_tag</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>attribute_tag</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>attack_template</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>attack_shape</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>effect_type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>damage</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>max_hp_damage_coefficient</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>cooldown</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>range</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>radius</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>width</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>length</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>projectile_speed</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>projectile_pierce</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>projectile_bounce</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>bounce_count</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>bounce_range</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>duration</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>tick_interval</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>max_targets</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>life_cost_percent</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>life_cost_flat</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>life_cost_min_hp_ratio</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>kill_heal_amount</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>rotation_speed</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>hit_interval</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>explosion_radius</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>debuff_duration</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>damage_reduction_percent</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>slow_percent</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>attack_speed_bonus</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>poison_dps</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>poison_duration</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>poison_can_stack</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>knockback_force</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>counter_range</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>counter_speed</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>heal_amount</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>shield_amount</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>shield_max</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>delayed_strike_count</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>delayed_strike_delay</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>delayed_strike_interval</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>visual_color</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>tier</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>cost</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>cultivation_requirement</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>shop_weight</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>summon_base_count</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>summon_hp</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>summon_attack</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>summon_attack_speed</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>summon_move_speed</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>summon_combat_radius</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>summon_return_radius</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>summon_respawn_time</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>summon_behavior_type</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>summon_special_effect</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>summon_death_burst</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>star2_damage_mult</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>star2_cooldown_mult</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>star3_damage_mult</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>star3_cooldown_mult</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>crit_chance</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>crit_damage_mult</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>extra_melee_wave_damage_mult</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>extra_melee_wave_range</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>extra_melee_wave_width</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>projectile_return_count</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>poison_explosion_radius</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>poison_explosion_damage_mult</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>shield_knockback_force</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>movement_speed_bonus</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>melee_arc_multiplier</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>star2_effect</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>star3_effect</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>attack_speed_formation</t>
+          <t>one_handed_sword</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>攻速阵</t>
+          <t>单手剑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>持续提高玩家法宝攻击速度，并周期性释放小范围灵刃脉冲。</t>
+          <t>向最近敌人方向挥出近战剑光，伤害和范围都较稳定。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>阵法</t>
+          <t>剑修</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>雷</t>
+          <t>金</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>formation</t>
+          <t>melee</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>aura</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>attack_speed</t>
-        </is>
-      </c>
+          <t>slash</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>0.75</v>
+      </c>
       <c r="L2" t="n">
-        <v>125</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+        <v>86</v>
+      </c>
+      <c r="M2" t="n">
+        <v>25</v>
+      </c>
+      <c r="N2" t="n">
+        <v>55</v>
+      </c>
+      <c r="O2" t="n">
+        <v>108</v>
+      </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>0.75</v>
+        <v>0.14</v>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
@@ -769,32 +988,18 @@
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Color(0.55, 1, 0.82, 0.06)</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>仙宝</t>
-        </is>
-      </c>
-      <c r="AK2" t="n">
-        <v>5</v>
-      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
@@ -802,71 +1007,125 @@
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>Color(0.75, 0.92, 1, 0.72)</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>凡器</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>无专属强化</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>blood_slash</t>
+          <t>two_handed_sword</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>血斩</t>
+          <t>双手剑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>发射宽大的血色剑气。攻击消耗3点生命，生命低于30%时不消耗；击杀敌人回复5点生命。</t>
+          <t>以较慢节奏挥出沉重剑光，造成高伤害的大范围扇形斩击。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>魔修</t>
+          <t>剑修</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>雷</t>
+          <t>土</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>projectile</t>
+          <t>melee</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>projectile</t>
+          <t>slash</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>13</v>
-      </c>
-      <c r="J3" t="n">
+        <v>52</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
         <v>1.35</v>
       </c>
-      <c r="K3" t="n">
-        <v>520</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>145</v>
+      </c>
       <c r="M3" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="N3" t="n">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="O3" t="n">
-        <v>360</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>0.22</v>
+      </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
@@ -880,22 +1139,12 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Color(1, 0.05, 0.15, 0.88)</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>仙宝</t>
-        </is>
-      </c>
-      <c r="AK3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
@@ -904,67 +1153,129 @@
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>Color(0.86, 0.68, 0.34, 0.72)</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>法器</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+      <c r="BO3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="inlineStr"/>
+      <c r="BX3" t="inlineStr"/>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="inlineStr"/>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>无专属强化</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>blood_sword</t>
+          <t>giant_sword_art</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>血剑</t>
+          <t>巨剑术</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>挥出高伤害血色剑光。攻击消耗3点生命，生命低于30%时不消耗；击杀敌人回复5点生命。</t>
+          <t>在角色身后凝聚巨剑，朝敌人发射，在较宽的直线范围内造成伤害。三星时以角色为中心横扫一整圈。</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>魔修</t>
+          <t>剑修</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>melee</t>
+          <t>projectile</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>slash</t>
+          <t>line</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>30</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+        <v>68</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="L4" t="n">
+        <v>760</v>
+      </c>
       <c r="M4" t="n">
-        <v>65</v>
+        <v>680</v>
       </c>
       <c r="N4" t="n">
-        <v>125</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+        <v>86</v>
+      </c>
+      <c r="O4" t="n">
+        <v>185</v>
+      </c>
+      <c r="P4" t="n">
+        <v>520</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>99</v>
+      </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="n">
+        <v>0.42</v>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
@@ -974,29 +1285,15 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="n">
-        <v>140</v>
-      </c>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Color(0.9, 0.03, 0.08, 0.72)</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>灵宝</t>
-        </is>
-      </c>
-      <c r="AK4" t="n">
-        <v>4</v>
-      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr"/>
@@ -1004,68 +1301,134 @@
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>Color(1, 0.82, 0.24, 0.86)</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>仙宝</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr"/>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="inlineStr"/>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>无专属强化</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>brush</t>
+          <t>flying_sword</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>毛笔</t>
+          <t>飞剑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>锁定最近敌人方向挥出直线墨迹，短暂延迟后整条墨迹同时爆发，穿透路径上的所有敌人。</t>
+          <t>向最近敌人发射一柄可穿透的飞剑，安全稳定但直伤偏低。</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>法修</t>
+          <t>剑修</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>雷</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>line_delayed</t>
+          <t>projectile</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>projectile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>15</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L5" t="n">
-        <v>24</v>
+        <v>560</v>
       </c>
       <c r="M5" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="N5" t="n">
-        <v>430</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="O5" t="n">
+        <v>26</v>
+      </c>
+      <c r="P5" t="n">
+        <v>520</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
@@ -1080,23 +1443,11 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Color(0.03, 0.025, 0.02, 0.72)</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>法器</t>
-        </is>
-      </c>
-      <c r="AK5" t="n">
-        <v>2</v>
-      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr"/>
@@ -1104,173 +1455,263 @@
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>Color(0.55, 0.85, 1, 1)</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>法器</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="inlineStr"/>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="inlineStr"/>
+      <c r="BU5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr"/>
+      <c r="BW5" t="inlineStr"/>
+      <c r="BX5" t="inlineStr"/>
+      <c r="BY5" t="inlineStr"/>
+      <c r="BZ5" t="inlineStr"/>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>无专属强化</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>copper_coin</t>
+          <t>guardian_flying_sword</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>铜钱</t>
+          <t>护体飞剑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>命中后在附近未命中的敌人之间弹射，适合补刀但单体较弱。</t>
+          <t>飞剑常驻环绕护身，敌人靠近时会自动刺出反击后返回。</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>法修</t>
+          <t>剑修</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>土</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>projectile</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>circle</t>
-        </is>
-      </c>
+          <t>orbit</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.3</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>650</v>
+        <v>0.85</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>15</v>
-      </c>
-      <c r="N6" t="n">
-        <v>15</v>
-      </c>
-      <c r="O6" t="n">
-        <v>390</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>160</v>
-      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>2</v>
+      </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.45</v>
+      </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Color(1, 0.78, 0.18, 1)</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>凡器</t>
-        </is>
-      </c>
-      <c r="AK6" t="n">
-        <v>1</v>
-      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="n">
+        <v>150</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>850</v>
+      </c>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>Color(0.82, 0.72, 0.36, 1)</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>灵宝</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="inlineStr"/>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="inlineStr"/>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>无专属强化</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>crossbow_puppet</t>
+          <t>long_spear</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>弩傀儡</t>
+          <t>长枪</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>召唤后排弩傀儡，和敌人保持距离并持续发射灵能箭。死亡后会在短时间后重生。</t>
+          <t>向最近敌人方向刺出长距离贯穿枪影，适合安全地穿透成排敌人。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>召唤</t>
+          <t>剑修</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>雷</t>
+          <t>金</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>summon</t>
+          <t>melee</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>projectile</t>
+          <t>stab</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.67</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>600</v>
+        <v>1.05</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>24</v>
+      </c>
       <c r="O7" t="n">
-        <v>560</v>
+        <v>220</v>
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="n">
-        <v>180</v>
-      </c>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="n">
+        <v>0.18</v>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
@@ -1284,23 +1725,11 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Color(0.48, 0.82, 1, 1)</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>灵器</t>
-        </is>
-      </c>
-      <c r="AK7" t="n">
-        <v>3</v>
-      </c>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr"/>
@@ -1308,6 +1737,60 @@
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>Color(0.65, 1, 0.82, 0.65)</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>灵器</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
+      <c r="BO7" t="inlineStr"/>
+      <c r="BP7" t="inlineStr"/>
+      <c r="BQ7" t="inlineStr"/>
+      <c r="BR7" t="inlineStr"/>
+      <c r="BS7" t="inlineStr"/>
+      <c r="BT7" t="inlineStr"/>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="inlineStr"/>
+      <c r="BW7" t="inlineStr"/>
+      <c r="BX7" t="inlineStr"/>
+      <c r="BY7" t="inlineStr"/>
+      <c r="BZ7" t="inlineStr"/>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>无专属强化</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1349,31 +1832,31 @@
       <c r="I8" t="n">
         <v>8</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="n">
         <v>0.3</v>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="n">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
         <v>16</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>64</v>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
-      <c r="T8" t="n">
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="n">
         <v>0.1</v>
       </c>
-      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
-      <c r="W8" t="n">
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="n">
         <v>2</v>
       </c>
-      <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
@@ -1384,23 +1867,11 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Color(0.42, 1, 0.35, 0.72)</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>凡器</t>
-        </is>
-      </c>
-      <c r="AK8" t="n">
-        <v>1</v>
-      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr"/>
@@ -1408,26 +1879,80 @@
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>Color(0.42, 1, 0.35, 0.72)</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>凡器</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+      <c r="BO8" t="inlineStr"/>
+      <c r="BP8" t="inlineStr"/>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr"/>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>无专属强化</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>damage_formation</t>
+          <t>fire_orb</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>伤害阵</t>
+          <t>法球</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>玩家脚下的常驻烈焰阵法，持续伤害范围内敌人。</t>
+          <t>向最近敌人发射火焰法球，直伤较低，命中后造成小范围爆炸。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>阵法</t>
+          <t>法修</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1437,38 +1962,42 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>formation</t>
+          <t>projectile</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>aura</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>damage</t>
-        </is>
-      </c>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>1.35</v>
+      </c>
       <c r="L9" t="n">
-        <v>115</v>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+        <v>500</v>
+      </c>
+      <c r="M9" t="n">
+        <v>10</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20</v>
+      </c>
+      <c r="O9" t="n">
+        <v>20</v>
+      </c>
+      <c r="P9" t="n">
+        <v>360</v>
+      </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="n">
-        <v>0.75</v>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
@@ -1478,27 +2007,17 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
+      <c r="AE9" t="n">
+        <v>60</v>
+      </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Color(1, 0.2, 0.06, 0.2)</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>灵器</t>
-        </is>
-      </c>
-      <c r="AK9" t="n">
-        <v>3</v>
-      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
@@ -1506,21 +2025,75 @@
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>Color(1, 0.32, 0.08, 1)</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>凡器</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr"/>
+      <c r="BR9" t="inlineStr"/>
+      <c r="BS9" t="inlineStr"/>
+      <c r="BT9" t="inlineStr"/>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="inlineStr"/>
+      <c r="BX9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr"/>
+      <c r="BZ9" t="inlineStr"/>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>无专属强化</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>divine_thunder</t>
+          <t>fire_gourd</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>神雷术</t>
+          <t>火葫芦</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>锁定一名敌人降下神雷，以该敌人为中心造成范围伤害。三星时神雷范围大幅增加。</t>
+          <t>向目标方向喷出锥形火焰，对范围内敌人造成伤害。</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1530,43 +2103,47 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>雷</t>
+          <t>火</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>target_aoe</t>
+          <t>melee</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>circle</t>
+          <t>cone</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>82</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.8</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>760</v>
+        <v>1.65</v>
       </c>
       <c r="L10" t="n">
-        <v>92</v>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+        <v>230</v>
+      </c>
+      <c r="M10" t="n">
+        <v>42</v>
+      </c>
+      <c r="N10" t="n">
+        <v>150</v>
+      </c>
+      <c r="O10" t="n">
+        <v>230</v>
+      </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="n">
+        <v>0.24</v>
+      </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
@@ -1580,53 +2157,87 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Color(0.58, 0.9, 1.0, 0.86)</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>仙宝</t>
-        </is>
-      </c>
-      <c r="AK10" t="n">
-        <v>5</v>
-      </c>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0.85</v>
-      </c>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>Color(1.0, 0.32, 0.05, 0.56)</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>灵宝</t>
+        </is>
+      </c>
+      <c r="AX10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr"/>
+      <c r="BQ10" t="inlineStr"/>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="inlineStr"/>
+      <c r="BT10" t="inlineStr"/>
+      <c r="BU10" t="inlineStr"/>
+      <c r="BV10" t="inlineStr"/>
+      <c r="BW10" t="inlineStr"/>
+      <c r="BX10" t="inlineStr"/>
+      <c r="BY10" t="inlineStr"/>
+      <c r="BZ10" t="inlineStr"/>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>无专属强化</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fire_gourd</t>
+          <t>guqin</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>火葫芦</t>
+          <t>古琴</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>向目标方向喷出锥形火焰，对范围内敌人造成伤害。</t>
+          <t>音符命中后短暂降低敌人伤害，直伤较低。</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1636,46 +2247,44 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>melee</t>
+          <t>projectile</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>cone</t>
+          <t>circle</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>34</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.65</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>230</v>
+        <v>1.15</v>
       </c>
       <c r="L11" t="n">
-        <v>42</v>
-      </c>
-      <c r="M11" t="n">
-        <v>150</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>230</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="O11" t="n">
+        <v>16</v>
+      </c>
+      <c r="P11" t="n">
+        <v>320</v>
+      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="n">
-        <v>0.24</v>
-      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
@@ -1687,26 +2296,18 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
+      <c r="AF11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.3</v>
+      </c>
       <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Color(1.0, 0.32, 0.05, 0.56)</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>灵宝</t>
-        </is>
-      </c>
-      <c r="AK11" t="n">
-        <v>4</v>
-      </c>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr"/>
@@ -1714,21 +2315,75 @@
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>Color(0.65, 1, 0.8, 1)</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>灵器</t>
+        </is>
+      </c>
+      <c r="AX11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+      <c r="BO11" t="inlineStr"/>
+      <c r="BP11" t="inlineStr"/>
+      <c r="BQ11" t="inlineStr"/>
+      <c r="BR11" t="inlineStr"/>
+      <c r="BS11" t="inlineStr"/>
+      <c r="BT11" t="inlineStr"/>
+      <c r="BU11" t="inlineStr"/>
+      <c r="BV11" t="inlineStr"/>
+      <c r="BW11" t="inlineStr"/>
+      <c r="BX11" t="inlineStr"/>
+      <c r="BY11" t="inlineStr"/>
+      <c r="BZ11" t="inlineStr"/>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>无专属强化</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>fire_orb</t>
+          <t>copper_coin</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>法球</t>
+          <t>铜钱</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>向最近敌人发射火焰法球，直伤较低，命中后造成小范围爆炸。</t>
+          <t>命中后在附近未命中的敌人之间弹射，适合补刀但单体较弱。</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1738,7 +2393,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1753,37 +2408,39 @@
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.35</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>500</v>
+        <v>1.3</v>
       </c>
       <c r="L12" t="n">
-        <v>10</v>
-      </c>
-      <c r="M12" t="n">
-        <v>20</v>
-      </c>
+        <v>650</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O12" t="n">
-        <v>360</v>
-      </c>
-      <c r="P12" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="P12" t="n">
+        <v>390</v>
+      </c>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>160</v>
+      </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="n">
-        <v>60</v>
-      </c>
+      <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
@@ -1794,23 +2451,11 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Color(1, 0.32, 0.08, 1)</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>凡器</t>
-        </is>
-      </c>
-      <c r="AK12" t="n">
-        <v>1</v>
-      </c>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr"/>
@@ -1818,67 +2463,123 @@
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>Color(1, 0.78, 0.18, 1)</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>凡器</t>
+        </is>
+      </c>
+      <c r="AX12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+      <c r="BO12" t="inlineStr"/>
+      <c r="BP12" t="inlineStr"/>
+      <c r="BQ12" t="inlineStr"/>
+      <c r="BR12" t="inlineStr"/>
+      <c r="BS12" t="inlineStr"/>
+      <c r="BT12" t="inlineStr"/>
+      <c r="BU12" t="inlineStr"/>
+      <c r="BV12" t="inlineStr"/>
+      <c r="BW12" t="inlineStr"/>
+      <c r="BX12" t="inlineStr"/>
+      <c r="BY12" t="inlineStr"/>
+      <c r="BZ12" t="inlineStr"/>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>无专属强化</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fist</t>
+          <t>brush</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>拳</t>
+          <t>毛笔</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>快速近身拳劲打击最近敌人，伤害高于远程法宝。</t>
+          <t>锁定最近敌人方向挥出直线墨迹，短暂延迟后整条墨迹同时爆发，穿透路径上的所有敌人。</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>体修</t>
+          <t>法修</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>melee</t>
+          <t>line_delayed</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stab</t>
+          <t>line</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>10</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>1.7</v>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="N13" t="n">
-        <v>76</v>
-      </c>
-      <c r="O13" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="O13" t="n">
+        <v>430</v>
+      </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="n">
+        <v>0.2</v>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
@@ -1888,97 +2589,147 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="n">
-        <v>120</v>
-      </c>
+      <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Color(1, 0.42, 0.12, 0.65)</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>凡器</t>
-        </is>
-      </c>
-      <c r="AK13" t="n">
-        <v>1</v>
-      </c>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
+      <c r="AS13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>Color(0.03, 0.025, 0.02, 0.72)</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>法器</t>
+        </is>
+      </c>
+      <c r="AX13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+      <c r="BO13" t="inlineStr"/>
+      <c r="BP13" t="inlineStr"/>
+      <c r="BQ13" t="inlineStr"/>
+      <c r="BR13" t="inlineStr"/>
+      <c r="BS13" t="inlineStr"/>
+      <c r="BT13" t="inlineStr"/>
+      <c r="BU13" t="inlineStr"/>
+      <c r="BV13" t="inlineStr"/>
+      <c r="BW13" t="inlineStr"/>
+      <c r="BX13" t="inlineStr"/>
+      <c r="BY13" t="inlineStr"/>
+      <c r="BZ13" t="inlineStr"/>
+      <c r="CA13" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>无专属强化</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>flame_robe</t>
+          <t>magic_ring</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>衣</t>
+          <t>法环</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>贴身火焰光环持续伤害周围敌人。</t>
+          <t>宽大的法环沿直线缓慢穿透敌人，清线稳定但直伤偏低。</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>体修</t>
+          <t>法修</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>formation</t>
+          <t>projectile</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>aura</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>damage</t>
-        </is>
-      </c>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L14" t="n">
+        <v>520</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>34</v>
+      </c>
+      <c r="O14" t="n">
+        <v>34</v>
+      </c>
+      <c r="P14" t="n">
+        <v>280</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3</v>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
-        <v>62</v>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="n">
-        <v>0.45</v>
-      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
@@ -1992,23 +2743,11 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Color(1, 0.2, 0.04, 0.1)</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>灵宝</t>
-        </is>
-      </c>
-      <c r="AK14" t="n">
-        <v>4</v>
-      </c>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="inlineStr"/>
@@ -2016,26 +2755,80 @@
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>Color(0.25, 0.7, 1, 0.8)</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>法器</t>
+        </is>
+      </c>
+      <c r="AX14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
+      <c r="BO14" t="inlineStr"/>
+      <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="inlineStr"/>
+      <c r="BR14" t="inlineStr"/>
+      <c r="BS14" t="inlineStr"/>
+      <c r="BT14" t="inlineStr"/>
+      <c r="BU14" t="inlineStr"/>
+      <c r="BV14" t="inlineStr"/>
+      <c r="BW14" t="inlineStr"/>
+      <c r="BX14" t="inlineStr"/>
+      <c r="BY14" t="inlineStr"/>
+      <c r="BZ14" t="inlineStr"/>
+      <c r="CA14" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>无专属强化</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>flying_sword</t>
+          <t>divine_thunder</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>飞剑</t>
+          <t>神雷术</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>向最近敌人发射一柄可穿透的飞剑，安全稳定但直伤偏低。</t>
+          <t>锁定一名敌人降下神雷，以该敌人为中心造成范围伤害。三星时神雷范围大幅增加。</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>剑修</t>
+          <t>法修</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2045,44 +2838,38 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>projectile</t>
+          <t>target_aoe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>projectile</t>
+          <t>circle</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.95</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>560</v>
+        <v>2.8</v>
       </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>760</v>
       </c>
       <c r="M15" t="n">
-        <v>8</v>
-      </c>
-      <c r="N15" t="n">
-        <v>26</v>
-      </c>
-      <c r="O15" t="n">
-        <v>520</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>0.22</v>
+      </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
@@ -2096,23 +2883,11 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Color(0.55, 0.85, 1, 1)</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>法器</t>
-        </is>
-      </c>
-      <c r="AK15" t="n">
-        <v>2</v>
-      </c>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM15" t="inlineStr"/>
       <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="inlineStr"/>
       <c r="AP15" t="inlineStr"/>
@@ -2120,63 +2895,131 @@
       <c r="AR15" t="inlineStr"/>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>Color(0.58, 0.9, 1.0, 0.86)</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>仙宝</t>
+        </is>
+      </c>
+      <c r="AX15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BP15" t="inlineStr"/>
+      <c r="BQ15" t="inlineStr"/>
+      <c r="BR15" t="inlineStr"/>
+      <c r="BS15" t="inlineStr"/>
+      <c r="BT15" t="inlineStr"/>
+      <c r="BU15" t="inlineStr"/>
+      <c r="BV15" t="inlineStr"/>
+      <c r="BW15" t="inlineStr"/>
+      <c r="BX15" t="inlineStr"/>
+      <c r="BY15" t="inlineStr"/>
+      <c r="BZ15" t="inlineStr"/>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>无专属强化</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ghost</t>
+          <t>fist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>幽魂</t>
+          <t>拳</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>召唤高速幽魂穿过敌人造成伤害，命中时回复玩家生命。幽魂无复杂碰撞体积，死亡后快速重生。</t>
+          <t>快速近身拳劲打击最近敌人，伤害高于远程法宝。</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>召唤</t>
+          <t>体修</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>summon</t>
+          <t>melee</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>stab</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>700</v>
+        <v>0.38</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>32</v>
+      </c>
+      <c r="O16" t="n">
+        <v>76</v>
+      </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
+      <c r="U16" t="n">
+        <v>0.1</v>
+      </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
@@ -2187,27 +3030,15 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="n">
-        <v>2</v>
-      </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Color(0.50, 0.78, 1, 0.72)</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>灵器</t>
-        </is>
-      </c>
-      <c r="AK16" t="n">
-        <v>3</v>
-      </c>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr"/>
@@ -2216,75 +3047,123 @@
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>Color(1, 0.42, 0.12, 0.65)</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>凡器</t>
+        </is>
+      </c>
+      <c r="AX16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr"/>
+      <c r="BO16" t="inlineStr"/>
+      <c r="BP16" t="inlineStr"/>
+      <c r="BQ16" t="inlineStr"/>
+      <c r="BR16" t="inlineStr"/>
+      <c r="BS16" t="inlineStr"/>
+      <c r="BT16" t="inlineStr"/>
+      <c r="BU16" t="inlineStr"/>
+      <c r="BV16" t="inlineStr"/>
+      <c r="BW16" t="inlineStr"/>
+      <c r="BX16" t="inlineStr"/>
+      <c r="BY16" t="inlineStr"/>
+      <c r="BZ16" t="inlineStr"/>
+      <c r="CA16" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>无专属强化</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>giant_sword_art</t>
+          <t>palm</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>巨剑术</t>
+          <t>掌</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>在角色身后凝聚巨剑，朝敌人发射，在较宽的直线范围内造成伤害。三星时以角色为中心横扫一整圈。</t>
+          <t>挥出掌劲打击前方扇形敌人，并将敌人击退。</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>剑修</t>
+          <t>体修</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>projectile</t>
+          <t>melee</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>cone</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="J17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>760</v>
-      </c>
-      <c r="L17" t="n">
-        <v>680</v>
-      </c>
-      <c r="M17" t="n">
-        <v>86</v>
-      </c>
+        <v>0.85</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="O17" t="n">
-        <v>520</v>
-      </c>
-      <c r="P17" t="n">
-        <v>99</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
-      <c r="T17" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="n">
+        <v>0.2</v>
+      </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
@@ -2298,53 +3177,89 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Color(1, 0.82, 0.24, 0.86)</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>仙宝</t>
-        </is>
-      </c>
-      <c r="AK17" t="n">
-        <v>5</v>
-      </c>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0.85</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>Color(0.35, 0.9, 0.42, 0.5)</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>凡器</t>
+        </is>
+      </c>
+      <c r="AX17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr"/>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="inlineStr"/>
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="inlineStr"/>
+      <c r="BO17" t="inlineStr"/>
+      <c r="BP17" t="inlineStr"/>
+      <c r="BQ17" t="inlineStr"/>
+      <c r="BR17" t="inlineStr"/>
+      <c r="BS17" t="inlineStr"/>
+      <c r="BT17" t="inlineStr"/>
+      <c r="BU17" t="inlineStr"/>
+      <c r="BV17" t="inlineStr"/>
+      <c r="BW17" t="inlineStr"/>
+      <c r="BX17" t="inlineStr"/>
+      <c r="BY17" t="inlineStr"/>
+      <c r="BZ17" t="inlineStr"/>
+      <c r="CA17" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>无专属强化</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>golden_shield</t>
+          <t>kick</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>罩</t>
+          <t>腿</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>周期性为玩家补充护盾。</t>
+          <t>贴身旋身扫腿，对周围一圈敌人造成较高伤害并轻微击退。</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2354,31 +3269,33 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>土</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>formation</t>
+          <t>melee</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>aura</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>shield</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="n">
-        <v>48</v>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>20</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>98</v>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -2387,7 +3304,7 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="n">
-        <v>4</v>
+        <v>0.22</v>
       </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
@@ -2400,28 +3317,14 @@
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Color(1, 0.85, 0.25, 0.06)</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>灵器</t>
-        </is>
-      </c>
-      <c r="AK18" t="n">
-        <v>3</v>
-      </c>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr"/>
@@ -2430,62 +3333,124 @@
       <c r="AR18" t="inlineStr"/>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>Color(0.65, 0.82, 1, 0.38)</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>法器</t>
+        </is>
+      </c>
+      <c r="AX18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
+      <c r="BO18" t="inlineStr"/>
+      <c r="BP18" t="inlineStr"/>
+      <c r="BQ18" t="inlineStr"/>
+      <c r="BR18" t="inlineStr"/>
+      <c r="BS18" t="inlineStr"/>
+      <c r="BT18" t="inlineStr"/>
+      <c r="BU18" t="inlineStr"/>
+      <c r="BV18" t="inlineStr"/>
+      <c r="BW18" t="inlineStr"/>
+      <c r="BX18" t="inlineStr"/>
+      <c r="BY18" t="inlineStr"/>
+      <c r="BZ18" t="inlineStr"/>
+      <c r="CA18" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>无专属强化</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>guardian_flying_sword</t>
+          <t>roar</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>护体飞剑</t>
+          <t>吼</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>飞剑常驻环绕护身，敌人靠近时会自动刺出反击后返回。</t>
+          <t>向目标方向发出锥形声浪，造成伤害并减速敌人。</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>剑修</t>
+          <t>体修</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>雷</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>orbit</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>melee</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>cone</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="n">
-        <v>62</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>170</v>
+      </c>
+      <c r="O19" t="n">
+        <v>190</v>
+      </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="n">
-        <v>2</v>
-      </c>
+      <c r="U19" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
@@ -2495,25 +3460,19 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
+      <c r="AF19" t="n">
+        <v>1.2</v>
+      </c>
       <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Color(0.82, 0.72, 0.36, 1)</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>灵宝</t>
-        </is>
-      </c>
-      <c r="AK19" t="n">
-        <v>4</v>
-      </c>
+      <c r="AH19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="inlineStr"/>
       <c r="AM19" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="inlineStr"/>
@@ -2522,26 +3481,80 @@
       <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>Color(0.62, 0.9, 1, 0.45)</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>法器</t>
+        </is>
+      </c>
+      <c r="AX19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
+      <c r="BO19" t="inlineStr"/>
+      <c r="BP19" t="inlineStr"/>
+      <c r="BQ19" t="inlineStr"/>
+      <c r="BR19" t="inlineStr"/>
+      <c r="BS19" t="inlineStr"/>
+      <c r="BT19" t="inlineStr"/>
+      <c r="BU19" t="inlineStr"/>
+      <c r="BV19" t="inlineStr"/>
+      <c r="BW19" t="inlineStr"/>
+      <c r="BX19" t="inlineStr"/>
+      <c r="BY19" t="inlineStr"/>
+      <c r="BZ19" t="inlineStr"/>
+      <c r="CA19" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>无专属强化</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>guqin</t>
+          <t>body_barrier</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>古琴</t>
+          <t>罩</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>音符命中后短暂降低敌人伤害，直伤较低。</t>
+          <t>周期释放震荡波，对周围敌人造成伤害，命中敌人时回复生命。</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>法修</t>
+          <t>体修</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2551,49 +3564,45 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>projectile</t>
+          <t>formation</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>circle</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>aura</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="K20" t="n">
-        <v>480</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>16</v>
-      </c>
-      <c r="N20" t="n">
-        <v>16</v>
-      </c>
-      <c r="O20" t="n">
-        <v>320</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>1.2</v>
+      </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0.3</v>
-      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
@@ -2602,55 +3611,99 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Color(0.65, 1, 0.8, 1)</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>灵器</t>
-        </is>
-      </c>
-      <c r="AK20" t="n">
-        <v>3</v>
-      </c>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM20" t="inlineStr"/>
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr"/>
-      <c r="AP20" t="inlineStr"/>
+      <c r="AP20" t="n">
+        <v>2</v>
+      </c>
       <c r="AQ20" t="inlineStr"/>
       <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>Color(0.28, 0.7, 1, 0.16)</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>灵器</t>
+        </is>
+      </c>
+      <c r="AX20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="inlineStr"/>
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr"/>
+      <c r="BJ20" t="inlineStr"/>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="inlineStr"/>
+      <c r="BM20" t="inlineStr"/>
+      <c r="BN20" t="inlineStr"/>
+      <c r="BO20" t="inlineStr"/>
+      <c r="BP20" t="inlineStr"/>
+      <c r="BQ20" t="inlineStr"/>
+      <c r="BR20" t="inlineStr"/>
+      <c r="BS20" t="inlineStr"/>
+      <c r="BT20" t="inlineStr"/>
+      <c r="BU20" t="inlineStr"/>
+      <c r="BV20" t="inlineStr"/>
+      <c r="BW20" t="inlineStr"/>
+      <c r="BX20" t="inlineStr"/>
+      <c r="BY20" t="inlineStr"/>
+      <c r="BZ20" t="inlineStr"/>
+      <c r="CA20" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>震荡波范围 +50%</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>healing_formation</t>
+          <t>thorn_armor</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>回血阵</t>
+          <t>反甲</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>领域周期性恢复玩家生命，并对阵内敌人造成少量水属性伤害。</t>
+          <t>受到伤害时触发，对角色周围敌人造成范围伤害。</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>阵法</t>
+          <t>体修</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2665,18 +3718,20 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>heal</t>
+          <t>counter_damage</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.06</v>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="n">
-        <v>125</v>
-      </c>
-      <c r="M21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>136</v>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -2684,10 +3739,10 @@
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>999</v>
+      </c>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
@@ -2697,28 +3752,14 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="n">
-        <v>3</v>
-      </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Color(0.2, 0.65, 1, 0.06)</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>法器</t>
-        </is>
-      </c>
-      <c r="AK21" t="n">
-        <v>2</v>
-      </c>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM21" t="inlineStr"/>
       <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="inlineStr"/>
@@ -2726,68 +3767,124 @@
       <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>Color(1, 0.82, 0.22, 0.13)</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>灵宝</t>
+        </is>
+      </c>
+      <c r="AX21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="inlineStr"/>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="inlineStr"/>
+      <c r="BM21" t="inlineStr"/>
+      <c r="BN21" t="inlineStr"/>
+      <c r="BO21" t="inlineStr"/>
+      <c r="BP21" t="inlineStr"/>
+      <c r="BQ21" t="inlineStr"/>
+      <c r="BR21" t="inlineStr"/>
+      <c r="BS21" t="inlineStr"/>
+      <c r="BT21" t="inlineStr"/>
+      <c r="BU21" t="inlineStr"/>
+      <c r="BV21" t="inlineStr"/>
+      <c r="BW21" t="inlineStr"/>
+      <c r="BX21" t="inlineStr"/>
+      <c r="BY21" t="inlineStr"/>
+      <c r="BZ21" t="inlineStr"/>
+      <c r="CA21" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>无专属强化</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>heaven_eye</t>
+          <t>golden_body_avatar</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>天眼</t>
+          <t>法相金身</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>短时间锁定最近敌人并持续发射光束，持续稳定但单体效率降低。</t>
+          <t>角色背后常驻半透明巨大法相，周期砸地造成大范围伤害。</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>魔修</t>
+          <t>体修</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>土</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>beam</t>
+          <t>formation</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>beam</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>aura</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>avatar_slam</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="n">
-        <v>5</v>
-      </c>
-      <c r="M22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>210</v>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
-      <c r="T22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="V22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>2.4</v>
+      </c>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
@@ -2800,23 +3897,11 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Color(0.35, 0.8, 1, 0.82)</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>仙宝</t>
-        </is>
-      </c>
-      <c r="AK22" t="n">
-        <v>5</v>
-      </c>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM22" t="inlineStr"/>
       <c r="AN22" t="inlineStr"/>
       <c r="AO22" t="inlineStr"/>
       <c r="AP22" t="inlineStr"/>
@@ -2824,96 +3909,146 @@
       <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>Color(0.9, 0.72, 0.36, 0.18)</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>仙宝</t>
+        </is>
+      </c>
+      <c r="AX22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr"/>
+      <c r="BJ22" t="inlineStr"/>
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="inlineStr"/>
+      <c r="BM22" t="inlineStr"/>
+      <c r="BN22" t="inlineStr"/>
+      <c r="BO22" t="inlineStr"/>
+      <c r="BP22" t="inlineStr"/>
+      <c r="BQ22" t="inlineStr"/>
+      <c r="BR22" t="inlineStr"/>
+      <c r="BS22" t="inlineStr"/>
+      <c r="BT22" t="inlineStr"/>
+      <c r="BU22" t="inlineStr"/>
+      <c r="BV22" t="inlineStr"/>
+      <c r="BW22" t="inlineStr"/>
+      <c r="BX22" t="inlineStr"/>
+      <c r="BY22" t="inlineStr"/>
+      <c r="BZ22" t="inlineStr"/>
+      <c r="CA22" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>无专属强化</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>iron_guard_puppet</t>
+          <t>blood_sword</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>铁卫傀儡</t>
+          <t>血剑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>召唤高生命铁卫傀儡，尽量挡在玩家与怪群之间，并周期性嘲讽附近敌人。死亡后会重生。</t>
+          <t>挥出高伤害血色剑光。攻击消耗3点生命，生命低于30%时不消耗；击杀敌人回复5点生命。</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>召唤</t>
+          <t>魔修</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>火</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>summon</t>
+          <t>melee</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stab</t>
+          <t>slash</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>8</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1.43</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
-        <v>450</v>
-      </c>
-      <c r="L23" t="n">
-        <v>300</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>46</v>
-      </c>
-      <c r="O23" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="O23" t="n">
+        <v>125</v>
+      </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
+      <c r="U23" t="n">
+        <v>0.18</v>
+      </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
+      <c r="Z23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>5</v>
+      </c>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Color(0.72, 0.60, 0.42, 1)</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>灵宝</t>
-        </is>
-      </c>
-      <c r="AK23" t="n">
-        <v>4</v>
-      </c>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="inlineStr"/>
       <c r="AM23" t="n">
-        <v>1</v>
+        <v>140</v>
       </c>
       <c r="AN23" t="inlineStr"/>
       <c r="AO23" t="inlineStr"/>
@@ -2922,26 +4057,80 @@
       <c r="AR23" t="inlineStr"/>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>Color(0.9, 0.03, 0.08, 0.72)</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>凡器</t>
+        </is>
+      </c>
+      <c r="AX23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr"/>
+      <c r="BJ23" t="inlineStr"/>
+      <c r="BK23" t="inlineStr"/>
+      <c r="BL23" t="inlineStr"/>
+      <c r="BM23" t="inlineStr"/>
+      <c r="BN23" t="inlineStr"/>
+      <c r="BO23" t="inlineStr"/>
+      <c r="BP23" t="inlineStr"/>
+      <c r="BQ23" t="inlineStr"/>
+      <c r="BR23" t="inlineStr"/>
+      <c r="BS23" t="inlineStr"/>
+      <c r="BT23" t="inlineStr"/>
+      <c r="BU23" t="inlineStr"/>
+      <c r="BV23" t="inlineStr"/>
+      <c r="BW23" t="inlineStr"/>
+      <c r="BX23" t="inlineStr"/>
+      <c r="BY23" t="inlineStr"/>
+      <c r="BZ23" t="inlineStr"/>
+      <c r="CA23" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>击杀回复 +3</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kick</t>
+          <t>blood_slash</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>腿</t>
+          <t>血斩</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>贴身旋身扫腿，对周围一圈敌人造成较高伤害并轻微击退。</t>
+          <t>发射宽大的血色剑气。攻击消耗3点生命，生命低于30%时不消耗；击杀敌人回复5点生命。</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>体修</t>
+          <t>魔修</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2951,68 +4140,66 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>melee</t>
+          <t>projectile</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>circle</t>
+          <t>projectile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>20</v>
-      </c>
-      <c r="J24" t="n">
+        <v>13</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L24" t="n">
+        <v>520</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>28</v>
+      </c>
+      <c r="O24" t="n">
+        <v>45</v>
+      </c>
+      <c r="P24" t="n">
+        <v>360</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="n">
-        <v>98</v>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" t="n">
-        <v>0.22</v>
-      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
+      <c r="Z24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>5</v>
+      </c>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="n">
-        <v>90</v>
-      </c>
+      <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Color(0.65, 0.82, 1, 0.38)</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>法器</t>
-        </is>
-      </c>
-      <c r="AK24" t="n">
-        <v>2</v>
-      </c>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="inlineStr"/>
       <c r="AP24" t="inlineStr"/>
@@ -3020,66 +4207,122 @@
       <c r="AR24" t="inlineStr"/>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>Color(1, 0.05, 0.15, 0.88)</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>法器</t>
+        </is>
+      </c>
+      <c r="AX24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
+      <c r="BH24" t="inlineStr"/>
+      <c r="BI24" t="inlineStr"/>
+      <c r="BJ24" t="inlineStr"/>
+      <c r="BK24" t="inlineStr"/>
+      <c r="BL24" t="inlineStr"/>
+      <c r="BM24" t="inlineStr"/>
+      <c r="BN24" t="inlineStr"/>
+      <c r="BO24" t="inlineStr"/>
+      <c r="BP24" t="inlineStr"/>
+      <c r="BQ24" t="inlineStr"/>
+      <c r="BR24" t="inlineStr"/>
+      <c r="BS24" t="inlineStr"/>
+      <c r="BT24" t="inlineStr"/>
+      <c r="BU24" t="inlineStr"/>
+      <c r="BV24" t="inlineStr"/>
+      <c r="BW24" t="inlineStr"/>
+      <c r="BX24" t="inlineStr"/>
+      <c r="BY24" t="inlineStr"/>
+      <c r="BZ24" t="inlineStr"/>
+      <c r="CA24" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>剑气飞行距离 +50%</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>long_spear</t>
+          <t>poison_needle</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>长枪</t>
+          <t>毒针</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>向最近敌人方向刺出长距离贯穿枪影，适合安全地穿透成排敌人。</t>
+          <t>高速发射毒针，直接伤害较低，但会让敌人持续中毒。</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>剑修</t>
+          <t>魔修</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>毒</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>melee</t>
+          <t>projectile</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>stab</t>
+          <t>projectile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>20</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="n">
-        <v>24</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L25" t="n">
+        <v>500</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>220</v>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="O25" t="n">
+        <v>22</v>
+      </c>
+      <c r="P25" t="n">
+        <v>620</v>
+      </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
-      <c r="T25" t="n">
-        <v>0.18</v>
-      </c>
+      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
@@ -3094,23 +4337,17 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Color(0.65, 1, 0.82, 0.65)</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>灵器</t>
-        </is>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="n">
+        <v>3</v>
       </c>
       <c r="AK25" t="n">
         <v>3</v>
       </c>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="n">
+      <c r="AL25" t="b">
         <v>1</v>
       </c>
+      <c r="AM25" t="inlineStr"/>
       <c r="AN25" t="inlineStr"/>
       <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="inlineStr"/>
@@ -3118,26 +4355,80 @@
       <c r="AR25" t="inlineStr"/>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>Color(0.35, 1, 0.2, 1)</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>法器</t>
+        </is>
+      </c>
+      <c r="AX25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr"/>
+      <c r="BJ25" t="inlineStr"/>
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="inlineStr"/>
+      <c r="BM25" t="inlineStr"/>
+      <c r="BN25" t="inlineStr"/>
+      <c r="BO25" t="inlineStr"/>
+      <c r="BP25" t="inlineStr"/>
+      <c r="BQ25" t="inlineStr"/>
+      <c r="BR25" t="inlineStr"/>
+      <c r="BS25" t="inlineStr"/>
+      <c r="BT25" t="inlineStr"/>
+      <c r="BU25" t="inlineStr"/>
+      <c r="BV25" t="inlineStr"/>
+      <c r="BW25" t="inlineStr"/>
+      <c r="BX25" t="inlineStr"/>
+      <c r="BY25" t="inlineStr"/>
+      <c r="BZ25" t="inlineStr"/>
+      <c r="CA25" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>命中位置产生毒爆，造成毒针伤害的 50%</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>magic_ring</t>
+          <t>heaven_eye</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>法环</t>
+          <t>天眼</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>宽大的法环沿直线缓慢穿透敌人，清线稳定但直伤偏低。</t>
+          <t>短时间锁定最近敌人并持续发射天眼光束。攻击期间持续扣除生命，击杀敌人后恢复生命。</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>法修</t>
+          <t>魔修</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3147,72 +4438,62 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>projectile</t>
+          <t>beam</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>circle</t>
+          <t>beam</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>6</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1.25</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="n">
-        <v>520</v>
+        <v>3</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
-        <v>34</v>
-      </c>
-      <c r="N26" t="n">
-        <v>34</v>
-      </c>
-      <c r="O26" t="n">
-        <v>280</v>
-      </c>
-      <c r="P26" t="n">
-        <v>3</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
+      <c r="U26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.2</v>
+      </c>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
+      <c r="Z26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>5</v>
+      </c>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Color(0.25, 0.7, 1, 0.8)</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>法器</t>
-        </is>
-      </c>
-      <c r="AK26" t="n">
-        <v>2</v>
-      </c>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr"/>
       <c r="AP26" t="inlineStr"/>
@@ -3220,31 +4501,85 @@
       <c r="AR26" t="inlineStr"/>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>Color(0.35, 0.8, 1, 0.82)</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>灵器</t>
+        </is>
+      </c>
+      <c r="AX26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="inlineStr"/>
+      <c r="BI26" t="inlineStr"/>
+      <c r="BJ26" t="inlineStr"/>
+      <c r="BK26" t="inlineStr"/>
+      <c r="BL26" t="inlineStr"/>
+      <c r="BM26" t="inlineStr"/>
+      <c r="BN26" t="inlineStr"/>
+      <c r="BO26" t="inlineStr"/>
+      <c r="BP26" t="inlineStr"/>
+      <c r="BQ26" t="inlineStr"/>
+      <c r="BR26" t="inlineStr"/>
+      <c r="BS26" t="inlineStr"/>
+      <c r="BT26" t="inlineStr"/>
+      <c r="BU26" t="inlineStr"/>
+      <c r="BV26" t="inlineStr"/>
+      <c r="BW26" t="inlineStr"/>
+      <c r="BX26" t="inlineStr"/>
+      <c r="BY26" t="inlineStr"/>
+      <c r="BZ26" t="inlineStr"/>
+      <c r="CA26" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>光束宽度 +50%</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>one_handed_sword</t>
+          <t>scythe</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>单手剑</t>
+          <t>镰刀</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>向最近敌人方向挥出近战剑光，伤害和范围都较稳定。</t>
+          <t>挥动镰刀造成伤害，只有镰刀头部有伤害。造成伤害的一部分会回复生命。</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>剑修</t>
+          <t>魔修</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3254,43 +4589,43 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>slash</t>
+          <t>head_slash</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>21</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.75</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="n">
-        <v>86</v>
-      </c>
-      <c r="L27" t="n">
-        <v>25</v>
-      </c>
-      <c r="M27" t="n">
-        <v>55</v>
-      </c>
+        <v>1.45</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>108</v>
-      </c>
-      <c r="O27" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="O27" t="n">
+        <v>150</v>
+      </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
-      <c r="T27" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="U27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="n">
+        <v>0.22</v>
+      </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
+      <c r="Z27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.3</v>
+      </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
@@ -3298,145 +4633,251 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Color(0.75, 0.92, 1, 0.72)</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>凡器</t>
-        </is>
-      </c>
-      <c r="AK27" t="n">
-        <v>1</v>
-      </c>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="inlineStr"/>
-      <c r="AP27" t="inlineStr"/>
+      <c r="AP27" t="n">
+        <v>0.25</v>
+      </c>
       <c r="AQ27" t="inlineStr"/>
       <c r="AR27" t="inlineStr"/>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>Color(0.72, 0.96, 1, 0.58)</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>灵宝</t>
+        </is>
+      </c>
+      <c r="AX27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr"/>
+      <c r="BH27" t="inlineStr"/>
+      <c r="BI27" t="inlineStr"/>
+      <c r="BJ27" t="inlineStr"/>
+      <c r="BK27" t="inlineStr"/>
+      <c r="BL27" t="inlineStr"/>
+      <c r="BM27" t="inlineStr"/>
+      <c r="BN27" t="inlineStr"/>
+      <c r="BO27" t="inlineStr"/>
+      <c r="BP27" t="inlineStr"/>
+      <c r="BQ27" t="inlineStr"/>
+      <c r="BR27" t="inlineStr"/>
+      <c r="BS27" t="inlineStr"/>
+      <c r="BT27" t="inlineStr"/>
+      <c r="BU27" t="inlineStr"/>
+      <c r="BV27" t="inlineStr"/>
+      <c r="BW27" t="inlineStr"/>
+      <c r="BX27" t="inlineStr"/>
+      <c r="BY27" t="inlineStr"/>
+      <c r="BZ27" t="inlineStr"/>
+      <c r="CA27" t="inlineStr">
+        <is>
+          <t>伤害提升，攻击间隔缩短</t>
+        </is>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>镰刀头部范围增加，吸血提高</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>palm</t>
+          <t>soul_banner</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>掌</t>
+          <t>招魂幡</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>挥出爆发掌劲打击前方扇形敌人，并将敌人击退。</t>
+          <t>连接多名敌人并压制，持续造成伤害。敌人死亡后化为幽魂冲击其他敌人，接触后爆炸并消失。</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>体修</t>
+          <t>魔修</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>木</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>melee</t>
+          <t>soul_banner</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>slash</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>beam</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>slow</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>22</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="n">
-        <v>110</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>230</v>
+      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>112</v>
+        <v>24</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="n">
+        <v>2</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.32</v>
+      </c>
       <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="n">
+        <v>4</v>
+      </c>
       <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
+      <c r="Z28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.3</v>
+      </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="n">
-        <v>360</v>
+        <v>58</v>
       </c>
       <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Color(0.35, 0.78, 1, 0.5)</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>法器</t>
-        </is>
-      </c>
-      <c r="AK28" t="n">
-        <v>2</v>
-      </c>
+      <c r="AG28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM28" t="inlineStr"/>
       <c r="AN28" t="inlineStr"/>
-      <c r="AO28" t="inlineStr"/>
+      <c r="AO28" t="n">
+        <v>620</v>
+      </c>
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr"/>
       <c r="AR28" t="inlineStr"/>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>Color(0.38, 1, 0.5, 0.52)</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>仙宝</t>
+        </is>
+      </c>
+      <c r="AX28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="inlineStr"/>
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr"/>
+      <c r="BF28" t="inlineStr"/>
+      <c r="BG28" t="inlineStr"/>
+      <c r="BH28" t="inlineStr"/>
+      <c r="BI28" t="inlineStr"/>
+      <c r="BJ28" t="inlineStr"/>
+      <c r="BK28" t="inlineStr"/>
+      <c r="BL28" t="inlineStr"/>
+      <c r="BM28" t="inlineStr"/>
+      <c r="BN28" t="inlineStr"/>
+      <c r="BO28" t="inlineStr"/>
+      <c r="BP28" t="inlineStr"/>
+      <c r="BQ28" t="inlineStr"/>
+      <c r="BR28" t="inlineStr"/>
+      <c r="BS28" t="inlineStr"/>
+      <c r="BT28" t="inlineStr"/>
+      <c r="BU28" t="inlineStr"/>
+      <c r="BV28" t="inlineStr"/>
+      <c r="BW28" t="inlineStr"/>
+      <c r="BX28" t="inlineStr"/>
+      <c r="BY28" t="inlineStr"/>
+      <c r="BZ28" t="inlineStr"/>
+      <c r="CA28" t="inlineStr">
+        <is>
+          <t>持续伤害提升，冷却缩短</t>
+        </is>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>压制范围内所有敌人</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>poison_bug</t>
+          <t>sword_puppet</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>毒虫</t>
+          <t>近战傀儡</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>召唤轻量虫群近战撕咬并附加中毒。敌人死亡时有概率补充毒虫，但总数不会超过上限。</t>
+          <t>召唤持续存在的近战傀儡，追击最近敌人并用近战挥砍。死亡后会在短时间后重生。</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3446,7 +4887,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>毒</t>
+          <t>木</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3456,25 +4897,27 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stab</t>
+          <t>slash</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>5</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.5</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="n">
-        <v>450</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>500</v>
+      </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>32</v>
-      </c>
-      <c r="O29" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="O29" t="n">
+        <v>58</v>
+      </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
@@ -3488,33 +4931,17 @@
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>3</v>
-      </c>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Color(0.42, 1, 0.22, 1)</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>仙宝</t>
-        </is>
-      </c>
-      <c r="AK29" t="n">
-        <v>5</v>
-      </c>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM29" t="inlineStr"/>
       <c r="AN29" t="inlineStr"/>
       <c r="AO29" t="inlineStr"/>
       <c r="AP29" t="inlineStr"/>
@@ -3522,36 +4949,114 @@
       <c r="AR29" t="inlineStr"/>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>Color(0.95, 0.86, 0.45, 1)</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>凡器</t>
+        </is>
+      </c>
+      <c r="AX29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>100</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>230</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>500</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>700</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI29" t="inlineStr">
+        <is>
+          <t>melee</t>
+        </is>
+      </c>
+      <c r="BJ29" t="inlineStr">
+        <is>
+          <t>近战主力输出</t>
+        </is>
+      </c>
+      <c r="BK29" t="inlineStr"/>
+      <c r="BL29" t="inlineStr"/>
+      <c r="BM29" t="inlineStr"/>
+      <c r="BN29" t="inlineStr"/>
+      <c r="BO29" t="inlineStr"/>
+      <c r="BP29" t="inlineStr"/>
+      <c r="BQ29" t="inlineStr"/>
+      <c r="BR29" t="inlineStr"/>
+      <c r="BS29" t="inlineStr"/>
+      <c r="BT29" t="inlineStr"/>
+      <c r="BU29" t="inlineStr"/>
+      <c r="BV29" t="inlineStr"/>
+      <c r="BW29" t="inlineStr"/>
+      <c r="BX29" t="inlineStr"/>
+      <c r="BY29" t="inlineStr"/>
+      <c r="BZ29" t="inlineStr"/>
+      <c r="CA29" t="inlineStr">
+        <is>
+          <t>生命和攻击提升</t>
+        </is>
+      </c>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t>攻击范围 +30%，每第三次攻击造成 200% 伤害</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>poison_needle</t>
+          <t>crossbow_puppet</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>毒针</t>
+          <t>远程傀儡</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>高速发射毒针，直接伤害较低，但会让敌人持续中毒。</t>
+          <t>召唤后排远程傀儡，和敌人保持距离并持续发射灵能箭。死亡后会在短时间后重生。</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>魔修</t>
+          <t>召唤</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>毒</t>
+          <t>雷</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>projectile</t>
+          <t>summon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3561,29 +5066,27 @@
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>4</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.65</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="n">
-        <v>500</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="n">
-        <v>5</v>
-      </c>
-      <c r="N30" t="n">
-        <v>22</v>
-      </c>
-      <c r="O30" t="n">
-        <v>620</v>
-      </c>
-      <c r="P30" t="inlineStr"/>
+        <v>0.67</v>
+      </c>
+      <c r="L30" t="n">
+        <v>600</v>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>560</v>
+      </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
+      <c r="T30" t="n">
+        <v>180</v>
+      </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
@@ -3592,33 +5095,17 @@
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>3</v>
-      </c>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Color(0.35, 1, 0.2, 1)</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>灵宝</t>
-        </is>
-      </c>
-      <c r="AK30" t="n">
-        <v>4</v>
-      </c>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM30" t="inlineStr"/>
       <c r="AN30" t="inlineStr"/>
       <c r="AO30" t="inlineStr"/>
       <c r="AP30" t="inlineStr"/>
@@ -3626,75 +5113,151 @@
       <c r="AR30" t="inlineStr"/>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>Color(0.48, 0.82, 1, 1)</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>凡器</t>
+        </is>
+      </c>
+      <c r="AX30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>70</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>185</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>600</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>700</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI30" t="inlineStr">
+        <is>
+          <t>ranged</t>
+        </is>
+      </c>
+      <c r="BJ30" t="inlineStr">
+        <is>
+          <t>后排持续输出</t>
+        </is>
+      </c>
+      <c r="BK30" t="inlineStr"/>
+      <c r="BL30" t="inlineStr"/>
+      <c r="BM30" t="inlineStr"/>
+      <c r="BN30" t="inlineStr"/>
+      <c r="BO30" t="inlineStr"/>
+      <c r="BP30" t="inlineStr"/>
+      <c r="BQ30" t="inlineStr"/>
+      <c r="BR30" t="inlineStr"/>
+      <c r="BS30" t="inlineStr"/>
+      <c r="BT30" t="inlineStr"/>
+      <c r="BU30" t="inlineStr"/>
+      <c r="BV30" t="inlineStr"/>
+      <c r="BW30" t="inlineStr"/>
+      <c r="BX30" t="inlineStr"/>
+      <c r="BY30" t="inlineStr"/>
+      <c r="BZ30" t="inlineStr"/>
+      <c r="CA30" t="inlineStr">
+        <is>
+          <t>攻击和攻速提升</t>
+        </is>
+      </c>
+      <c r="CB30" t="inlineStr">
+        <is>
+          <t>灵能箭弹射 +1 次</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>slow_formation</t>
+          <t>iron_guard_puppet</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>减速阵</t>
+          <t>铁甲傀儡</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>领域内敌人移动速度降低，并持续受到少量木属性伤害。</t>
+          <t>召唤高生命铁卫傀儡，尽量挡在玩家与怪群之间，并周期性嘲讽附近敌人。死亡后会重生。</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>阵法</t>
+          <t>召唤</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>土</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>formation</t>
+          <t>summon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>aura</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>slow</t>
-        </is>
-      </c>
+          <t>stab</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>1.43</v>
+      </c>
       <c r="L31" t="n">
-        <v>125</v>
-      </c>
-      <c r="M31" t="inlineStr"/>
+        <v>450</v>
+      </c>
+      <c r="M31" t="n">
+        <v>300</v>
+      </c>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="O31" t="n">
+        <v>46</v>
+      </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="n">
-        <v>0.35</v>
-      </c>
+      <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr"/>
@@ -3702,23 +5265,11 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Color(0.25, 0.85, 0.35, 0.08)</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>凡器</t>
-        </is>
-      </c>
-      <c r="AK31" t="n">
-        <v>1</v>
-      </c>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM31" t="inlineStr"/>
       <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="inlineStr"/>
@@ -3726,21 +5277,99 @@
       <c r="AR31" t="inlineStr"/>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>Color(0.72, 0.60, 0.42, 1)</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>法器</t>
+        </is>
+      </c>
+      <c r="AX31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>300</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>150</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>450</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>600</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI31" t="inlineStr">
+        <is>
+          <t>tank</t>
+        </is>
+      </c>
+      <c r="BJ31" t="inlineStr">
+        <is>
+          <t>前排坦克，5秒嘲讽</t>
+        </is>
+      </c>
+      <c r="BK31" t="inlineStr"/>
+      <c r="BL31" t="inlineStr"/>
+      <c r="BM31" t="inlineStr"/>
+      <c r="BN31" t="inlineStr"/>
+      <c r="BO31" t="inlineStr"/>
+      <c r="BP31" t="inlineStr"/>
+      <c r="BQ31" t="inlineStr"/>
+      <c r="BR31" t="inlineStr"/>
+      <c r="BS31" t="inlineStr"/>
+      <c r="BT31" t="inlineStr"/>
+      <c r="BU31" t="inlineStr"/>
+      <c r="BV31" t="inlineStr"/>
+      <c r="BW31" t="inlineStr"/>
+      <c r="BX31" t="inlineStr"/>
+      <c r="BY31" t="inlineStr"/>
+      <c r="BZ31" t="inlineStr"/>
+      <c r="CA31" t="inlineStr">
+        <is>
+          <t>生命提升</t>
+        </is>
+      </c>
+      <c r="CB31" t="inlineStr">
+        <is>
+          <t>嘲讽范围 +50%，受到攻击时释放震荡波</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>sword_puppet</t>
+          <t>turret</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>剑傀儡</t>
+          <t>炮台</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>召唤持续存在的剑傀儡，追击最近敌人并用近战扇形挥砍。死亡后会在短时间后重生。</t>
+          <t>召唤固定炮台自动索敌并发射爆炸炮弹。玩家离开过远时，炮台会延迟重新部署到玩家附近。</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3750,7 +5379,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3760,28 +5389,26 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>slash</t>
+          <t>projectile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>15</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="n">
-        <v>500</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="n">
-        <v>52</v>
-      </c>
-      <c r="N32" t="n">
-        <v>58</v>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L32" t="n">
+        <v>700</v>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>420</v>
+      </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
@@ -3796,27 +5423,17 @@
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="inlineStr"/>
+      <c r="AE32" t="n">
+        <v>58</v>
+      </c>
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Color(0.95, 0.86, 0.45, 1)</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>凡器</t>
-        </is>
-      </c>
-      <c r="AK32" t="n">
-        <v>1</v>
-      </c>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM32" t="inlineStr"/>
       <c r="AN32" t="inlineStr"/>
       <c r="AO32" t="inlineStr"/>
       <c r="AP32" t="inlineStr"/>
@@ -3824,21 +5441,99 @@
       <c r="AR32" t="inlineStr"/>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>Color(1, 0.32, 0.10, 1)</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>灵器</t>
+        </is>
+      </c>
+      <c r="AX32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>120</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>700</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>900</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI32" t="inlineStr">
+        <is>
+          <t>turret</t>
+        </is>
+      </c>
+      <c r="BJ32" t="inlineStr">
+        <is>
+          <t>固定阵地输出，距离玩家超过900后2秒重新部署</t>
+        </is>
+      </c>
+      <c r="BK32" t="inlineStr"/>
+      <c r="BL32" t="inlineStr"/>
+      <c r="BM32" t="inlineStr"/>
+      <c r="BN32" t="inlineStr"/>
+      <c r="BO32" t="inlineStr"/>
+      <c r="BP32" t="inlineStr"/>
+      <c r="BQ32" t="inlineStr"/>
+      <c r="BR32" t="inlineStr"/>
+      <c r="BS32" t="inlineStr"/>
+      <c r="BT32" t="inlineStr"/>
+      <c r="BU32" t="inlineStr"/>
+      <c r="BV32" t="inlineStr"/>
+      <c r="BW32" t="inlineStr"/>
+      <c r="BX32" t="inlineStr"/>
+      <c r="BY32" t="inlineStr"/>
+      <c r="BZ32" t="inlineStr"/>
+      <c r="CA32" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB32" t="inlineStr">
+        <is>
+          <t>无专属强化</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>turret</t>
+          <t>ghost</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>炮台</t>
+          <t>幽魂</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>召唤固定炮台自动索敌并发射爆炸炮弹。玩家离开过远时，炮台会延迟重新部署到玩家附近。</t>
+          <t>召唤没有仇恨值的幽魂。幽魂锁定敌人后加速冲击，穿过敌人造成伤害，并在敌人身后短距离停下后重新锁定目标。幽魂不会受到伤害。</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3848,7 +5543,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3858,24 +5553,26 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>projectile</t>
+          <t>line</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>18</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1.25</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L33" t="n">
         <v>700</v>
       </c>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>42</v>
+      </c>
       <c r="O33" t="n">
-        <v>420</v>
+        <v>72</v>
       </c>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
@@ -3885,9 +5582,7 @@
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
-      <c r="X33" t="n">
-        <v>58</v>
-      </c>
+      <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr"/>
@@ -3898,94 +5593,156 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Color(1, 0.32, 0.10, 1)</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>法器</t>
-        </is>
-      </c>
-      <c r="AK33" t="n">
-        <v>2</v>
-      </c>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM33" t="inlineStr"/>
       <c r="AN33" t="inlineStr"/>
       <c r="AO33" t="inlineStr"/>
-      <c r="AP33" t="inlineStr"/>
+      <c r="AP33" t="n">
+        <v>2</v>
+      </c>
       <c r="AQ33" t="inlineStr"/>
       <c r="AR33" t="inlineStr"/>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>Color(0.50, 0.78, 1, 0.72)</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>灵宝</t>
+        </is>
+      </c>
+      <c r="AX33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>60</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>320</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>700</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>900</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI33" t="inlineStr">
+        <is>
+          <t>ghost</t>
+        </is>
+      </c>
+      <c r="BJ33" t="inlineStr">
+        <is>
+          <t>无仇恨，不受伤害，锁定冲击</t>
+        </is>
+      </c>
+      <c r="BK33" t="inlineStr"/>
+      <c r="BL33" t="inlineStr"/>
+      <c r="BM33" t="inlineStr"/>
+      <c r="BN33" t="inlineStr"/>
+      <c r="BO33" t="inlineStr"/>
+      <c r="BP33" t="inlineStr"/>
+      <c r="BQ33" t="inlineStr"/>
+      <c r="BR33" t="inlineStr"/>
+      <c r="BS33" t="inlineStr"/>
+      <c r="BT33" t="inlineStr"/>
+      <c r="BU33" t="inlineStr"/>
+      <c r="BV33" t="inlineStr"/>
+      <c r="BW33" t="inlineStr"/>
+      <c r="BX33" t="inlineStr"/>
+      <c r="BY33" t="inlineStr"/>
+      <c r="BZ33" t="inlineStr"/>
+      <c r="CA33" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB33" t="inlineStr">
+        <is>
+          <t>无专属强化</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>two_handed_sword</t>
+          <t>poison_bug</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>双手剑</t>
+          <t>毒虫</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>以较慢节奏挥出沉重剑光，造成高伤害的大范围扇形斩击。</t>
+          <t>召唤没有仇恨值的毒虫群。毒虫不会被敌人主动攻击，但仍会被范围伤害波及。毒虫近战撕咬并附加中毒。</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>剑修</t>
+          <t>召唤</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>毒</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>melee</t>
+          <t>summon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>slash</t>
+          <t>stab</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>52</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1.35</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="n">
-        <v>145</v>
+        <v>0.5</v>
       </c>
       <c r="L34" t="n">
-        <v>38</v>
-      </c>
-      <c r="M34" t="n">
-        <v>96</v>
-      </c>
-      <c r="N34" t="n">
-        <v>165</v>
-      </c>
-      <c r="O34" t="inlineStr"/>
+        <v>450</v>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="n">
+        <v>32</v>
+      </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
-      <c r="T34" t="n">
-        <v>0.22</v>
-      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
@@ -3996,29 +5753,19 @@
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="n">
-        <v>90</v>
-      </c>
+      <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Color(0.86, 0.68, 0.34, 0.72)</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>法器</t>
-        </is>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="n">
+        <v>2</v>
       </c>
       <c r="AK34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM34" t="inlineStr"/>
       <c r="AN34" t="inlineStr"/>
       <c r="AO34" t="inlineStr"/>
       <c r="AP34" t="inlineStr"/>
@@ -4026,6 +5773,84 @@
       <c r="AR34" t="inlineStr"/>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr"/>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>Color(0.42, 1, 0.22, 1)</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>仙宝</t>
+        </is>
+      </c>
+      <c r="AX34" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>235</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>450</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>650</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI34" t="inlineStr">
+        <is>
+          <t>swarm</t>
+        </is>
+      </c>
+      <c r="BJ34" t="inlineStr">
+        <is>
+          <t>无仇恨，可被范围伤害波及，击杀20%概率补充毒虫</t>
+        </is>
+      </c>
+      <c r="BK34" t="inlineStr"/>
+      <c r="BL34" t="inlineStr"/>
+      <c r="BM34" t="inlineStr"/>
+      <c r="BN34" t="inlineStr"/>
+      <c r="BO34" t="inlineStr"/>
+      <c r="BP34" t="inlineStr"/>
+      <c r="BQ34" t="inlineStr"/>
+      <c r="BR34" t="inlineStr"/>
+      <c r="BS34" t="inlineStr"/>
+      <c r="BT34" t="inlineStr"/>
+      <c r="BU34" t="inlineStr"/>
+      <c r="BV34" t="inlineStr"/>
+      <c r="BW34" t="inlineStr"/>
+      <c r="BX34" t="inlineStr"/>
+      <c r="BY34" t="inlineStr"/>
+      <c r="BZ34" t="inlineStr"/>
+      <c r="CA34" t="inlineStr">
+        <is>
+          <t>按默认升星成长</t>
+        </is>
+      </c>
+      <c r="CB34" t="inlineStr">
+        <is>
+          <t>无专属强化</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AT34"/>
@@ -4039,68 +5864,80 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="35" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>synergy_type</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>threshold</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>trigger</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>affected</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>attack_speed_per_stack</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>max_stacks</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>max_attack_speed_bonus</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>max_hp_bonus</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>size_bonus</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>reset_timing</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -4139,12 +5976,12 @@
       <c r="H2" t="n">
         <v>0.4</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>每场战斗开始/结束</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>机制简单，不新增专属名词</t>
         </is>
@@ -4183,12 +6020,12 @@
       <c r="H3" t="n">
         <v>1.2</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>每场战斗开始/结束</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>达到上限后不再增加</t>
         </is>
@@ -4227,14 +6064,137 @@
       <c r="H4" t="n">
         <v>2.4</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>每场战斗开始/结束</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>未来新增剑修法宝同样适用</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>体修</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>体修法宝上阵数量达到阈值</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>玩家与所有体修法宝</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>实时随羁绊变化</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>最大生命值 +30%，体型 +10%；体修法宝攻击范围受体型影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>体修</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>体修法宝上阵数量达到阈值</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>玩家与所有体修法宝</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>实时随羁绊变化</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>最大生命值 +80%，体型 +25%；体修法宝攻击范围受体型影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>体修</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>体修法宝上阵数量达到阈值</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>玩家与所有体修法宝</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>实时随羁绊变化</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>最大生命值 +150%，体型 +50%；体修法宝攻击范围受体型影响</t>
         </is>
       </c>
     </row>

--- a/docs/GameBalance.xlsx
+++ b/docs/GameBalance.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="Rd9bd643a925b4c6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法宝总表" sheetId="2" r:id="Rbefcb0f74a604c88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法宝星级预览" sheetId="3" r:id="R69af75ee9d9f4eae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命" sheetId="4" r:id="Re4e5818b1a7f4570"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奇遇" sheetId="5" r:id="R2ed3f5e7ebfa4241"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊阈值" sheetId="6" r:id="R9af52f36ff0d4805"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济与修为" sheetId="7" r:id="R5291520231e54837"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="Rae0ab4a483644c3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法宝总表" sheetId="2" r:id="R15935318e68a473c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法宝星级预览" sheetId="3" r:id="Rfc75f47852264e26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命" sheetId="4" r:id="R6610705b0bc54335"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奇遇" sheetId="5" r:id="R6bd0912bb68d45f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊阈值" sheetId="6" r:id="R7a05d31d268c42aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济与修为" sheetId="7" r:id="R7835337b736f44df"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -476,7 +476,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B3" s="5" t="n">
-        <x:v>46200.64382762732</x:v>
+        <x:v>46200.78340822917</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1284,10 +1284,18 @@
       <x:c r="C5" s="14" t="str">
         <x:v>锁定最近敌人方向挥出直线墨迹，短暂延迟后整条墨迹同时爆发，穿透路径上的所有敌人。</x:v>
       </x:c>
-      <x:c r="D5" s="14" t="str"/>
-      <x:c r="E5" s="14" t="str"/>
-      <x:c r="F5" s="14" t="str"/>
-      <x:c r="G5" s="14" t="str"/>
+      <x:c r="D5" s="14" t="str">
+        <x:v>毛笔飞向目标区域，三笔写出抽象符印，完整形成后统一爆发。</x:v>
+      </x:c>
+      <x:c r="E5" s="14" t="str">
+        <x:v>爆发后残留墨阵，按固定脉冲造成低伤并减速。</x:v>
+      </x:c>
+      <x:c r="F5" s="14" t="str">
+        <x:v>3费延迟AOE、区域布置和控场。</x:v>
+      </x:c>
+      <x:c r="G5" s="14" t="str">
+        <x:v>radius, delayed_strike_interval, tick_interval, duration, secondary_damage_mult, slow_percent</x:v>
+      </x:c>
       <x:c r="H5" s="14" t="str">
         <x:v>法修</x:v>
       </x:c>
@@ -1312,25 +1320,25 @@
       </x:c>
       <x:c r="P5" s="14" t="str"/>
       <x:c r="Q5" s="14" t="n">
-        <x:v>34</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R5" s="14" t="n">
-        <x:v>1.21</x:v>
+        <x:v>1.35</x:v>
       </x:c>
       <x:c r="S5" s="14" t="n">
-        <x:v>28.1</x:v>
+        <x:v>35.56</x:v>
       </x:c>
       <x:c r="T5" s="14" t="n">
         <x:v>320</x:v>
       </x:c>
       <x:c r="U5" s="14" t="n">
-        <x:v>24</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="V5" s="14" t="n">
         <x:v>44</x:v>
       </x:c>
       <x:c r="W5" s="14" t="n">
-        <x:v>430</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="X5" s="14" t="n">
         <x:v>1</x:v>
@@ -1348,7 +1356,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AC5" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="AD5" s="14" t="n">
         <x:v>0</x:v>
@@ -1402,13 +1410,13 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="AU5" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="AV5" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="AW5" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="AX5" s="14" t="n">
         <x:v>0.5</x:v>
@@ -1451,10 +1459,18 @@
       <x:c r="C6" s="14" t="str">
         <x:v>命中后在附近未命中的敌人之间弹射，适合补刀但单体较弱。</x:v>
       </x:c>
-      <x:c r="D6" s="14" t="str"/>
-      <x:c r="E6" s="14" t="str"/>
-      <x:c r="F6" s="14" t="str"/>
-      <x:c r="G6" s="14" t="str"/>
+      <x:c r="D6" s="14" t="str">
+        <x:v>铜钱旋转发射，命中后按目标搜索范围折线弹射并留下短暂金色轨迹。</x:v>
+      </x:c>
+      <x:c r="E6" s="14" t="str">
+        <x:v>最后一次弹射后分裂为多枚小铜钱，优先攻击不同目标。</x:v>
+      </x:c>
+      <x:c r="F6" s="14" t="str">
+        <x:v>1费高频弹射，连续打击多个目标。</x:v>
+      </x:c>
+      <x:c r="G6" s="14" t="str">
+        <x:v>bounce_count, bounce_range, projectile_speed, count, secondary_damage_mult, secondary_radius</x:v>
+      </x:c>
       <x:c r="H6" s="14" t="str">
         <x:v>法修</x:v>
       </x:c>
@@ -1500,7 +1516,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="X6" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="Y6" s="14" t="n">
         <x:v>0</x:v>
@@ -1560,19 +1576,19 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="AR6" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="AS6" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="AT6" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="AU6" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="AV6" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="AW6" s="14" t="n">
         <x:v>0</x:v>
@@ -1960,10 +1976,18 @@
       <x:c r="C9" s="14" t="str">
         <x:v>锁定一名敌人降下神雷，以该敌人为中心造成范围伤害。三星时神雷范围大幅增加。</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="str"/>
-      <x:c r="E9" s="14" t="str"/>
-      <x:c r="F9" s="14" t="str"/>
-      <x:c r="G9" s="14" t="str"/>
+      <x:c r="D9" s="14" t="str">
+        <x:v>稳定选择敌人密集区域，预警圈后主雷落下，并连锁附近目标。</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="str">
+        <x:v>主雷后生成雷劫区域，按间隔落下多道副雷。</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="str">
+        <x:v>5费远程天降爆发，大范围高伤和连锁清场。</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="str">
+        <x:v>windup_time, radius, count, bounce_range, delayed_strike_count, delayed_strike_interval, secondary_radius</x:v>
+      </x:c>
       <x:c r="H9" s="14" t="str">
         <x:v>法修</x:v>
       </x:c>
@@ -2009,7 +2033,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="X9" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Y9" s="14" t="n">
         <x:v>0</x:v>
@@ -2018,7 +2042,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA9" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AB9" s="14" t="n">
         <x:v>0</x:v>
@@ -2069,7 +2093,7 @@
         <x:v>0.85</x:v>
       </x:c>
       <x:c r="AR9" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="AS9" s="14" t="n">
         <x:v>0</x:v>
@@ -2078,10 +2102,10 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="AU9" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.32</x:v>
       </x:c>
       <x:c r="AV9" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1.18</x:v>
       </x:c>
       <x:c r="AW9" s="14" t="n">
         <x:v>0</x:v>
@@ -2127,10 +2151,18 @@
       <x:c r="C10" s="14" t="str">
         <x:v>向目标方向喷出锥形火焰，对范围内敌人造成伤害。</x:v>
       </x:c>
-      <x:c r="D10" s="14" t="str"/>
-      <x:c r="E10" s="14" t="str"/>
-      <x:c r="F10" s="14" t="str"/>
-      <x:c r="G10" s="14" t="str"/>
+      <x:c r="D10" s="14" t="str">
+        <x:v>火葫芦锁定密集方向，短前摇后按固定脉冲喷出多层锥形火浪。</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="str">
+        <x:v>喷火结束后吐出火种，爆炸并留下固定脉冲燃烧区域。</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="str">
+        <x:v>4费中近距离持续锥形清群，多段伤害和灼烧。</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="str">
+        <x:v>windup_time, duration, tick_interval, fan_angle, poison_dps, explosion_radius, delayed_strike_interval</x:v>
+      </x:c>
       <x:c r="H10" s="14" t="str">
         <x:v>法修</x:v>
       </x:c>
@@ -2158,10 +2190,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="R10" s="14" t="n">
-        <x:v>1.18</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="S10" s="14" t="n">
-        <x:v>60.17</x:v>
+        <x:v>47.33</x:v>
       </x:c>
       <x:c r="T10" s="14" t="n">
         <x:v>230</x:v>
@@ -2200,10 +2232,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AF10" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="AG10" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="AH10" s="14" t="n">
         <x:v>0</x:v>
@@ -2236,7 +2268,7 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="AR10" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="AS10" s="14" t="n">
         <x:v>0</x:v>
@@ -2245,13 +2277,13 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="AU10" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.32</x:v>
       </x:c>
       <x:c r="AV10" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="AW10" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AX10" s="14" t="n">
         <x:v>0.5</x:v>
@@ -2260,7 +2292,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AZ10" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="BA10" s="14" t="n">
         <x:v>0</x:v>
@@ -2294,10 +2326,18 @@
       <x:c r="C11" s="14" t="str">
         <x:v>向最近敌人发射火焰法球，直伤较低，命中后造成小范围爆炸。</x:v>
       </x:c>
-      <x:c r="D11" s="14" t="str"/>
-      <x:c r="E11" s="14" t="str"/>
-      <x:c r="F11" s="14" t="str"/>
-      <x:c r="G11" s="14" t="str"/>
+      <x:c r="D11" s="14" t="str">
+        <x:v>光点凝聚成法球，短暂停顿后飞行，命中后收缩并爆炸为圆形冲击波。</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="str">
+        <x:v>第一次爆炸后延迟触发更大、更淡、低伤的第二次爆炸。</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="str">
+        <x:v>1费标准法修发射物，中速基础AOE。</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="str">
+        <x:v>windup_time, explosion_radius, secondary_delay, secondary_radius, secondary_damage_mult</x:v>
+      </x:c>
       <x:c r="H11" s="14" t="str">
         <x:v>法修</x:v>
       </x:c>
@@ -2403,22 +2443,22 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="AR11" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="AS11" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="AT11" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="AU11" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="AV11" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1.35</x:v>
       </x:c>
       <x:c r="AW11" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="AX11" s="14" t="n">
         <x:v>0.5</x:v>
@@ -3487,10 +3527,18 @@
       <x:c r="C18" s="14" t="str">
         <x:v>音符命中后短暂降低敌人伤害，直伤较低。</x:v>
       </x:c>
-      <x:c r="D18" s="14" t="str"/>
-      <x:c r="E18" s="14" t="str"/>
-      <x:c r="F18" s="14" t="str"/>
-      <x:c r="G18" s="14" t="str"/>
+      <x:c r="D18" s="14" t="str">
+        <x:v>古琴虚影拨弦，按顺序释放三层弧形音波并施加伤害降低。</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="str">
+        <x:v>第三层音波改为以角色为中心的环形音波。</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="str">
+        <x:v>3费大范围多段音波辅助，偏生存和削弱。</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="str">
+        <x:v>range, fan_angle, delayed_strike_interval, damage_reduction_percent, debuff_duration</x:v>
+      </x:c>
       <x:c r="H18" s="14" t="str">
         <x:v>法修</x:v>
       </x:c>
@@ -3518,10 +3566,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="R18" s="14" t="n">
-        <x:v>0.82</x:v>
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="S18" s="14" t="n">
-        <x:v>25.61</x:v>
+        <x:v>16.8</x:v>
       </x:c>
       <x:c r="T18" s="14" t="n">
         <x:v>480</x:v>
@@ -3530,7 +3578,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="V18" s="14" t="n">
-        <x:v>16</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="W18" s="14" t="n">
         <x:v>16</x:v>
@@ -3620,7 +3668,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AZ18" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="BA18" s="14" t="n">
         <x:v>0</x:v>
@@ -4330,10 +4378,18 @@
       <x:c r="C23" s="14" t="str">
         <x:v>宽大的法环沿直线缓慢穿透敌人，清线稳定但直伤偏低。</x:v>
       </x:c>
-      <x:c r="D23" s="14" t="str"/>
-      <x:c r="E23" s="14" t="str"/>
-      <x:c r="F23" s="14" t="str"/>
-      <x:c r="G23" s="14" t="str"/>
+      <x:c r="D23" s="14" t="str">
+        <x:v>法环展开并蓄力，随后轰出短持续超长直线光束。</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="str">
+        <x:v>主光束路径留下光痕，延迟后整条路径二次爆发。</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="str">
+        <x:v>2费短前摇、高爆发、贯穿光束。</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="str">
+        <x:v>windup_time, range, width, secondary_delay, secondary_radius, secondary_damage_mult</x:v>
+      </x:c>
       <x:c r="H23" s="14" t="str">
         <x:v>法修</x:v>
       </x:c>
@@ -4358,22 +4414,22 @@
       </x:c>
       <x:c r="P23" s="14" t="str"/>
       <x:c r="Q23" s="14" t="n">
-        <x:v>25</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="R23" s="14" t="n">
-        <x:v>0.89</x:v>
+        <x:v>1.15</x:v>
       </x:c>
       <x:c r="S23" s="14" t="n">
-        <x:v>28.09</x:v>
+        <x:v>36.52</x:v>
       </x:c>
       <x:c r="T23" s="14" t="n">
-        <x:v>520</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="U23" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
       <x:c r="V23" s="14" t="n">
-        <x:v>34</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="W23" s="14" t="n">
         <x:v>34</x:v>
@@ -4439,7 +4495,7 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="AR23" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="AS23" s="14" t="n">
         <x:v>0</x:v>
@@ -4448,13 +4504,13 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="AU23" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="AV23" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AW23" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="AX23" s="14" t="n">
         <x:v>0.5</x:v>
@@ -6713,13 +6769,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G11" s="14" t="n">
-        <x:v>34</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H11" s="14" t="n">
-        <x:v>1.21</x:v>
+        <x:v>1.35</x:v>
       </x:c>
       <x:c r="I11" s="14" t="n">
-        <x:v>28.1</x:v>
+        <x:v>35.56</x:v>
       </x:c>
       <x:c r="J11" s="14" t="str"/>
       <x:c r="K11" s="14" t="str"/>
@@ -6745,13 +6801,13 @@
         <x:v>0.85</x:v>
       </x:c>
       <x:c r="G12" s="14" t="n">
-        <x:v>52.7</x:v>
+        <x:v>74.4</x:v>
       </x:c>
       <x:c r="H12" s="14" t="n">
-        <x:v>1.028</x:v>
+        <x:v>1.147</x:v>
       </x:c>
       <x:c r="I12" s="14" t="n">
-        <x:v>51.24</x:v>
+        <x:v>64.84</x:v>
       </x:c>
       <x:c r="J12" s="14" t="str"/>
       <x:c r="K12" s="14" t="str"/>
@@ -6777,13 +6833,13 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="G13" s="14" t="n">
-        <x:v>76.5</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H13" s="14" t="n">
-        <x:v>0.847</x:v>
+        <x:v>0.945</x:v>
       </x:c>
       <x:c r="I13" s="14" t="n">
-        <x:v>90.32</x:v>
+        <x:v>114.29</x:v>
       </x:c>
       <x:c r="J13" s="14" t="str"/>
       <x:c r="K13" s="14" t="str"/>
@@ -7202,10 +7258,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="H26" s="14" t="n">
-        <x:v>1.18</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="I26" s="14" t="n">
-        <x:v>60.17</x:v>
+        <x:v>47.33</x:v>
       </x:c>
       <x:c r="J26" s="14" t="str"/>
       <x:c r="K26" s="14" t="str"/>
@@ -7234,10 +7290,10 @@
         <x:v>110.05</x:v>
       </x:c>
       <x:c r="H27" s="14" t="n">
-        <x:v>1.003</x:v>
+        <x:v>1.275</x:v>
       </x:c>
       <x:c r="I27" s="14" t="n">
-        <x:v>109.72</x:v>
+        <x:v>86.31</x:v>
       </x:c>
       <x:c r="J27" s="14" t="str"/>
       <x:c r="K27" s="14" t="str"/>
@@ -7266,10 +7322,10 @@
         <x:v>159.75</x:v>
       </x:c>
       <x:c r="H28" s="14" t="n">
-        <x:v>0.826</x:v>
+        <x:v>1.05</x:v>
       </x:c>
       <x:c r="I28" s="14" t="n">
-        <x:v>193.4</x:v>
+        <x:v>152.14</x:v>
       </x:c>
       <x:c r="J28" s="14" t="str"/>
       <x:c r="K28" s="14" t="str"/>
@@ -7976,10 +8032,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="H50" s="14" t="n">
-        <x:v>0.82</x:v>
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="I50" s="14" t="n">
-        <x:v>25.61</x:v>
+        <x:v>16.8</x:v>
       </x:c>
       <x:c r="J50" s="14" t="str"/>
       <x:c r="K50" s="14" t="str"/>
@@ -8008,10 +8064,10 @@
         <x:v>32.55</x:v>
       </x:c>
       <x:c r="H51" s="14" t="n">
-        <x:v>0.697</x:v>
+        <x:v>1.063</x:v>
       </x:c>
       <x:c r="I51" s="14" t="n">
-        <x:v>46.7</x:v>
+        <x:v>30.64</x:v>
       </x:c>
       <x:c r="J51" s="14" t="str"/>
       <x:c r="K51" s="14" t="str"/>
@@ -8040,10 +8096,10 @@
         <x:v>47.25</x:v>
       </x:c>
       <x:c r="H52" s="14" t="n">
-        <x:v>0.574</x:v>
+        <x:v>0.875</x:v>
       </x:c>
       <x:c r="I52" s="14" t="n">
-        <x:v>82.32</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J52" s="14" t="str"/>
       <x:c r="K52" s="14" t="str"/>
@@ -8459,13 +8515,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G65" s="14" t="n">
-        <x:v>25</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H65" s="14" t="n">
-        <x:v>0.89</x:v>
+        <x:v>1.15</x:v>
       </x:c>
       <x:c r="I65" s="14" t="n">
-        <x:v>28.09</x:v>
+        <x:v>36.52</x:v>
       </x:c>
       <x:c r="J65" s="14" t="str"/>
       <x:c r="K65" s="14" t="str"/>
@@ -8491,13 +8547,13 @@
         <x:v>0.85</x:v>
       </x:c>
       <x:c r="G66" s="14" t="n">
-        <x:v>38.75</x:v>
+        <x:v>65.1</x:v>
       </x:c>
       <x:c r="H66" s="14" t="n">
-        <x:v>0.756</x:v>
+        <x:v>0.977</x:v>
       </x:c>
       <x:c r="I66" s="14" t="n">
-        <x:v>51.22</x:v>
+        <x:v>66.6</x:v>
       </x:c>
       <x:c r="J66" s="14" t="str"/>
       <x:c r="K66" s="14" t="str"/>
@@ -8523,13 +8579,13 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="G67" s="14" t="n">
-        <x:v>56.25</x:v>
+        <x:v>94.5</x:v>
       </x:c>
       <x:c r="H67" s="14" t="n">
-        <x:v>0.623</x:v>
+        <x:v>0.805</x:v>
       </x:c>
       <x:c r="I67" s="14" t="n">
-        <x:v>90.29</x:v>
+        <x:v>117.39</x:v>
       </x:c>
       <x:c r="J67" s="14" t="str"/>
       <x:c r="K67" s="14" t="str"/>

--- a/docs/GameBalance.xlsx
+++ b/docs/GameBalance.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="Rae0ab4a483644c3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法宝总表" sheetId="2" r:id="R15935318e68a473c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法宝星级预览" sheetId="3" r:id="Rfc75f47852264e26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命" sheetId="4" r:id="R6610705b0bc54335"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奇遇" sheetId="5" r:id="R6bd0912bb68d45f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊阈值" sheetId="6" r:id="R7a05d31d268c42aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济与修为" sheetId="7" r:id="R7835337b736f44df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R1cdfe74267c440b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法宝总表" sheetId="2" r:id="Rf1ffaf0aff1d4a04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法宝星级预览" sheetId="3" r:id="R783e6b3f963a4b97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命" sheetId="4" r:id="Rc88b96ed18a4442a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奇遇" sheetId="5" r:id="Rb8636c1829c34c50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊阈值" sheetId="6" r:id="R205f75a1f16244b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济与修为" sheetId="7" r:id="R0d02d8ad861a42f8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -476,7 +476,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B3" s="5" t="n">
-        <x:v>46200.78340822917</x:v>
+        <x:v>46200.79495604167</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -781,10 +781,18 @@
       <x:c r="C2" s="14" t="str">
         <x:v>发射宽大的血色剑气。攻击消耗3点生命，生命低于30%时不消耗；击杀敌人回复1点生命。</x:v>
       </x:c>
-      <x:c r="D2" s="14" t="str"/>
-      <x:c r="E2" s="14" t="str"/>
-      <x:c r="F2" s="14" t="str"/>
-      <x:c r="G2" s="14" t="str"/>
+      <x:c r="D2" s="14" t="str">
+        <x:v>血流压缩成宽大弯月血刃，蓄力后直线飞出，沿途穿透并留下残月血色轨迹。</x:v>
+      </x:c>
+      <x:c r="E2" s="14" t="str">
+        <x:v>到达最大距离后按pause_time停顿，再以return_speed返回；去程和回程分别维护命中记录。</x:v>
+      </x:c>
+      <x:c r="F2" s="14" t="str">
+        <x:v>2费宽直线清线，消耗生命，击杀回血。</x:v>
+      </x:c>
+      <x:c r="G2" s="14" t="str">
+        <x:v>life_cost_flat, life_cost_min_hp_ratio, kill_heal_amount, windup_time, return_speed, pause_time, secondary_damage_mult</x:v>
+      </x:c>
       <x:c r="H2" s="14" t="str">
         <x:v>魔修</x:v>
       </x:c>
@@ -890,16 +898,16 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="AR2" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="AS2" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AT2" s="14" t="n">
-        <x:v>0.12</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="AU2" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.62</x:v>
       </x:c>
       <x:c r="AV2" s="14" t="n">
         <x:v>0</x:v>
@@ -911,7 +919,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="AY2" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="AZ2" s="14" t="n">
         <x:v>0</x:v>
@@ -926,7 +934,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BD2" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="BE2" s="14" t="n">
         <x:v>0</x:v>
@@ -948,10 +956,18 @@
       <x:c r="C3" s="14" t="str">
         <x:v>挥出高伤害血色剑光。攻击消耗3点生命，生命低于30%时不消耗；击杀敌人回复1点生命。</x:v>
       </x:c>
-      <x:c r="D3" s="14" t="str"/>
-      <x:c r="E3" s="14" t="str"/>
-      <x:c r="F3" s="14" t="str"/>
-      <x:c r="G3" s="14" t="str"/>
+      <x:c r="D3" s="14" t="str">
+        <x:v>抽出血色流光凝成短血剑，近距离厚重血色剑光挥砍，命中留下短血痕，结束后崩成血雾。</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="str">
+        <x:v>命中的敌人留下血痕，按secondary_delay延迟爆裂，按secondary_damage_mult造成小范围低伤。</x:v>
+      </x:c>
+      <x:c r="F3" s="14" t="str">
+        <x:v>1费近战高伤害，消耗生命换输出，击杀按kill_heal_amount回血。</x:v>
+      </x:c>
+      <x:c r="G3" s="14" t="str">
+        <x:v>life_cost_flat, life_cost_min_hp_ratio, kill_heal_amount, windup_time, secondary_damage_mult, secondary_radius, secondary_delay</x:v>
+      </x:c>
       <x:c r="H3" s="14" t="str">
         <x:v>魔修</x:v>
       </x:c>
@@ -1057,22 +1073,22 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="AR3" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="AS3" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AT3" s="14" t="n">
-        <x:v>0.12</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="AU3" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.38</x:v>
       </x:c>
       <x:c r="AV3" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="AW3" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.28</x:v>
       </x:c>
       <x:c r="AX3" s="14" t="n">
         <x:v>0.5</x:v>
@@ -3702,10 +3718,18 @@
       <x:c r="C19" s="14" t="str">
         <x:v>短时间锁定最近敌人并持续发射天眼光束。攻击期间持续扣除生命，击杀敌人后恢复生命。</x:v>
       </x:c>
-      <x:c r="D19" s="14" t="str"/>
-      <x:c r="E19" s="14" t="str"/>
-      <x:c r="F19" s="14" t="str"/>
-      <x:c r="G19" s="14" t="str"/>
+      <x:c r="D19" s="14" t="str">
+        <x:v>天眼睁开并锁定目标，光束按tick_interval固定脉冲造成持续伤害，击杀后自动转火。</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="str">
+        <x:v>主光束外额外分出两条副光束，副光束优先锁定不同目标并按side_projectile_damage_mult造成伤害。</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="str">
+        <x:v>3费持续单体压制，对精英和Boss稳定，持续耗血并击杀回血。</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="str">
+        <x:v>duration, tick_interval, range, life_cost_flat, life_cost_min_hp_ratio, kill_heal_amount, side_projectile_damage_mult</x:v>
+      </x:c>
       <x:c r="H19" s="14" t="str">
         <x:v>魔修</x:v>
       </x:c>
@@ -3739,7 +3763,7 @@
         <x:v>10.28</x:v>
       </x:c>
       <x:c r="T19" s="14" t="n">
-        <x:v>320</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="U19" s="14" t="n">
         <x:v>5</x:v>
@@ -3811,7 +3835,7 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="AR19" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="AS19" s="14" t="n">
         <x:v>0</x:v>
@@ -3823,13 +3847,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AV19" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="AW19" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AX19" s="14" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.42</x:v>
       </x:c>
       <x:c r="AY19" s="14" t="n">
         <x:v>0</x:v>
@@ -5062,10 +5086,18 @@
       <x:c r="C27" s="14" t="str">
         <x:v>高速发射毒针，直接伤害较低，但会让敌人持续中毒。</x:v>
       </x:c>
-      <x:c r="D27" s="14" t="str"/>
-      <x:c r="E27" s="14" t="str"/>
-      <x:c r="F27" s="14" t="str"/>
-      <x:c r="G27" s="14" t="str"/>
+      <x:c r="D27" s="14" t="str">
+        <x:v>身侧浮现数根细毒针，短暂停顿后以极短间隔连续射出，命中附加非无限叠加中毒标记。</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="str">
+        <x:v>每delayed_strike_count次普通攻击追加一轮扇形针雨，数量=bounce_count，伤害按secondary_damage_mult。</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="str">
+        <x:v>2费高频低直伤，主要依靠中毒持续输出，不消耗生命。</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="str">
+        <x:v>count, delayed_strike_count, delayed_strike_interval, bounce_count, fan_angle, secondary_damage_mult, poison_can_stack</x:v>
+      </x:c>
       <x:c r="H27" s="14" t="str">
         <x:v>魔修</x:v>
       </x:c>
@@ -5111,7 +5143,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="X27" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="Y27" s="14" t="n">
         <x:v>0</x:v>
@@ -5120,7 +5152,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA27" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="AB27" s="14" t="n">
         <x:v>0</x:v>
@@ -5180,13 +5212,13 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="AU27" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.55</x:v>
       </x:c>
       <x:c r="AV27" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AW27" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="AX27" s="14" t="n">
         <x:v>0.5</x:v>
@@ -5195,7 +5227,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AZ27" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="BA27" s="14" t="n">
         <x:v>0</x:v>
@@ -5396,10 +5428,18 @@
       <x:c r="C29" s="14" t="str">
         <x:v>挥动镰刀造成伤害，只有镰刀头部有伤害。造成伤害的一部分会回复生命。</x:v>
       </x:c>
-      <x:c r="D29" s="14" t="str"/>
-      <x:c r="E29" s="14" t="str"/>
-      <x:c r="F29" s="14" t="str"/>
-      <x:c r="G29" s="14" t="str"/>
+      <x:c r="D29" s="14" t="str">
+        <x:v>长柄镰刀后拉后大弧挥砍，仅外圈镰刃环带造成伤害，命中抽出生命丝线回血。</x:v>
+      </x:c>
+      <x:c r="E29" s="14" t="str">
+        <x:v>第一轮结束后按secondary_delay反向再挥一轮，第二轮伤害按secondary_damage_mult。</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="str">
+        <x:v>4费中近距离外圈收割和续航，回血按实际伤害比例并受shield_max单轮上限限制。</x:v>
+      </x:c>
+      <x:c r="G29" s="14" t="str">
+        <x:v>fan_angle, length, width, heal_amount, shield_max, secondary_damage_mult, secondary_delay</x:v>
+      </x:c>
       <x:c r="H29" s="14" t="str">
         <x:v>魔修</x:v>
       </x:c>
@@ -5514,13 +5554,13 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="AU29" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.58</x:v>
       </x:c>
       <x:c r="AV29" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AW29" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="AX29" s="14" t="n">
         <x:v>0.5</x:v>
@@ -5529,7 +5569,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AZ29" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="BA29" s="14" t="n">
         <x:v>0</x:v>
@@ -5544,7 +5584,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BE29" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="BF29" s="14" t="n">
         <x:v>0</x:v>
@@ -5563,10 +5603,18 @@
       <x:c r="C30" s="14" t="str">
         <x:v>连接多名敌人并压制，持续造成伤害。敌人死亡后化为幽魂冲击其他敌人，接触后爆炸并消失。</x:v>
       </x:c>
-      <x:c r="D30" s="14" t="str"/>
-      <x:c r="E30" s="14" t="str"/>
-      <x:c r="F30" s="14" t="str"/>
-      <x:c r="G30" s="14" t="str"/>
+      <x:c r="D30" s="14" t="str">
+        <x:v>招魂幡连接多名敌人，魂线按tick_interval固定脉冲压制和伤害；被本轮连接/伤害过的敌人死亡生成幽魂冲击。</x:v>
+      </x:c>
+      <x:c r="E30" s="14" t="str">
+        <x:v>连接数提升到count，幽魂体积和爆炸范围按secondary_radius放大；累计delayed_strike_count只幽魂释放魂波。</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="str">
+        <x:v>5费多目标持续压制和拘魂清场，幽魂数量、寿命和搜索范围均有限制。</x:v>
+      </x:c>
+      <x:c r="G30" s="14" t="str">
+        <x:v>max_targets, count, summon_base_count, summon_respawn_time, summon_combat_radius, secondary_damage_mult, secondary_radius, delayed_strike_count, poison_explosion_damage_mult</x:v>
+      </x:c>
       <x:c r="H30" s="14" t="str">
         <x:v>魔修</x:v>
       </x:c>
@@ -5602,7 +5650,7 @@
         <x:v>10.04</x:v>
       </x:c>
       <x:c r="T30" s="14" t="n">
-        <x:v>230</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="U30" s="14" t="n">
         <x:v>32</x:v>
@@ -5614,7 +5662,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="X30" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Y30" s="14" t="n">
         <x:v>4</x:v>
@@ -5650,7 +5698,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AJ30" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AK30" s="14" t="n">
         <x:v>0</x:v>
@@ -5683,13 +5731,13 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="AU30" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1.55</x:v>
       </x:c>
       <x:c r="AV30" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1.35</x:v>
       </x:c>
       <x:c r="AW30" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="AX30" s="14" t="n">
         <x:v>0.5</x:v>
@@ -9184,26 +9232,28 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D86" s="14" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="E86" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F86" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E86" s="14" t="str"/>
+      <x:c r="F86" s="14" t="str"/>
       <x:c r="G86" s="14" t="n">
-        <x:v>23</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H86" s="14" t="n">
-        <x:v>2.29</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I86" s="14" t="n">
-        <x:v>10.04</x:v>
-      </x:c>
-      <x:c r="J86" s="14" t="str"/>
-      <x:c r="K86" s="14" t="str"/>
-      <x:c r="L86" s="15" t="str"/>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J86" s="14" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K86" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L86" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
       <x:c r="A87" s="13" t="str">
@@ -9216,26 +9266,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D87" s="14" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="E87" s="14" t="n">
-        <x:v>1.55</x:v>
-      </x:c>
-      <x:c r="F87" s="14" t="n">
-        <x:v>0.85</x:v>
-      </x:c>
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E87" s="14" t="str"/>
+      <x:c r="F87" s="14" t="str"/>
       <x:c r="G87" s="14" t="n">
-        <x:v>35.65</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H87" s="14" t="n">
-        <x:v>1.946</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I87" s="14" t="n">
-        <x:v>18.31</x:v>
-      </x:c>
-      <x:c r="J87" s="14" t="str"/>
-      <x:c r="K87" s="14" t="str"/>
-      <x:c r="L87" s="15" t="str"/>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J87" s="14" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K87" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L87" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
       <x:c r="A88" s="13" t="str">
@@ -9248,26 +9300,28 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D88" s="14" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="E88" s="14" t="n">
-        <x:v>2.25</x:v>
-      </x:c>
-      <x:c r="F88" s="14" t="n">
-        <x:v>0.7</x:v>
-      </x:c>
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E88" s="14" t="str"/>
+      <x:c r="F88" s="14" t="str"/>
       <x:c r="G88" s="14" t="n">
-        <x:v>51.75</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H88" s="14" t="n">
-        <x:v>1.603</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I88" s="14" t="n">
-        <x:v>32.28</x:v>
-      </x:c>
-      <x:c r="J88" s="14" t="str"/>
-      <x:c r="K88" s="14" t="str"/>
-      <x:c r="L88" s="15" t="str"/>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J88" s="14" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K88" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L88" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="89" ht="15" hidden="0" customHeight="1">
       <x:c r="A89" s="13" t="str">

--- a/docs/GameBalance.xlsx
+++ b/docs/GameBalance.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R1cdfe74267c440b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法宝总表" sheetId="2" r:id="Rf1ffaf0aff1d4a04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法宝星级预览" sheetId="3" r:id="R783e6b3f963a4b97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命" sheetId="4" r:id="Rc88b96ed18a4442a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奇遇" sheetId="5" r:id="Rb8636c1829c34c50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊阈值" sheetId="6" r:id="R205f75a1f16244b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济与修为" sheetId="7" r:id="R0d02d8ad861a42f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R329299f3b2e14651"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法宝总表" sheetId="2" r:id="Rb709be8a575445dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法宝星级预览" sheetId="3" r:id="R686af5ce4c914e59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命" sheetId="4" r:id="Ra4808ae1490e4e36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奇遇" sheetId="5" r:id="R07b9fed0caad4d66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊阈值" sheetId="6" r:id="R4d80e1bf4f354e49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济与修为" sheetId="7" r:id="R4d1f62df9f20493e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -476,7 +476,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B3" s="5" t="n">
-        <x:v>46200.79495604167</x:v>
+        <x:v>46200.80713267361</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -541,19 +541,19 @@
     <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="15" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="10" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="15" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="15" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="15" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="15" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="10" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="15" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="10" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="10" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="10" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="15" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="15" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="15" hidden="0" customWidth="1"/>
     <x:col min="20" max="20" width="15" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="15" hidden="0" customWidth="1"/>
-    <x:col min="22" max="22" width="15" hidden="0" customWidth="1"/>
-    <x:col min="23" max="23" width="15" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="10" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="10" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="10" hidden="0" customWidth="1"/>
     <x:col min="24" max="24" width="15" hidden="0" customWidth="1"/>
     <x:col min="25" max="25" width="15" hidden="0" customWidth="1"/>
     <x:col min="26" max="26" width="15" hidden="0" customWidth="1"/>
@@ -589,7 +589,11 @@
     <x:col min="56" max="56" width="15" hidden="0" customWidth="1"/>
     <x:col min="57" max="57" width="14.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="58" max="58" width="14.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="59" max="59" width="23.75" hidden="0" customWidth="1"/>
+    <x:col min="59" max="59" width="14.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="60" max="60" width="14.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="61" max="61" width="14.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="62" max="62" width="14.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="63" max="63" width="23.75" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
@@ -606,168 +610,180 @@
         <x:v>攻击表现</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
+        <x:v>AI行为</x:v>
+      </x:c>
+      <x:c r="F1" s="11" t="str">
+        <x:v>是否有仇恨值</x:v>
+      </x:c>
+      <x:c r="G1" s="11" t="str">
+        <x:v>是否可受伤</x:v>
+      </x:c>
+      <x:c r="H1" s="11" t="str">
+        <x:v>死亡与重生规则</x:v>
+      </x:c>
+      <x:c r="I1" s="11" t="str">
         <x:v>三星机制</x:v>
       </x:c>
-      <x:c r="F1" s="11" t="str">
+      <x:c r="J1" s="11" t="str">
         <x:v>战斗定位</x:v>
       </x:c>
-      <x:c r="G1" s="11" t="str">
+      <x:c r="K1" s="11" t="str">
         <x:v>新增关键字段</x:v>
       </x:c>
-      <x:c r="H1" s="11" t="str">
+      <x:c r="L1" s="11" t="str">
         <x:v>流派</x:v>
       </x:c>
-      <x:c r="I1" s="11" t="str">
+      <x:c r="M1" s="11" t="str">
         <x:v>属性</x:v>
       </x:c>
-      <x:c r="J1" s="11" t="str">
+      <x:c r="N1" s="11" t="str">
         <x:v>品阶</x:v>
       </x:c>
-      <x:c r="K1" s="11" t="str">
+      <x:c r="O1" s="11" t="str">
         <x:v>价格</x:v>
       </x:c>
-      <x:c r="L1" s="11" t="str">
+      <x:c r="P1" s="11" t="str">
         <x:v>修为要求</x:v>
       </x:c>
-      <x:c r="M1" s="11" t="str">
+      <x:c r="Q1" s="11" t="str">
         <x:v>商店权重</x:v>
       </x:c>
-      <x:c r="N1" s="11" t="str">
+      <x:c r="R1" s="11" t="str">
         <x:v>模板</x:v>
       </x:c>
-      <x:c r="O1" s="11" t="str">
+      <x:c r="S1" s="11" t="str">
         <x:v>形状</x:v>
       </x:c>
-      <x:c r="P1" s="11" t="str">
+      <x:c r="T1" s="11" t="str">
         <x:v>效果类型</x:v>
       </x:c>
-      <x:c r="Q1" s="11" t="str">
+      <x:c r="U1" s="11" t="str">
         <x:v>伤害</x:v>
       </x:c>
-      <x:c r="R1" s="11" t="str">
+      <x:c r="V1" s="11" t="str">
         <x:v>冷却秒</x:v>
       </x:c>
-      <x:c r="S1" s="11" t="str">
+      <x:c r="W1" s="11" t="str">
         <x:v>DPS估算</x:v>
       </x:c>
-      <x:c r="T1" s="11" t="str">
+      <x:c r="X1" s="11" t="str">
         <x:v>范围</x:v>
       </x:c>
-      <x:c r="U1" s="11" t="str">
+      <x:c r="Y1" s="11" t="str">
         <x:v>半径</x:v>
       </x:c>
-      <x:c r="V1" s="11" t="str">
+      <x:c r="Z1" s="11" t="str">
         <x:v>宽度</x:v>
       </x:c>
-      <x:c r="W1" s="11" t="str">
+      <x:c r="AA1" s="11" t="str">
         <x:v>长度</x:v>
       </x:c>
-      <x:c r="X1" s="11" t="str">
+      <x:c r="AB1" s="11" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="Y1" s="11" t="str">
+      <x:c r="AC1" s="11" t="str">
         <x:v>最大目标</x:v>
       </x:c>
-      <x:c r="Z1" s="11" t="str">
+      <x:c r="AD1" s="11" t="str">
         <x:v>穿透</x:v>
       </x:c>
-      <x:c r="AA1" s="11" t="str">
+      <x:c r="AE1" s="11" t="str">
         <x:v>弹射</x:v>
       </x:c>
-      <x:c r="AB1" s="11" t="str">
+      <x:c r="AF1" s="11" t="str">
         <x:v>击退</x:v>
       </x:c>
-      <x:c r="AC1" s="11" t="str">
+      <x:c r="AG1" s="11" t="str">
         <x:v>减速</x:v>
       </x:c>
-      <x:c r="AD1" s="11" t="str">
+      <x:c r="AH1" s="11" t="str">
         <x:v>治疗</x:v>
       </x:c>
-      <x:c r="AE1" s="11" t="str">
+      <x:c r="AI1" s="11" t="str">
         <x:v>护盾</x:v>
       </x:c>
-      <x:c r="AF1" s="11" t="str">
+      <x:c r="AJ1" s="11" t="str">
         <x:v>中毒DPS</x:v>
       </x:c>
-      <x:c r="AG1" s="11" t="str">
+      <x:c r="AK1" s="11" t="str">
         <x:v>中毒持续</x:v>
       </x:c>
-      <x:c r="AH1" s="11" t="str">
+      <x:c r="AL1" s="11" t="str">
         <x:v>生命消耗百分比</x:v>
       </x:c>
-      <x:c r="AI1" s="11" t="str">
+      <x:c r="AM1" s="11" t="str">
         <x:v>生命消耗固定</x:v>
       </x:c>
-      <x:c r="AJ1" s="11" t="str">
+      <x:c r="AN1" s="11" t="str">
         <x:v>召唤数量</x:v>
       </x:c>
-      <x:c r="AK1" s="11" t="str">
+      <x:c r="AO1" s="11" t="str">
         <x:v>召唤生命</x:v>
       </x:c>
-      <x:c r="AL1" s="11" t="str">
+      <x:c r="AP1" s="11" t="str">
         <x:v>召唤攻击</x:v>
       </x:c>
-      <x:c r="AM1" s="11" t="str">
+      <x:c r="AQ1" s="11" t="str">
         <x:v>召唤攻速</x:v>
       </x:c>
-      <x:c r="AN1" s="11" t="str">
+      <x:c r="AR1" s="11" t="str">
         <x:v>2星伤害倍率</x:v>
       </x:c>
-      <x:c r="AO1" s="11" t="str">
+      <x:c r="AS1" s="11" t="str">
         <x:v>2星冷却倍率</x:v>
       </x:c>
-      <x:c r="AP1" s="11" t="str">
+      <x:c r="AT1" s="11" t="str">
         <x:v>3星伤害倍率</x:v>
       </x:c>
-      <x:c r="AQ1" s="11" t="str">
+      <x:c r="AU1" s="11" t="str">
         <x:v>3星冷却倍率</x:v>
       </x:c>
-      <x:c r="AR1" s="11" t="str">
+      <x:c r="AV1" s="11" t="str">
         <x:v>windup_time</x:v>
       </x:c>
-      <x:c r="AS1" s="11" t="str">
+      <x:c r="AW1" s="11" t="str">
         <x:v>trail_length</x:v>
       </x:c>
-      <x:c r="AT1" s="11" t="str">
+      <x:c r="AX1" s="11" t="str">
         <x:v>hit_flash_duration</x:v>
       </x:c>
-      <x:c r="AU1" s="11" t="str">
+      <x:c r="AY1" s="11" t="str">
         <x:v>secondary_damage_mult</x:v>
       </x:c>
-      <x:c r="AV1" s="11" t="str">
+      <x:c r="AZ1" s="11" t="str">
         <x:v>secondary_radius</x:v>
       </x:c>
-      <x:c r="AW1" s="11" t="str">
+      <x:c r="BA1" s="11" t="str">
         <x:v>secondary_delay</x:v>
       </x:c>
-      <x:c r="AX1" s="11" t="str">
+      <x:c r="BB1" s="11" t="str">
         <x:v>side_projectile_damage_mult</x:v>
       </x:c>
-      <x:c r="AY1" s="11" t="str">
+      <x:c r="BC1" s="11" t="str">
         <x:v>return_speed</x:v>
       </x:c>
-      <x:c r="AZ1" s="11" t="str">
+      <x:c r="BD1" s="11" t="str">
         <x:v>fan_angle</x:v>
       </x:c>
-      <x:c r="BA1" s="11" t="str">
+      <x:c r="BE1" s="11" t="str">
         <x:v>converge_speed</x:v>
       </x:c>
-      <x:c r="BB1" s="11" t="str">
+      <x:c r="BF1" s="11" t="str">
         <x:v>self_rotation_speed</x:v>
       </x:c>
-      <x:c r="BC1" s="11" t="str">
+      <x:c r="BG1" s="11" t="str">
         <x:v>reveal_time</x:v>
       </x:c>
-      <x:c r="BD1" s="11" t="str">
+      <x:c r="BH1" s="11" t="str">
         <x:v>pause_time</x:v>
       </x:c>
-      <x:c r="BE1" s="11" t="str">
+      <x:c r="BI1" s="11" t="str">
         <x:v>sweep_rotation_speed</x:v>
       </x:c>
-      <x:c r="BF1" s="11" t="str">
+      <x:c r="BJ1" s="11" t="str">
         <x:v>screen_shake_strength</x:v>
       </x:c>
-      <x:c r="BG1" s="12" t="str">
+      <x:c r="BK1" s="12" t="str">
         <x:v>来源</x:v>
       </x:c>
     </x:row>
@@ -784,79 +800,71 @@
       <x:c r="D2" s="14" t="str">
         <x:v>血流压缩成宽大弯月血刃，蓄力后直线飞出，沿途穿透并留下残月血色轨迹。</x:v>
       </x:c>
-      <x:c r="E2" s="14" t="str">
+      <x:c r="E2" s="14" t="str"/>
+      <x:c r="F2" s="14" t="str"/>
+      <x:c r="G2" s="14" t="str"/>
+      <x:c r="H2" s="14" t="str"/>
+      <x:c r="I2" s="14" t="str">
         <x:v>到达最大距离后按pause_time停顿，再以return_speed返回；去程和回程分别维护命中记录。</x:v>
       </x:c>
-      <x:c r="F2" s="14" t="str">
+      <x:c r="J2" s="14" t="str">
         <x:v>2费宽直线清线，消耗生命，击杀回血。</x:v>
       </x:c>
-      <x:c r="G2" s="14" t="str">
+      <x:c r="K2" s="14" t="str">
         <x:v>life_cost_flat, life_cost_min_hp_ratio, kill_heal_amount, windup_time, return_speed, pause_time, secondary_damage_mult</x:v>
       </x:c>
-      <x:c r="H2" s="14" t="str">
+      <x:c r="L2" s="14" t="str">
         <x:v>魔修</x:v>
       </x:c>
-      <x:c r="I2" s="14" t="str">
+      <x:c r="M2" s="14" t="str">
         <x:v>雷</x:v>
       </x:c>
-      <x:c r="J2" s="14" t="str">
+      <x:c r="N2" s="14" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="K2" s="14" t="n">
+      <x:c r="O2" s="14" t="n">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="L2" s="14" t="str"/>
-      <x:c r="M2" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N2" s="14" t="str">
-        <x:v>projectile</x:v>
-      </x:c>
-      <x:c r="O2" s="14" t="str">
-        <x:v>projectile</x:v>
       </x:c>
       <x:c r="P2" s="14" t="str"/>
       <x:c r="Q2" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R2" s="14" t="str">
+        <x:v>projectile</x:v>
+      </x:c>
+      <x:c r="S2" s="14" t="str">
+        <x:v>projectile</x:v>
+      </x:c>
+      <x:c r="T2" s="14" t="str"/>
+      <x:c r="U2" s="14" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="R2" s="14" t="n">
+      <x:c r="V2" s="14" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="S2" s="14" t="n">
+      <x:c r="W2" s="14" t="n">
         <x:v>32.29</x:v>
       </x:c>
-      <x:c r="T2" s="14" t="n">
+      <x:c r="X2" s="14" t="n">
         <x:v>520</x:v>
       </x:c>
-      <x:c r="U2" s="14" t="n">
+      <x:c r="Y2" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="V2" s="14" t="n">
+      <x:c r="Z2" s="14" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="W2" s="14" t="n">
+      <x:c r="AA2" s="14" t="n">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="X2" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y2" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z2" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA2" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB2" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC2" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AD2" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AE2" s="14" t="n">
         <x:v>0</x:v>
@@ -871,78 +879,90 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AI2" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AJ2" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK2" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL2" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AM2" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AJ2" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AK2" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AL2" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AM2" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AN2" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO2" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP2" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ2" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR2" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO2" s="14" t="n">
+      <x:c r="AS2" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP2" s="14" t="n">
+      <x:c r="AT2" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ2" s="14" t="n">
+      <x:c r="AU2" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR2" s="14" t="n">
+      <x:c r="AV2" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AS2" s="14" t="n">
+      <x:c r="AW2" s="14" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="AT2" s="14" t="n">
+      <x:c r="AX2" s="14" t="n">
         <x:v>0.18</x:v>
       </x:c>
-      <x:c r="AU2" s="14" t="n">
+      <x:c r="AY2" s="14" t="n">
         <x:v>0.62</x:v>
       </x:c>
-      <x:c r="AV2" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW2" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX2" s="14" t="n">
+      <x:c r="AZ2" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA2" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BB2" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY2" s="14" t="n">
+      <x:c r="BC2" s="14" t="n">
         <x:v>520</x:v>
       </x:c>
-      <x:c r="AZ2" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA2" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB2" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BC2" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD2" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE2" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BF2" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BG2" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH2" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="BE2" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BF2" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BG2" s="15" t="str">
+      <x:c r="BI2" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ2" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK2" s="15" t="str">
         <x:v>data/artifacts/blood_slash.tres</x:v>
       </x:c>
     </x:row>
@@ -959,86 +979,78 @@
       <x:c r="D3" s="14" t="str">
         <x:v>抽出血色流光凝成短血剑，近距离厚重血色剑光挥砍，命中留下短血痕，结束后崩成血雾。</x:v>
       </x:c>
-      <x:c r="E3" s="14" t="str">
+      <x:c r="E3" s="14" t="str"/>
+      <x:c r="F3" s="14" t="str"/>
+      <x:c r="G3" s="14" t="str"/>
+      <x:c r="H3" s="14" t="str"/>
+      <x:c r="I3" s="14" t="str">
         <x:v>命中的敌人留下血痕，按secondary_delay延迟爆裂，按secondary_damage_mult造成小范围低伤。</x:v>
       </x:c>
-      <x:c r="F3" s="14" t="str">
+      <x:c r="J3" s="14" t="str">
         <x:v>1费近战高伤害，消耗生命换输出，击杀按kill_heal_amount回血。</x:v>
       </x:c>
-      <x:c r="G3" s="14" t="str">
+      <x:c r="K3" s="14" t="str">
         <x:v>life_cost_flat, life_cost_min_hp_ratio, kill_heal_amount, windup_time, secondary_damage_mult, secondary_radius, secondary_delay</x:v>
       </x:c>
-      <x:c r="H3" s="14" t="str">
+      <x:c r="L3" s="14" t="str">
         <x:v>魔修</x:v>
       </x:c>
-      <x:c r="I3" s="14" t="str">
+      <x:c r="M3" s="14" t="str">
         <x:v>火</x:v>
       </x:c>
-      <x:c r="J3" s="14" t="str">
+      <x:c r="N3" s="14" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="K3" s="14" t="n">
+      <x:c r="O3" s="14" t="n">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="L3" s="14" t="str"/>
-      <x:c r="M3" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N3" s="14" t="str">
-        <x:v>melee</x:v>
-      </x:c>
-      <x:c r="O3" s="14" t="str">
-        <x:v>slash</x:v>
       </x:c>
       <x:c r="P3" s="14" t="str"/>
       <x:c r="Q3" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R3" s="14" t="str">
+        <x:v>melee</x:v>
+      </x:c>
+      <x:c r="S3" s="14" t="str">
+        <x:v>slash</x:v>
+      </x:c>
+      <x:c r="T3" s="14" t="str"/>
+      <x:c r="U3" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="R3" s="14" t="n">
+      <x:c r="V3" s="14" t="n">
         <x:v>0.86</x:v>
       </x:c>
-      <x:c r="S3" s="14" t="n">
+      <x:c r="W3" s="14" t="n">
         <x:v>34.88</x:v>
       </x:c>
-      <x:c r="T3" s="14" t="n">
+      <x:c r="X3" s="14" t="n">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="U3" s="14" t="n">
+      <x:c r="Y3" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="V3" s="14" t="n">
+      <x:c r="Z3" s="14" t="n">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="W3" s="14" t="n">
+      <x:c r="AA3" s="14" t="n">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="X3" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y3" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z3" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA3" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB3" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC3" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD3" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE3" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF3" s="14" t="n">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="AC3" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AD3" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AE3" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF3" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AG3" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1046,65 +1058,65 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AI3" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AJ3" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK3" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL3" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AM3" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AJ3" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AK3" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AL3" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AM3" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AN3" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO3" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP3" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ3" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR3" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO3" s="14" t="n">
+      <x:c r="AS3" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP3" s="14" t="n">
+      <x:c r="AT3" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ3" s="14" t="n">
+      <x:c r="AU3" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR3" s="14" t="n">
+      <x:c r="AV3" s="14" t="n">
         <x:v>0.08</x:v>
       </x:c>
-      <x:c r="AS3" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT3" s="14" t="n">
+      <x:c r="AW3" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX3" s="14" t="n">
         <x:v>0.22</x:v>
       </x:c>
-      <x:c r="AU3" s="14" t="n">
+      <x:c r="AY3" s="14" t="n">
         <x:v>0.38</x:v>
       </x:c>
-      <x:c r="AV3" s="14" t="n">
+      <x:c r="AZ3" s="14" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="AW3" s="14" t="n">
+      <x:c r="BA3" s="14" t="n">
         <x:v>0.28</x:v>
       </x:c>
-      <x:c r="AX3" s="14" t="n">
+      <x:c r="BB3" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY3" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ3" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA3" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB3" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC3" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1117,7 +1129,19 @@
       <x:c r="BF3" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG3" s="15" t="str">
+      <x:c r="BG3" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH3" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI3" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ3" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK3" s="15" t="str">
         <x:v>data/artifacts/blood_sword.tres</x:v>
       </x:c>
     </x:row>
@@ -1135,85 +1159,77 @@
       <x:c r="E4" s="14" t="str"/>
       <x:c r="F4" s="14" t="str"/>
       <x:c r="G4" s="14" t="str"/>
-      <x:c r="H4" s="14" t="str">
+      <x:c r="H4" s="14" t="str"/>
+      <x:c r="I4" s="14" t="str"/>
+      <x:c r="J4" s="14" t="str"/>
+      <x:c r="K4" s="14" t="str"/>
+      <x:c r="L4" s="14" t="str">
         <x:v>体修</x:v>
       </x:c>
-      <x:c r="I4" s="14" t="str">
+      <x:c r="M4" s="14" t="str">
         <x:v>水</x:v>
       </x:c>
-      <x:c r="J4" s="14" t="str">
+      <x:c r="N4" s="14" t="str">
         <x:v>灵器</x:v>
       </x:c>
-      <x:c r="K4" s="14" t="n">
+      <x:c r="O4" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="L4" s="14" t="str"/>
-      <x:c r="M4" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N4" s="14" t="str">
+      <x:c r="P4" s="14" t="str"/>
+      <x:c r="Q4" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R4" s="14" t="str">
         <x:v>formation</x:v>
       </x:c>
-      <x:c r="O4" s="14" t="str">
+      <x:c r="S4" s="14" t="str">
         <x:v>aura</x:v>
       </x:c>
-      <x:c r="P4" s="14" t="str">
+      <x:c r="T4" s="14" t="str">
         <x:v>damage</x:v>
       </x:c>
-      <x:c r="Q4" s="14" t="n">
+      <x:c r="U4" s="14" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="R4" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S4" s="14" t="n">
+      <x:c r="V4" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W4" s="14" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="T4" s="14" t="n">
+      <x:c r="X4" s="14" t="n">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="U4" s="14" t="n">
+      <x:c r="Y4" s="14" t="n">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="V4" s="14" t="n">
+      <x:c r="Z4" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="W4" s="14" t="n">
+      <x:c r="AA4" s="14" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="X4" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y4" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z4" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA4" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB4" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC4" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AD4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH4" s="14" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AE4" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF4" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AG4" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AH4" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AI4" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1227,53 +1243,53 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM4" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AN4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ4" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR4" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO4" s="14" t="n">
+      <x:c r="AS4" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP4" s="14" t="n">
+      <x:c r="AT4" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ4" s="14" t="n">
+      <x:c r="AU4" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR4" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS4" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT4" s="14" t="n">
+      <x:c r="AV4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AW4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX4" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU4" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AV4" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW4" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX4" s="14" t="n">
+      <x:c r="AY4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AZ4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BB4" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY4" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ4" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA4" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB4" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC4" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1286,7 +1302,19 @@
       <x:c r="BF4" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG4" s="15" t="str">
+      <x:c r="BG4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK4" s="15" t="str">
         <x:v>data/artifacts/body_barrier.tres</x:v>
       </x:c>
     </x:row>
@@ -1303,89 +1331,81 @@
       <x:c r="D5" s="14" t="str">
         <x:v>毛笔飞向目标区域，三笔写出抽象符印，完整形成后统一爆发。</x:v>
       </x:c>
-      <x:c r="E5" s="14" t="str">
+      <x:c r="E5" s="14" t="str"/>
+      <x:c r="F5" s="14" t="str"/>
+      <x:c r="G5" s="14" t="str"/>
+      <x:c r="H5" s="14" t="str"/>
+      <x:c r="I5" s="14" t="str">
         <x:v>爆发后残留墨阵，按固定脉冲造成低伤并减速。</x:v>
       </x:c>
-      <x:c r="F5" s="14" t="str">
+      <x:c r="J5" s="14" t="str">
         <x:v>3费延迟AOE、区域布置和控场。</x:v>
       </x:c>
-      <x:c r="G5" s="14" t="str">
+      <x:c r="K5" s="14" t="str">
         <x:v>radius, delayed_strike_interval, tick_interval, duration, secondary_damage_mult, slow_percent</x:v>
       </x:c>
-      <x:c r="H5" s="14" t="str">
+      <x:c r="L5" s="14" t="str">
         <x:v>法修</x:v>
       </x:c>
-      <x:c r="I5" s="14" t="str">
+      <x:c r="M5" s="14" t="str">
         <x:v>木</x:v>
       </x:c>
-      <x:c r="J5" s="14" t="str">
+      <x:c r="N5" s="14" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="K5" s="14" t="n">
+      <x:c r="O5" s="14" t="n">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="L5" s="14" t="str"/>
-      <x:c r="M5" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N5" s="14" t="str">
-        <x:v>line_delayed</x:v>
-      </x:c>
-      <x:c r="O5" s="14" t="str">
-        <x:v>line</x:v>
       </x:c>
       <x:c r="P5" s="14" t="str"/>
       <x:c r="Q5" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R5" s="14" t="str">
+        <x:v>line_delayed</x:v>
+      </x:c>
+      <x:c r="S5" s="14" t="str">
+        <x:v>line</x:v>
+      </x:c>
+      <x:c r="T5" s="14" t="str"/>
+      <x:c r="U5" s="14" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="R5" s="14" t="n">
+      <x:c r="V5" s="14" t="n">
         <x:v>1.35</x:v>
       </x:c>
-      <x:c r="S5" s="14" t="n">
+      <x:c r="W5" s="14" t="n">
         <x:v>35.56</x:v>
       </x:c>
-      <x:c r="T5" s="14" t="n">
+      <x:c r="X5" s="14" t="n">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="U5" s="14" t="n">
+      <x:c r="Y5" s="14" t="n">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="V5" s="14" t="n">
+      <x:c r="Z5" s="14" t="n">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="W5" s="14" t="n">
+      <x:c r="AA5" s="14" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="X5" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y5" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z5" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA5" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB5" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG5" s="14" t="n">
         <x:v>0.35</x:v>
       </x:c>
-      <x:c r="AD5" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AE5" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF5" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AG5" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AH5" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1402,53 +1422,53 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM5" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AN5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ5" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR5" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO5" s="14" t="n">
+      <x:c r="AS5" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP5" s="14" t="n">
+      <x:c r="AT5" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ5" s="14" t="n">
+      <x:c r="AU5" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR5" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS5" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT5" s="14" t="n">
+      <x:c r="AV5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AW5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX5" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU5" s="14" t="n">
+      <x:c r="AY5" s="14" t="n">
         <x:v>0.24</x:v>
       </x:c>
-      <x:c r="AV5" s="14" t="n">
+      <x:c r="AZ5" s="14" t="n">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="AW5" s="14" t="n">
+      <x:c r="BA5" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AX5" s="14" t="n">
+      <x:c r="BB5" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY5" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ5" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA5" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB5" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC5" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1461,7 +1481,19 @@
       <x:c r="BF5" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG5" s="15" t="str">
+      <x:c r="BG5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK5" s="15" t="str">
         <x:v>data/artifacts/brush.tres</x:v>
       </x:c>
     </x:row>
@@ -1478,83 +1510,75 @@
       <x:c r="D6" s="14" t="str">
         <x:v>铜钱旋转发射，命中后按目标搜索范围折线弹射并留下短暂金色轨迹。</x:v>
       </x:c>
-      <x:c r="E6" s="14" t="str">
+      <x:c r="E6" s="14" t="str"/>
+      <x:c r="F6" s="14" t="str"/>
+      <x:c r="G6" s="14" t="str"/>
+      <x:c r="H6" s="14" t="str"/>
+      <x:c r="I6" s="14" t="str">
         <x:v>最后一次弹射后分裂为多枚小铜钱，优先攻击不同目标。</x:v>
       </x:c>
-      <x:c r="F6" s="14" t="str">
+      <x:c r="J6" s="14" t="str">
         <x:v>1费高频弹射，连续打击多个目标。</x:v>
       </x:c>
-      <x:c r="G6" s="14" t="str">
+      <x:c r="K6" s="14" t="str">
         <x:v>bounce_count, bounce_range, projectile_speed, count, secondary_damage_mult, secondary_radius</x:v>
       </x:c>
-      <x:c r="H6" s="14" t="str">
+      <x:c r="L6" s="14" t="str">
         <x:v>法修</x:v>
       </x:c>
-      <x:c r="I6" s="14" t="str">
+      <x:c r="M6" s="14" t="str">
         <x:v>金</x:v>
       </x:c>
-      <x:c r="J6" s="14" t="str">
+      <x:c r="N6" s="14" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="K6" s="14" t="n">
+      <x:c r="O6" s="14" t="n">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="L6" s="14" t="str"/>
-      <x:c r="M6" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N6" s="14" t="str">
-        <x:v>projectile</x:v>
-      </x:c>
-      <x:c r="O6" s="14" t="str">
-        <x:v>circle</x:v>
       </x:c>
       <x:c r="P6" s="14" t="str"/>
       <x:c r="Q6" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R6" s="14" t="str">
+        <x:v>projectile</x:v>
+      </x:c>
+      <x:c r="S6" s="14" t="str">
+        <x:v>circle</x:v>
+      </x:c>
+      <x:c r="T6" s="14" t="str"/>
+      <x:c r="U6" s="14" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="R6" s="14" t="n">
+      <x:c r="V6" s="14" t="n">
         <x:v>0.93</x:v>
       </x:c>
-      <x:c r="S6" s="14" t="n">
+      <x:c r="W6" s="14" t="n">
         <x:v>22.58</x:v>
       </x:c>
-      <x:c r="T6" s="14" t="n">
+      <x:c r="X6" s="14" t="n">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="U6" s="14" t="n">
+      <x:c r="Y6" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="V6" s="14" t="n">
+      <x:c r="Z6" s="14" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="W6" s="14" t="n">
+      <x:c r="AA6" s="14" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="X6" s="14" t="n">
+      <x:c r="AB6" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="Y6" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z6" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA6" s="14" t="n">
+      <x:c r="AC6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE6" s="14" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AB6" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AC6" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AD6" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AE6" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AF6" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1577,53 +1601,53 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM6" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AN6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ6" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR6" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO6" s="14" t="n">
+      <x:c r="AS6" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP6" s="14" t="n">
+      <x:c r="AT6" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ6" s="14" t="n">
+      <x:c r="AU6" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR6" s="14" t="n">
+      <x:c r="AV6" s="14" t="n">
         <x:v>0.06</x:v>
       </x:c>
-      <x:c r="AS6" s="14" t="n">
+      <x:c r="AW6" s="14" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="AT6" s="14" t="n">
+      <x:c r="AX6" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU6" s="14" t="n">
+      <x:c r="AY6" s="14" t="n">
         <x:v>0.45</x:v>
       </x:c>
-      <x:c r="AV6" s="14" t="n">
+      <x:c r="AZ6" s="14" t="n">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="AW6" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX6" s="14" t="n">
+      <x:c r="BA6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BB6" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY6" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ6" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA6" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB6" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC6" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1636,7 +1660,19 @@
       <x:c r="BF6" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG6" s="15" t="str">
+      <x:c r="BG6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK6" s="15" t="str">
         <x:v>data/artifacts/copper_coin.tres</x:v>
       </x:c>
     </x:row>
@@ -1650,68 +1686,76 @@
       <x:c r="C7" s="14" t="str">
         <x:v>召唤后排远程傀儡，和敌人保持距离并持续发射灵能箭。死亡后会在短时间后重生。</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="str"/>
-      <x:c r="E7" s="14" t="str"/>
-      <x:c r="F7" s="14" t="str"/>
-      <x:c r="G7" s="14" t="str"/>
+      <x:c r="D7" s="14" t="str">
+        <x:v>侧后方召唤阵显形，保持secondary_radius理想距离，蓄能后发射带拖尾灵能箭；多单位有短蓄能窗口形成齐射感。</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="str">
+        <x:v>保持secondary_radius理想距离；过近后退，过远靠近；超过活动范围返回。</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="str">
+        <x:v>有仇恨，可被敌人主动选择。</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="str">
+        <x:v>可受伤。</x:v>
+      </x:c>
       <x:c r="H7" s="14" t="str">
+        <x:v>死亡后按summon_respawn_time在玩家附近重生，清理旧目标和状态。</x:v>
+      </x:c>
+      <x:c r="I7" s="14" t="str">
+        <x:v>每delayed_strike_count次攻击蓄力齐射三支扇形箭，侧箭按side_projectile_damage_mult造成伤害。</x:v>
+      </x:c>
+      <x:c r="J7" s="14" t="str">
+        <x:v>1费基础后排持续输出，可被攻击，死亡后重生。</x:v>
+      </x:c>
+      <x:c r="K7" s="14" t="str">
+        <x:v>summon_attack_speed, projectile_speed, secondary_radius, delayed_strike_delay, delayed_strike_count, fan_angle, side_projectile_damage_mult</x:v>
+      </x:c>
+      <x:c r="L7" s="14" t="str">
         <x:v>召唤</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="str">
+      <x:c r="M7" s="14" t="str">
         <x:v>雷</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="str">
+      <x:c r="N7" s="14" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="n">
+      <x:c r="O7" s="14" t="n">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="L7" s="14" t="str"/>
-      <x:c r="M7" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N7" s="14" t="str">
-        <x:v>summon</x:v>
-      </x:c>
-      <x:c r="O7" s="14" t="str">
-        <x:v>projectile</x:v>
       </x:c>
       <x:c r="P7" s="14" t="str"/>
       <x:c r="Q7" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R7" s="14" t="str">
+        <x:v>summon</x:v>
+      </x:c>
+      <x:c r="S7" s="14" t="str">
+        <x:v>projectile</x:v>
+      </x:c>
+      <x:c r="T7" s="14" t="str"/>
+      <x:c r="U7" s="14" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="R7" s="14" t="n">
+      <x:c r="V7" s="14" t="n">
         <x:v>0.48</x:v>
       </x:c>
-      <x:c r="S7" s="14" t="n">
+      <x:c r="W7" s="14" t="n">
         <x:v>29.17</x:v>
       </x:c>
-      <x:c r="T7" s="14" t="n">
+      <x:c r="X7" s="14" t="n">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="U7" s="14" t="n">
+      <x:c r="Y7" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="V7" s="14" t="n">
+      <x:c r="Z7" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="W7" s="14" t="n">
+      <x:c r="AA7" s="14" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="X7" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y7" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z7" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA7" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB7" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC7" s="14" t="n">
         <x:v>0</x:v>
@@ -1735,67 +1779,67 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AJ7" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AK7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AM7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AN7" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO7" s="14" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="AL7" s="14" t="n">
+      <x:c r="AP7" s="14" t="n">
         <x:v>12.5</x:v>
       </x:c>
-      <x:c r="AM7" s="14" t="n">
+      <x:c r="AQ7" s="14" t="n">
         <x:v>2.1</x:v>
       </x:c>
-      <x:c r="AN7" s="14" t="n">
+      <x:c r="AR7" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO7" s="14" t="n">
+      <x:c r="AS7" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP7" s="14" t="n">
+      <x:c r="AT7" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ7" s="14" t="n">
+      <x:c r="AU7" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR7" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS7" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT7" s="14" t="n">
+      <x:c r="AV7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AW7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX7" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU7" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AV7" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW7" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX7" s="14" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
       <x:c r="AY7" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AZ7" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="BA7" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="BB7" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.55</x:v>
       </x:c>
       <x:c r="BC7" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="BD7" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="BE7" s="14" t="n">
         <x:v>0</x:v>
@@ -1803,7 +1847,19 @@
       <x:c r="BF7" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG7" s="15" t="str">
+      <x:c r="BG7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK7" s="15" t="str">
         <x:v>data/artifacts/crossbow_puppet.tres</x:v>
       </x:c>
     </x:row>
@@ -1820,76 +1876,68 @@
       <x:c r="D8" s="14" t="str">
         <x:v>极短距离锁定最近敌人，细闪光线+匕首残影穿刺，目标身后小AOE。</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="str">
+      <x:c r="E8" s="14" t="str"/>
+      <x:c r="F8" s="14" t="str"/>
+      <x:c r="G8" s="14" t="str"/>
+      <x:c r="H8" s="14" t="str"/>
+      <x:c r="I8" s="14" t="str">
         <x:v>从相反方向追加第二次低伤害刺击，不重复大范围AOE。</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="str">
+      <x:c r="J8" s="14" t="str">
         <x:v>1费快速近身刺杀，近乎单体，背后极小范围溅射。</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="str">
+      <x:c r="K8" s="14" t="str">
         <x:v>range, secondary_radius, secondary_damage_mult, secondary_delay</x:v>
       </x:c>
-      <x:c r="H8" s="14" t="str">
+      <x:c r="L8" s="14" t="str">
         <x:v>剑修</x:v>
       </x:c>
-      <x:c r="I8" s="14" t="str">
+      <x:c r="M8" s="14" t="str">
         <x:v>毒</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="str">
+      <x:c r="N8" s="14" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="O8" s="14" t="n">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="L8" s="14" t="str"/>
-      <x:c r="M8" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N8" s="14" t="str">
-        <x:v>melee</x:v>
-      </x:c>
-      <x:c r="O8" s="14" t="str">
-        <x:v>stab</x:v>
       </x:c>
       <x:c r="P8" s="14" t="str"/>
       <x:c r="Q8" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R8" s="14" t="str">
+        <x:v>melee</x:v>
+      </x:c>
+      <x:c r="S8" s="14" t="str">
+        <x:v>stab</x:v>
+      </x:c>
+      <x:c r="T8" s="14" t="str"/>
+      <x:c r="U8" s="14" t="n">
         <x:v>7.5</x:v>
       </x:c>
-      <x:c r="R8" s="14" t="n">
+      <x:c r="V8" s="14" t="n">
         <x:v>0.21</x:v>
       </x:c>
-      <x:c r="S8" s="14" t="n">
+      <x:c r="W8" s="14" t="n">
         <x:v>35.71</x:v>
       </x:c>
-      <x:c r="T8" s="14" t="n">
+      <x:c r="X8" s="14" t="n">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="U8" s="14" t="n">
+      <x:c r="Y8" s="14" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="V8" s="14" t="n">
+      <x:c r="Z8" s="14" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="W8" s="14" t="n">
+      <x:c r="AA8" s="14" t="n">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="X8" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y8" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z8" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA8" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB8" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC8" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD8" s="14" t="n">
         <x:v>0</x:v>
@@ -1919,53 +1967,53 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM8" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AN8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ8" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR8" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO8" s="14" t="n">
+      <x:c r="AS8" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP8" s="14" t="n">
+      <x:c r="AT8" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ8" s="14" t="n">
+      <x:c r="AU8" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR8" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS8" s="14" t="n">
+      <x:c r="AV8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AW8" s="14" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="AT8" s="14" t="n">
+      <x:c r="AX8" s="14" t="n">
         <x:v>0.08</x:v>
       </x:c>
-      <x:c r="AU8" s="14" t="n">
+      <x:c r="AY8" s="14" t="n">
         <x:v>0.35</x:v>
       </x:c>
-      <x:c r="AV8" s="14" t="n">
+      <x:c r="AZ8" s="14" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="AW8" s="14" t="n">
+      <x:c r="BA8" s="14" t="n">
         <x:v>0.045</x:v>
       </x:c>
-      <x:c r="AX8" s="14" t="n">
+      <x:c r="BB8" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY8" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ8" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA8" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB8" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC8" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1978,7 +2026,19 @@
       <x:c r="BF8" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG8" s="15" t="str">
+      <x:c r="BG8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK8" s="15" t="str">
         <x:v>data/artifacts/dagger.tres</x:v>
       </x:c>
     </x:row>
@@ -1995,74 +2055,66 @@
       <x:c r="D9" s="14" t="str">
         <x:v>稳定选择敌人密集区域，预警圈后主雷落下，并连锁附近目标。</x:v>
       </x:c>
-      <x:c r="E9" s="14" t="str">
+      <x:c r="E9" s="14" t="str"/>
+      <x:c r="F9" s="14" t="str"/>
+      <x:c r="G9" s="14" t="str"/>
+      <x:c r="H9" s="14" t="str"/>
+      <x:c r="I9" s="14" t="str">
         <x:v>主雷后生成雷劫区域，按间隔落下多道副雷。</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="str">
+      <x:c r="J9" s="14" t="str">
         <x:v>5费远程天降爆发，大范围高伤和连锁清场。</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="str">
+      <x:c r="K9" s="14" t="str">
         <x:v>windup_time, radius, count, bounce_range, delayed_strike_count, delayed_strike_interval, secondary_radius</x:v>
       </x:c>
-      <x:c r="H9" s="14" t="str">
+      <x:c r="L9" s="14" t="str">
         <x:v>法修</x:v>
       </x:c>
-      <x:c r="I9" s="14" t="str">
+      <x:c r="M9" s="14" t="str">
         <x:v>雷</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="str">
+      <x:c r="N9" s="14" t="str">
         <x:v>仙宝</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="O9" s="14" t="n">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="L9" s="14" t="str"/>
-      <x:c r="M9" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N9" s="14" t="str">
-        <x:v>target_aoe</x:v>
-      </x:c>
-      <x:c r="O9" s="14" t="str">
-        <x:v>circle</x:v>
       </x:c>
       <x:c r="P9" s="14" t="str"/>
       <x:c r="Q9" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R9" s="14" t="str">
+        <x:v>target_aoe</x:v>
+      </x:c>
+      <x:c r="S9" s="14" t="str">
+        <x:v>circle</x:v>
+      </x:c>
+      <x:c r="T9" s="14" t="str"/>
+      <x:c r="U9" s="14" t="n">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="R9" s="14" t="n">
+      <x:c r="V9" s="14" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="S9" s="14" t="n">
+      <x:c r="W9" s="14" t="n">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="T9" s="14" t="n">
+      <x:c r="X9" s="14" t="n">
         <x:v>760</x:v>
       </x:c>
-      <x:c r="U9" s="14" t="n">
+      <x:c r="Y9" s="14" t="n">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="V9" s="14" t="n">
+      <x:c r="Z9" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="W9" s="14" t="n">
+      <x:c r="AA9" s="14" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="X9" s="14" t="n">
+      <x:c r="AB9" s="14" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="Y9" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z9" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA9" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB9" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AC9" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2070,7 +2122,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AE9" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AF9" s="14" t="n">
         <x:v>0</x:v>
@@ -2094,53 +2146,53 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM9" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AN9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ9" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR9" s="14" t="n">
         <x:v>1.65</x:v>
       </x:c>
-      <x:c r="AO9" s="14" t="n">
+      <x:c r="AS9" s="14" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="AP9" s="14" t="n">
+      <x:c r="AT9" s="14" t="n">
         <x:v>2.35</x:v>
       </x:c>
-      <x:c r="AQ9" s="14" t="n">
+      <x:c r="AU9" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AR9" s="14" t="n">
+      <x:c r="AV9" s="14" t="n">
         <x:v>0.22</x:v>
       </x:c>
-      <x:c r="AS9" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT9" s="14" t="n">
+      <x:c r="AW9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX9" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU9" s="14" t="n">
+      <x:c r="AY9" s="14" t="n">
         <x:v>0.32</x:v>
       </x:c>
-      <x:c r="AV9" s="14" t="n">
+      <x:c r="AZ9" s="14" t="n">
         <x:v>1.18</x:v>
       </x:c>
-      <x:c r="AW9" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX9" s="14" t="n">
+      <x:c r="BA9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BB9" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY9" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ9" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA9" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB9" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC9" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2153,7 +2205,19 @@
       <x:c r="BF9" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG9" s="15" t="str">
+      <x:c r="BG9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK9" s="15" t="str">
         <x:v>data/artifacts/divine_thunder.tres</x:v>
       </x:c>
     </x:row>
@@ -2170,73 +2234,65 @@
       <x:c r="D10" s="14" t="str">
         <x:v>火葫芦锁定密集方向，短前摇后按固定脉冲喷出多层锥形火浪。</x:v>
       </x:c>
-      <x:c r="E10" s="14" t="str">
+      <x:c r="E10" s="14" t="str"/>
+      <x:c r="F10" s="14" t="str"/>
+      <x:c r="G10" s="14" t="str"/>
+      <x:c r="H10" s="14" t="str"/>
+      <x:c r="I10" s="14" t="str">
         <x:v>喷火结束后吐出火种，爆炸并留下固定脉冲燃烧区域。</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="str">
+      <x:c r="J10" s="14" t="str">
         <x:v>4费中近距离持续锥形清群，多段伤害和灼烧。</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="str">
+      <x:c r="K10" s="14" t="str">
         <x:v>windup_time, duration, tick_interval, fan_angle, poison_dps, explosion_radius, delayed_strike_interval</x:v>
       </x:c>
-      <x:c r="H10" s="14" t="str">
+      <x:c r="L10" s="14" t="str">
         <x:v>法修</x:v>
       </x:c>
-      <x:c r="I10" s="14" t="str">
+      <x:c r="M10" s="14" t="str">
         <x:v>火</x:v>
       </x:c>
-      <x:c r="J10" s="14" t="str">
+      <x:c r="N10" s="14" t="str">
         <x:v>灵宝</x:v>
       </x:c>
-      <x:c r="K10" s="14" t="n">
+      <x:c r="O10" s="14" t="n">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="L10" s="14" t="str"/>
-      <x:c r="M10" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N10" s="14" t="str">
-        <x:v>melee</x:v>
-      </x:c>
-      <x:c r="O10" s="14" t="str">
-        <x:v>cone</x:v>
       </x:c>
       <x:c r="P10" s="14" t="str"/>
       <x:c r="Q10" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R10" s="14" t="str">
+        <x:v>melee</x:v>
+      </x:c>
+      <x:c r="S10" s="14" t="str">
+        <x:v>cone</x:v>
+      </x:c>
+      <x:c r="T10" s="14" t="str"/>
+      <x:c r="U10" s="14" t="n">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="R10" s="14" t="n">
+      <x:c r="V10" s="14" t="n">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="S10" s="14" t="n">
+      <x:c r="W10" s="14" t="n">
         <x:v>47.33</x:v>
       </x:c>
-      <x:c r="T10" s="14" t="n">
+      <x:c r="X10" s="14" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="U10" s="14" t="n">
+      <x:c r="Y10" s="14" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="V10" s="14" t="n">
+      <x:c r="Z10" s="14" t="n">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="W10" s="14" t="n">
+      <x:c r="AA10" s="14" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="X10" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y10" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z10" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA10" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB10" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC10" s="14" t="n">
         <x:v>0</x:v>
@@ -2248,87 +2304,99 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AF10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AI10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AJ10" s="14" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="AG10" s="14" t="n">
+      <x:c r="AK10" s="14" t="n">
         <x:v>1.8</x:v>
       </x:c>
-      <x:c r="AH10" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AI10" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AJ10" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AK10" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AL10" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM10" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AN10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ10" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR10" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO10" s="14" t="n">
+      <x:c r="AS10" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP10" s="14" t="n">
+      <x:c r="AT10" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ10" s="14" t="n">
+      <x:c r="AU10" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR10" s="14" t="n">
+      <x:c r="AV10" s="14" t="n">
         <x:v>0.18</x:v>
       </x:c>
-      <x:c r="AS10" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT10" s="14" t="n">
+      <x:c r="AW10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX10" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU10" s="14" t="n">
+      <x:c r="AY10" s="14" t="n">
         <x:v>0.32</x:v>
       </x:c>
-      <x:c r="AV10" s="14" t="n">
+      <x:c r="AZ10" s="14" t="n">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="AW10" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AX10" s="14" t="n">
+      <x:c r="BA10" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB10" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY10" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ10" s="14" t="n">
+      <x:c r="BC10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD10" s="14" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="BA10" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB10" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BC10" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BD10" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BE10" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="BF10" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG10" s="15" t="str">
+      <x:c r="BG10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK10" s="15" t="str">
         <x:v>data/artifacts/fire_gourd.tres</x:v>
       </x:c>
     </x:row>
@@ -2345,73 +2413,65 @@
       <x:c r="D11" s="14" t="str">
         <x:v>光点凝聚成法球，短暂停顿后飞行，命中后收缩并爆炸为圆形冲击波。</x:v>
       </x:c>
-      <x:c r="E11" s="14" t="str">
+      <x:c r="E11" s="14" t="str"/>
+      <x:c r="F11" s="14" t="str"/>
+      <x:c r="G11" s="14" t="str"/>
+      <x:c r="H11" s="14" t="str"/>
+      <x:c r="I11" s="14" t="str">
         <x:v>第一次爆炸后延迟触发更大、更淡、低伤的第二次爆炸。</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="str">
+      <x:c r="J11" s="14" t="str">
         <x:v>1费标准法修发射物，中速基础AOE。</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="str">
+      <x:c r="K11" s="14" t="str">
         <x:v>windup_time, explosion_radius, secondary_delay, secondary_radius, secondary_damage_mult</x:v>
       </x:c>
-      <x:c r="H11" s="14" t="str">
+      <x:c r="L11" s="14" t="str">
         <x:v>法修</x:v>
       </x:c>
-      <x:c r="I11" s="14" t="str">
+      <x:c r="M11" s="14" t="str">
         <x:v>火</x:v>
       </x:c>
-      <x:c r="J11" s="14" t="str">
+      <x:c r="N11" s="14" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="K11" s="14" t="n">
+      <x:c r="O11" s="14" t="n">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="L11" s="14" t="str"/>
-      <x:c r="M11" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N11" s="14" t="str">
-        <x:v>projectile</x:v>
-      </x:c>
-      <x:c r="O11" s="14" t="str">
-        <x:v>circle</x:v>
       </x:c>
       <x:c r="P11" s="14" t="str"/>
       <x:c r="Q11" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R11" s="14" t="str">
+        <x:v>projectile</x:v>
+      </x:c>
+      <x:c r="S11" s="14" t="str">
+        <x:v>circle</x:v>
+      </x:c>
+      <x:c r="T11" s="14" t="str"/>
+      <x:c r="U11" s="14" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="R11" s="14" t="n">
+      <x:c r="V11" s="14" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="S11" s="14" t="n">
+      <x:c r="W11" s="14" t="n">
         <x:v>23.96</x:v>
       </x:c>
-      <x:c r="T11" s="14" t="n">
+      <x:c r="X11" s="14" t="n">
         <x:v>500</x:v>
       </x:c>
-      <x:c r="U11" s="14" t="n">
+      <x:c r="Y11" s="14" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="V11" s="14" t="n">
+      <x:c r="Z11" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="W11" s="14" t="n">
+      <x:c r="AA11" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="X11" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y11" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z11" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA11" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB11" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC11" s="14" t="n">
         <x:v>0</x:v>
@@ -2444,53 +2504,53 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM11" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AN11" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO11" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP11" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ11" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR11" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO11" s="14" t="n">
+      <x:c r="AS11" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP11" s="14" t="n">
+      <x:c r="AT11" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ11" s="14" t="n">
+      <x:c r="AU11" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR11" s="14" t="n">
+      <x:c r="AV11" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AS11" s="14" t="n">
+      <x:c r="AW11" s="14" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="AT11" s="14" t="n">
+      <x:c r="AX11" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU11" s="14" t="n">
+      <x:c r="AY11" s="14" t="n">
         <x:v>0.45</x:v>
       </x:c>
-      <x:c r="AV11" s="14" t="n">
+      <x:c r="AZ11" s="14" t="n">
         <x:v>1.35</x:v>
       </x:c>
-      <x:c r="AW11" s="14" t="n">
+      <x:c r="BA11" s="14" t="n">
         <x:v>0.18</x:v>
       </x:c>
-      <x:c r="AX11" s="14" t="n">
+      <x:c r="BB11" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY11" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ11" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA11" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB11" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC11" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2503,7 +2563,19 @@
       <x:c r="BF11" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG11" s="15" t="str">
+      <x:c r="BG11" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH11" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI11" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ11" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK11" s="15" t="str">
         <x:v>data/artifacts/fire_orb.tres</x:v>
       </x:c>
     </x:row>
@@ -2521,77 +2593,69 @@
       <x:c r="E12" s="14" t="str"/>
       <x:c r="F12" s="14" t="str"/>
       <x:c r="G12" s="14" t="str"/>
-      <x:c r="H12" s="14" t="str">
+      <x:c r="H12" s="14" t="str"/>
+      <x:c r="I12" s="14" t="str"/>
+      <x:c r="J12" s="14" t="str"/>
+      <x:c r="K12" s="14" t="str"/>
+      <x:c r="L12" s="14" t="str">
         <x:v>体修</x:v>
       </x:c>
-      <x:c r="I12" s="14" t="str">
+      <x:c r="M12" s="14" t="str">
         <x:v>火</x:v>
       </x:c>
-      <x:c r="J12" s="14" t="str">
+      <x:c r="N12" s="14" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="K12" s="14" t="n">
+      <x:c r="O12" s="14" t="n">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="L12" s="14" t="str"/>
-      <x:c r="M12" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N12" s="14" t="str">
-        <x:v>melee</x:v>
-      </x:c>
-      <x:c r="O12" s="14" t="str">
-        <x:v>stab</x:v>
       </x:c>
       <x:c r="P12" s="14" t="str"/>
       <x:c r="Q12" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R12" s="14" t="str">
+        <x:v>melee</x:v>
+      </x:c>
+      <x:c r="S12" s="14" t="str">
+        <x:v>stab</x:v>
+      </x:c>
+      <x:c r="T12" s="14" t="str"/>
+      <x:c r="U12" s="14" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="R12" s="14" t="n">
+      <x:c r="V12" s="14" t="n">
         <x:v>0.27</x:v>
       </x:c>
-      <x:c r="S12" s="14" t="n">
+      <x:c r="W12" s="14" t="n">
         <x:v>37.04</x:v>
       </x:c>
-      <x:c r="T12" s="14" t="n">
+      <x:c r="X12" s="14" t="n">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="U12" s="14" t="n">
+      <x:c r="Y12" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="V12" s="14" t="n">
+      <x:c r="Z12" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="W12" s="14" t="n">
+      <x:c r="AA12" s="14" t="n">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="X12" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y12" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z12" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA12" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB12" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF12" s="14" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="AC12" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AD12" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AE12" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF12" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AG12" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2611,53 +2675,53 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM12" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AN12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ12" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR12" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO12" s="14" t="n">
+      <x:c r="AS12" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP12" s="14" t="n">
+      <x:c r="AT12" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ12" s="14" t="n">
+      <x:c r="AU12" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR12" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS12" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT12" s="14" t="n">
+      <x:c r="AV12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AW12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX12" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU12" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AV12" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW12" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX12" s="14" t="n">
+      <x:c r="AY12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AZ12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BB12" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY12" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ12" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA12" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB12" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC12" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2670,7 +2734,19 @@
       <x:c r="BF12" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG12" s="15" t="str">
+      <x:c r="BG12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK12" s="15" t="str">
         <x:v>data/artifacts/fist.tres</x:v>
       </x:c>
     </x:row>
@@ -2687,80 +2763,72 @@
       <x:c r="D13" s="14" t="str">
         <x:v>飞剑浮现、短蓄力后穿透飞出，到最大距离后返航，去返分别命中。</x:v>
       </x:c>
-      <x:c r="E13" s="14" t="str">
+      <x:c r="E13" s="14" t="str"/>
+      <x:c r="F13" s="14" t="str"/>
+      <x:c r="G13" s="14" t="str"/>
+      <x:c r="H13" s="14" t="str"/>
+      <x:c r="I13" s="14" t="str">
         <x:v>三把飞剑扇形出发，副剑按side_projectile_damage_mult造成伤害。</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="str">
+      <x:c r="J13" s="14" t="str">
         <x:v>2费御剑攻击，主动操控感，非普通直线子弹。</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="str">
+      <x:c r="K13" s="14" t="str">
         <x:v>windup_time, return_speed, fan_angle, side_projectile_damage_mult, trail_length</x:v>
       </x:c>
-      <x:c r="H13" s="14" t="str">
+      <x:c r="L13" s="14" t="str">
         <x:v>剑修</x:v>
       </x:c>
-      <x:c r="I13" s="14" t="str">
+      <x:c r="M13" s="14" t="str">
         <x:v>雷</x:v>
       </x:c>
-      <x:c r="J13" s="14" t="str">
+      <x:c r="N13" s="14" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="K13" s="14" t="n">
+      <x:c r="O13" s="14" t="n">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="L13" s="14" t="str"/>
-      <x:c r="M13" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N13" s="14" t="str">
-        <x:v>projectile</x:v>
-      </x:c>
-      <x:c r="O13" s="14" t="str">
-        <x:v>projectile</x:v>
       </x:c>
       <x:c r="P13" s="14" t="str"/>
       <x:c r="Q13" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R13" s="14" t="str">
+        <x:v>projectile</x:v>
+      </x:c>
+      <x:c r="S13" s="14" t="str">
+        <x:v>projectile</x:v>
+      </x:c>
+      <x:c r="T13" s="14" t="str"/>
+      <x:c r="U13" s="14" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="R13" s="14" t="n">
+      <x:c r="V13" s="14" t="n">
         <x:v>0.68</x:v>
       </x:c>
-      <x:c r="S13" s="14" t="n">
+      <x:c r="W13" s="14" t="n">
         <x:v>32.35</x:v>
       </x:c>
-      <x:c r="T13" s="14" t="n">
+      <x:c r="X13" s="14" t="n">
         <x:v>560</x:v>
       </x:c>
-      <x:c r="U13" s="14" t="n">
+      <x:c r="Y13" s="14" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="V13" s="14" t="n">
+      <x:c r="Z13" s="14" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="W13" s="14" t="n">
+      <x:c r="AA13" s="14" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="X13" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y13" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z13" s="14" t="n">
+      <x:c r="AB13" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD13" s="14" t="n">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="AA13" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AB13" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AC13" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AD13" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AE13" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2786,66 +2854,78 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM13" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AN13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ13" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR13" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO13" s="14" t="n">
+      <x:c r="AS13" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP13" s="14" t="n">
+      <x:c r="AT13" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ13" s="14" t="n">
+      <x:c r="AU13" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR13" s="14" t="n">
+      <x:c r="AV13" s="14" t="n">
         <x:v>0.08</x:v>
       </x:c>
-      <x:c r="AS13" s="14" t="n">
+      <x:c r="AW13" s="14" t="n">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="AT13" s="14" t="n">
+      <x:c r="AX13" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU13" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AV13" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW13" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX13" s="14" t="n">
+      <x:c r="AY13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AZ13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BB13" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY13" s="14" t="n">
+      <x:c r="BC13" s="14" t="n">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="AZ13" s="14" t="n">
+      <x:c r="BD13" s="14" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="BA13" s="14" t="n">
+      <x:c r="BE13" s="14" t="n">
         <x:v>0.35</x:v>
       </x:c>
-      <x:c r="BB13" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BC13" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BD13" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BE13" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BF13" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG13" s="15" t="str">
+      <x:c r="BG13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK13" s="15" t="str">
         <x:v>data/artifacts/flying_sword.tres</x:v>
       </x:c>
     </x:row>
@@ -2859,147 +2939,155 @@
       <x:c r="C14" s="14" t="str">
         <x:v>召唤没有仇恨值的幽魂。幽魂锁定敌人后加速冲击，穿过敌人造成伤害，并在敌人身后短距离停下后重新锁定目标。幽魂不会受到伤害。</x:v>
       </x:c>
-      <x:c r="D14" s="14" t="str"/>
-      <x:c r="E14" s="14" t="str"/>
-      <x:c r="F14" s="14" t="str"/>
-      <x:c r="G14" s="14" t="str"/>
+      <x:c r="D14" s="14" t="str">
+        <x:v>水波召唤印记中浮现，无实体阻挡、无仇恨、普通伤害无效；锁敌后拉长并穿过目标，留下半透明拖尾。</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="str">
+        <x:v>玩家附近漂浮；锁敌后直线冲刺穿过并在目标后方停顿；过远返回。</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="str">
+        <x:v>无仇恨，敌人不会主动锁定。</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="str">
+        <x:v>普通伤害无效。</x:v>
+      </x:c>
       <x:c r="H14" s="14" t="str">
+        <x:v>无死亡和重生。</x:v>
+      </x:c>
+      <x:c r="I14" s="14" t="str">
+        <x:v>第一次穿过后在secondary_radius内寻找第二目标，立即二段转向冲刺，伤害按secondary_damage_mult。</x:v>
+      </x:c>
+      <x:c r="J14" s="14" t="str">
+        <x:v>4费无敌无仇恨高速穿透输出，不承担坦克职责，无死亡重生。</x:v>
+      </x:c>
+      <x:c r="K14" s="14" t="str">
+        <x:v>summon_base_count, summon_move_speed, length, width, secondary_damage_mult, secondary_radius, secondary_delay</x:v>
+      </x:c>
+      <x:c r="L14" s="14" t="str">
         <x:v>召唤</x:v>
       </x:c>
-      <x:c r="I14" s="14" t="str">
+      <x:c r="M14" s="14" t="str">
         <x:v>水</x:v>
       </x:c>
-      <x:c r="J14" s="14" t="str">
+      <x:c r="N14" s="14" t="str">
         <x:v>灵宝</x:v>
       </x:c>
-      <x:c r="K14" s="14" t="n">
+      <x:c r="O14" s="14" t="n">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="L14" s="14" t="str"/>
-      <x:c r="M14" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N14" s="14" t="str">
-        <x:v>summon</x:v>
-      </x:c>
-      <x:c r="O14" s="14" t="str">
-        <x:v>line</x:v>
       </x:c>
       <x:c r="P14" s="14" t="str"/>
       <x:c r="Q14" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R14" s="14" t="str">
+        <x:v>summon</x:v>
+      </x:c>
+      <x:c r="S14" s="14" t="str">
+        <x:v>line</x:v>
+      </x:c>
+      <x:c r="T14" s="14" t="str"/>
+      <x:c r="U14" s="14" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="R14" s="14" t="n">
+      <x:c r="V14" s="14" t="n">
         <x:v>0.59</x:v>
       </x:c>
-      <x:c r="S14" s="14" t="n">
+      <x:c r="W14" s="14" t="n">
         <x:v>13.56</x:v>
       </x:c>
-      <x:c r="T14" s="14" t="n">
+      <x:c r="X14" s="14" t="n">
         <x:v>700</x:v>
       </x:c>
-      <x:c r="U14" s="14" t="n">
+      <x:c r="Y14" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="V14" s="14" t="n">
+      <x:c r="Z14" s="14" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="W14" s="14" t="n">
+      <x:c r="AA14" s="14" t="n">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="X14" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y14" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z14" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA14" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB14" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC14" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AD14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH14" s="14" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AE14" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF14" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AG14" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AH14" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AI14" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AJ14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AM14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AN14" s="14" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AK14" s="14" t="n">
+      <x:c r="AO14" s="14" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="AL14" s="14" t="n">
+      <x:c r="AP14" s="14" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="AM14" s="14" t="n">
+      <x:c r="AQ14" s="14" t="n">
         <x:v>1.68</x:v>
       </x:c>
-      <x:c r="AN14" s="14" t="n">
+      <x:c r="AR14" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO14" s="14" t="n">
+      <x:c r="AS14" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP14" s="14" t="n">
+      <x:c r="AT14" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ14" s="14" t="n">
+      <x:c r="AU14" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR14" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS14" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT14" s="14" t="n">
+      <x:c r="AV14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AW14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX14" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU14" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AV14" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW14" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX14" s="14" t="n">
+      <x:c r="AY14" s="14" t="n">
+        <x:v>0.58</x:v>
+      </x:c>
+      <x:c r="AZ14" s="14" t="n">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="BA14" s="14" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="BB14" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY14" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ14" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA14" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB14" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC14" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3012,7 +3100,19 @@
       <x:c r="BF14" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG14" s="15" t="str">
+      <x:c r="BG14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK14" s="15" t="str">
         <x:v>data/artifacts/ghost.tres</x:v>
       </x:c>
     </x:row>
@@ -3029,80 +3129,72 @@
       <x:c r="D15" s="14" t="str">
         <x:v>脚下剑阵，选择敌人密集方向，巨剑分段显现后向前贯穿。</x:v>
       </x:c>
-      <x:c r="E15" s="14" t="str">
+      <x:c r="E15" s="14" t="str"/>
+      <x:c r="F15" s="14" t="str"/>
+      <x:c r="G15" s="14" t="str"/>
+      <x:c r="H15" s="14" t="str"/>
+      <x:c r="I15" s="14" t="str">
         <x:v>改为以角色为中心360度横扫一周。</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="str">
+      <x:c r="J15" s="14" t="str">
         <x:v>5费超大范围视觉高潮和清场输出。</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="str">
+      <x:c r="K15" s="14" t="str">
         <x:v>reveal_time, pause_time, sweep_rotation_speed, trail_length</x:v>
       </x:c>
-      <x:c r="H15" s="14" t="str">
+      <x:c r="L15" s="14" t="str">
         <x:v>剑修</x:v>
       </x:c>
-      <x:c r="I15" s="14" t="str">
+      <x:c r="M15" s="14" t="str">
         <x:v>金</x:v>
       </x:c>
-      <x:c r="J15" s="14" t="str">
+      <x:c r="N15" s="14" t="str">
         <x:v>仙宝</x:v>
       </x:c>
-      <x:c r="K15" s="14" t="n">
+      <x:c r="O15" s="14" t="n">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="L15" s="14" t="str"/>
-      <x:c r="M15" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N15" s="14" t="str">
-        <x:v>projectile</x:v>
-      </x:c>
-      <x:c r="O15" s="14" t="str">
-        <x:v>line</x:v>
       </x:c>
       <x:c r="P15" s="14" t="str"/>
       <x:c r="Q15" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R15" s="14" t="str">
+        <x:v>projectile</x:v>
+      </x:c>
+      <x:c r="S15" s="14" t="str">
+        <x:v>line</x:v>
+      </x:c>
+      <x:c r="T15" s="14" t="str"/>
+      <x:c r="U15" s="14" t="n">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="R15" s="14" t="n">
+      <x:c r="V15" s="14" t="n">
         <x:v>1.68</x:v>
       </x:c>
-      <x:c r="S15" s="14" t="n">
+      <x:c r="W15" s="14" t="n">
         <x:v>79.76</x:v>
       </x:c>
-      <x:c r="T15" s="14" t="n">
+      <x:c r="X15" s="14" t="n">
         <x:v>760</x:v>
       </x:c>
-      <x:c r="U15" s="14" t="n">
+      <x:c r="Y15" s="14" t="n">
         <x:v>680</x:v>
       </x:c>
-      <x:c r="V15" s="14" t="n">
+      <x:c r="Z15" s="14" t="n">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="W15" s="14" t="n">
+      <x:c r="AA15" s="14" t="n">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="X15" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y15" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z15" s="14" t="n">
+      <x:c r="AB15" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD15" s="14" t="n">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="AA15" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AB15" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AC15" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AD15" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AE15" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3128,66 +3220,78 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM15" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AN15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ15" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR15" s="14" t="n">
         <x:v>1.75</x:v>
       </x:c>
-      <x:c r="AO15" s="14" t="n">
+      <x:c r="AS15" s="14" t="n">
         <x:v>0.95</x:v>
       </x:c>
-      <x:c r="AP15" s="14" t="n">
+      <x:c r="AT15" s="14" t="n">
         <x:v>2.4</x:v>
       </x:c>
-      <x:c r="AQ15" s="14" t="n">
+      <x:c r="AU15" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AR15" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS15" s="14" t="n">
+      <x:c r="AV15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AW15" s="14" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="AT15" s="14" t="n">
+      <x:c r="AX15" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU15" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AV15" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW15" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX15" s="14" t="n">
+      <x:c r="AY15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AZ15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BB15" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY15" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ15" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA15" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB15" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BF15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BG15" s="14" t="n">
         <x:v>0.36</x:v>
       </x:c>
-      <x:c r="BD15" s="14" t="n">
+      <x:c r="BH15" s="14" t="n">
         <x:v>0.16</x:v>
       </x:c>
-      <x:c r="BE15" s="14" t="n">
+      <x:c r="BI15" s="14" t="n">
         <x:v>6.283</x:v>
       </x:c>
-      <x:c r="BF15" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BG15" s="15" t="str">
+      <x:c r="BJ15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK15" s="15" t="str">
         <x:v>data/artifacts/giant_sword_art.tres</x:v>
       </x:c>
     </x:row>
@@ -3205,66 +3309,58 @@
       <x:c r="E16" s="14" t="str"/>
       <x:c r="F16" s="14" t="str"/>
       <x:c r="G16" s="14" t="str"/>
-      <x:c r="H16" s="14" t="str">
+      <x:c r="H16" s="14" t="str"/>
+      <x:c r="I16" s="14" t="str"/>
+      <x:c r="J16" s="14" t="str"/>
+      <x:c r="K16" s="14" t="str"/>
+      <x:c r="L16" s="14" t="str">
         <x:v>体修</x:v>
       </x:c>
-      <x:c r="I16" s="14" t="str">
+      <x:c r="M16" s="14" t="str">
         <x:v>土</x:v>
       </x:c>
-      <x:c r="J16" s="14" t="str">
+      <x:c r="N16" s="14" t="str">
         <x:v>仙宝</x:v>
       </x:c>
-      <x:c r="K16" s="14" t="n">
+      <x:c r="O16" s="14" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L16" s="14" t="str"/>
-      <x:c r="M16" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N16" s="14" t="str">
+      <x:c r="P16" s="14" t="str"/>
+      <x:c r="Q16" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R16" s="14" t="str">
         <x:v>formation</x:v>
       </x:c>
-      <x:c r="O16" s="14" t="str">
+      <x:c r="S16" s="14" t="str">
         <x:v>aura</x:v>
       </x:c>
-      <x:c r="P16" s="14" t="str">
+      <x:c r="T16" s="14" t="str">
         <x:v>avatar_slam</x:v>
       </x:c>
-      <x:c r="Q16" s="14" t="n">
+      <x:c r="U16" s="14" t="n">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="R16" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S16" s="14" t="n">
+      <x:c r="V16" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W16" s="14" t="n">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="T16" s="14" t="n">
+      <x:c r="X16" s="14" t="n">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="U16" s="14" t="n">
+      <x:c r="Y16" s="14" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="V16" s="14" t="n">
+      <x:c r="Z16" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="W16" s="14" t="n">
+      <x:c r="AA16" s="14" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="X16" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y16" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z16" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA16" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB16" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC16" s="14" t="n">
         <x:v>0</x:v>
@@ -3297,53 +3393,53 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM16" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AN16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ16" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR16" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO16" s="14" t="n">
+      <x:c r="AS16" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP16" s="14" t="n">
+      <x:c r="AT16" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ16" s="14" t="n">
+      <x:c r="AU16" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR16" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS16" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT16" s="14" t="n">
+      <x:c r="AV16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AW16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX16" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU16" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AV16" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW16" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX16" s="14" t="n">
+      <x:c r="AY16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AZ16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BB16" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY16" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ16" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA16" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB16" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC16" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3356,7 +3452,19 @@
       <x:c r="BF16" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG16" s="15" t="str">
+      <x:c r="BG16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK16" s="15" t="str">
         <x:v>data/artifacts/golden_body_avatar.tres</x:v>
       </x:c>
     </x:row>
@@ -3373,72 +3481,64 @@
       <x:c r="D17" s="14" t="str">
         <x:v>3个小型剑轮均匀环绕角色，高速公转并按显式间隔切割。</x:v>
       </x:c>
-      <x:c r="E17" s="14" t="str">
+      <x:c r="E17" s="14" t="str"/>
+      <x:c r="F17" s="14" t="str"/>
+      <x:c r="G17" s="14" t="str"/>
+      <x:c r="H17" s="14" t="str"/>
+      <x:c r="I17" s="14" t="str">
         <x:v>剑轮数量增加到4个。</x:v>
       </x:c>
-      <x:c r="F17" s="14" t="str">
+      <x:c r="J17" s="14" t="str">
         <x:v>4费中近距离持续切割，伤害不依赖帧率。</x:v>
       </x:c>
-      <x:c r="G17" s="14" t="str">
+      <x:c r="K17" s="14" t="str">
         <x:v>count, radius, rotation_speed, self_rotation_speed, hit_interval</x:v>
       </x:c>
-      <x:c r="H17" s="14" t="str">
+      <x:c r="L17" s="14" t="str">
         <x:v>剑修</x:v>
       </x:c>
-      <x:c r="I17" s="14" t="str">
+      <x:c r="M17" s="14" t="str">
         <x:v>木</x:v>
       </x:c>
-      <x:c r="J17" s="14" t="str">
+      <x:c r="N17" s="14" t="str">
         <x:v>灵宝</x:v>
       </x:c>
-      <x:c r="K17" s="14" t="n">
+      <x:c r="O17" s="14" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="L17" s="14" t="str"/>
-      <x:c r="M17" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N17" s="14" t="str">
-        <x:v>orbit</x:v>
-      </x:c>
-      <x:c r="O17" s="14" t="str"/>
       <x:c r="P17" s="14" t="str"/>
       <x:c r="Q17" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R17" s="14" t="str">
+        <x:v>orbit</x:v>
+      </x:c>
+      <x:c r="S17" s="14" t="str"/>
+      <x:c r="T17" s="14" t="str"/>
+      <x:c r="U17" s="14" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="R17" s="14" t="n">
+      <x:c r="V17" s="14" t="n">
         <x:v>0.61</x:v>
       </x:c>
-      <x:c r="S17" s="14" t="n">
+      <x:c r="W17" s="14" t="n">
         <x:v>55.74</x:v>
       </x:c>
-      <x:c r="T17" s="14" t="n">
+      <x:c r="X17" s="14" t="n">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="U17" s="14" t="n">
+      <x:c r="Y17" s="14" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="V17" s="14" t="n">
+      <x:c r="Z17" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="W17" s="14" t="n">
+      <x:c r="AA17" s="14" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="X17" s="14" t="n">
+      <x:c r="AB17" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="Y17" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z17" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA17" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AB17" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AC17" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3470,66 +3570,78 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM17" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AN17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ17" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR17" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO17" s="14" t="n">
+      <x:c r="AS17" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP17" s="14" t="n">
+      <x:c r="AT17" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ17" s="14" t="n">
+      <x:c r="AU17" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR17" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS17" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT17" s="14" t="n">
+      <x:c r="AV17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AW17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX17" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU17" s="14" t="n">
+      <x:c r="AY17" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AV17" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW17" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX17" s="14" t="n">
+      <x:c r="AZ17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BB17" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY17" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ17" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA17" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB17" s="14" t="n">
+      <x:c r="BC17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BF17" s="14" t="n">
         <x:v>4.2</x:v>
       </x:c>
-      <x:c r="BC17" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BD17" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BE17" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BF17" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BG17" s="15" t="str">
+      <x:c r="BG17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK17" s="15" t="str">
         <x:v>data/artifacts/guardian_flying_sword.tres</x:v>
       </x:c>
     </x:row>
@@ -3546,73 +3658,65 @@
       <x:c r="D18" s="14" t="str">
         <x:v>古琴虚影拨弦，按顺序释放三层弧形音波并施加伤害降低。</x:v>
       </x:c>
-      <x:c r="E18" s="14" t="str">
+      <x:c r="E18" s="14" t="str"/>
+      <x:c r="F18" s="14" t="str"/>
+      <x:c r="G18" s="14" t="str"/>
+      <x:c r="H18" s="14" t="str"/>
+      <x:c r="I18" s="14" t="str">
         <x:v>第三层音波改为以角色为中心的环形音波。</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="str">
+      <x:c r="J18" s="14" t="str">
         <x:v>3费大范围多段音波辅助，偏生存和削弱。</x:v>
       </x:c>
-      <x:c r="G18" s="14" t="str">
+      <x:c r="K18" s="14" t="str">
         <x:v>range, fan_angle, delayed_strike_interval, damage_reduction_percent, debuff_duration</x:v>
       </x:c>
-      <x:c r="H18" s="14" t="str">
+      <x:c r="L18" s="14" t="str">
         <x:v>法修</x:v>
       </x:c>
-      <x:c r="I18" s="14" t="str">
+      <x:c r="M18" s="14" t="str">
         <x:v>水</x:v>
       </x:c>
-      <x:c r="J18" s="14" t="str">
+      <x:c r="N18" s="14" t="str">
         <x:v>灵器</x:v>
       </x:c>
-      <x:c r="K18" s="14" t="n">
+      <x:c r="O18" s="14" t="n">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="L18" s="14" t="str"/>
-      <x:c r="M18" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N18" s="14" t="str">
-        <x:v>projectile</x:v>
-      </x:c>
-      <x:c r="O18" s="14" t="str">
-        <x:v>circle</x:v>
       </x:c>
       <x:c r="P18" s="14" t="str"/>
       <x:c r="Q18" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R18" s="14" t="str">
+        <x:v>projectile</x:v>
+      </x:c>
+      <x:c r="S18" s="14" t="str">
+        <x:v>circle</x:v>
+      </x:c>
+      <x:c r="T18" s="14" t="str"/>
+      <x:c r="U18" s="14" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="R18" s="14" t="n">
+      <x:c r="V18" s="14" t="n">
         <x:v>1.25</x:v>
       </x:c>
-      <x:c r="S18" s="14" t="n">
+      <x:c r="W18" s="14" t="n">
         <x:v>16.8</x:v>
       </x:c>
-      <x:c r="T18" s="14" t="n">
+      <x:c r="X18" s="14" t="n">
         <x:v>480</x:v>
       </x:c>
-      <x:c r="U18" s="14" t="n">
+      <x:c r="Y18" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="V18" s="14" t="n">
+      <x:c r="Z18" s="14" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="W18" s="14" t="n">
+      <x:c r="AA18" s="14" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="X18" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y18" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z18" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA18" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB18" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC18" s="14" t="n">
         <x:v>0</x:v>
@@ -3645,66 +3749,78 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM18" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AN18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ18" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR18" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO18" s="14" t="n">
+      <x:c r="AS18" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP18" s="14" t="n">
+      <x:c r="AT18" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ18" s="14" t="n">
+      <x:c r="AU18" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR18" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS18" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT18" s="14" t="n">
+      <x:c r="AV18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AW18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX18" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU18" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AV18" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW18" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX18" s="14" t="n">
+      <x:c r="AY18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AZ18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BB18" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY18" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ18" s="14" t="n">
+      <x:c r="BC18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD18" s="14" t="n">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="BA18" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB18" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BC18" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BD18" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BE18" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="BF18" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG18" s="15" t="str">
+      <x:c r="BG18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK18" s="15" t="str">
         <x:v>data/artifacts/guqin.tres</x:v>
       </x:c>
     </x:row>
@@ -3721,73 +3837,65 @@
       <x:c r="D19" s="14" t="str">
         <x:v>天眼睁开并锁定目标，光束按tick_interval固定脉冲造成持续伤害，击杀后自动转火。</x:v>
       </x:c>
-      <x:c r="E19" s="14" t="str">
+      <x:c r="E19" s="14" t="str"/>
+      <x:c r="F19" s="14" t="str"/>
+      <x:c r="G19" s="14" t="str"/>
+      <x:c r="H19" s="14" t="str"/>
+      <x:c r="I19" s="14" t="str">
         <x:v>主光束外额外分出两条副光束，副光束优先锁定不同目标并按side_projectile_damage_mult造成伤害。</x:v>
       </x:c>
-      <x:c r="F19" s="14" t="str">
+      <x:c r="J19" s="14" t="str">
         <x:v>3费持续单体压制，对精英和Boss稳定，持续耗血并击杀回血。</x:v>
       </x:c>
-      <x:c r="G19" s="14" t="str">
+      <x:c r="K19" s="14" t="str">
         <x:v>duration, tick_interval, range, life_cost_flat, life_cost_min_hp_ratio, kill_heal_amount, side_projectile_damage_mult</x:v>
       </x:c>
-      <x:c r="H19" s="14" t="str">
+      <x:c r="L19" s="14" t="str">
         <x:v>魔修</x:v>
       </x:c>
-      <x:c r="I19" s="14" t="str">
+      <x:c r="M19" s="14" t="str">
         <x:v>水</x:v>
       </x:c>
-      <x:c r="J19" s="14" t="str">
+      <x:c r="N19" s="14" t="str">
         <x:v>灵器</x:v>
       </x:c>
-      <x:c r="K19" s="14" t="n">
+      <x:c r="O19" s="14" t="n">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="L19" s="14" t="str"/>
-      <x:c r="M19" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N19" s="14" t="str">
-        <x:v>beam</x:v>
-      </x:c>
-      <x:c r="O19" s="14" t="str">
-        <x:v>beam</x:v>
       </x:c>
       <x:c r="P19" s="14" t="str"/>
       <x:c r="Q19" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R19" s="14" t="str">
+        <x:v>beam</x:v>
+      </x:c>
+      <x:c r="S19" s="14" t="str">
+        <x:v>beam</x:v>
+      </x:c>
+      <x:c r="T19" s="14" t="str"/>
+      <x:c r="U19" s="14" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="R19" s="14" t="n">
+      <x:c r="V19" s="14" t="n">
         <x:v>2.14</x:v>
       </x:c>
-      <x:c r="S19" s="14" t="n">
+      <x:c r="W19" s="14" t="n">
         <x:v>10.28</x:v>
       </x:c>
-      <x:c r="T19" s="14" t="n">
+      <x:c r="X19" s="14" t="n">
         <x:v>520</x:v>
       </x:c>
-      <x:c r="U19" s="14" t="n">
+      <x:c r="Y19" s="14" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="V19" s="14" t="n">
+      <x:c r="Z19" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="W19" s="14" t="n">
+      <x:c r="AA19" s="14" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="X19" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y19" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z19" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA19" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB19" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC19" s="14" t="n">
         <x:v>0</x:v>
@@ -3808,7 +3916,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AI19" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AJ19" s="14" t="n">
         <x:v>0</x:v>
@@ -3823,50 +3931,50 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AN19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ19" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR19" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO19" s="14" t="n">
+      <x:c r="AS19" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP19" s="14" t="n">
+      <x:c r="AT19" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ19" s="14" t="n">
+      <x:c r="AU19" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR19" s="14" t="n">
+      <x:c r="AV19" s="14" t="n">
         <x:v>0.16</x:v>
       </x:c>
-      <x:c r="AS19" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT19" s="14" t="n">
+      <x:c r="AW19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX19" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU19" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AV19" s="14" t="n">
+      <x:c r="AY19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AZ19" s="14" t="n">
         <x:v>520</x:v>
       </x:c>
-      <x:c r="AW19" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX19" s="14" t="n">
+      <x:c r="BA19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BB19" s="14" t="n">
         <x:v>0.42</x:v>
       </x:c>
-      <x:c r="AY19" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ19" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA19" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB19" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC19" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3879,7 +3987,19 @@
       <x:c r="BF19" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG19" s="15" t="str">
+      <x:c r="BG19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK19" s="15" t="str">
         <x:v>data/artifacts/heaven_eye.tres</x:v>
       </x:c>
     </x:row>
@@ -3893,68 +4013,76 @@
       <x:c r="C20" s="14" t="str">
         <x:v>召唤高生命铁卫傀儡，尽量挡在玩家与怪群之间，并周期性嘲讽附近敌人。死亡后会重生。</x:v>
       </x:c>
-      <x:c r="D20" s="14" t="str"/>
-      <x:c r="E20" s="14" t="str"/>
-      <x:c r="F20" s="14" t="str"/>
-      <x:c r="G20" s="14" t="str"/>
+      <x:c r="D20" s="14" t="str">
+        <x:v>厚重召唤阵落地，移动到玩家与目标之间，慢速重击并周期性释放嘲讽波纹和敌人标记。</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="str">
+        <x:v>优先站在玩家与目标之间；周期嘲讽radius内敌人；过远返回。</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="str">
+        <x:v>有仇恨，且嘲讽期间强制附近敌人攻击它。</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="str">
+        <x:v>可受伤，三星嘲讽期间自身减伤。</x:v>
+      </x:c>
       <x:c r="H20" s="14" t="str">
+        <x:v>死亡碎裂并显示重生印记，summon_respawn_time后重新部署到玩家附近。</x:v>
+      </x:c>
+      <x:c r="I20" s="14" t="str">
+        <x:v>嘲讽时展开短时护盾领域，自身按secondary_damage_mult获得减伤，持续duration。</x:v>
+      </x:c>
+      <x:c r="J20" s="14" t="str">
+        <x:v>2费核心坦克，可被攻击，高生命，死亡后重生。</x:v>
+      </x:c>
+      <x:c r="K20" s="14" t="str">
+        <x:v>summon_hp, radius, summon_return_radius, duration, secondary_damage_mult, secondary_delay, secondary_radius</x:v>
+      </x:c>
+      <x:c r="L20" s="14" t="str">
         <x:v>召唤</x:v>
       </x:c>
-      <x:c r="I20" s="14" t="str">
+      <x:c r="M20" s="14" t="str">
         <x:v>土</x:v>
       </x:c>
-      <x:c r="J20" s="14" t="str">
+      <x:c r="N20" s="14" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="K20" s="14" t="n">
+      <x:c r="O20" s="14" t="n">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="L20" s="14" t="str"/>
-      <x:c r="M20" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N20" s="14" t="str">
-        <x:v>summon</x:v>
-      </x:c>
-      <x:c r="O20" s="14" t="str">
-        <x:v>stab</x:v>
       </x:c>
       <x:c r="P20" s="14" t="str"/>
       <x:c r="Q20" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R20" s="14" t="str">
+        <x:v>summon</x:v>
+      </x:c>
+      <x:c r="S20" s="14" t="str">
+        <x:v>stab</x:v>
+      </x:c>
+      <x:c r="T20" s="14" t="str"/>
+      <x:c r="U20" s="14" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="R20" s="14" t="n">
+      <x:c r="V20" s="14" t="n">
         <x:v>1.02</x:v>
       </x:c>
-      <x:c r="S20" s="14" t="n">
+      <x:c r="W20" s="14" t="n">
         <x:v>7.84</x:v>
       </x:c>
-      <x:c r="T20" s="14" t="n">
+      <x:c r="X20" s="14" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="U20" s="14" t="n">
+      <x:c r="Y20" s="14" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="V20" s="14" t="n">
+      <x:c r="Z20" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="W20" s="14" t="n">
+      <x:c r="AA20" s="14" t="n">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="X20" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y20" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z20" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA20" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB20" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC20" s="14" t="n">
         <x:v>0</x:v>
@@ -3978,62 +4106,62 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AJ20" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AK20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AM20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AN20" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO20" s="14" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="AL20" s="14" t="n">
+      <x:c r="AP20" s="14" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="AM20" s="14" t="n">
+      <x:c r="AQ20" s="14" t="n">
         <x:v>0.98</x:v>
       </x:c>
-      <x:c r="AN20" s="14" t="n">
+      <x:c r="AR20" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO20" s="14" t="n">
+      <x:c r="AS20" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP20" s="14" t="n">
+      <x:c r="AT20" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ20" s="14" t="n">
+      <x:c r="AU20" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR20" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS20" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT20" s="14" t="n">
+      <x:c r="AV20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AW20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX20" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU20" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AV20" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW20" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX20" s="14" t="n">
+      <x:c r="AY20" s="14" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="AZ20" s="14" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="BA20" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BB20" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY20" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ20" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA20" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB20" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC20" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4046,7 +4174,19 @@
       <x:c r="BF20" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG20" s="15" t="str">
+      <x:c r="BG20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK20" s="15" t="str">
         <x:v>data/artifacts/iron_guard_puppet.tres</x:v>
       </x:c>
     </x:row>
@@ -4064,77 +4204,69 @@
       <x:c r="E21" s="14" t="str"/>
       <x:c r="F21" s="14" t="str"/>
       <x:c r="G21" s="14" t="str"/>
-      <x:c r="H21" s="14" t="str">
+      <x:c r="H21" s="14" t="str"/>
+      <x:c r="I21" s="14" t="str"/>
+      <x:c r="J21" s="14" t="str"/>
+      <x:c r="K21" s="14" t="str"/>
+      <x:c r="L21" s="14" t="str">
         <x:v>体修</x:v>
       </x:c>
-      <x:c r="I21" s="14" t="str">
+      <x:c r="M21" s="14" t="str">
         <x:v>土</x:v>
       </x:c>
-      <x:c r="J21" s="14" t="str">
+      <x:c r="N21" s="14" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="K21" s="14" t="n">
+      <x:c r="O21" s="14" t="n">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="L21" s="14" t="str"/>
-      <x:c r="M21" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N21" s="14" t="str">
-        <x:v>melee</x:v>
-      </x:c>
-      <x:c r="O21" s="14" t="str">
-        <x:v>circle</x:v>
       </x:c>
       <x:c r="P21" s="14" t="str"/>
       <x:c r="Q21" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R21" s="14" t="str">
+        <x:v>melee</x:v>
+      </x:c>
+      <x:c r="S21" s="14" t="str">
+        <x:v>circle</x:v>
+      </x:c>
+      <x:c r="T21" s="14" t="str"/>
+      <x:c r="U21" s="14" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="R21" s="14" t="n">
+      <x:c r="V21" s="14" t="n">
         <x:v>0.71</x:v>
       </x:c>
-      <x:c r="S21" s="14" t="n">
+      <x:c r="W21" s="14" t="n">
         <x:v>33.8</x:v>
       </x:c>
-      <x:c r="T21" s="14" t="n">
+      <x:c r="X21" s="14" t="n">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="U21" s="14" t="n">
+      <x:c r="Y21" s="14" t="n">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="V21" s="14" t="n">
+      <x:c r="Z21" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="W21" s="14" t="n">
+      <x:c r="AA21" s="14" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="X21" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y21" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z21" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA21" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB21" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC21" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD21" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE21" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF21" s="14" t="n">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="AC21" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AD21" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AE21" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF21" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AG21" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4154,53 +4286,53 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM21" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AN21" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO21" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP21" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ21" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR21" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO21" s="14" t="n">
+      <x:c r="AS21" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP21" s="14" t="n">
+      <x:c r="AT21" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ21" s="14" t="n">
+      <x:c r="AU21" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR21" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS21" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT21" s="14" t="n">
+      <x:c r="AV21" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AW21" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX21" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU21" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AV21" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW21" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX21" s="14" t="n">
+      <x:c r="AY21" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AZ21" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA21" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BB21" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY21" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ21" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA21" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB21" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC21" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4213,7 +4345,19 @@
       <x:c r="BF21" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG21" s="15" t="str">
+      <x:c r="BG21" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH21" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI21" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ21" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK21" s="15" t="str">
         <x:v>data/artifacts/kick.tres</x:v>
       </x:c>
     </x:row>
@@ -4230,73 +4374,65 @@
       <x:c r="D22" s="14" t="str">
         <x:v>枪尖光点蓄力，长枪影快速伸长并延伸枪罡直线贯穿。</x:v>
       </x:c>
-      <x:c r="E22" s="14" t="str">
+      <x:c r="E22" s="14" t="str"/>
+      <x:c r="F22" s="14" t="str"/>
+      <x:c r="G22" s="14" t="str"/>
+      <x:c r="H22" s="14" t="str"/>
+      <x:c r="I22" s="14" t="str">
         <x:v>枪罡终点必定产生小范围冲击波。</x:v>
       </x:c>
-      <x:c r="F22" s="14" t="str">
+      <x:c r="J22" s="14" t="str">
         <x:v>3费极长距离窄直线贯穿。</x:v>
       </x:c>
-      <x:c r="G22" s="14" t="str">
+      <x:c r="K22" s="14" t="str">
         <x:v>windup_time, length, secondary_radius, secondary_damage_mult, trail_length</x:v>
       </x:c>
-      <x:c r="H22" s="14" t="str">
+      <x:c r="L22" s="14" t="str">
         <x:v>剑修</x:v>
       </x:c>
-      <x:c r="I22" s="14" t="str">
+      <x:c r="M22" s="14" t="str">
         <x:v>火</x:v>
       </x:c>
-      <x:c r="J22" s="14" t="str">
+      <x:c r="N22" s="14" t="str">
         <x:v>灵器</x:v>
       </x:c>
-      <x:c r="K22" s="14" t="n">
+      <x:c r="O22" s="14" t="n">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="L22" s="14" t="str"/>
-      <x:c r="M22" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N22" s="14" t="str">
-        <x:v>melee</x:v>
-      </x:c>
-      <x:c r="O22" s="14" t="str">
-        <x:v>stab</x:v>
       </x:c>
       <x:c r="P22" s="14" t="str"/>
       <x:c r="Q22" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R22" s="14" t="str">
+        <x:v>melee</x:v>
+      </x:c>
+      <x:c r="S22" s="14" t="str">
+        <x:v>stab</x:v>
+      </x:c>
+      <x:c r="T22" s="14" t="str"/>
+      <x:c r="U22" s="14" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="R22" s="14" t="n">
+      <x:c r="V22" s="14" t="n">
         <x:v>0.75</x:v>
       </x:c>
-      <x:c r="S22" s="14" t="n">
+      <x:c r="W22" s="14" t="n">
         <x:v>46.67</x:v>
       </x:c>
-      <x:c r="T22" s="14" t="n">
+      <x:c r="X22" s="14" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="U22" s="14" t="n">
+      <x:c r="Y22" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="V22" s="14" t="n">
+      <x:c r="Z22" s="14" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="W22" s="14" t="n">
+      <x:c r="AA22" s="14" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="X22" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y22" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z22" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA22" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB22" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC22" s="14" t="n">
         <x:v>0</x:v>
@@ -4329,53 +4465,53 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM22" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AN22" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO22" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP22" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ22" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR22" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO22" s="14" t="n">
+      <x:c r="AS22" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP22" s="14" t="n">
+      <x:c r="AT22" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ22" s="14" t="n">
+      <x:c r="AU22" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR22" s="14" t="n">
+      <x:c r="AV22" s="14" t="n">
         <x:v>0.14</x:v>
       </x:c>
-      <x:c r="AS22" s="14" t="n">
+      <x:c r="AW22" s="14" t="n">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="AT22" s="14" t="n">
+      <x:c r="AX22" s="14" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="AU22" s="14" t="n">
+      <x:c r="AY22" s="14" t="n">
         <x:v>0.45</x:v>
       </x:c>
-      <x:c r="AV22" s="14" t="n">
+      <x:c r="AZ22" s="14" t="n">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="AW22" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX22" s="14" t="n">
+      <x:c r="BA22" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BB22" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY22" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ22" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA22" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB22" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC22" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4388,7 +4524,19 @@
       <x:c r="BF22" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG22" s="15" t="str">
+      <x:c r="BG22" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH22" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI22" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ22" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK22" s="15" t="str">
         <x:v>data/artifacts/long_spear.tres</x:v>
       </x:c>
     </x:row>
@@ -4405,80 +4553,72 @@
       <x:c r="D23" s="14" t="str">
         <x:v>法环展开并蓄力，随后轰出短持续超长直线光束。</x:v>
       </x:c>
-      <x:c r="E23" s="14" t="str">
+      <x:c r="E23" s="14" t="str"/>
+      <x:c r="F23" s="14" t="str"/>
+      <x:c r="G23" s="14" t="str"/>
+      <x:c r="H23" s="14" t="str"/>
+      <x:c r="I23" s="14" t="str">
         <x:v>主光束路径留下光痕，延迟后整条路径二次爆发。</x:v>
       </x:c>
-      <x:c r="F23" s="14" t="str">
+      <x:c r="J23" s="14" t="str">
         <x:v>2费短前摇、高爆发、贯穿光束。</x:v>
       </x:c>
-      <x:c r="G23" s="14" t="str">
+      <x:c r="K23" s="14" t="str">
         <x:v>windup_time, range, width, secondary_delay, secondary_radius, secondary_damage_mult</x:v>
       </x:c>
-      <x:c r="H23" s="14" t="str">
+      <x:c r="L23" s="14" t="str">
         <x:v>法修</x:v>
       </x:c>
-      <x:c r="I23" s="14" t="str">
+      <x:c r="M23" s="14" t="str">
         <x:v>水</x:v>
       </x:c>
-      <x:c r="J23" s="14" t="str">
+      <x:c r="N23" s="14" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="K23" s="14" t="n">
+      <x:c r="O23" s="14" t="n">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="L23" s="14" t="str"/>
-      <x:c r="M23" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N23" s="14" t="str">
-        <x:v>projectile</x:v>
-      </x:c>
-      <x:c r="O23" s="14" t="str">
-        <x:v>circle</x:v>
       </x:c>
       <x:c r="P23" s="14" t="str"/>
       <x:c r="Q23" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R23" s="14" t="str">
+        <x:v>projectile</x:v>
+      </x:c>
+      <x:c r="S23" s="14" t="str">
+        <x:v>circle</x:v>
+      </x:c>
+      <x:c r="T23" s="14" t="str"/>
+      <x:c r="U23" s="14" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="R23" s="14" t="n">
+      <x:c r="V23" s="14" t="n">
         <x:v>1.15</x:v>
       </x:c>
-      <x:c r="S23" s="14" t="n">
+      <x:c r="W23" s="14" t="n">
         <x:v>36.52</x:v>
       </x:c>
-      <x:c r="T23" s="14" t="n">
+      <x:c r="X23" s="14" t="n">
         <x:v>620</x:v>
       </x:c>
-      <x:c r="U23" s="14" t="n">
+      <x:c r="Y23" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="V23" s="14" t="n">
+      <x:c r="Z23" s="14" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="W23" s="14" t="n">
+      <x:c r="AA23" s="14" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="X23" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y23" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z23" s="14" t="n">
+      <x:c r="AB23" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC23" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD23" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AA23" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AB23" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AC23" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AD23" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AE23" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4504,53 +4644,53 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM23" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AN23" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO23" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP23" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ23" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR23" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO23" s="14" t="n">
+      <x:c r="AS23" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP23" s="14" t="n">
+      <x:c r="AT23" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ23" s="14" t="n">
+      <x:c r="AU23" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR23" s="14" t="n">
+      <x:c r="AV23" s="14" t="n">
         <x:v>0.22</x:v>
       </x:c>
-      <x:c r="AS23" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT23" s="14" t="n">
+      <x:c r="AW23" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX23" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU23" s="14" t="n">
+      <x:c r="AY23" s="14" t="n">
         <x:v>0.45</x:v>
       </x:c>
-      <x:c r="AV23" s="14" t="n">
+      <x:c r="AZ23" s="14" t="n">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="AW23" s="14" t="n">
+      <x:c r="BA23" s="14" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="AX23" s="14" t="n">
+      <x:c r="BB23" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY23" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ23" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA23" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB23" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC23" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4563,7 +4703,19 @@
       <x:c r="BF23" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG23" s="15" t="str">
+      <x:c r="BG23" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH23" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI23" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ23" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK23" s="15" t="str">
         <x:v>data/artifacts/magic_ring.tres</x:v>
       </x:c>
     </x:row>
@@ -4580,73 +4732,65 @@
       <x:c r="D24" s="14" t="str">
         <x:v>左右交替短剑光，命中生成短促十字闪光。</x:v>
       </x:c>
-      <x:c r="E24" s="14" t="str">
+      <x:c r="E24" s="14" t="str"/>
+      <x:c r="F24" s="14" t="str"/>
+      <x:c r="G24" s="14" t="str"/>
+      <x:c r="H24" s="14" t="str"/>
+      <x:c r="I24" s="14" t="str">
         <x:v>每第三击变为X形双斩，额外剑光按secondary_damage_mult造成伤害。</x:v>
       </x:c>
-      <x:c r="F24" s="14" t="str">
+      <x:c r="J24" s="14" t="str">
         <x:v>1费基础剑修，正常范围、正常伤害、正常攻速。</x:v>
       </x:c>
-      <x:c r="G24" s="14" t="str">
+      <x:c r="K24" s="14" t="str">
         <x:v>trail_length, hit_flash_duration, secondary_damage_mult</x:v>
       </x:c>
-      <x:c r="H24" s="14" t="str">
+      <x:c r="L24" s="14" t="str">
         <x:v>剑修</x:v>
       </x:c>
-      <x:c r="I24" s="14" t="str">
+      <x:c r="M24" s="14" t="str">
         <x:v>金</x:v>
       </x:c>
-      <x:c r="J24" s="14" t="str">
+      <x:c r="N24" s="14" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="K24" s="14" t="n">
+      <x:c r="O24" s="14" t="n">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="L24" s="14" t="str"/>
-      <x:c r="M24" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N24" s="14" t="str">
-        <x:v>melee</x:v>
-      </x:c>
-      <x:c r="O24" s="14" t="str">
-        <x:v>slash</x:v>
       </x:c>
       <x:c r="P24" s="14" t="str"/>
       <x:c r="Q24" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R24" s="14" t="str">
+        <x:v>melee</x:v>
+      </x:c>
+      <x:c r="S24" s="14" t="str">
+        <x:v>slash</x:v>
+      </x:c>
+      <x:c r="T24" s="14" t="str"/>
+      <x:c r="U24" s="14" t="n">
         <x:v>19.5</x:v>
       </x:c>
-      <x:c r="R24" s="14" t="n">
+      <x:c r="V24" s="14" t="n">
         <x:v>0.54</x:v>
       </x:c>
-      <x:c r="S24" s="14" t="n">
+      <x:c r="W24" s="14" t="n">
         <x:v>36.11</x:v>
       </x:c>
-      <x:c r="T24" s="14" t="n">
+      <x:c r="X24" s="14" t="n">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="U24" s="14" t="n">
+      <x:c r="Y24" s="14" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="V24" s="14" t="n">
+      <x:c r="Z24" s="14" t="n">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="W24" s="14" t="n">
+      <x:c r="AA24" s="14" t="n">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="X24" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y24" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z24" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA24" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB24" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC24" s="14" t="n">
         <x:v>0</x:v>
@@ -4679,53 +4823,53 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM24" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AN24" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO24" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP24" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ24" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR24" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO24" s="14" t="n">
+      <x:c r="AS24" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP24" s="14" t="n">
+      <x:c r="AT24" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ24" s="14" t="n">
+      <x:c r="AU24" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR24" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS24" s="14" t="n">
+      <x:c r="AV24" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AW24" s="14" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="AT24" s="14" t="n">
+      <x:c r="AX24" s="14" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="AU24" s="14" t="n">
+      <x:c r="AY24" s="14" t="n">
         <x:v>0.65</x:v>
       </x:c>
-      <x:c r="AV24" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW24" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX24" s="14" t="n">
+      <x:c r="AZ24" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA24" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BB24" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY24" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ24" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA24" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB24" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC24" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4738,7 +4882,19 @@
       <x:c r="BF24" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG24" s="15" t="str">
+      <x:c r="BG24" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH24" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI24" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ24" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK24" s="15" t="str">
         <x:v>data/artifacts/one_handed_sword.tres</x:v>
       </x:c>
     </x:row>
@@ -4756,77 +4912,69 @@
       <x:c r="E25" s="14" t="str"/>
       <x:c r="F25" s="14" t="str"/>
       <x:c r="G25" s="14" t="str"/>
-      <x:c r="H25" s="14" t="str">
+      <x:c r="H25" s="14" t="str"/>
+      <x:c r="I25" s="14" t="str"/>
+      <x:c r="J25" s="14" t="str"/>
+      <x:c r="K25" s="14" t="str"/>
+      <x:c r="L25" s="14" t="str">
         <x:v>体修</x:v>
       </x:c>
-      <x:c r="I25" s="14" t="str">
+      <x:c r="M25" s="14" t="str">
         <x:v>木</x:v>
       </x:c>
-      <x:c r="J25" s="14" t="str">
+      <x:c r="N25" s="14" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="K25" s="14" t="n">
+      <x:c r="O25" s="14" t="n">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="L25" s="14" t="str"/>
-      <x:c r="M25" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N25" s="14" t="str">
-        <x:v>melee</x:v>
-      </x:c>
-      <x:c r="O25" s="14" t="str">
-        <x:v>cone</x:v>
       </x:c>
       <x:c r="P25" s="14" t="str"/>
       <x:c r="Q25" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R25" s="14" t="str">
+        <x:v>melee</x:v>
+      </x:c>
+      <x:c r="S25" s="14" t="str">
+        <x:v>cone</x:v>
+      </x:c>
+      <x:c r="T25" s="14" t="str"/>
+      <x:c r="U25" s="14" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R25" s="14" t="n">
+      <x:c r="V25" s="14" t="n">
         <x:v>0.61</x:v>
       </x:c>
-      <x:c r="S25" s="14" t="n">
+      <x:c r="W25" s="14" t="n">
         <x:v>27.87</x:v>
       </x:c>
-      <x:c r="T25" s="14" t="n">
+      <x:c r="X25" s="14" t="n">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="U25" s="14" t="n">
+      <x:c r="Y25" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="V25" s="14" t="n">
+      <x:c r="Z25" s="14" t="n">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="W25" s="14" t="n">
+      <x:c r="AA25" s="14" t="n">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="X25" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y25" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z25" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA25" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB25" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC25" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD25" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE25" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF25" s="14" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="AC25" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AD25" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AE25" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF25" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AG25" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4846,53 +4994,53 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM25" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AN25" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO25" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP25" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ25" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR25" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO25" s="14" t="n">
+      <x:c r="AS25" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP25" s="14" t="n">
+      <x:c r="AT25" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ25" s="14" t="n">
+      <x:c r="AU25" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR25" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS25" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT25" s="14" t="n">
+      <x:c r="AV25" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AW25" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX25" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU25" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AV25" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW25" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX25" s="14" t="n">
+      <x:c r="AY25" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AZ25" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA25" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BB25" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY25" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ25" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA25" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB25" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC25" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4905,7 +5053,19 @@
       <x:c r="BF25" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG25" s="15" t="str">
+      <x:c r="BG25" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH25" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI25" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ25" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK25" s="15" t="str">
         <x:v>data/artifacts/palm.tres</x:v>
       </x:c>
     </x:row>
@@ -4919,68 +5079,76 @@
       <x:c r="C26" s="14" t="str">
         <x:v>召唤没有仇恨值的毒虫群。毒虫不会被敌人主动攻击，但仍会被范围伤害波及。毒虫近战撕咬并附加中毒。</x:v>
       </x:c>
-      <x:c r="D26" s="14" t="str"/>
-      <x:c r="E26" s="14" t="str"/>
-      <x:c r="F26" s="14" t="str"/>
-      <x:c r="G26" s="14" t="str"/>
+      <x:c r="D26" s="14" t="str">
+        <x:v>毒色召唤纹路中爬出虫群，低频批量索敌并按槽位分配目标，软分离围攻撕咬并附加不无限叠加中毒。</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="str">
+        <x:v>低频分批索敌；按槽位分配最近目标；软分离围攻，避免全员完全重叠。</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="str">
+        <x:v>无仇恨，敌人不会主动锁定。</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="str">
+        <x:v>可被范围伤害或非锁定伤害波及。</x:v>
+      </x:c>
       <x:c r="H26" s="14" t="str">
+        <x:v>沿用现有毒虫补充逻辑；不为每只虫单独无限重生。</x:v>
+      </x:c>
+      <x:c r="I26" s="14" t="str">
+        <x:v>数量额外增加；中毒敌人死亡触发小型毒爆，范围=poison_explosion_radius，伤害=poison_explosion_damage_mult，并受delayed_strike_count连锁上限约束。</x:v>
+      </x:c>
+      <x:c r="J26" s="14" t="str">
+        <x:v>5费虫潮数量压制，无仇恨但可被范围伤害波及，沿用现有补充规则。</x:v>
+      </x:c>
+      <x:c r="K26" s="14" t="str">
+        <x:v>summon_base_count, summon_combat_radius, poison_can_stack, poison_explosion_radius, poison_explosion_damage_mult, delayed_strike_count</x:v>
+      </x:c>
+      <x:c r="L26" s="14" t="str">
         <x:v>召唤</x:v>
       </x:c>
-      <x:c r="I26" s="14" t="str">
+      <x:c r="M26" s="14" t="str">
         <x:v>毒</x:v>
       </x:c>
-      <x:c r="J26" s="14" t="str">
+      <x:c r="N26" s="14" t="str">
         <x:v>仙宝</x:v>
       </x:c>
-      <x:c r="K26" s="14" t="n">
+      <x:c r="O26" s="14" t="n">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="L26" s="14" t="str"/>
-      <x:c r="M26" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N26" s="14" t="str">
-        <x:v>summon</x:v>
-      </x:c>
-      <x:c r="O26" s="14" t="str">
-        <x:v>stab</x:v>
       </x:c>
       <x:c r="P26" s="14" t="str"/>
       <x:c r="Q26" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R26" s="14" t="str">
+        <x:v>summon</x:v>
+      </x:c>
+      <x:c r="S26" s="14" t="str">
+        <x:v>stab</x:v>
+      </x:c>
+      <x:c r="T26" s="14" t="str"/>
+      <x:c r="U26" s="14" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="R26" s="14" t="n">
+      <x:c r="V26" s="14" t="n">
         <x:v>0.36</x:v>
       </x:c>
-      <x:c r="S26" s="14" t="n">
+      <x:c r="W26" s="14" t="n">
         <x:v>13.89</x:v>
       </x:c>
-      <x:c r="T26" s="14" t="n">
+      <x:c r="X26" s="14" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="U26" s="14" t="n">
+      <x:c r="Y26" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="V26" s="14" t="n">
+      <x:c r="Z26" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="W26" s="14" t="n">
+      <x:c r="AA26" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="X26" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y26" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z26" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA26" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB26" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC26" s="14" t="n">
         <x:v>0</x:v>
@@ -4992,74 +5160,74 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AF26" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG26" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH26" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AI26" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AJ26" s="14" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AG26" s="14" t="n">
+      <x:c r="AK26" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AH26" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AI26" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AJ26" s="14" t="n">
+      <x:c r="AL26" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AM26" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AN26" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AK26" s="14" t="n">
+      <x:c r="AO26" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="AL26" s="14" t="n">
+      <x:c r="AP26" s="14" t="n">
         <x:v>9.5</x:v>
       </x:c>
-      <x:c r="AM26" s="14" t="n">
+      <x:c r="AQ26" s="14" t="n">
         <x:v>2.8</x:v>
       </x:c>
-      <x:c r="AN26" s="14" t="n">
+      <x:c r="AR26" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO26" s="14" t="n">
+      <x:c r="AS26" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP26" s="14" t="n">
+      <x:c r="AT26" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ26" s="14" t="n">
+      <x:c r="AU26" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR26" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS26" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT26" s="14" t="n">
+      <x:c r="AV26" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AW26" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX26" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU26" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AV26" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW26" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX26" s="14" t="n">
+      <x:c r="AY26" s="14" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="AZ26" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA26" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BB26" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY26" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ26" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA26" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB26" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC26" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5072,7 +5240,19 @@
       <x:c r="BF26" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG26" s="15" t="str">
+      <x:c r="BG26" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH26" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI26" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ26" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK26" s="15" t="str">
         <x:v>data/artifacts/poison_bug.tres</x:v>
       </x:c>
     </x:row>
@@ -5089,165 +5269,169 @@
       <x:c r="D27" s="14" t="str">
         <x:v>身侧浮现数根细毒针，短暂停顿后以极短间隔连续射出，命中附加非无限叠加中毒标记。</x:v>
       </x:c>
-      <x:c r="E27" s="14" t="str">
+      <x:c r="E27" s="14" t="str"/>
+      <x:c r="F27" s="14" t="str"/>
+      <x:c r="G27" s="14" t="str"/>
+      <x:c r="H27" s="14" t="str"/>
+      <x:c r="I27" s="14" t="str">
         <x:v>每delayed_strike_count次普通攻击追加一轮扇形针雨，数量=bounce_count，伤害按secondary_damage_mult。</x:v>
       </x:c>
-      <x:c r="F27" s="14" t="str">
+      <x:c r="J27" s="14" t="str">
         <x:v>2费高频低直伤，主要依靠中毒持续输出，不消耗生命。</x:v>
       </x:c>
-      <x:c r="G27" s="14" t="str">
+      <x:c r="K27" s="14" t="str">
         <x:v>count, delayed_strike_count, delayed_strike_interval, bounce_count, fan_angle, secondary_damage_mult, poison_can_stack</x:v>
       </x:c>
-      <x:c r="H27" s="14" t="str">
+      <x:c r="L27" s="14" t="str">
         <x:v>魔修</x:v>
       </x:c>
-      <x:c r="I27" s="14" t="str">
+      <x:c r="M27" s="14" t="str">
         <x:v>毒</x:v>
       </x:c>
-      <x:c r="J27" s="14" t="str">
+      <x:c r="N27" s="14" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="K27" s="14" t="n">
+      <x:c r="O27" s="14" t="n">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="L27" s="14" t="str"/>
-      <x:c r="M27" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N27" s="14" t="str">
-        <x:v>projectile</x:v>
-      </x:c>
-      <x:c r="O27" s="14" t="str">
-        <x:v>projectile</x:v>
       </x:c>
       <x:c r="P27" s="14" t="str"/>
       <x:c r="Q27" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R27" s="14" t="str">
+        <x:v>projectile</x:v>
+      </x:c>
+      <x:c r="S27" s="14" t="str">
+        <x:v>projectile</x:v>
+      </x:c>
+      <x:c r="T27" s="14" t="str"/>
+      <x:c r="U27" s="14" t="n">
         <x:v>9.5</x:v>
       </x:c>
-      <x:c r="R27" s="14" t="n">
+      <x:c r="V27" s="14" t="n">
         <x:v>0.46</x:v>
       </x:c>
-      <x:c r="S27" s="14" t="n">
+      <x:c r="W27" s="14" t="n">
         <x:v>20.65</x:v>
       </x:c>
-      <x:c r="T27" s="14" t="n">
+      <x:c r="X27" s="14" t="n">
         <x:v>500</x:v>
       </x:c>
-      <x:c r="U27" s="14" t="n">
+      <x:c r="Y27" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="V27" s="14" t="n">
+      <x:c r="Z27" s="14" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="W27" s="14" t="n">
+      <x:c r="AA27" s="14" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="X27" s="14" t="n">
+      <x:c r="AB27" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="Y27" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z27" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA27" s="14" t="n">
+      <x:c r="AC27" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD27" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE27" s="14" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="AB27" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AC27" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AD27" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AE27" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AF27" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG27" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH27" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AI27" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AJ27" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AG27" s="14" t="n">
+      <x:c r="AK27" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AH27" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AI27" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AJ27" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AK27" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AL27" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM27" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AN27" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO27" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP27" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ27" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR27" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO27" s="14" t="n">
+      <x:c r="AS27" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP27" s="14" t="n">
+      <x:c r="AT27" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ27" s="14" t="n">
+      <x:c r="AU27" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR27" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS27" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT27" s="14" t="n">
+      <x:c r="AV27" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AW27" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX27" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU27" s="14" t="n">
+      <x:c r="AY27" s="14" t="n">
         <x:v>0.55</x:v>
       </x:c>
-      <x:c r="AV27" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW27" s="14" t="n">
+      <x:c r="AZ27" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA27" s="14" t="n">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="AX27" s="14" t="n">
+      <x:c r="BB27" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY27" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ27" s="14" t="n">
+      <x:c r="BC27" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD27" s="14" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="BA27" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB27" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BC27" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BD27" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BE27" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="BF27" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG27" s="15" t="str">
+      <x:c r="BG27" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH27" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI27" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ27" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK27" s="15" t="str">
         <x:v>data/artifacts/poison_needle.tres</x:v>
       </x:c>
     </x:row>
@@ -5265,80 +5449,72 @@
       <x:c r="E28" s="14" t="str"/>
       <x:c r="F28" s="14" t="str"/>
       <x:c r="G28" s="14" t="str"/>
-      <x:c r="H28" s="14" t="str">
+      <x:c r="H28" s="14" t="str"/>
+      <x:c r="I28" s="14" t="str"/>
+      <x:c r="J28" s="14" t="str"/>
+      <x:c r="K28" s="14" t="str"/>
+      <x:c r="L28" s="14" t="str">
         <x:v>体修</x:v>
       </x:c>
-      <x:c r="I28" s="14" t="str">
+      <x:c r="M28" s="14" t="str">
         <x:v>雷</x:v>
       </x:c>
-      <x:c r="J28" s="14" t="str">
+      <x:c r="N28" s="14" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="K28" s="14" t="n">
+      <x:c r="O28" s="14" t="n">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="L28" s="14" t="str"/>
-      <x:c r="M28" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N28" s="14" t="str">
-        <x:v>melee</x:v>
-      </x:c>
-      <x:c r="O28" s="14" t="str">
-        <x:v>cone</x:v>
       </x:c>
       <x:c r="P28" s="14" t="str"/>
       <x:c r="Q28" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R28" s="14" t="str">
+        <x:v>melee</x:v>
+      </x:c>
+      <x:c r="S28" s="14" t="str">
+        <x:v>cone</x:v>
+      </x:c>
+      <x:c r="T28" s="14" t="str"/>
+      <x:c r="U28" s="14" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="R28" s="14" t="n">
+      <x:c r="V28" s="14" t="n">
         <x:v>1.11</x:v>
       </x:c>
-      <x:c r="S28" s="14" t="n">
+      <x:c r="W28" s="14" t="n">
         <x:v>29.73</x:v>
       </x:c>
-      <x:c r="T28" s="14" t="n">
+      <x:c r="X28" s="14" t="n">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="U28" s="14" t="n">
+      <x:c r="Y28" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="V28" s="14" t="n">
+      <x:c r="Z28" s="14" t="n">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="W28" s="14" t="n">
+      <x:c r="AA28" s="14" t="n">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="X28" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y28" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z28" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA28" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB28" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC28" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD28" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE28" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF28" s="14" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="AC28" s="14" t="n">
+      <x:c r="AG28" s="14" t="n">
         <x:v>0.35</x:v>
       </x:c>
-      <x:c r="AD28" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AE28" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF28" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AG28" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AH28" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5355,53 +5531,53 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM28" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AN28" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO28" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP28" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ28" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR28" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO28" s="14" t="n">
+      <x:c r="AS28" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP28" s="14" t="n">
+      <x:c r="AT28" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ28" s="14" t="n">
+      <x:c r="AU28" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR28" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS28" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT28" s="14" t="n">
+      <x:c r="AV28" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AW28" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX28" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU28" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AV28" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW28" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX28" s="14" t="n">
+      <x:c r="AY28" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AZ28" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA28" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BB28" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY28" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ28" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA28" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB28" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC28" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5414,7 +5590,19 @@
       <x:c r="BF28" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG28" s="15" t="str">
+      <x:c r="BG28" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH28" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI28" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ28" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK28" s="15" t="str">
         <x:v>data/artifacts/roar.tres</x:v>
       </x:c>
     </x:row>
@@ -5431,165 +5619,169 @@
       <x:c r="D29" s="14" t="str">
         <x:v>长柄镰刀后拉后大弧挥砍，仅外圈镰刃环带造成伤害，命中抽出生命丝线回血。</x:v>
       </x:c>
-      <x:c r="E29" s="14" t="str">
+      <x:c r="E29" s="14" t="str"/>
+      <x:c r="F29" s="14" t="str"/>
+      <x:c r="G29" s="14" t="str"/>
+      <x:c r="H29" s="14" t="str"/>
+      <x:c r="I29" s="14" t="str">
         <x:v>第一轮结束后按secondary_delay反向再挥一轮，第二轮伤害按secondary_damage_mult。</x:v>
       </x:c>
-      <x:c r="F29" s="14" t="str">
+      <x:c r="J29" s="14" t="str">
         <x:v>4费中近距离外圈收割和续航，回血按实际伤害比例并受shield_max单轮上限限制。</x:v>
       </x:c>
-      <x:c r="G29" s="14" t="str">
+      <x:c r="K29" s="14" t="str">
         <x:v>fan_angle, length, width, heal_amount, shield_max, secondary_damage_mult, secondary_delay</x:v>
       </x:c>
-      <x:c r="H29" s="14" t="str">
+      <x:c r="L29" s="14" t="str">
         <x:v>魔修</x:v>
       </x:c>
-      <x:c r="I29" s="14" t="str">
+      <x:c r="M29" s="14" t="str">
         <x:v>水</x:v>
       </x:c>
-      <x:c r="J29" s="14" t="str">
+      <x:c r="N29" s="14" t="str">
         <x:v>灵宝</x:v>
       </x:c>
-      <x:c r="K29" s="14" t="n">
+      <x:c r="O29" s="14" t="n">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="L29" s="14" t="str"/>
-      <x:c r="M29" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N29" s="14" t="str">
-        <x:v>melee</x:v>
-      </x:c>
-      <x:c r="O29" s="14" t="str">
-        <x:v>head_slash</x:v>
       </x:c>
       <x:c r="P29" s="14" t="str"/>
       <x:c r="Q29" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R29" s="14" t="str">
+        <x:v>melee</x:v>
+      </x:c>
+      <x:c r="S29" s="14" t="str">
+        <x:v>head_slash</x:v>
+      </x:c>
+      <x:c r="T29" s="14" t="str"/>
+      <x:c r="U29" s="14" t="n">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="R29" s="14" t="n">
+      <x:c r="V29" s="14" t="n">
         <x:v>1.04</x:v>
       </x:c>
-      <x:c r="S29" s="14" t="n">
+      <x:c r="W29" s="14" t="n">
         <x:v>64.42</x:v>
       </x:c>
-      <x:c r="T29" s="14" t="n">
+      <x:c r="X29" s="14" t="n">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="U29" s="14" t="n">
+      <x:c r="Y29" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="V29" s="14" t="n">
+      <x:c r="Z29" s="14" t="n">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="W29" s="14" t="n">
+      <x:c r="AA29" s="14" t="n">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="X29" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB29" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF29" s="14" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="AC29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AD29" s="14" t="n">
+      <x:c r="AG29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH29" s="14" t="n">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="AE29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AG29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AH29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AI29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AJ29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AM29" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AJ29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AK29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AL29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AM29" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AN29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ29" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR29" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO29" s="14" t="n">
+      <x:c r="AS29" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP29" s="14" t="n">
+      <x:c r="AT29" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ29" s="14" t="n">
+      <x:c r="AU29" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT29" s="14" t="n">
+      <x:c r="AV29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AW29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX29" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU29" s="14" t="n">
+      <x:c r="AY29" s="14" t="n">
         <x:v>0.58</x:v>
       </x:c>
-      <x:c r="AV29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW29" s="14" t="n">
+      <x:c r="AZ29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA29" s="14" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="AX29" s="14" t="n">
+      <x:c r="BB29" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ29" s="14" t="n">
+      <x:c r="BC29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BD29" s="14" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="BA29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BC29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BD29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BE29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BF29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BG29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI29" s="14" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="BF29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BG29" s="15" t="str">
+      <x:c r="BJ29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK29" s="15" t="str">
         <x:v>data/artifacts/scythe.tres</x:v>
       </x:c>
     </x:row>
@@ -5606,154 +5798,146 @@
       <x:c r="D30" s="14" t="str">
         <x:v>招魂幡连接多名敌人，魂线按tick_interval固定脉冲压制和伤害；被本轮连接/伤害过的敌人死亡生成幽魂冲击。</x:v>
       </x:c>
-      <x:c r="E30" s="14" t="str">
+      <x:c r="E30" s="14" t="str"/>
+      <x:c r="F30" s="14" t="str"/>
+      <x:c r="G30" s="14" t="str"/>
+      <x:c r="H30" s="14" t="str"/>
+      <x:c r="I30" s="14" t="str">
         <x:v>连接数提升到count，幽魂体积和爆炸范围按secondary_radius放大；累计delayed_strike_count只幽魂释放魂波。</x:v>
       </x:c>
-      <x:c r="F30" s="14" t="str">
+      <x:c r="J30" s="14" t="str">
         <x:v>5费多目标持续压制和拘魂清场，幽魂数量、寿命和搜索范围均有限制。</x:v>
       </x:c>
-      <x:c r="G30" s="14" t="str">
+      <x:c r="K30" s="14" t="str">
         <x:v>max_targets, count, summon_base_count, summon_respawn_time, summon_combat_radius, secondary_damage_mult, secondary_radius, delayed_strike_count, poison_explosion_damage_mult</x:v>
       </x:c>
-      <x:c r="H30" s="14" t="str">
+      <x:c r="L30" s="14" t="str">
         <x:v>魔修</x:v>
       </x:c>
-      <x:c r="I30" s="14" t="str">
+      <x:c r="M30" s="14" t="str">
         <x:v>木</x:v>
       </x:c>
-      <x:c r="J30" s="14" t="str">
+      <x:c r="N30" s="14" t="str">
         <x:v>仙宝</x:v>
       </x:c>
-      <x:c r="K30" s="14" t="n">
+      <x:c r="O30" s="14" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L30" s="14" t="str"/>
-      <x:c r="M30" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N30" s="14" t="str">
+      <x:c r="P30" s="14" t="str"/>
+      <x:c r="Q30" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R30" s="14" t="str">
         <x:v>soul_banner</x:v>
       </x:c>
-      <x:c r="O30" s="14" t="str">
+      <x:c r="S30" s="14" t="str">
         <x:v>beam</x:v>
       </x:c>
-      <x:c r="P30" s="14" t="str">
+      <x:c r="T30" s="14" t="str">
         <x:v>slow</x:v>
       </x:c>
-      <x:c r="Q30" s="14" t="n">
+      <x:c r="U30" s="14" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="R30" s="14" t="n">
+      <x:c r="V30" s="14" t="n">
         <x:v>2.29</x:v>
       </x:c>
-      <x:c r="S30" s="14" t="n">
+      <x:c r="W30" s="14" t="n">
         <x:v>10.04</x:v>
       </x:c>
-      <x:c r="T30" s="14" t="n">
+      <x:c r="X30" s="14" t="n">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="U30" s="14" t="n">
+      <x:c r="Y30" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="V30" s="14" t="n">
+      <x:c r="Z30" s="14" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="W30" s="14" t="n">
+      <x:c r="AA30" s="14" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="X30" s="14" t="n">
+      <x:c r="AB30" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="Y30" s="14" t="n">
+      <x:c r="AC30" s="14" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="Z30" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA30" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AB30" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AC30" s="14" t="n">
+      <x:c r="AD30" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE30" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF30" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG30" s="14" t="n">
         <x:v>0.45</x:v>
       </x:c>
-      <x:c r="AD30" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AE30" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF30" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AG30" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AH30" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AI30" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AJ30" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK30" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL30" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AM30" s="14" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="AJ30" s="14" t="n">
+      <x:c r="AN30" s="14" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="AK30" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AL30" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AM30" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN30" s="14" t="n">
+      <x:c r="AO30" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP30" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ30" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR30" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO30" s="14" t="n">
+      <x:c r="AS30" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP30" s="14" t="n">
+      <x:c r="AT30" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ30" s="14" t="n">
+      <x:c r="AU30" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR30" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS30" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT30" s="14" t="n">
+      <x:c r="AV30" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AW30" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX30" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU30" s="14" t="n">
+      <x:c r="AY30" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AV30" s="14" t="n">
+      <x:c r="AZ30" s="14" t="n">
         <x:v>1.35</x:v>
       </x:c>
-      <x:c r="AW30" s="14" t="n">
+      <x:c r="BA30" s="14" t="n">
         <x:v>0.22</x:v>
       </x:c>
-      <x:c r="AX30" s="14" t="n">
+      <x:c r="BB30" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY30" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ30" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA30" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB30" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC30" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5766,7 +5950,19 @@
       <x:c r="BF30" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG30" s="15" t="str">
+      <x:c r="BG30" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH30" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI30" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ30" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK30" s="15" t="str">
         <x:v>data/artifacts/soul_banner.tres</x:v>
       </x:c>
     </x:row>
@@ -5780,68 +5976,76 @@
       <x:c r="C31" s="14" t="str">
         <x:v>召唤持续存在的近战傀儡，追击最近敌人并用近战挥砍。死亡后会在短时间后重生。</x:v>
       </x:c>
-      <x:c r="D31" s="14" t="str"/>
-      <x:c r="E31" s="14" t="str"/>
-      <x:c r="F31" s="14" t="str"/>
-      <x:c r="G31" s="14" t="str"/>
+      <x:c r="D31" s="14" t="str">
+        <x:v>玩家身旁召唤阵显形，木质几何人形落地后追击近敌，近战挥砍产生短刀光和命中闪光。</x:v>
+      </x:c>
+      <x:c r="E31" s="14" t="str">
+        <x:v>主动追击近敌；超过summon_return_radius优先返回玩家附近；轻量软分离。</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="str">
+        <x:v>有仇恨，可被敌人主动选择。</x:v>
+      </x:c>
+      <x:c r="G31" s="14" t="str">
+        <x:v>可受伤。</x:v>
+      </x:c>
       <x:c r="H31" s="14" t="str">
+        <x:v>死亡隐藏并禁用碰撞，显示重生印记，summon_respawn_time后在玩家附近满状态重生。</x:v>
+      </x:c>
+      <x:c r="I31" s="14" t="str">
+        <x:v>普通挥砍后按secondary_delay独立冷却触发短距离跃斩，落点按explosion_radius造成范围伤害。</x:v>
+      </x:c>
+      <x:c r="J31" s="14" t="str">
+        <x:v>1费基础前排近战输出，可被攻击，死亡后按summon_respawn_time重生。</x:v>
+      </x:c>
+      <x:c r="K31" s="14" t="str">
+        <x:v>summon_base_count, summon_hp, summon_attack, summon_attack_speed, summon_return_radius, secondary_damage_mult, secondary_radius, secondary_delay, explosion_radius</x:v>
+      </x:c>
+      <x:c r="L31" s="14" t="str">
         <x:v>召唤</x:v>
       </x:c>
-      <x:c r="I31" s="14" t="str">
+      <x:c r="M31" s="14" t="str">
         <x:v>木</x:v>
       </x:c>
-      <x:c r="J31" s="14" t="str">
+      <x:c r="N31" s="14" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="K31" s="14" t="n">
+      <x:c r="O31" s="14" t="n">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="L31" s="14" t="str"/>
-      <x:c r="M31" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N31" s="14" t="str">
-        <x:v>summon</x:v>
-      </x:c>
-      <x:c r="O31" s="14" t="str">
-        <x:v>slash</x:v>
       </x:c>
       <x:c r="P31" s="14" t="str"/>
       <x:c r="Q31" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R31" s="14" t="str">
+        <x:v>summon</x:v>
+      </x:c>
+      <x:c r="S31" s="14" t="str">
+        <x:v>slash</x:v>
+      </x:c>
+      <x:c r="T31" s="14" t="str"/>
+      <x:c r="U31" s="14" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="R31" s="14" t="n">
+      <x:c r="V31" s="14" t="n">
         <x:v>0.71</x:v>
       </x:c>
-      <x:c r="S31" s="14" t="n">
+      <x:c r="W31" s="14" t="n">
         <x:v>21.13</x:v>
       </x:c>
-      <x:c r="T31" s="14" t="n">
+      <x:c r="X31" s="14" t="n">
         <x:v>500</x:v>
       </x:c>
-      <x:c r="U31" s="14" t="n">
+      <x:c r="Y31" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="V31" s="14" t="n">
+      <x:c r="Z31" s="14" t="n">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="W31" s="14" t="n">
+      <x:c r="AA31" s="14" t="n">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="X31" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y31" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z31" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA31" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB31" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC31" s="14" t="n">
         <x:v>0</x:v>
@@ -5865,62 +6069,62 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AJ31" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AK31" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL31" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AM31" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AN31" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO31" s="14" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="AL31" s="14" t="n">
+      <x:c r="AP31" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="AM31" s="14" t="n">
+      <x:c r="AQ31" s="14" t="n">
         <x:v>1.4</x:v>
       </x:c>
-      <x:c r="AN31" s="14" t="n">
+      <x:c r="AR31" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO31" s="14" t="n">
+      <x:c r="AS31" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP31" s="14" t="n">
+      <x:c r="AT31" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ31" s="14" t="n">
+      <x:c r="AU31" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR31" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS31" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT31" s="14" t="n">
+      <x:c r="AV31" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AW31" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX31" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU31" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AV31" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW31" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX31" s="14" t="n">
+      <x:c r="AY31" s="14" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="AZ31" s="14" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="BA31" s="14" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="BB31" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY31" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ31" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA31" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB31" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC31" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5933,7 +6137,19 @@
       <x:c r="BF31" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG31" s="15" t="str">
+      <x:c r="BG31" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH31" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI31" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ31" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK31" s="15" t="str">
         <x:v>data/artifacts/sword_puppet.tres</x:v>
       </x:c>
     </x:row>
@@ -5951,66 +6167,58 @@
       <x:c r="E32" s="14" t="str"/>
       <x:c r="F32" s="14" t="str"/>
       <x:c r="G32" s="14" t="str"/>
-      <x:c r="H32" s="14" t="str">
+      <x:c r="H32" s="14" t="str"/>
+      <x:c r="I32" s="14" t="str"/>
+      <x:c r="J32" s="14" t="str"/>
+      <x:c r="K32" s="14" t="str"/>
+      <x:c r="L32" s="14" t="str">
         <x:v>体修</x:v>
       </x:c>
-      <x:c r="I32" s="14" t="str">
+      <x:c r="M32" s="14" t="str">
         <x:v>金</x:v>
       </x:c>
-      <x:c r="J32" s="14" t="str">
+      <x:c r="N32" s="14" t="str">
         <x:v>灵宝</x:v>
       </x:c>
-      <x:c r="K32" s="14" t="n">
+      <x:c r="O32" s="14" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="L32" s="14" t="str"/>
-      <x:c r="M32" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N32" s="14" t="str">
+      <x:c r="P32" s="14" t="str"/>
+      <x:c r="Q32" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R32" s="14" t="str">
         <x:v>formation</x:v>
       </x:c>
-      <x:c r="O32" s="14" t="str">
+      <x:c r="S32" s="14" t="str">
         <x:v>aura</x:v>
       </x:c>
-      <x:c r="P32" s="14" t="str">
+      <x:c r="T32" s="14" t="str">
         <x:v>counter_damage</x:v>
       </x:c>
-      <x:c r="Q32" s="14" t="n">
+      <x:c r="U32" s="14" t="n">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="R32" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S32" s="14" t="n">
+      <x:c r="V32" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W32" s="14" t="n">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="T32" s="14" t="n">
+      <x:c r="X32" s="14" t="n">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="U32" s="14" t="n">
+      <x:c r="Y32" s="14" t="n">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="V32" s="14" t="n">
+      <x:c r="Z32" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="W32" s="14" t="n">
+      <x:c r="AA32" s="14" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="X32" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y32" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z32" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA32" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB32" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC32" s="14" t="n">
         <x:v>0</x:v>
@@ -6043,53 +6251,53 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM32" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AN32" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO32" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP32" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ32" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR32" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO32" s="14" t="n">
+      <x:c r="AS32" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP32" s="14" t="n">
+      <x:c r="AT32" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ32" s="14" t="n">
+      <x:c r="AU32" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR32" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS32" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT32" s="14" t="n">
+      <x:c r="AV32" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AW32" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX32" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU32" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AV32" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW32" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX32" s="14" t="n">
+      <x:c r="AY32" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AZ32" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA32" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BB32" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY32" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ32" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA32" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB32" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC32" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -6102,7 +6310,19 @@
       <x:c r="BF32" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG32" s="15" t="str">
+      <x:c r="BG32" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH32" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI32" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ32" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK32" s="15" t="str">
         <x:v>data/artifacts/thorn_armor.tres</x:v>
       </x:c>
     </x:row>
@@ -6116,68 +6336,76 @@
       <x:c r="C33" s="14" t="str">
         <x:v>召唤固定炮台自动索敌并发射爆炸炮弹。玩家离开过远时，炮台会延迟重新部署到玩家附近。</x:v>
       </x:c>
-      <x:c r="D33" s="14" t="str"/>
-      <x:c r="E33" s="14" t="str"/>
-      <x:c r="F33" s="14" t="str"/>
-      <x:c r="G33" s="14" t="str"/>
+      <x:c r="D33" s="14" t="str">
+        <x:v>地面部署阵后固定升起，炮管锁敌蓄能发射爆炸炮弹；离玩家超过summon_return_radius后按secondary_delay重新部署。</x:v>
+      </x:c>
+      <x:c r="E33" s="14" t="str">
+        <x:v>固定不移动；自动索敌；玩家离开过远后收起并延迟重新部署。</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="str">
+        <x:v>有仇恨，保持当前项目默认可被敌人选择。</x:v>
+      </x:c>
+      <x:c r="G33" s="14" t="str">
+        <x:v>可受伤。</x:v>
+      </x:c>
       <x:c r="H33" s="14" t="str">
+        <x:v>沿用召唤物死亡/重生；另有过远重新部署逻辑。</x:v>
+      </x:c>
+      <x:c r="I33" s="14" t="str">
+        <x:v>增加副炮口，每次攻击极短间隔追加第二枚炮弹，副炮按secondary_damage_mult造成伤害并优先不同目标。</x:v>
+      </x:c>
+      <x:c r="J33" s="14" t="str">
+        <x:v>3费固定远程范围火力，默认可受伤，重新部署期间不攻击。</x:v>
+      </x:c>
+      <x:c r="K33" s="14" t="str">
+        <x:v>summon_return_radius, secondary_delay, explosion_radius, delayed_strike_interval, secondary_damage_mult</x:v>
+      </x:c>
+      <x:c r="L33" s="14" t="str">
         <x:v>召唤</x:v>
       </x:c>
-      <x:c r="I33" s="14" t="str">
+      <x:c r="M33" s="14" t="str">
         <x:v>火</x:v>
       </x:c>
-      <x:c r="J33" s="14" t="str">
+      <x:c r="N33" s="14" t="str">
         <x:v>灵器</x:v>
       </x:c>
-      <x:c r="K33" s="14" t="n">
+      <x:c r="O33" s="14" t="n">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="L33" s="14" t="str"/>
-      <x:c r="M33" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N33" s="14" t="str">
-        <x:v>summon</x:v>
-      </x:c>
-      <x:c r="O33" s="14" t="str">
-        <x:v>projectile</x:v>
       </x:c>
       <x:c r="P33" s="14" t="str"/>
       <x:c r="Q33" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R33" s="14" t="str">
+        <x:v>summon</x:v>
+      </x:c>
+      <x:c r="S33" s="14" t="str">
+        <x:v>projectile</x:v>
+      </x:c>
+      <x:c r="T33" s="14" t="str"/>
+      <x:c r="U33" s="14" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="R33" s="14" t="n">
+      <x:c r="V33" s="14" t="n">
         <x:v>0.89</x:v>
       </x:c>
-      <x:c r="S33" s="14" t="n">
+      <x:c r="W33" s="14" t="n">
         <x:v>20.22</x:v>
       </x:c>
-      <x:c r="T33" s="14" t="n">
+      <x:c r="X33" s="14" t="n">
         <x:v>700</x:v>
       </x:c>
-      <x:c r="U33" s="14" t="n">
+      <x:c r="Y33" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="V33" s="14" t="n">
+      <x:c r="Z33" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="W33" s="14" t="n">
+      <x:c r="AA33" s="14" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="X33" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y33" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z33" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA33" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB33" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC33" s="14" t="n">
         <x:v>0</x:v>
@@ -6201,62 +6429,62 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AJ33" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AK33" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL33" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AM33" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AN33" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO33" s="14" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="AL33" s="14" t="n">
+      <x:c r="AP33" s="14" t="n">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="AM33" s="14" t="n">
+      <x:c r="AQ33" s="14" t="n">
         <x:v>1.12</x:v>
       </x:c>
-      <x:c r="AN33" s="14" t="n">
+      <x:c r="AR33" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO33" s="14" t="n">
+      <x:c r="AS33" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP33" s="14" t="n">
+      <x:c r="AT33" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ33" s="14" t="n">
+      <x:c r="AU33" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR33" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS33" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT33" s="14" t="n">
+      <x:c r="AV33" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AW33" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX33" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU33" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AV33" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW33" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX33" s="14" t="n">
+      <x:c r="AY33" s="14" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="AZ33" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA33" s="14" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BB33" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY33" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ33" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA33" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB33" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC33" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -6269,7 +6497,19 @@
       <x:c r="BF33" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG33" s="15" t="str">
+      <x:c r="BG33" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH33" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI33" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ33" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK33" s="15" t="str">
         <x:v>data/artifacts/turret.tres</x:v>
       </x:c>
     </x:row>
@@ -6286,86 +6526,78 @@
       <x:c r="D34" s="17" t="str">
         <x:v>半透明大剑影短蓄力后重劈，落点保留主剑痕和环形冲击痕。</x:v>
       </x:c>
-      <x:c r="E34" s="17" t="str">
+      <x:c r="E34" s="17" t="str"/>
+      <x:c r="F34" s="17" t="str"/>
+      <x:c r="G34" s="17" t="str"/>
+      <x:c r="H34" s="17" t="str"/>
+      <x:c r="I34" s="17" t="str">
         <x:v>剑痕约0.5秒后亮起并二次爆裂。</x:v>
       </x:c>
-      <x:c r="F34" s="17" t="str">
+      <x:c r="J34" s="17" t="str">
         <x:v>2费低攻速高单次伤害，带前摇和厚重感。</x:v>
       </x:c>
-      <x:c r="G34" s="17" t="str">
+      <x:c r="K34" s="17" t="str">
         <x:v>windup_time, secondary_delay, secondary_radius, secondary_damage_mult, screen_shake_strength</x:v>
       </x:c>
-      <x:c r="H34" s="17" t="str">
+      <x:c r="L34" s="17" t="str">
         <x:v>剑修</x:v>
       </x:c>
-      <x:c r="I34" s="17" t="str">
+      <x:c r="M34" s="17" t="str">
         <x:v>土</x:v>
       </x:c>
-      <x:c r="J34" s="17" t="str">
+      <x:c r="N34" s="17" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="K34" s="17" t="n">
+      <x:c r="O34" s="17" t="n">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="L34" s="17" t="str"/>
-      <x:c r="M34" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N34" s="17" t="str">
-        <x:v>melee</x:v>
-      </x:c>
-      <x:c r="O34" s="17" t="str">
-        <x:v>slash</x:v>
       </x:c>
       <x:c r="P34" s="17" t="str"/>
       <x:c r="Q34" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R34" s="17" t="str">
+        <x:v>melee</x:v>
+      </x:c>
+      <x:c r="S34" s="17" t="str">
+        <x:v>slash</x:v>
+      </x:c>
+      <x:c r="T34" s="17" t="str"/>
+      <x:c r="U34" s="17" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="R34" s="17" t="n">
+      <x:c r="V34" s="17" t="n">
         <x:v>1.35</x:v>
       </x:c>
-      <x:c r="S34" s="17" t="n">
+      <x:c r="W34" s="17" t="n">
         <x:v>25.93</x:v>
       </x:c>
-      <x:c r="T34" s="17" t="n">
+      <x:c r="X34" s="17" t="n">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="U34" s="17" t="n">
+      <x:c r="Y34" s="17" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="V34" s="17" t="n">
+      <x:c r="Z34" s="17" t="n">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="W34" s="17" t="n">
+      <x:c r="AA34" s="17" t="n">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="X34" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y34" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z34" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA34" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB34" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC34" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD34" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE34" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF34" s="17" t="n">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="AC34" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AD34" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AE34" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF34" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AG34" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -6385,53 +6617,53 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM34" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AN34" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO34" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP34" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ34" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR34" s="17" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AO34" s="17" t="n">
+      <x:c r="AS34" s="17" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AP34" s="17" t="n">
+      <x:c r="AT34" s="17" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AQ34" s="17" t="n">
+      <x:c r="AU34" s="17" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AR34" s="17" t="n">
+      <x:c r="AV34" s="17" t="n">
         <x:v>0.24</x:v>
       </x:c>
-      <x:c r="AS34" s="17" t="n">
+      <x:c r="AW34" s="17" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="AT34" s="17" t="n">
+      <x:c r="AX34" s="17" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AU34" s="17" t="n">
+      <x:c r="AY34" s="17" t="n">
         <x:v>0.55</x:v>
       </x:c>
-      <x:c r="AV34" s="17" t="n">
+      <x:c r="AZ34" s="17" t="n">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="AW34" s="17" t="n">
+      <x:c r="BA34" s="17" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AX34" s="17" t="n">
+      <x:c r="BB34" s="17" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AY34" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ34" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA34" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB34" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BC34" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -6444,7 +6676,19 @@
       <x:c r="BF34" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BG34" s="18" t="str">
+      <x:c r="BG34" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH34" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI34" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ34" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BK34" s="18" t="str">
         <x:v>data/artifacts/two_handed_sword.tres</x:v>
       </x:c>
     </x:row>
@@ -8924,7 +9168,7 @@
         <x:v>61.85</x:v>
       </x:c>
       <x:c r="J76" s="14" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K76" s="14" t="n">
         <x:v>30</x:v>

--- a/docs/GameBalance.xlsx
+++ b/docs/GameBalance.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R329299f3b2e14651"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法宝总表" sheetId="2" r:id="Rb709be8a575445dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法宝星级预览" sheetId="3" r:id="R686af5ce4c914e59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命" sheetId="4" r:id="Ra4808ae1490e4e36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奇遇" sheetId="5" r:id="R07b9fed0caad4d66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊阈值" sheetId="6" r:id="R4d80e1bf4f354e49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济与修为" sheetId="7" r:id="R4d1f62df9f20493e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="Rfd1e972ae2744fbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法宝总表" sheetId="2" r:id="Ra603700321c1460a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法宝星级预览" sheetId="3" r:id="Rf6dc18897d804e05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命" sheetId="4" r:id="Rde401093ea46448f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奇遇" sheetId="5" r:id="Ra0e6ea25f12b459c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊阈值" sheetId="6" r:id="Rb80342351d274a5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济与修为" sheetId="7" r:id="R925b6596af0b4c47"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -476,7 +476,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B3" s="5" t="n">
-        <x:v>46200.80713267361</x:v>
+        <x:v>46200.98271164352</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -532,9 +532,9 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="16.25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16.25" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="45" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16.25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="45" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
@@ -545,16 +545,16 @@
     <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="15" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="15" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="10" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="15" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="15" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="10" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="15" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="15" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="15" hidden="0" customWidth="1"/>
     <x:col min="20" max="20" width="15" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="10" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="15" hidden="0" customWidth="1"/>
     <x:col min="22" max="22" width="10" hidden="0" customWidth="1"/>
     <x:col min="23" max="23" width="10" hidden="0" customWidth="1"/>
-    <x:col min="24" max="24" width="15" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="10" hidden="0" customWidth="1"/>
     <x:col min="25" max="25" width="15" hidden="0" customWidth="1"/>
     <x:col min="26" max="26" width="15" hidden="0" customWidth="1"/>
     <x:col min="27" max="27" width="15" hidden="0" customWidth="1"/>
@@ -593,7 +593,8 @@
     <x:col min="60" max="60" width="14.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="61" max="61" width="14.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="62" max="62" width="14.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="63" max="63" width="23.75" hidden="0" customWidth="1"/>
+    <x:col min="63" max="63" width="14.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="64" max="64" width="23.75" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
@@ -601,189 +602,192 @@
         <x:v>id</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
+        <x:v>原名称</x:v>
+      </x:c>
+      <x:c r="C1" s="11" t="str">
         <x:v>名称</x:v>
       </x:c>
-      <x:c r="C1" s="11" t="str">
+      <x:c r="D1" s="11" t="str">
         <x:v>描述</x:v>
       </x:c>
-      <x:c r="D1" s="11" t="str">
+      <x:c r="E1" s="11" t="str">
         <x:v>攻击表现</x:v>
       </x:c>
-      <x:c r="E1" s="11" t="str">
+      <x:c r="F1" s="11" t="str">
         <x:v>AI行为</x:v>
       </x:c>
-      <x:c r="F1" s="11" t="str">
+      <x:c r="G1" s="11" t="str">
         <x:v>是否有仇恨值</x:v>
       </x:c>
-      <x:c r="G1" s="11" t="str">
+      <x:c r="H1" s="11" t="str">
         <x:v>是否可受伤</x:v>
       </x:c>
-      <x:c r="H1" s="11" t="str">
+      <x:c r="I1" s="11" t="str">
         <x:v>死亡与重生规则</x:v>
       </x:c>
-      <x:c r="I1" s="11" t="str">
+      <x:c r="J1" s="11" t="str">
         <x:v>三星机制</x:v>
       </x:c>
-      <x:c r="J1" s="11" t="str">
+      <x:c r="K1" s="11" t="str">
         <x:v>战斗定位</x:v>
       </x:c>
-      <x:c r="K1" s="11" t="str">
+      <x:c r="L1" s="11" t="str">
         <x:v>新增关键字段</x:v>
       </x:c>
-      <x:c r="L1" s="11" t="str">
+      <x:c r="M1" s="11" t="str">
         <x:v>流派</x:v>
       </x:c>
-      <x:c r="M1" s="11" t="str">
+      <x:c r="N1" s="11" t="str">
         <x:v>属性</x:v>
       </x:c>
-      <x:c r="N1" s="11" t="str">
+      <x:c r="O1" s="11" t="str">
         <x:v>品阶</x:v>
       </x:c>
-      <x:c r="O1" s="11" t="str">
+      <x:c r="P1" s="11" t="str">
         <x:v>价格</x:v>
       </x:c>
-      <x:c r="P1" s="11" t="str">
+      <x:c r="Q1" s="11" t="str">
         <x:v>修为要求</x:v>
       </x:c>
-      <x:c r="Q1" s="11" t="str">
+      <x:c r="R1" s="11" t="str">
         <x:v>商店权重</x:v>
       </x:c>
-      <x:c r="R1" s="11" t="str">
+      <x:c r="S1" s="11" t="str">
         <x:v>模板</x:v>
       </x:c>
-      <x:c r="S1" s="11" t="str">
+      <x:c r="T1" s="11" t="str">
         <x:v>形状</x:v>
       </x:c>
-      <x:c r="T1" s="11" t="str">
+      <x:c r="U1" s="11" t="str">
         <x:v>效果类型</x:v>
       </x:c>
-      <x:c r="U1" s="11" t="str">
+      <x:c r="V1" s="11" t="str">
         <x:v>伤害</x:v>
       </x:c>
-      <x:c r="V1" s="11" t="str">
+      <x:c r="W1" s="11" t="str">
         <x:v>冷却秒</x:v>
       </x:c>
-      <x:c r="W1" s="11" t="str">
+      <x:c r="X1" s="11" t="str">
         <x:v>DPS估算</x:v>
       </x:c>
-      <x:c r="X1" s="11" t="str">
+      <x:c r="Y1" s="11" t="str">
         <x:v>范围</x:v>
       </x:c>
-      <x:c r="Y1" s="11" t="str">
+      <x:c r="Z1" s="11" t="str">
         <x:v>半径</x:v>
       </x:c>
-      <x:c r="Z1" s="11" t="str">
+      <x:c r="AA1" s="11" t="str">
         <x:v>宽度</x:v>
       </x:c>
-      <x:c r="AA1" s="11" t="str">
+      <x:c r="AB1" s="11" t="str">
         <x:v>长度</x:v>
       </x:c>
-      <x:c r="AB1" s="11" t="str">
+      <x:c r="AC1" s="11" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="AC1" s="11" t="str">
+      <x:c r="AD1" s="11" t="str">
         <x:v>最大目标</x:v>
       </x:c>
-      <x:c r="AD1" s="11" t="str">
+      <x:c r="AE1" s="11" t="str">
         <x:v>穿透</x:v>
       </x:c>
-      <x:c r="AE1" s="11" t="str">
+      <x:c r="AF1" s="11" t="str">
         <x:v>弹射</x:v>
       </x:c>
-      <x:c r="AF1" s="11" t="str">
+      <x:c r="AG1" s="11" t="str">
         <x:v>击退</x:v>
       </x:c>
-      <x:c r="AG1" s="11" t="str">
+      <x:c r="AH1" s="11" t="str">
         <x:v>减速</x:v>
       </x:c>
-      <x:c r="AH1" s="11" t="str">
+      <x:c r="AI1" s="11" t="str">
         <x:v>治疗</x:v>
       </x:c>
-      <x:c r="AI1" s="11" t="str">
+      <x:c r="AJ1" s="11" t="str">
         <x:v>护盾</x:v>
       </x:c>
-      <x:c r="AJ1" s="11" t="str">
+      <x:c r="AK1" s="11" t="str">
         <x:v>中毒DPS</x:v>
       </x:c>
-      <x:c r="AK1" s="11" t="str">
+      <x:c r="AL1" s="11" t="str">
         <x:v>中毒持续</x:v>
       </x:c>
-      <x:c r="AL1" s="11" t="str">
+      <x:c r="AM1" s="11" t="str">
         <x:v>生命消耗百分比</x:v>
       </x:c>
-      <x:c r="AM1" s="11" t="str">
+      <x:c r="AN1" s="11" t="str">
         <x:v>生命消耗固定</x:v>
       </x:c>
-      <x:c r="AN1" s="11" t="str">
+      <x:c r="AO1" s="11" t="str">
         <x:v>召唤数量</x:v>
       </x:c>
-      <x:c r="AO1" s="11" t="str">
+      <x:c r="AP1" s="11" t="str">
         <x:v>召唤生命</x:v>
       </x:c>
-      <x:c r="AP1" s="11" t="str">
+      <x:c r="AQ1" s="11" t="str">
         <x:v>召唤攻击</x:v>
       </x:c>
-      <x:c r="AQ1" s="11" t="str">
+      <x:c r="AR1" s="11" t="str">
         <x:v>召唤攻速</x:v>
       </x:c>
-      <x:c r="AR1" s="11" t="str">
+      <x:c r="AS1" s="11" t="str">
         <x:v>2星伤害倍率</x:v>
       </x:c>
-      <x:c r="AS1" s="11" t="str">
+      <x:c r="AT1" s="11" t="str">
         <x:v>2星冷却倍率</x:v>
       </x:c>
-      <x:c r="AT1" s="11" t="str">
+      <x:c r="AU1" s="11" t="str">
         <x:v>3星伤害倍率</x:v>
       </x:c>
-      <x:c r="AU1" s="11" t="str">
+      <x:c r="AV1" s="11" t="str">
         <x:v>3星冷却倍率</x:v>
       </x:c>
-      <x:c r="AV1" s="11" t="str">
+      <x:c r="AW1" s="11" t="str">
         <x:v>windup_time</x:v>
       </x:c>
-      <x:c r="AW1" s="11" t="str">
+      <x:c r="AX1" s="11" t="str">
         <x:v>trail_length</x:v>
       </x:c>
-      <x:c r="AX1" s="11" t="str">
+      <x:c r="AY1" s="11" t="str">
         <x:v>hit_flash_duration</x:v>
       </x:c>
-      <x:c r="AY1" s="11" t="str">
+      <x:c r="AZ1" s="11" t="str">
         <x:v>secondary_damage_mult</x:v>
       </x:c>
-      <x:c r="AZ1" s="11" t="str">
+      <x:c r="BA1" s="11" t="str">
         <x:v>secondary_radius</x:v>
       </x:c>
-      <x:c r="BA1" s="11" t="str">
+      <x:c r="BB1" s="11" t="str">
         <x:v>secondary_delay</x:v>
       </x:c>
-      <x:c r="BB1" s="11" t="str">
+      <x:c r="BC1" s="11" t="str">
         <x:v>side_projectile_damage_mult</x:v>
       </x:c>
-      <x:c r="BC1" s="11" t="str">
+      <x:c r="BD1" s="11" t="str">
         <x:v>return_speed</x:v>
       </x:c>
-      <x:c r="BD1" s="11" t="str">
+      <x:c r="BE1" s="11" t="str">
         <x:v>fan_angle</x:v>
       </x:c>
-      <x:c r="BE1" s="11" t="str">
+      <x:c r="BF1" s="11" t="str">
         <x:v>converge_speed</x:v>
       </x:c>
-      <x:c r="BF1" s="11" t="str">
+      <x:c r="BG1" s="11" t="str">
         <x:v>self_rotation_speed</x:v>
       </x:c>
-      <x:c r="BG1" s="11" t="str">
+      <x:c r="BH1" s="11" t="str">
         <x:v>reveal_time</x:v>
       </x:c>
-      <x:c r="BH1" s="11" t="str">
+      <x:c r="BI1" s="11" t="str">
         <x:v>pause_time</x:v>
       </x:c>
-      <x:c r="BI1" s="11" t="str">
+      <x:c r="BJ1" s="11" t="str">
         <x:v>sweep_rotation_speed</x:v>
       </x:c>
-      <x:c r="BJ1" s="11" t="str">
+      <x:c r="BK1" s="11" t="str">
         <x:v>screen_shake_strength</x:v>
       </x:c>
-      <x:c r="BK1" s="12" t="str">
+      <x:c r="BL1" s="12" t="str">
         <x:v>来源</x:v>
       </x:c>
     </x:row>
@@ -791,83 +795,81 @@
       <x:c r="A2" s="13" t="str">
         <x:v>blood_slash</x:v>
       </x:c>
-      <x:c r="B2" s="14" t="str">
+      <x:c r="B2" s="14" t="str"/>
+      <x:c r="C2" s="14" t="str">
         <x:v>血斩</x:v>
       </x:c>
-      <x:c r="C2" s="14" t="str">
+      <x:c r="D2" s="14" t="str">
         <x:v>发射宽大的血色剑气。攻击消耗3点生命，生命低于30%时不消耗；击杀敌人回复1点生命。</x:v>
       </x:c>
-      <x:c r="D2" s="14" t="str">
+      <x:c r="E2" s="14" t="str">
         <x:v>血流压缩成宽大弯月血刃，蓄力后直线飞出，沿途穿透并留下残月血色轨迹。</x:v>
       </x:c>
-      <x:c r="E2" s="14" t="str"/>
       <x:c r="F2" s="14" t="str"/>
       <x:c r="G2" s="14" t="str"/>
       <x:c r="H2" s="14" t="str"/>
-      <x:c r="I2" s="14" t="str">
+      <x:c r="I2" s="14" t="str"/>
+      <x:c r="J2" s="14" t="str">
         <x:v>到达最大距离后按pause_time停顿，再以return_speed返回；去程和回程分别维护命中记录。</x:v>
       </x:c>
-      <x:c r="J2" s="14" t="str">
+      <x:c r="K2" s="14" t="str">
         <x:v>2费宽直线清线，消耗生命，击杀回血。</x:v>
       </x:c>
-      <x:c r="K2" s="14" t="str">
+      <x:c r="L2" s="14" t="str">
         <x:v>life_cost_flat, life_cost_min_hp_ratio, kill_heal_amount, windup_time, return_speed, pause_time, secondary_damage_mult</x:v>
       </x:c>
-      <x:c r="L2" s="14" t="str">
+      <x:c r="M2" s="14" t="str">
         <x:v>魔修</x:v>
       </x:c>
-      <x:c r="M2" s="14" t="str">
+      <x:c r="N2" s="14" t="str">
         <x:v>雷</x:v>
       </x:c>
-      <x:c r="N2" s="14" t="str">
+      <x:c r="O2" s="14" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="O2" s="14" t="n">
+      <x:c r="P2" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="P2" s="14" t="str"/>
-      <x:c r="Q2" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R2" s="14" t="str">
-        <x:v>projectile</x:v>
+      <x:c r="Q2" s="14" t="str"/>
+      <x:c r="R2" s="14" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="S2" s="14" t="str">
         <x:v>projectile</x:v>
       </x:c>
-      <x:c r="T2" s="14" t="str"/>
-      <x:c r="U2" s="14" t="n">
+      <x:c r="T2" s="14" t="str">
+        <x:v>projectile</x:v>
+      </x:c>
+      <x:c r="U2" s="14" t="str"/>
+      <x:c r="V2" s="14" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="V2" s="14" t="n">
+      <x:c r="W2" s="14" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="W2" s="14" t="n">
+      <x:c r="X2" s="14" t="n">
         <x:v>32.29</x:v>
       </x:c>
-      <x:c r="X2" s="14" t="n">
+      <x:c r="Y2" s="14" t="n">
         <x:v>520</x:v>
       </x:c>
-      <x:c r="Y2" s="14" t="n">
+      <x:c r="Z2" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="Z2" s="14" t="n">
+      <x:c r="AA2" s="14" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="AA2" s="14" t="n">
+      <x:c r="AB2" s="14" t="n">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="AB2" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC2" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD2" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AE2" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AF2" s="14" t="n">
         <x:v>0</x:v>
@@ -891,11 +893,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM2" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AN2" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AN2" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AO2" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -903,47 +905,47 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ2" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR2" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS2" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS2" s="14" t="n">
+      <x:c r="AT2" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT2" s="14" t="n">
+      <x:c r="AU2" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU2" s="14" t="n">
+      <x:c r="AV2" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV2" s="14" t="n">
+      <x:c r="AW2" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AW2" s="14" t="n">
+      <x:c r="AX2" s="14" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="AX2" s="14" t="n">
+      <x:c r="AY2" s="14" t="n">
         <x:v>0.18</x:v>
       </x:c>
-      <x:c r="AY2" s="14" t="n">
+      <x:c r="AZ2" s="14" t="n">
         <x:v>0.62</x:v>
       </x:c>
-      <x:c r="AZ2" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BA2" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="BB2" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BC2" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC2" s="14" t="n">
+      <x:c r="BD2" s="14" t="n">
         <x:v>520</x:v>
       </x:c>
-      <x:c r="BD2" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BE2" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -954,15 +956,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BH2" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BI2" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="BI2" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BJ2" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK2" s="15" t="str">
+      <x:c r="BK2" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL2" s="15" t="str">
         <x:v>data/artifacts/blood_slash.tres</x:v>
       </x:c>
     </x:row>
@@ -970,77 +975,75 @@
       <x:c r="A3" s="13" t="str">
         <x:v>blood_sword</x:v>
       </x:c>
-      <x:c r="B3" s="14" t="str">
+      <x:c r="B3" s="14" t="str"/>
+      <x:c r="C3" s="14" t="str">
         <x:v>血剑</x:v>
       </x:c>
-      <x:c r="C3" s="14" t="str">
+      <x:c r="D3" s="14" t="str">
         <x:v>挥出高伤害血色剑光。攻击消耗3点生命，生命低于30%时不消耗；击杀敌人回复1点生命。</x:v>
       </x:c>
-      <x:c r="D3" s="14" t="str">
+      <x:c r="E3" s="14" t="str">
         <x:v>抽出血色流光凝成短血剑，近距离厚重血色剑光挥砍，命中留下短血痕，结束后崩成血雾。</x:v>
       </x:c>
-      <x:c r="E3" s="14" t="str"/>
       <x:c r="F3" s="14" t="str"/>
       <x:c r="G3" s="14" t="str"/>
       <x:c r="H3" s="14" t="str"/>
-      <x:c r="I3" s="14" t="str">
+      <x:c r="I3" s="14" t="str"/>
+      <x:c r="J3" s="14" t="str">
         <x:v>命中的敌人留下血痕，按secondary_delay延迟爆裂，按secondary_damage_mult造成小范围低伤。</x:v>
       </x:c>
-      <x:c r="J3" s="14" t="str">
+      <x:c r="K3" s="14" t="str">
         <x:v>1费近战高伤害，消耗生命换输出，击杀按kill_heal_amount回血。</x:v>
       </x:c>
-      <x:c r="K3" s="14" t="str">
+      <x:c r="L3" s="14" t="str">
         <x:v>life_cost_flat, life_cost_min_hp_ratio, kill_heal_amount, windup_time, secondary_damage_mult, secondary_radius, secondary_delay</x:v>
       </x:c>
-      <x:c r="L3" s="14" t="str">
+      <x:c r="M3" s="14" t="str">
         <x:v>魔修</x:v>
       </x:c>
-      <x:c r="M3" s="14" t="str">
+      <x:c r="N3" s="14" t="str">
         <x:v>火</x:v>
       </x:c>
-      <x:c r="N3" s="14" t="str">
+      <x:c r="O3" s="14" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="O3" s="14" t="n">
+      <x:c r="P3" s="14" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="P3" s="14" t="str"/>
-      <x:c r="Q3" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R3" s="14" t="str">
+      <x:c r="Q3" s="14" t="str"/>
+      <x:c r="R3" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S3" s="14" t="str">
         <x:v>melee</x:v>
       </x:c>
-      <x:c r="S3" s="14" t="str">
+      <x:c r="T3" s="14" t="str">
         <x:v>slash</x:v>
       </x:c>
-      <x:c r="T3" s="14" t="str"/>
-      <x:c r="U3" s="14" t="n">
+      <x:c r="U3" s="14" t="str"/>
+      <x:c r="V3" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="V3" s="14" t="n">
+      <x:c r="W3" s="14" t="n">
         <x:v>0.86</x:v>
       </x:c>
-      <x:c r="W3" s="14" t="n">
+      <x:c r="X3" s="14" t="n">
         <x:v>34.88</x:v>
       </x:c>
-      <x:c r="X3" s="14" t="n">
+      <x:c r="Y3" s="14" t="n">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="Y3" s="14" t="n">
+      <x:c r="Z3" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="Z3" s="14" t="n">
+      <x:c r="AA3" s="14" t="n">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="AA3" s="14" t="n">
+      <x:c r="AB3" s="14" t="n">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="AB3" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC3" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD3" s="14" t="n">
         <x:v>0</x:v>
@@ -1049,11 +1052,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AF3" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG3" s="14" t="n">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="AG3" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AH3" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1070,11 +1073,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM3" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AN3" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AN3" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AO3" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1082,44 +1085,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ3" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR3" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS3" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS3" s="14" t="n">
+      <x:c r="AT3" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT3" s="14" t="n">
+      <x:c r="AU3" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU3" s="14" t="n">
+      <x:c r="AV3" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV3" s="14" t="n">
+      <x:c r="AW3" s="14" t="n">
         <x:v>0.08</x:v>
       </x:c>
-      <x:c r="AW3" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AX3" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY3" s="14" t="n">
         <x:v>0.22</x:v>
       </x:c>
-      <x:c r="AY3" s="14" t="n">
+      <x:c r="AZ3" s="14" t="n">
         <x:v>0.38</x:v>
       </x:c>
-      <x:c r="AZ3" s="14" t="n">
+      <x:c r="BA3" s="14" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="BA3" s="14" t="n">
+      <x:c r="BB3" s="14" t="n">
         <x:v>0.28</x:v>
       </x:c>
-      <x:c r="BB3" s="14" t="n">
+      <x:c r="BC3" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC3" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD3" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1141,7 +1144,10 @@
       <x:c r="BJ3" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK3" s="15" t="str">
+      <x:c r="BK3" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL3" s="15" t="str">
         <x:v>data/artifacts/blood_sword.tres</x:v>
       </x:c>
     </x:row>
@@ -1153,67 +1159,75 @@
         <x:v>罩</x:v>
       </x:c>
       <x:c r="C4" s="14" t="str">
-        <x:v>周期释放震荡波，对周围敌人造成伤害，命中敌人时回复生命。</x:v>
-      </x:c>
-      <x:c r="D4" s="14" t="str"/>
-      <x:c r="E4" s="14" t="str"/>
+        <x:v>气血护体</x:v>
+      </x:c>
+      <x:c r="D4" s="14" t="str">
+        <x:v>周身形成气血护罩，收缩后爆发震荡波，对近身敌人造成伤害、击退并按命中回复生命。</x:v>
+      </x:c>
+      <x:c r="E4" s="14" t="str">
+        <x:v>角色周围形成气血护罩，先收缩再爆发成厚重震荡波，命中敌人后气血流光回到角色。</x:v>
+      </x:c>
       <x:c r="F4" s="14" t="str"/>
       <x:c r="G4" s="14" t="str"/>
       <x:c r="H4" s="14" t="str"/>
       <x:c r="I4" s="14" t="str"/>
-      <x:c r="J4" s="14" t="str"/>
-      <x:c r="K4" s="14" t="str"/>
+      <x:c r="J4" s="14" t="str">
+        <x:v>第一次爆发后保留余罩，按secondary_delay触发第二次较低伤震荡和较低上限回血。</x:v>
+      </x:c>
+      <x:c r="K4" s="14" t="str">
+        <x:v>3费周身周期爆发、近身防护与续航。</x:v>
+      </x:c>
       <x:c r="L4" s="14" t="str">
+        <x:v>radius, duration, windup_time, tick_interval, knockback_force, heal_amount, shield_max, shield_amount, secondary_damage_mult, secondary_radius, secondary_delay</x:v>
+      </x:c>
+      <x:c r="M4" s="14" t="str">
         <x:v>体修</x:v>
       </x:c>
-      <x:c r="M4" s="14" t="str">
+      <x:c r="N4" s="14" t="str">
         <x:v>水</x:v>
       </x:c>
-      <x:c r="N4" s="14" t="str">
+      <x:c r="O4" s="14" t="str">
         <x:v>灵器</x:v>
       </x:c>
-      <x:c r="O4" s="14" t="n">
+      <x:c r="P4" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="P4" s="14" t="str"/>
-      <x:c r="Q4" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R4" s="14" t="str">
+      <x:c r="Q4" s="14" t="str"/>
+      <x:c r="R4" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S4" s="14" t="str">
         <x:v>formation</x:v>
       </x:c>
-      <x:c r="S4" s="14" t="str">
+      <x:c r="T4" s="14" t="str">
         <x:v>aura</x:v>
       </x:c>
-      <x:c r="T4" s="14" t="str">
+      <x:c r="U4" s="14" t="str">
         <x:v>damage</x:v>
       </x:c>
-      <x:c r="U4" s="14" t="n">
+      <x:c r="V4" s="14" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="V4" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="W4" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X4" s="14" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="X4" s="14" t="n">
+      <x:c r="Y4" s="14" t="n">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="Y4" s="14" t="n">
-        <x:v>118</x:v>
-      </x:c>
       <x:c r="Z4" s="14" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="AA4" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="AA4" s="14" t="n">
+      <x:c r="AB4" s="14" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="AB4" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC4" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD4" s="14" t="n">
         <x:v>0</x:v>
@@ -1225,16 +1239,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG4" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="AH4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AI4" s="14" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AI4" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AJ4" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AK4" s="14" t="n">
         <x:v>0</x:v>
@@ -1255,44 +1269,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ4" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR4" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS4" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS4" s="14" t="n">
+      <x:c r="AT4" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT4" s="14" t="n">
+      <x:c r="AU4" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU4" s="14" t="n">
+      <x:c r="AV4" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV4" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AW4" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="AX4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY4" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY4" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AZ4" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="BA4" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="BB4" s="14" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="BC4" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC4" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD4" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1314,7 +1328,10 @@
       <x:c r="BJ4" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK4" s="15" t="str">
+      <x:c r="BK4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL4" s="15" t="str">
         <x:v>data/artifacts/body_barrier.tres</x:v>
       </x:c>
     </x:row>
@@ -1322,77 +1339,75 @@
       <x:c r="A5" s="13" t="str">
         <x:v>brush</x:v>
       </x:c>
-      <x:c r="B5" s="14" t="str">
+      <x:c r="B5" s="14" t="str"/>
+      <x:c r="C5" s="14" t="str">
         <x:v>毛笔</x:v>
       </x:c>
-      <x:c r="C5" s="14" t="str">
+      <x:c r="D5" s="14" t="str">
         <x:v>锁定最近敌人方向挥出直线墨迹，短暂延迟后整条墨迹同时爆发，穿透路径上的所有敌人。</x:v>
       </x:c>
-      <x:c r="D5" s="14" t="str">
+      <x:c r="E5" s="14" t="str">
         <x:v>毛笔飞向目标区域，三笔写出抽象符印，完整形成后统一爆发。</x:v>
       </x:c>
-      <x:c r="E5" s="14" t="str"/>
       <x:c r="F5" s="14" t="str"/>
       <x:c r="G5" s="14" t="str"/>
       <x:c r="H5" s="14" t="str"/>
-      <x:c r="I5" s="14" t="str">
+      <x:c r="I5" s="14" t="str"/>
+      <x:c r="J5" s="14" t="str">
         <x:v>爆发后残留墨阵，按固定脉冲造成低伤并减速。</x:v>
       </x:c>
-      <x:c r="J5" s="14" t="str">
+      <x:c r="K5" s="14" t="str">
         <x:v>3费延迟AOE、区域布置和控场。</x:v>
       </x:c>
-      <x:c r="K5" s="14" t="str">
+      <x:c r="L5" s="14" t="str">
         <x:v>radius, delayed_strike_interval, tick_interval, duration, secondary_damage_mult, slow_percent</x:v>
       </x:c>
-      <x:c r="L5" s="14" t="str">
+      <x:c r="M5" s="14" t="str">
         <x:v>法修</x:v>
       </x:c>
-      <x:c r="M5" s="14" t="str">
+      <x:c r="N5" s="14" t="str">
         <x:v>木</x:v>
       </x:c>
-      <x:c r="N5" s="14" t="str">
+      <x:c r="O5" s="14" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="O5" s="14" t="n">
+      <x:c r="P5" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="P5" s="14" t="str"/>
-      <x:c r="Q5" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R5" s="14" t="str">
+      <x:c r="Q5" s="14" t="str"/>
+      <x:c r="R5" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S5" s="14" t="str">
         <x:v>line_delayed</x:v>
       </x:c>
-      <x:c r="S5" s="14" t="str">
+      <x:c r="T5" s="14" t="str">
         <x:v>line</x:v>
       </x:c>
-      <x:c r="T5" s="14" t="str"/>
-      <x:c r="U5" s="14" t="n">
+      <x:c r="U5" s="14" t="str"/>
+      <x:c r="V5" s="14" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="V5" s="14" t="n">
+      <x:c r="W5" s="14" t="n">
         <x:v>1.35</x:v>
       </x:c>
-      <x:c r="W5" s="14" t="n">
+      <x:c r="X5" s="14" t="n">
         <x:v>35.56</x:v>
       </x:c>
-      <x:c r="X5" s="14" t="n">
+      <x:c r="Y5" s="14" t="n">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="Y5" s="14" t="n">
+      <x:c r="Z5" s="14" t="n">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="Z5" s="14" t="n">
+      <x:c r="AA5" s="14" t="n">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="AA5" s="14" t="n">
+      <x:c r="AB5" s="14" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="AB5" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC5" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD5" s="14" t="n">
         <x:v>0</x:v>
@@ -1404,11 +1419,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH5" s="14" t="n">
         <x:v>0.35</x:v>
       </x:c>
-      <x:c r="AH5" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AI5" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1434,44 +1449,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ5" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR5" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS5" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS5" s="14" t="n">
+      <x:c r="AT5" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT5" s="14" t="n">
+      <x:c r="AU5" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU5" s="14" t="n">
+      <x:c r="AV5" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV5" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AW5" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AX5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY5" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY5" s="14" t="n">
+      <x:c r="AZ5" s="14" t="n">
         <x:v>0.24</x:v>
       </x:c>
-      <x:c r="AZ5" s="14" t="n">
+      <x:c r="BA5" s="14" t="n">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="BA5" s="14" t="n">
+      <x:c r="BB5" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="BB5" s="14" t="n">
+      <x:c r="BC5" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC5" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD5" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1493,7 +1508,10 @@
       <x:c r="BJ5" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK5" s="15" t="str">
+      <x:c r="BK5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL5" s="15" t="str">
         <x:v>data/artifacts/brush.tres</x:v>
       </x:c>
     </x:row>
@@ -1501,87 +1519,85 @@
       <x:c r="A6" s="13" t="str">
         <x:v>copper_coin</x:v>
       </x:c>
-      <x:c r="B6" s="14" t="str">
+      <x:c r="B6" s="14" t="str"/>
+      <x:c r="C6" s="14" t="str">
         <x:v>铜钱</x:v>
       </x:c>
-      <x:c r="C6" s="14" t="str">
+      <x:c r="D6" s="14" t="str">
         <x:v>命中后在附近未命中的敌人之间弹射，适合补刀但单体较弱。</x:v>
       </x:c>
-      <x:c r="D6" s="14" t="str">
+      <x:c r="E6" s="14" t="str">
         <x:v>铜钱旋转发射，命中后按目标搜索范围折线弹射并留下短暂金色轨迹。</x:v>
       </x:c>
-      <x:c r="E6" s="14" t="str"/>
       <x:c r="F6" s="14" t="str"/>
       <x:c r="G6" s="14" t="str"/>
       <x:c r="H6" s="14" t="str"/>
-      <x:c r="I6" s="14" t="str">
+      <x:c r="I6" s="14" t="str"/>
+      <x:c r="J6" s="14" t="str">
         <x:v>最后一次弹射后分裂为多枚小铜钱，优先攻击不同目标。</x:v>
       </x:c>
-      <x:c r="J6" s="14" t="str">
+      <x:c r="K6" s="14" t="str">
         <x:v>1费高频弹射，连续打击多个目标。</x:v>
       </x:c>
-      <x:c r="K6" s="14" t="str">
+      <x:c r="L6" s="14" t="str">
         <x:v>bounce_count, bounce_range, projectile_speed, count, secondary_damage_mult, secondary_radius</x:v>
       </x:c>
-      <x:c r="L6" s="14" t="str">
+      <x:c r="M6" s="14" t="str">
         <x:v>法修</x:v>
       </x:c>
-      <x:c r="M6" s="14" t="str">
+      <x:c r="N6" s="14" t="str">
         <x:v>金</x:v>
       </x:c>
-      <x:c r="N6" s="14" t="str">
+      <x:c r="O6" s="14" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="O6" s="14" t="n">
+      <x:c r="P6" s="14" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="P6" s="14" t="str"/>
-      <x:c r="Q6" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R6" s="14" t="str">
+      <x:c r="Q6" s="14" t="str"/>
+      <x:c r="R6" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S6" s="14" t="str">
         <x:v>projectile</x:v>
       </x:c>
-      <x:c r="S6" s="14" t="str">
+      <x:c r="T6" s="14" t="str">
         <x:v>circle</x:v>
       </x:c>
-      <x:c r="T6" s="14" t="str"/>
-      <x:c r="U6" s="14" t="n">
+      <x:c r="U6" s="14" t="str"/>
+      <x:c r="V6" s="14" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="V6" s="14" t="n">
+      <x:c r="W6" s="14" t="n">
         <x:v>0.93</x:v>
       </x:c>
-      <x:c r="W6" s="14" t="n">
+      <x:c r="X6" s="14" t="n">
         <x:v>22.58</x:v>
       </x:c>
-      <x:c r="X6" s="14" t="n">
+      <x:c r="Y6" s="14" t="n">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="Y6" s="14" t="n">
+      <x:c r="Z6" s="14" t="n">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="Z6" s="14" t="n">
-        <x:v>15</x:v>
       </x:c>
       <x:c r="AA6" s="14" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="AB6" s="14" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="AC6" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AC6" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AD6" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AE6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF6" s="14" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AF6" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AG6" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1613,44 +1629,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ6" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR6" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS6" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS6" s="14" t="n">
+      <x:c r="AT6" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT6" s="14" t="n">
+      <x:c r="AU6" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU6" s="14" t="n">
+      <x:c r="AV6" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV6" s="14" t="n">
+      <x:c r="AW6" s="14" t="n">
         <x:v>0.06</x:v>
       </x:c>
-      <x:c r="AW6" s="14" t="n">
+      <x:c r="AX6" s="14" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="AX6" s="14" t="n">
+      <x:c r="AY6" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY6" s="14" t="n">
+      <x:c r="AZ6" s="14" t="n">
         <x:v>0.45</x:v>
       </x:c>
-      <x:c r="AZ6" s="14" t="n">
+      <x:c r="BA6" s="14" t="n">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="BA6" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BB6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BC6" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC6" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD6" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1672,7 +1688,10 @@
       <x:c r="BJ6" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK6" s="15" t="str">
+      <x:c r="BK6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL6" s="15" t="str">
         <x:v>data/artifacts/copper_coin.tres</x:v>
       </x:c>
     </x:row>
@@ -1680,85 +1699,83 @@
       <x:c r="A7" s="13" t="str">
         <x:v>crossbow_puppet</x:v>
       </x:c>
-      <x:c r="B7" s="14" t="str">
+      <x:c r="B7" s="14" t="str"/>
+      <x:c r="C7" s="14" t="str">
         <x:v>远程傀儡</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="str">
+      <x:c r="D7" s="14" t="str">
         <x:v>召唤后排远程傀儡，和敌人保持距离并持续发射灵能箭。死亡后会在短时间后重生。</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="str">
+      <x:c r="E7" s="14" t="str">
         <x:v>侧后方召唤阵显形，保持secondary_radius理想距离，蓄能后发射带拖尾灵能箭；多单位有短蓄能窗口形成齐射感。</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="str">
+      <x:c r="F7" s="14" t="str">
         <x:v>保持secondary_radius理想距离；过近后退，过远靠近；超过活动范围返回。</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="str">
+      <x:c r="G7" s="14" t="str">
         <x:v>有仇恨，可被敌人主动选择。</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="str">
+      <x:c r="H7" s="14" t="str">
         <x:v>可受伤。</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="str">
+      <x:c r="I7" s="14" t="str">
         <x:v>死亡后按summon_respawn_time在玩家附近重生，清理旧目标和状态。</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="str">
+      <x:c r="J7" s="14" t="str">
         <x:v>每delayed_strike_count次攻击蓄力齐射三支扇形箭，侧箭按side_projectile_damage_mult造成伤害。</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="str">
+      <x:c r="K7" s="14" t="str">
         <x:v>1费基础后排持续输出，可被攻击，死亡后重生。</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="str">
+      <x:c r="L7" s="14" t="str">
         <x:v>summon_attack_speed, projectile_speed, secondary_radius, delayed_strike_delay, delayed_strike_count, fan_angle, side_projectile_damage_mult</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="str">
+      <x:c r="M7" s="14" t="str">
         <x:v>召唤</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="str">
+      <x:c r="N7" s="14" t="str">
         <x:v>雷</x:v>
       </x:c>
-      <x:c r="N7" s="14" t="str">
+      <x:c r="O7" s="14" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="O7" s="14" t="n">
+      <x:c r="P7" s="14" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="P7" s="14" t="str"/>
-      <x:c r="Q7" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R7" s="14" t="str">
+      <x:c r="Q7" s="14" t="str"/>
+      <x:c r="R7" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S7" s="14" t="str">
         <x:v>summon</x:v>
       </x:c>
-      <x:c r="S7" s="14" t="str">
+      <x:c r="T7" s="14" t="str">
         <x:v>projectile</x:v>
       </x:c>
-      <x:c r="T7" s="14" t="str"/>
-      <x:c r="U7" s="14" t="n">
+      <x:c r="U7" s="14" t="str"/>
+      <x:c r="V7" s="14" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="V7" s="14" t="n">
+      <x:c r="W7" s="14" t="n">
         <x:v>0.48</x:v>
       </x:c>
-      <x:c r="W7" s="14" t="n">
+      <x:c r="X7" s="14" t="n">
         <x:v>29.17</x:v>
       </x:c>
-      <x:c r="X7" s="14" t="n">
+      <x:c r="Y7" s="14" t="n">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="Y7" s="14" t="n">
+      <x:c r="Z7" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="Z7" s="14" t="n">
+      <x:c r="AA7" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="AA7" s="14" t="n">
+      <x:c r="AB7" s="14" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="AB7" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC7" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD7" s="14" t="n">
         <x:v>0</x:v>
@@ -1791,59 +1808,59 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AN7" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AO7" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP7" s="14" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="AP7" s="14" t="n">
+      <x:c r="AQ7" s="14" t="n">
         <x:v>12.5</x:v>
       </x:c>
-      <x:c r="AQ7" s="14" t="n">
+      <x:c r="AR7" s="14" t="n">
         <x:v>2.1</x:v>
       </x:c>
-      <x:c r="AR7" s="14" t="n">
+      <x:c r="AS7" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS7" s="14" t="n">
+      <x:c r="AT7" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT7" s="14" t="n">
+      <x:c r="AU7" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU7" s="14" t="n">
+      <x:c r="AV7" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV7" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AW7" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AX7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY7" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY7" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AZ7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA7" s="14" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="BA7" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BB7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BC7" s="14" t="n">
         <x:v>0.55</x:v>
       </x:c>
-      <x:c r="BC7" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE7" s="14" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="BE7" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BF7" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1859,7 +1876,10 @@
       <x:c r="BJ7" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK7" s="15" t="str">
+      <x:c r="BK7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL7" s="15" t="str">
         <x:v>data/artifacts/crossbow_puppet.tres</x:v>
       </x:c>
     </x:row>
@@ -1867,80 +1887,78 @@
       <x:c r="A8" s="13" t="str">
         <x:v>dagger</x:v>
       </x:c>
-      <x:c r="B8" s="14" t="str">
+      <x:c r="B8" s="14" t="str"/>
+      <x:c r="C8" s="14" t="str">
         <x:v>匕首</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="str">
+      <x:c r="D8" s="14" t="str">
         <x:v>高频短距离刺击，可命中少量近身敌人。</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="str">
+      <x:c r="E8" s="14" t="str">
         <x:v>极短距离锁定最近敌人，细闪光线+匕首残影穿刺，目标身后小AOE。</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="str"/>
       <x:c r="F8" s="14" t="str"/>
       <x:c r="G8" s="14" t="str"/>
       <x:c r="H8" s="14" t="str"/>
-      <x:c r="I8" s="14" t="str">
+      <x:c r="I8" s="14" t="str"/>
+      <x:c r="J8" s="14" t="str">
         <x:v>从相反方向追加第二次低伤害刺击，不重复大范围AOE。</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="str">
+      <x:c r="K8" s="14" t="str">
         <x:v>1费快速近身刺杀，近乎单体，背后极小范围溅射。</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="str">
+      <x:c r="L8" s="14" t="str">
         <x:v>range, secondary_radius, secondary_damage_mult, secondary_delay</x:v>
       </x:c>
-      <x:c r="L8" s="14" t="str">
+      <x:c r="M8" s="14" t="str">
         <x:v>剑修</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="str">
+      <x:c r="N8" s="14" t="str">
         <x:v>毒</x:v>
       </x:c>
-      <x:c r="N8" s="14" t="str">
+      <x:c r="O8" s="14" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="O8" s="14" t="n">
+      <x:c r="P8" s="14" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="P8" s="14" t="str"/>
-      <x:c r="Q8" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R8" s="14" t="str">
+      <x:c r="Q8" s="14" t="str"/>
+      <x:c r="R8" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S8" s="14" t="str">
         <x:v>melee</x:v>
       </x:c>
-      <x:c r="S8" s="14" t="str">
+      <x:c r="T8" s="14" t="str">
         <x:v>stab</x:v>
       </x:c>
-      <x:c r="T8" s="14" t="str"/>
-      <x:c r="U8" s="14" t="n">
+      <x:c r="U8" s="14" t="str"/>
+      <x:c r="V8" s="14" t="n">
         <x:v>7.5</x:v>
       </x:c>
-      <x:c r="V8" s="14" t="n">
+      <x:c r="W8" s="14" t="n">
         <x:v>0.21</x:v>
       </x:c>
-      <x:c r="W8" s="14" t="n">
+      <x:c r="X8" s="14" t="n">
         <x:v>35.71</x:v>
       </x:c>
-      <x:c r="X8" s="14" t="n">
+      <x:c r="Y8" s="14" t="n">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="Y8" s="14" t="n">
+      <x:c r="Z8" s="14" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="Z8" s="14" t="n">
+      <x:c r="AA8" s="14" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="AA8" s="14" t="n">
+      <x:c r="AB8" s="14" t="n">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="AB8" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC8" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="AD8" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AE8" s="14" t="n">
         <x:v>0</x:v>
@@ -1979,44 +1997,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ8" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR8" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS8" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS8" s="14" t="n">
+      <x:c r="AT8" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT8" s="14" t="n">
+      <x:c r="AU8" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU8" s="14" t="n">
+      <x:c r="AV8" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV8" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AW8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX8" s="14" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="AX8" s="14" t="n">
+      <x:c r="AY8" s="14" t="n">
         <x:v>0.08</x:v>
       </x:c>
-      <x:c r="AY8" s="14" t="n">
+      <x:c r="AZ8" s="14" t="n">
         <x:v>0.35</x:v>
       </x:c>
-      <x:c r="AZ8" s="14" t="n">
+      <x:c r="BA8" s="14" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="BA8" s="14" t="n">
+      <x:c r="BB8" s="14" t="n">
         <x:v>0.045</x:v>
       </x:c>
-      <x:c r="BB8" s="14" t="n">
+      <x:c r="BC8" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC8" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD8" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2038,7 +2056,10 @@
       <x:c r="BJ8" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK8" s="15" t="str">
+      <x:c r="BK8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL8" s="15" t="str">
         <x:v>data/artifacts/dagger.tres</x:v>
       </x:c>
     </x:row>
@@ -2046,86 +2067,84 @@
       <x:c r="A9" s="13" t="str">
         <x:v>divine_thunder</x:v>
       </x:c>
-      <x:c r="B9" s="14" t="str">
+      <x:c r="B9" s="14" t="str"/>
+      <x:c r="C9" s="14" t="str">
         <x:v>神雷术</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="str">
+      <x:c r="D9" s="14" t="str">
         <x:v>锁定一名敌人降下神雷，以该敌人为中心造成范围伤害。三星时神雷范围大幅增加。</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="str">
+      <x:c r="E9" s="14" t="str">
         <x:v>稳定选择敌人密集区域，预警圈后主雷落下，并连锁附近目标。</x:v>
       </x:c>
-      <x:c r="E9" s="14" t="str"/>
       <x:c r="F9" s="14" t="str"/>
       <x:c r="G9" s="14" t="str"/>
       <x:c r="H9" s="14" t="str"/>
-      <x:c r="I9" s="14" t="str">
+      <x:c r="I9" s="14" t="str"/>
+      <x:c r="J9" s="14" t="str">
         <x:v>主雷后生成雷劫区域，按间隔落下多道副雷。</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="str">
+      <x:c r="K9" s="14" t="str">
         <x:v>5费远程天降爆发，大范围高伤和连锁清场。</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="str">
+      <x:c r="L9" s="14" t="str">
         <x:v>windup_time, radius, count, bounce_range, delayed_strike_count, delayed_strike_interval, secondary_radius</x:v>
       </x:c>
-      <x:c r="L9" s="14" t="str">
+      <x:c r="M9" s="14" t="str">
         <x:v>法修</x:v>
       </x:c>
-      <x:c r="M9" s="14" t="str">
+      <x:c r="N9" s="14" t="str">
         <x:v>雷</x:v>
       </x:c>
-      <x:c r="N9" s="14" t="str">
+      <x:c r="O9" s="14" t="str">
         <x:v>仙宝</x:v>
       </x:c>
-      <x:c r="O9" s="14" t="n">
+      <x:c r="P9" s="14" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="P9" s="14" t="str"/>
-      <x:c r="Q9" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R9" s="14" t="str">
+      <x:c r="Q9" s="14" t="str"/>
+      <x:c r="R9" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S9" s="14" t="str">
         <x:v>target_aoe</x:v>
       </x:c>
-      <x:c r="S9" s="14" t="str">
+      <x:c r="T9" s="14" t="str">
         <x:v>circle</x:v>
       </x:c>
-      <x:c r="T9" s="14" t="str"/>
-      <x:c r="U9" s="14" t="n">
+      <x:c r="U9" s="14" t="str"/>
+      <x:c r="V9" s="14" t="n">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="V9" s="14" t="n">
+      <x:c r="W9" s="14" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="W9" s="14" t="n">
+      <x:c r="X9" s="14" t="n">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="X9" s="14" t="n">
+      <x:c r="Y9" s="14" t="n">
         <x:v>760</x:v>
       </x:c>
-      <x:c r="Y9" s="14" t="n">
+      <x:c r="Z9" s="14" t="n">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="Z9" s="14" t="n">
+      <x:c r="AA9" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="AA9" s="14" t="n">
+      <x:c r="AB9" s="14" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="AB9" s="14" t="n">
+      <x:c r="AC9" s="14" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="AC9" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AD9" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AE9" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF9" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AG9" s="14" t="n">
         <x:v>0</x:v>
@@ -2158,44 +2177,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ9" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR9" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS9" s="14" t="n">
         <x:v>1.65</x:v>
       </x:c>
-      <x:c r="AS9" s="14" t="n">
+      <x:c r="AT9" s="14" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="AT9" s="14" t="n">
+      <x:c r="AU9" s="14" t="n">
         <x:v>2.35</x:v>
       </x:c>
-      <x:c r="AU9" s="14" t="n">
+      <x:c r="AV9" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AV9" s="14" t="n">
+      <x:c r="AW9" s="14" t="n">
         <x:v>0.22</x:v>
       </x:c>
-      <x:c r="AW9" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AX9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY9" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY9" s="14" t="n">
+      <x:c r="AZ9" s="14" t="n">
         <x:v>0.32</x:v>
       </x:c>
-      <x:c r="AZ9" s="14" t="n">
+      <x:c r="BA9" s="14" t="n">
         <x:v>1.18</x:v>
       </x:c>
-      <x:c r="BA9" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BB9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BC9" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC9" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD9" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2217,7 +2236,10 @@
       <x:c r="BJ9" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK9" s="15" t="str">
+      <x:c r="BK9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL9" s="15" t="str">
         <x:v>data/artifacts/divine_thunder.tres</x:v>
       </x:c>
     </x:row>
@@ -2225,77 +2247,75 @@
       <x:c r="A10" s="13" t="str">
         <x:v>fire_gourd</x:v>
       </x:c>
-      <x:c r="B10" s="14" t="str">
+      <x:c r="B10" s="14" t="str"/>
+      <x:c r="C10" s="14" t="str">
         <x:v>火葫芦</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="str">
+      <x:c r="D10" s="14" t="str">
         <x:v>向目标方向喷出锥形火焰，对范围内敌人造成伤害。</x:v>
       </x:c>
-      <x:c r="D10" s="14" t="str">
+      <x:c r="E10" s="14" t="str">
         <x:v>火葫芦锁定密集方向，短前摇后按固定脉冲喷出多层锥形火浪。</x:v>
       </x:c>
-      <x:c r="E10" s="14" t="str"/>
       <x:c r="F10" s="14" t="str"/>
       <x:c r="G10" s="14" t="str"/>
       <x:c r="H10" s="14" t="str"/>
-      <x:c r="I10" s="14" t="str">
+      <x:c r="I10" s="14" t="str"/>
+      <x:c r="J10" s="14" t="str">
         <x:v>喷火结束后吐出火种，爆炸并留下固定脉冲燃烧区域。</x:v>
       </x:c>
-      <x:c r="J10" s="14" t="str">
+      <x:c r="K10" s="14" t="str">
         <x:v>4费中近距离持续锥形清群，多段伤害和灼烧。</x:v>
       </x:c>
-      <x:c r="K10" s="14" t="str">
+      <x:c r="L10" s="14" t="str">
         <x:v>windup_time, duration, tick_interval, fan_angle, poison_dps, explosion_radius, delayed_strike_interval</x:v>
       </x:c>
-      <x:c r="L10" s="14" t="str">
+      <x:c r="M10" s="14" t="str">
         <x:v>法修</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="str">
+      <x:c r="N10" s="14" t="str">
         <x:v>火</x:v>
       </x:c>
-      <x:c r="N10" s="14" t="str">
+      <x:c r="O10" s="14" t="str">
         <x:v>灵宝</x:v>
       </x:c>
-      <x:c r="O10" s="14" t="n">
+      <x:c r="P10" s="14" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="P10" s="14" t="str"/>
-      <x:c r="Q10" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R10" s="14" t="str">
+      <x:c r="Q10" s="14" t="str"/>
+      <x:c r="R10" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S10" s="14" t="str">
         <x:v>melee</x:v>
       </x:c>
-      <x:c r="S10" s="14" t="str">
+      <x:c r="T10" s="14" t="str">
         <x:v>cone</x:v>
       </x:c>
-      <x:c r="T10" s="14" t="str"/>
-      <x:c r="U10" s="14" t="n">
+      <x:c r="U10" s="14" t="str"/>
+      <x:c r="V10" s="14" t="n">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="V10" s="14" t="n">
+      <x:c r="W10" s="14" t="n">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="W10" s="14" t="n">
+      <x:c r="X10" s="14" t="n">
         <x:v>47.33</x:v>
       </x:c>
-      <x:c r="X10" s="14" t="n">
+      <x:c r="Y10" s="14" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="Y10" s="14" t="n">
+      <x:c r="Z10" s="14" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="Z10" s="14" t="n">
+      <x:c r="AA10" s="14" t="n">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="AA10" s="14" t="n">
+      <x:c r="AB10" s="14" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="AB10" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC10" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD10" s="14" t="n">
         <x:v>0</x:v>
@@ -2316,14 +2336,14 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AJ10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK10" s="14" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="AK10" s="14" t="n">
+      <x:c r="AL10" s="14" t="n">
         <x:v>1.8</x:v>
       </x:c>
-      <x:c r="AL10" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AM10" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2337,50 +2357,50 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ10" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR10" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS10" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS10" s="14" t="n">
+      <x:c r="AT10" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT10" s="14" t="n">
+      <x:c r="AU10" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU10" s="14" t="n">
+      <x:c r="AV10" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV10" s="14" t="n">
+      <x:c r="AW10" s="14" t="n">
         <x:v>0.18</x:v>
       </x:c>
-      <x:c r="AW10" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AX10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY10" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY10" s="14" t="n">
+      <x:c r="AZ10" s="14" t="n">
         <x:v>0.32</x:v>
       </x:c>
-      <x:c r="AZ10" s="14" t="n">
+      <x:c r="BA10" s="14" t="n">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="BA10" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="BB10" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC10" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC10" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE10" s="14" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="BE10" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BF10" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2396,7 +2416,10 @@
       <x:c r="BJ10" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK10" s="15" t="str">
+      <x:c r="BK10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL10" s="15" t="str">
         <x:v>data/artifacts/fire_gourd.tres</x:v>
       </x:c>
     </x:row>
@@ -2404,77 +2427,75 @@
       <x:c r="A11" s="13" t="str">
         <x:v>fire_orb</x:v>
       </x:c>
-      <x:c r="B11" s="14" t="str">
+      <x:c r="B11" s="14" t="str"/>
+      <x:c r="C11" s="14" t="str">
         <x:v>法球</x:v>
       </x:c>
-      <x:c r="C11" s="14" t="str">
+      <x:c r="D11" s="14" t="str">
         <x:v>向最近敌人发射火焰法球，直伤较低，命中后造成小范围爆炸。</x:v>
       </x:c>
-      <x:c r="D11" s="14" t="str">
+      <x:c r="E11" s="14" t="str">
         <x:v>光点凝聚成法球，短暂停顿后飞行，命中后收缩并爆炸为圆形冲击波。</x:v>
       </x:c>
-      <x:c r="E11" s="14" t="str"/>
       <x:c r="F11" s="14" t="str"/>
       <x:c r="G11" s="14" t="str"/>
       <x:c r="H11" s="14" t="str"/>
-      <x:c r="I11" s="14" t="str">
+      <x:c r="I11" s="14" t="str"/>
+      <x:c r="J11" s="14" t="str">
         <x:v>第一次爆炸后延迟触发更大、更淡、低伤的第二次爆炸。</x:v>
       </x:c>
-      <x:c r="J11" s="14" t="str">
+      <x:c r="K11" s="14" t="str">
         <x:v>1费标准法修发射物，中速基础AOE。</x:v>
       </x:c>
-      <x:c r="K11" s="14" t="str">
+      <x:c r="L11" s="14" t="str">
         <x:v>windup_time, explosion_radius, secondary_delay, secondary_radius, secondary_damage_mult</x:v>
       </x:c>
-      <x:c r="L11" s="14" t="str">
+      <x:c r="M11" s="14" t="str">
         <x:v>法修</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="str">
+      <x:c r="N11" s="14" t="str">
         <x:v>火</x:v>
       </x:c>
-      <x:c r="N11" s="14" t="str">
+      <x:c r="O11" s="14" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="O11" s="14" t="n">
+      <x:c r="P11" s="14" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="P11" s="14" t="str"/>
-      <x:c r="Q11" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R11" s="14" t="str">
+      <x:c r="Q11" s="14" t="str"/>
+      <x:c r="R11" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S11" s="14" t="str">
         <x:v>projectile</x:v>
       </x:c>
-      <x:c r="S11" s="14" t="str">
+      <x:c r="T11" s="14" t="str">
         <x:v>circle</x:v>
       </x:c>
-      <x:c r="T11" s="14" t="str"/>
-      <x:c r="U11" s="14" t="n">
+      <x:c r="U11" s="14" t="str"/>
+      <x:c r="V11" s="14" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="V11" s="14" t="n">
+      <x:c r="W11" s="14" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="W11" s="14" t="n">
+      <x:c r="X11" s="14" t="n">
         <x:v>23.96</x:v>
       </x:c>
-      <x:c r="X11" s="14" t="n">
+      <x:c r="Y11" s="14" t="n">
         <x:v>500</x:v>
       </x:c>
-      <x:c r="Y11" s="14" t="n">
+      <x:c r="Z11" s="14" t="n">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="Z11" s="14" t="n">
-        <x:v>20</x:v>
       </x:c>
       <x:c r="AA11" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="AB11" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="AC11" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD11" s="14" t="n">
         <x:v>0</x:v>
@@ -2516,44 +2537,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ11" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR11" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS11" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS11" s="14" t="n">
+      <x:c r="AT11" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT11" s="14" t="n">
+      <x:c r="AU11" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU11" s="14" t="n">
+      <x:c r="AV11" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV11" s="14" t="n">
+      <x:c r="AW11" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AW11" s="14" t="n">
+      <x:c r="AX11" s="14" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="AX11" s="14" t="n">
+      <x:c r="AY11" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY11" s="14" t="n">
+      <x:c r="AZ11" s="14" t="n">
         <x:v>0.45</x:v>
       </x:c>
-      <x:c r="AZ11" s="14" t="n">
+      <x:c r="BA11" s="14" t="n">
         <x:v>1.35</x:v>
       </x:c>
-      <x:c r="BA11" s="14" t="n">
+      <x:c r="BB11" s="14" t="n">
         <x:v>0.18</x:v>
       </x:c>
-      <x:c r="BB11" s="14" t="n">
+      <x:c r="BC11" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC11" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD11" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2575,7 +2596,10 @@
       <x:c r="BJ11" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK11" s="15" t="str">
+      <x:c r="BK11" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL11" s="15" t="str">
         <x:v>data/artifacts/fire_orb.tres</x:v>
       </x:c>
     </x:row>
@@ -2583,69 +2607,75 @@
       <x:c r="A12" s="13" t="str">
         <x:v>fist</x:v>
       </x:c>
-      <x:c r="B12" s="14" t="str">
+      <x:c r="B12" s="14" t="str"/>
+      <x:c r="C12" s="14" t="str">
         <x:v>拳</x:v>
       </x:c>
-      <x:c r="C12" s="14" t="str">
+      <x:c r="D12" s="14" t="str">
         <x:v>快速近身拳劲打击最近敌人，伤害高于远程法宝。</x:v>
       </x:c>
-      <x:c r="D12" s="14" t="str"/>
-      <x:c r="E12" s="14" t="str"/>
+      <x:c r="E12" s="14" t="str">
+        <x:v>角色前方快速凝出左右交替拳影，短距离冲出命中最近敌人，命中有短促冲击闪光。</x:v>
+      </x:c>
       <x:c r="F12" s="14" t="str"/>
       <x:c r="G12" s="14" t="str"/>
       <x:c r="H12" s="14" t="str"/>
       <x:c r="I12" s="14" t="str"/>
-      <x:c r="J12" s="14" t="str"/>
-      <x:c r="K12" s="14" t="str"/>
+      <x:c r="J12" s="14" t="str">
+        <x:v>每delayed_strike_count次攻击触发三连拳，第三拳更大并按secondary_radius产生小范围冲击波。</x:v>
+      </x:c>
+      <x:c r="K12" s="14" t="str">
+        <x:v>1费快速近身单体输出，高频稳定打最近目标。</x:v>
+      </x:c>
       <x:c r="L12" s="14" t="str">
+        <x:v>count, delayed_strike_count, delayed_strike_interval, secondary_damage_mult, secondary_radius, side_projectile_damage_mult</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="str">
         <x:v>体修</x:v>
       </x:c>
-      <x:c r="M12" s="14" t="str">
+      <x:c r="N12" s="14" t="str">
         <x:v>火</x:v>
       </x:c>
-      <x:c r="N12" s="14" t="str">
+      <x:c r="O12" s="14" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="O12" s="14" t="n">
+      <x:c r="P12" s="14" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="P12" s="14" t="str"/>
-      <x:c r="Q12" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R12" s="14" t="str">
+      <x:c r="Q12" s="14" t="str"/>
+      <x:c r="R12" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S12" s="14" t="str">
         <x:v>melee</x:v>
       </x:c>
-      <x:c r="S12" s="14" t="str">
+      <x:c r="T12" s="14" t="str">
         <x:v>stab</x:v>
       </x:c>
-      <x:c r="T12" s="14" t="str"/>
-      <x:c r="U12" s="14" t="n">
+      <x:c r="U12" s="14" t="str"/>
+      <x:c r="V12" s="14" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="V12" s="14" t="n">
+      <x:c r="W12" s="14" t="n">
         <x:v>0.27</x:v>
       </x:c>
-      <x:c r="W12" s="14" t="n">
+      <x:c r="X12" s="14" t="n">
         <x:v>37.04</x:v>
       </x:c>
-      <x:c r="X12" s="14" t="n">
+      <x:c r="Y12" s="14" t="n">
         <x:v>320</x:v>
-      </x:c>
-      <x:c r="Y12" s="14" t="n">
-        <x:v>32</x:v>
       </x:c>
       <x:c r="Z12" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
       <x:c r="AA12" s="14" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="AB12" s="14" t="n">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="AB12" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC12" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AD12" s="14" t="n">
         <x:v>0</x:v>
@@ -2654,11 +2684,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AF12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG12" s="14" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="AG12" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AH12" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2687,43 +2717,43 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ12" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR12" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS12" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS12" s="14" t="n">
+      <x:c r="AT12" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT12" s="14" t="n">
+      <x:c r="AU12" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU12" s="14" t="n">
+      <x:c r="AV12" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV12" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AW12" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AX12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY12" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY12" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AZ12" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1.35</x:v>
       </x:c>
       <x:c r="BA12" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="BB12" s="14" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BC12" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.72</x:v>
       </x:c>
       <x:c r="BD12" s="14" t="n">
         <x:v>0</x:v>
@@ -2746,7 +2776,10 @@
       <x:c r="BJ12" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK12" s="15" t="str">
+      <x:c r="BK12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL12" s="15" t="str">
         <x:v>data/artifacts/fist.tres</x:v>
       </x:c>
     </x:row>
@@ -2754,84 +2787,82 @@
       <x:c r="A13" s="13" t="str">
         <x:v>flying_sword</x:v>
       </x:c>
-      <x:c r="B13" s="14" t="str">
+      <x:c r="B13" s="14" t="str"/>
+      <x:c r="C13" s="14" t="str">
         <x:v>飞剑</x:v>
       </x:c>
-      <x:c r="C13" s="14" t="str">
+      <x:c r="D13" s="14" t="str">
         <x:v>向最近敌人发射一柄可穿透的飞剑，安全稳定但直伤偏低。</x:v>
       </x:c>
-      <x:c r="D13" s="14" t="str">
+      <x:c r="E13" s="14" t="str">
         <x:v>飞剑浮现、短蓄力后穿透飞出，到最大距离后返航，去返分别命中。</x:v>
       </x:c>
-      <x:c r="E13" s="14" t="str"/>
       <x:c r="F13" s="14" t="str"/>
       <x:c r="G13" s="14" t="str"/>
       <x:c r="H13" s="14" t="str"/>
-      <x:c r="I13" s="14" t="str">
+      <x:c r="I13" s="14" t="str"/>
+      <x:c r="J13" s="14" t="str">
         <x:v>三把飞剑扇形出发，副剑按side_projectile_damage_mult造成伤害。</x:v>
       </x:c>
-      <x:c r="J13" s="14" t="str">
+      <x:c r="K13" s="14" t="str">
         <x:v>2费御剑攻击，主动操控感，非普通直线子弹。</x:v>
       </x:c>
-      <x:c r="K13" s="14" t="str">
+      <x:c r="L13" s="14" t="str">
         <x:v>windup_time, return_speed, fan_angle, side_projectile_damage_mult, trail_length</x:v>
       </x:c>
-      <x:c r="L13" s="14" t="str">
+      <x:c r="M13" s="14" t="str">
         <x:v>剑修</x:v>
       </x:c>
-      <x:c r="M13" s="14" t="str">
+      <x:c r="N13" s="14" t="str">
         <x:v>雷</x:v>
       </x:c>
-      <x:c r="N13" s="14" t="str">
+      <x:c r="O13" s="14" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="O13" s="14" t="n">
+      <x:c r="P13" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="P13" s="14" t="str"/>
-      <x:c r="Q13" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R13" s="14" t="str">
-        <x:v>projectile</x:v>
+      <x:c r="Q13" s="14" t="str"/>
+      <x:c r="R13" s="14" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="S13" s="14" t="str">
         <x:v>projectile</x:v>
       </x:c>
-      <x:c r="T13" s="14" t="str"/>
-      <x:c r="U13" s="14" t="n">
+      <x:c r="T13" s="14" t="str">
+        <x:v>projectile</x:v>
+      </x:c>
+      <x:c r="U13" s="14" t="str"/>
+      <x:c r="V13" s="14" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="V13" s="14" t="n">
+      <x:c r="W13" s="14" t="n">
         <x:v>0.68</x:v>
       </x:c>
-      <x:c r="W13" s="14" t="n">
+      <x:c r="X13" s="14" t="n">
         <x:v>32.35</x:v>
       </x:c>
-      <x:c r="X13" s="14" t="n">
+      <x:c r="Y13" s="14" t="n">
         <x:v>560</x:v>
       </x:c>
-      <x:c r="Y13" s="14" t="n">
+      <x:c r="Z13" s="14" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="Z13" s="14" t="n">
+      <x:c r="AA13" s="14" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="AA13" s="14" t="n">
+      <x:c r="AB13" s="14" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="AB13" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC13" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE13" s="14" t="n">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="AE13" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AF13" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2866,32 +2897,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ13" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR13" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS13" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS13" s="14" t="n">
+      <x:c r="AT13" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT13" s="14" t="n">
+      <x:c r="AU13" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU13" s="14" t="n">
+      <x:c r="AV13" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV13" s="14" t="n">
+      <x:c r="AW13" s="14" t="n">
         <x:v>0.08</x:v>
       </x:c>
-      <x:c r="AW13" s="14" t="n">
+      <x:c r="AX13" s="14" t="n">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="AX13" s="14" t="n">
+      <x:c r="AY13" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY13" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AZ13" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2899,20 +2930,20 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BB13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BC13" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC13" s="14" t="n">
+      <x:c r="BD13" s="14" t="n">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="BD13" s="14" t="n">
+      <x:c r="BE13" s="14" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="BE13" s="14" t="n">
+      <x:c r="BF13" s="14" t="n">
         <x:v>0.35</x:v>
       </x:c>
-      <x:c r="BF13" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BG13" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2925,7 +2956,10 @@
       <x:c r="BJ13" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK13" s="15" t="str">
+      <x:c r="BK13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL13" s="15" t="str">
         <x:v>data/artifacts/flying_sword.tres</x:v>
       </x:c>
     </x:row>
@@ -2933,85 +2967,83 @@
       <x:c r="A14" s="13" t="str">
         <x:v>ghost</x:v>
       </x:c>
-      <x:c r="B14" s="14" t="str">
+      <x:c r="B14" s="14" t="str"/>
+      <x:c r="C14" s="14" t="str">
         <x:v>幽魂</x:v>
       </x:c>
-      <x:c r="C14" s="14" t="str">
+      <x:c r="D14" s="14" t="str">
         <x:v>召唤没有仇恨值的幽魂。幽魂锁定敌人后加速冲击，穿过敌人造成伤害，并在敌人身后短距离停下后重新锁定目标。幽魂不会受到伤害。</x:v>
       </x:c>
-      <x:c r="D14" s="14" t="str">
+      <x:c r="E14" s="14" t="str">
         <x:v>水波召唤印记中浮现，无实体阻挡、无仇恨、普通伤害无效；锁敌后拉长并穿过目标，留下半透明拖尾。</x:v>
       </x:c>
-      <x:c r="E14" s="14" t="str">
+      <x:c r="F14" s="14" t="str">
         <x:v>玩家附近漂浮；锁敌后直线冲刺穿过并在目标后方停顿；过远返回。</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="str">
+      <x:c r="G14" s="14" t="str">
         <x:v>无仇恨，敌人不会主动锁定。</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="str">
+      <x:c r="H14" s="14" t="str">
         <x:v>普通伤害无效。</x:v>
       </x:c>
-      <x:c r="H14" s="14" t="str">
+      <x:c r="I14" s="14" t="str">
         <x:v>无死亡和重生。</x:v>
       </x:c>
-      <x:c r="I14" s="14" t="str">
+      <x:c r="J14" s="14" t="str">
         <x:v>第一次穿过后在secondary_radius内寻找第二目标，立即二段转向冲刺，伤害按secondary_damage_mult。</x:v>
       </x:c>
-      <x:c r="J14" s="14" t="str">
+      <x:c r="K14" s="14" t="str">
         <x:v>4费无敌无仇恨高速穿透输出，不承担坦克职责，无死亡重生。</x:v>
       </x:c>
-      <x:c r="K14" s="14" t="str">
+      <x:c r="L14" s="14" t="str">
         <x:v>summon_base_count, summon_move_speed, length, width, secondary_damage_mult, secondary_radius, secondary_delay</x:v>
       </x:c>
-      <x:c r="L14" s="14" t="str">
+      <x:c r="M14" s="14" t="str">
         <x:v>召唤</x:v>
       </x:c>
-      <x:c r="M14" s="14" t="str">
+      <x:c r="N14" s="14" t="str">
         <x:v>水</x:v>
       </x:c>
-      <x:c r="N14" s="14" t="str">
+      <x:c r="O14" s="14" t="str">
         <x:v>灵宝</x:v>
       </x:c>
-      <x:c r="O14" s="14" t="n">
+      <x:c r="P14" s="14" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="P14" s="14" t="str"/>
-      <x:c r="Q14" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R14" s="14" t="str">
+      <x:c r="Q14" s="14" t="str"/>
+      <x:c r="R14" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S14" s="14" t="str">
         <x:v>summon</x:v>
       </x:c>
-      <x:c r="S14" s="14" t="str">
+      <x:c r="T14" s="14" t="str">
         <x:v>line</x:v>
       </x:c>
-      <x:c r="T14" s="14" t="str"/>
-      <x:c r="U14" s="14" t="n">
+      <x:c r="U14" s="14" t="str"/>
+      <x:c r="V14" s="14" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="V14" s="14" t="n">
+      <x:c r="W14" s="14" t="n">
         <x:v>0.59</x:v>
       </x:c>
-      <x:c r="W14" s="14" t="n">
+      <x:c r="X14" s="14" t="n">
         <x:v>13.56</x:v>
       </x:c>
-      <x:c r="X14" s="14" t="n">
+      <x:c r="Y14" s="14" t="n">
         <x:v>700</x:v>
       </x:c>
-      <x:c r="Y14" s="14" t="n">
+      <x:c r="Z14" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="Z14" s="14" t="n">
+      <x:c r="AA14" s="14" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="AA14" s="14" t="n">
+      <x:c r="AB14" s="14" t="n">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="AB14" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC14" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD14" s="14" t="n">
         <x:v>0</x:v>
@@ -3026,11 +3058,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AH14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AI14" s="14" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AI14" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AJ14" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3044,53 +3076,53 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AN14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO14" s="14" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AO14" s="14" t="n">
+      <x:c r="AP14" s="14" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="AP14" s="14" t="n">
+      <x:c r="AQ14" s="14" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="AQ14" s="14" t="n">
+      <x:c r="AR14" s="14" t="n">
         <x:v>1.68</x:v>
       </x:c>
-      <x:c r="AR14" s="14" t="n">
+      <x:c r="AS14" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS14" s="14" t="n">
+      <x:c r="AT14" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT14" s="14" t="n">
+      <x:c r="AU14" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU14" s="14" t="n">
+      <x:c r="AV14" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV14" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AW14" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AX14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY14" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY14" s="14" t="n">
+      <x:c r="AZ14" s="14" t="n">
         <x:v>0.58</x:v>
       </x:c>
-      <x:c r="AZ14" s="14" t="n">
+      <x:c r="BA14" s="14" t="n">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="BA14" s="14" t="n">
+      <x:c r="BB14" s="14" t="n">
         <x:v>0.18</x:v>
       </x:c>
-      <x:c r="BB14" s="14" t="n">
+      <x:c r="BC14" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC14" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD14" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3112,7 +3144,10 @@
       <x:c r="BJ14" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK14" s="15" t="str">
+      <x:c r="BK14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL14" s="15" t="str">
         <x:v>data/artifacts/ghost.tres</x:v>
       </x:c>
     </x:row>
@@ -3120,84 +3155,82 @@
       <x:c r="A15" s="13" t="str">
         <x:v>giant_sword_art</x:v>
       </x:c>
-      <x:c r="B15" s="14" t="str">
+      <x:c r="B15" s="14" t="str"/>
+      <x:c r="C15" s="14" t="str">
         <x:v>巨剑术</x:v>
       </x:c>
-      <x:c r="C15" s="14" t="str">
+      <x:c r="D15" s="14" t="str">
         <x:v>在角色身后凝聚巨剑，朝敌人发射，在较宽的直线范围内造成伤害。三星时以角色为中心横扫一整圈。</x:v>
       </x:c>
-      <x:c r="D15" s="14" t="str">
+      <x:c r="E15" s="14" t="str">
         <x:v>脚下剑阵，选择敌人密集方向，巨剑分段显现后向前贯穿。</x:v>
       </x:c>
-      <x:c r="E15" s="14" t="str"/>
       <x:c r="F15" s="14" t="str"/>
       <x:c r="G15" s="14" t="str"/>
       <x:c r="H15" s="14" t="str"/>
-      <x:c r="I15" s="14" t="str">
+      <x:c r="I15" s="14" t="str"/>
+      <x:c r="J15" s="14" t="str">
         <x:v>改为以角色为中心360度横扫一周。</x:v>
       </x:c>
-      <x:c r="J15" s="14" t="str">
+      <x:c r="K15" s="14" t="str">
         <x:v>5费超大范围视觉高潮和清场输出。</x:v>
       </x:c>
-      <x:c r="K15" s="14" t="str">
+      <x:c r="L15" s="14" t="str">
         <x:v>reveal_time, pause_time, sweep_rotation_speed, trail_length</x:v>
       </x:c>
-      <x:c r="L15" s="14" t="str">
+      <x:c r="M15" s="14" t="str">
         <x:v>剑修</x:v>
       </x:c>
-      <x:c r="M15" s="14" t="str">
+      <x:c r="N15" s="14" t="str">
         <x:v>金</x:v>
       </x:c>
-      <x:c r="N15" s="14" t="str">
+      <x:c r="O15" s="14" t="str">
         <x:v>仙宝</x:v>
       </x:c>
-      <x:c r="O15" s="14" t="n">
+      <x:c r="P15" s="14" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="P15" s="14" t="str"/>
-      <x:c r="Q15" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R15" s="14" t="str">
+      <x:c r="Q15" s="14" t="str"/>
+      <x:c r="R15" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S15" s="14" t="str">
         <x:v>projectile</x:v>
       </x:c>
-      <x:c r="S15" s="14" t="str">
+      <x:c r="T15" s="14" t="str">
         <x:v>line</x:v>
       </x:c>
-      <x:c r="T15" s="14" t="str"/>
-      <x:c r="U15" s="14" t="n">
+      <x:c r="U15" s="14" t="str"/>
+      <x:c r="V15" s="14" t="n">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="V15" s="14" t="n">
+      <x:c r="W15" s="14" t="n">
         <x:v>1.68</x:v>
       </x:c>
-      <x:c r="W15" s="14" t="n">
+      <x:c r="X15" s="14" t="n">
         <x:v>79.76</x:v>
       </x:c>
-      <x:c r="X15" s="14" t="n">
+      <x:c r="Y15" s="14" t="n">
         <x:v>760</x:v>
       </x:c>
-      <x:c r="Y15" s="14" t="n">
+      <x:c r="Z15" s="14" t="n">
         <x:v>680</x:v>
       </x:c>
-      <x:c r="Z15" s="14" t="n">
+      <x:c r="AA15" s="14" t="n">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="AA15" s="14" t="n">
+      <x:c r="AB15" s="14" t="n">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="AB15" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC15" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE15" s="14" t="n">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="AE15" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AF15" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3232,32 +3265,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ15" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR15" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS15" s="14" t="n">
         <x:v>1.75</x:v>
       </x:c>
-      <x:c r="AS15" s="14" t="n">
+      <x:c r="AT15" s="14" t="n">
         <x:v>0.95</x:v>
       </x:c>
-      <x:c r="AT15" s="14" t="n">
+      <x:c r="AU15" s="14" t="n">
         <x:v>2.4</x:v>
       </x:c>
-      <x:c r="AU15" s="14" t="n">
+      <x:c r="AV15" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AV15" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AW15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX15" s="14" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="AX15" s="14" t="n">
+      <x:c r="AY15" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY15" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AZ15" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3265,11 +3298,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BB15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BC15" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC15" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD15" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3280,18 +3313,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BG15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BH15" s="14" t="n">
         <x:v>0.36</x:v>
       </x:c>
-      <x:c r="BH15" s="14" t="n">
+      <x:c r="BI15" s="14" t="n">
         <x:v>0.16</x:v>
       </x:c>
-      <x:c r="BI15" s="14" t="n">
+      <x:c r="BJ15" s="14" t="n">
         <x:v>6.283</x:v>
       </x:c>
-      <x:c r="BJ15" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BK15" s="15" t="str">
+      <x:c r="BK15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL15" s="15" t="str">
         <x:v>data/artifacts/giant_sword_art.tres</x:v>
       </x:c>
     </x:row>
@@ -3299,71 +3335,77 @@
       <x:c r="A16" s="13" t="str">
         <x:v>golden_body_avatar</x:v>
       </x:c>
-      <x:c r="B16" s="14" t="str">
+      <x:c r="B16" s="14" t="str"/>
+      <x:c r="C16" s="14" t="str">
         <x:v>法相金身</x:v>
       </x:c>
-      <x:c r="C16" s="14" t="str">
-        <x:v>角色背后常驻半透明巨大法相，周期砸地造成大范围伤害。</x:v>
-      </x:c>
-      <x:c r="D16" s="14" t="str"/>
-      <x:c r="E16" s="14" t="str"/>
+      <x:c r="D16" s="14" t="str">
+        <x:v>角色背后常驻半透明巨大法相，周期抬手砸向敌人密集区域，造成大范围伤害和击退。</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="str">
+        <x:v>角色背后常驻低透明法相，攻击时增亮抬手，砸向敌人密集区域并生成冲击波和地裂。</x:v>
+      </x:c>
       <x:c r="F16" s="14" t="str"/>
       <x:c r="G16" s="14" t="str"/>
       <x:c r="H16" s="14" t="str"/>
       <x:c r="I16" s="14" t="str"/>
-      <x:c r="J16" s="14" t="str"/>
-      <x:c r="K16" s="14" t="str"/>
+      <x:c r="J16" s="14" t="str">
+        <x:v>法相变大，第一次砸地后按secondary_delay偏移位置进行第二次低伤大范围砸地。</x:v>
+      </x:c>
+      <x:c r="K16" s="14" t="str">
+        <x:v>5费体修最终大范围高伤、高击退、低频视觉高潮。</x:v>
+      </x:c>
       <x:c r="L16" s="14" t="str">
+        <x:v>range, radius, windup_time, tick_interval, knockback_force, secondary_damage_mult, secondary_radius, secondary_delay, screen_shake_strength</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="str">
         <x:v>体修</x:v>
       </x:c>
-      <x:c r="M16" s="14" t="str">
+      <x:c r="N16" s="14" t="str">
         <x:v>土</x:v>
       </x:c>
-      <x:c r="N16" s="14" t="str">
+      <x:c r="O16" s="14" t="str">
         <x:v>仙宝</x:v>
       </x:c>
-      <x:c r="O16" s="14" t="n">
+      <x:c r="P16" s="14" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="P16" s="14" t="str"/>
-      <x:c r="Q16" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R16" s="14" t="str">
+      <x:c r="Q16" s="14" t="str"/>
+      <x:c r="R16" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S16" s="14" t="str">
         <x:v>formation</x:v>
       </x:c>
-      <x:c r="S16" s="14" t="str">
+      <x:c r="T16" s="14" t="str">
         <x:v>aura</x:v>
       </x:c>
-      <x:c r="T16" s="14" t="str">
+      <x:c r="U16" s="14" t="str">
         <x:v>avatar_slam</x:v>
       </x:c>
-      <x:c r="U16" s="14" t="n">
+      <x:c r="V16" s="14" t="n">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="V16" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="W16" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X16" s="14" t="n">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="X16" s="14" t="n">
-        <x:v>320</x:v>
-      </x:c>
       <x:c r="Y16" s="14" t="n">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="Z16" s="14" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="Z16" s="14" t="n">
+      <x:c r="AA16" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="AA16" s="14" t="n">
+      <x:c r="AB16" s="14" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="AB16" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC16" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD16" s="14" t="n">
         <x:v>0</x:v>
@@ -3375,7 +3417,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG16" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="AH16" s="14" t="n">
         <x:v>0</x:v>
@@ -3405,44 +3447,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ16" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR16" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS16" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS16" s="14" t="n">
+      <x:c r="AT16" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT16" s="14" t="n">
+      <x:c r="AU16" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU16" s="14" t="n">
+      <x:c r="AV16" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV16" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AW16" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.28</x:v>
       </x:c>
       <x:c r="AX16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY16" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY16" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AZ16" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="BA16" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1.18</x:v>
       </x:c>
       <x:c r="BB16" s="14" t="n">
+        <x:v>0.26</x:v>
+      </x:c>
+      <x:c r="BC16" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC16" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD16" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3464,7 +3506,10 @@
       <x:c r="BJ16" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK16" s="15" t="str">
+      <x:c r="BK16" s="14" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="BL16" s="15" t="str">
         <x:v>data/artifacts/golden_body_avatar.tres</x:v>
       </x:c>
     </x:row>
@@ -3472,76 +3517,74 @@
       <x:c r="A17" s="13" t="str">
         <x:v>guardian_flying_sword</x:v>
       </x:c>
-      <x:c r="B17" s="14" t="str">
+      <x:c r="B17" s="14" t="str"/>
+      <x:c r="C17" s="14" t="str">
         <x:v>护体剑轮</x:v>
       </x:c>
-      <x:c r="C17" s="14" t="str">
+      <x:c r="D17" s="14" t="str">
         <x:v>多个小型剑轮围绕角色高速公转，接触敌人时按固定间隔造成持续切割伤害。三星时剑轮数量增加。</x:v>
       </x:c>
-      <x:c r="D17" s="14" t="str">
+      <x:c r="E17" s="14" t="str">
         <x:v>3个小型剑轮均匀环绕角色，高速公转并按显式间隔切割。</x:v>
       </x:c>
-      <x:c r="E17" s="14" t="str"/>
       <x:c r="F17" s="14" t="str"/>
       <x:c r="G17" s="14" t="str"/>
       <x:c r="H17" s="14" t="str"/>
-      <x:c r="I17" s="14" t="str">
+      <x:c r="I17" s="14" t="str"/>
+      <x:c r="J17" s="14" t="str">
         <x:v>剑轮数量增加到4个。</x:v>
       </x:c>
-      <x:c r="J17" s="14" t="str">
+      <x:c r="K17" s="14" t="str">
         <x:v>4费中近距离持续切割，伤害不依赖帧率。</x:v>
       </x:c>
-      <x:c r="K17" s="14" t="str">
+      <x:c r="L17" s="14" t="str">
         <x:v>count, radius, rotation_speed, self_rotation_speed, hit_interval</x:v>
       </x:c>
-      <x:c r="L17" s="14" t="str">
+      <x:c r="M17" s="14" t="str">
         <x:v>剑修</x:v>
       </x:c>
-      <x:c r="M17" s="14" t="str">
+      <x:c r="N17" s="14" t="str">
         <x:v>木</x:v>
       </x:c>
-      <x:c r="N17" s="14" t="str">
+      <x:c r="O17" s="14" t="str">
         <x:v>灵宝</x:v>
       </x:c>
-      <x:c r="O17" s="14" t="n">
+      <x:c r="P17" s="14" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="P17" s="14" t="str"/>
-      <x:c r="Q17" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R17" s="14" t="str">
+      <x:c r="Q17" s="14" t="str"/>
+      <x:c r="R17" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S17" s="14" t="str">
         <x:v>orbit</x:v>
       </x:c>
-      <x:c r="S17" s="14" t="str"/>
       <x:c r="T17" s="14" t="str"/>
-      <x:c r="U17" s="14" t="n">
+      <x:c r="U17" s="14" t="str"/>
+      <x:c r="V17" s="14" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="V17" s="14" t="n">
+      <x:c r="W17" s="14" t="n">
         <x:v>0.61</x:v>
       </x:c>
-      <x:c r="W17" s="14" t="n">
+      <x:c r="X17" s="14" t="n">
         <x:v>55.74</x:v>
       </x:c>
-      <x:c r="X17" s="14" t="n">
+      <x:c r="Y17" s="14" t="n">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="Y17" s="14" t="n">
+      <x:c r="Z17" s="14" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="Z17" s="14" t="n">
+      <x:c r="AA17" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="AA17" s="14" t="n">
+      <x:c r="AB17" s="14" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="AB17" s="14" t="n">
+      <x:c r="AC17" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AC17" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AD17" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3582,44 +3625,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ17" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR17" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS17" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS17" s="14" t="n">
+      <x:c r="AT17" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT17" s="14" t="n">
+      <x:c r="AU17" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU17" s="14" t="n">
+      <x:c r="AV17" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV17" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AW17" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AX17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY17" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY17" s="14" t="n">
+      <x:c r="AZ17" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="AZ17" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BA17" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="BB17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BC17" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC17" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD17" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3627,11 +3670,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BF17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BG17" s="14" t="n">
         <x:v>4.2</x:v>
       </x:c>
-      <x:c r="BG17" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BH17" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3641,7 +3684,10 @@
       <x:c r="BJ17" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK17" s="15" t="str">
+      <x:c r="BK17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL17" s="15" t="str">
         <x:v>data/artifacts/guardian_flying_sword.tres</x:v>
       </x:c>
     </x:row>
@@ -3649,77 +3695,75 @@
       <x:c r="A18" s="13" t="str">
         <x:v>guqin</x:v>
       </x:c>
-      <x:c r="B18" s="14" t="str">
+      <x:c r="B18" s="14" t="str"/>
+      <x:c r="C18" s="14" t="str">
         <x:v>古琴</x:v>
       </x:c>
-      <x:c r="C18" s="14" t="str">
+      <x:c r="D18" s="14" t="str">
         <x:v>音符命中后短暂降低敌人伤害，直伤较低。</x:v>
       </x:c>
-      <x:c r="D18" s="14" t="str">
+      <x:c r="E18" s="14" t="str">
         <x:v>古琴虚影拨弦，按顺序释放三层弧形音波并施加伤害降低。</x:v>
       </x:c>
-      <x:c r="E18" s="14" t="str"/>
       <x:c r="F18" s="14" t="str"/>
       <x:c r="G18" s="14" t="str"/>
       <x:c r="H18" s="14" t="str"/>
-      <x:c r="I18" s="14" t="str">
+      <x:c r="I18" s="14" t="str"/>
+      <x:c r="J18" s="14" t="str">
         <x:v>第三层音波改为以角色为中心的环形音波。</x:v>
       </x:c>
-      <x:c r="J18" s="14" t="str">
+      <x:c r="K18" s="14" t="str">
         <x:v>3费大范围多段音波辅助，偏生存和削弱。</x:v>
       </x:c>
-      <x:c r="K18" s="14" t="str">
+      <x:c r="L18" s="14" t="str">
         <x:v>range, fan_angle, delayed_strike_interval, damage_reduction_percent, debuff_duration</x:v>
       </x:c>
-      <x:c r="L18" s="14" t="str">
+      <x:c r="M18" s="14" t="str">
         <x:v>法修</x:v>
       </x:c>
-      <x:c r="M18" s="14" t="str">
+      <x:c r="N18" s="14" t="str">
         <x:v>水</x:v>
       </x:c>
-      <x:c r="N18" s="14" t="str">
+      <x:c r="O18" s="14" t="str">
         <x:v>灵器</x:v>
       </x:c>
-      <x:c r="O18" s="14" t="n">
+      <x:c r="P18" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="P18" s="14" t="str"/>
-      <x:c r="Q18" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R18" s="14" t="str">
+      <x:c r="Q18" s="14" t="str"/>
+      <x:c r="R18" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S18" s="14" t="str">
         <x:v>projectile</x:v>
       </x:c>
-      <x:c r="S18" s="14" t="str">
+      <x:c r="T18" s="14" t="str">
         <x:v>circle</x:v>
       </x:c>
-      <x:c r="T18" s="14" t="str"/>
-      <x:c r="U18" s="14" t="n">
+      <x:c r="U18" s="14" t="str"/>
+      <x:c r="V18" s="14" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="V18" s="14" t="n">
+      <x:c r="W18" s="14" t="n">
         <x:v>1.25</x:v>
       </x:c>
-      <x:c r="W18" s="14" t="n">
+      <x:c r="X18" s="14" t="n">
         <x:v>16.8</x:v>
       </x:c>
-      <x:c r="X18" s="14" t="n">
+      <x:c r="Y18" s="14" t="n">
         <x:v>480</x:v>
       </x:c>
-      <x:c r="Y18" s="14" t="n">
+      <x:c r="Z18" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="Z18" s="14" t="n">
+      <x:c r="AA18" s="14" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="AA18" s="14" t="n">
+      <x:c r="AB18" s="14" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="AB18" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC18" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD18" s="14" t="n">
         <x:v>0</x:v>
@@ -3761,32 +3805,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ18" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR18" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS18" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS18" s="14" t="n">
+      <x:c r="AT18" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT18" s="14" t="n">
+      <x:c r="AU18" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU18" s="14" t="n">
+      <x:c r="AV18" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV18" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AW18" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AX18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY18" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY18" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AZ18" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3794,17 +3838,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BB18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BC18" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC18" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE18" s="14" t="n">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="BE18" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BF18" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3820,7 +3864,10 @@
       <x:c r="BJ18" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK18" s="15" t="str">
+      <x:c r="BK18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL18" s="15" t="str">
         <x:v>data/artifacts/guqin.tres</x:v>
       </x:c>
     </x:row>
@@ -3828,77 +3875,75 @@
       <x:c r="A19" s="13" t="str">
         <x:v>heaven_eye</x:v>
       </x:c>
-      <x:c r="B19" s="14" t="str">
+      <x:c r="B19" s="14" t="str"/>
+      <x:c r="C19" s="14" t="str">
         <x:v>天眼</x:v>
       </x:c>
-      <x:c r="C19" s="14" t="str">
+      <x:c r="D19" s="14" t="str">
         <x:v>短时间锁定最近敌人并持续发射天眼光束。攻击期间持续扣除生命，击杀敌人后恢复生命。</x:v>
       </x:c>
-      <x:c r="D19" s="14" t="str">
+      <x:c r="E19" s="14" t="str">
         <x:v>天眼睁开并锁定目标，光束按tick_interval固定脉冲造成持续伤害，击杀后自动转火。</x:v>
       </x:c>
-      <x:c r="E19" s="14" t="str"/>
       <x:c r="F19" s="14" t="str"/>
       <x:c r="G19" s="14" t="str"/>
       <x:c r="H19" s="14" t="str"/>
-      <x:c r="I19" s="14" t="str">
+      <x:c r="I19" s="14" t="str"/>
+      <x:c r="J19" s="14" t="str">
         <x:v>主光束外额外分出两条副光束，副光束优先锁定不同目标并按side_projectile_damage_mult造成伤害。</x:v>
       </x:c>
-      <x:c r="J19" s="14" t="str">
+      <x:c r="K19" s="14" t="str">
         <x:v>3费持续单体压制，对精英和Boss稳定，持续耗血并击杀回血。</x:v>
       </x:c>
-      <x:c r="K19" s="14" t="str">
+      <x:c r="L19" s="14" t="str">
         <x:v>duration, tick_interval, range, life_cost_flat, life_cost_min_hp_ratio, kill_heal_amount, side_projectile_damage_mult</x:v>
       </x:c>
-      <x:c r="L19" s="14" t="str">
+      <x:c r="M19" s="14" t="str">
         <x:v>魔修</x:v>
       </x:c>
-      <x:c r="M19" s="14" t="str">
+      <x:c r="N19" s="14" t="str">
         <x:v>水</x:v>
       </x:c>
-      <x:c r="N19" s="14" t="str">
+      <x:c r="O19" s="14" t="str">
         <x:v>灵器</x:v>
       </x:c>
-      <x:c r="O19" s="14" t="n">
+      <x:c r="P19" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="P19" s="14" t="str"/>
-      <x:c r="Q19" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R19" s="14" t="str">
-        <x:v>beam</x:v>
+      <x:c r="Q19" s="14" t="str"/>
+      <x:c r="R19" s="14" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="S19" s="14" t="str">
         <x:v>beam</x:v>
       </x:c>
-      <x:c r="T19" s="14" t="str"/>
-      <x:c r="U19" s="14" t="n">
+      <x:c r="T19" s="14" t="str">
+        <x:v>beam</x:v>
+      </x:c>
+      <x:c r="U19" s="14" t="str"/>
+      <x:c r="V19" s="14" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="V19" s="14" t="n">
+      <x:c r="W19" s="14" t="n">
         <x:v>2.14</x:v>
       </x:c>
-      <x:c r="W19" s="14" t="n">
+      <x:c r="X19" s="14" t="n">
         <x:v>10.28</x:v>
       </x:c>
-      <x:c r="X19" s="14" t="n">
+      <x:c r="Y19" s="14" t="n">
         <x:v>520</x:v>
       </x:c>
-      <x:c r="Y19" s="14" t="n">
+      <x:c r="Z19" s="14" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="Z19" s="14" t="n">
+      <x:c r="AA19" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="AA19" s="14" t="n">
+      <x:c r="AB19" s="14" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="AB19" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC19" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD19" s="14" t="n">
         <x:v>0</x:v>
@@ -3928,10 +3973,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM19" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AN19" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AO19" s="14" t="n">
         <x:v>0</x:v>
@@ -3940,44 +3985,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ19" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR19" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS19" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS19" s="14" t="n">
+      <x:c r="AT19" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT19" s="14" t="n">
+      <x:c r="AU19" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU19" s="14" t="n">
+      <x:c r="AV19" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV19" s="14" t="n">
+      <x:c r="AW19" s="14" t="n">
         <x:v>0.16</x:v>
       </x:c>
-      <x:c r="AW19" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AX19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY19" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY19" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AZ19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA19" s="14" t="n">
         <x:v>520</x:v>
       </x:c>
-      <x:c r="BA19" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BB19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BC19" s="14" t="n">
         <x:v>0.42</x:v>
       </x:c>
-      <x:c r="BC19" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD19" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3999,7 +4044,10 @@
       <x:c r="BJ19" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK19" s="15" t="str">
+      <x:c r="BK19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL19" s="15" t="str">
         <x:v>data/artifacts/heaven_eye.tres</x:v>
       </x:c>
     </x:row>
@@ -4007,85 +4055,83 @@
       <x:c r="A20" s="13" t="str">
         <x:v>iron_guard_puppet</x:v>
       </x:c>
-      <x:c r="B20" s="14" t="str">
+      <x:c r="B20" s="14" t="str"/>
+      <x:c r="C20" s="14" t="str">
         <x:v>铁甲傀儡</x:v>
       </x:c>
-      <x:c r="C20" s="14" t="str">
+      <x:c r="D20" s="14" t="str">
         <x:v>召唤高生命铁卫傀儡，尽量挡在玩家与怪群之间，并周期性嘲讽附近敌人。死亡后会重生。</x:v>
       </x:c>
-      <x:c r="D20" s="14" t="str">
+      <x:c r="E20" s="14" t="str">
         <x:v>厚重召唤阵落地，移动到玩家与目标之间，慢速重击并周期性释放嘲讽波纹和敌人标记。</x:v>
       </x:c>
-      <x:c r="E20" s="14" t="str">
+      <x:c r="F20" s="14" t="str">
         <x:v>优先站在玩家与目标之间；周期嘲讽radius内敌人；过远返回。</x:v>
       </x:c>
-      <x:c r="F20" s="14" t="str">
+      <x:c r="G20" s="14" t="str">
         <x:v>有仇恨，且嘲讽期间强制附近敌人攻击它。</x:v>
       </x:c>
-      <x:c r="G20" s="14" t="str">
+      <x:c r="H20" s="14" t="str">
         <x:v>可受伤，三星嘲讽期间自身减伤。</x:v>
       </x:c>
-      <x:c r="H20" s="14" t="str">
+      <x:c r="I20" s="14" t="str">
         <x:v>死亡碎裂并显示重生印记，summon_respawn_time后重新部署到玩家附近。</x:v>
       </x:c>
-      <x:c r="I20" s="14" t="str">
+      <x:c r="J20" s="14" t="str">
         <x:v>嘲讽时展开短时护盾领域，自身按secondary_damage_mult获得减伤，持续duration。</x:v>
       </x:c>
-      <x:c r="J20" s="14" t="str">
+      <x:c r="K20" s="14" t="str">
         <x:v>2费核心坦克，可被攻击，高生命，死亡后重生。</x:v>
       </x:c>
-      <x:c r="K20" s="14" t="str">
+      <x:c r="L20" s="14" t="str">
         <x:v>summon_hp, radius, summon_return_radius, duration, secondary_damage_mult, secondary_delay, secondary_radius</x:v>
       </x:c>
-      <x:c r="L20" s="14" t="str">
+      <x:c r="M20" s="14" t="str">
         <x:v>召唤</x:v>
       </x:c>
-      <x:c r="M20" s="14" t="str">
+      <x:c r="N20" s="14" t="str">
         <x:v>土</x:v>
       </x:c>
-      <x:c r="N20" s="14" t="str">
+      <x:c r="O20" s="14" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="O20" s="14" t="n">
+      <x:c r="P20" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="P20" s="14" t="str"/>
-      <x:c r="Q20" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R20" s="14" t="str">
+      <x:c r="Q20" s="14" t="str"/>
+      <x:c r="R20" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S20" s="14" t="str">
         <x:v>summon</x:v>
       </x:c>
-      <x:c r="S20" s="14" t="str">
+      <x:c r="T20" s="14" t="str">
         <x:v>stab</x:v>
       </x:c>
-      <x:c r="T20" s="14" t="str"/>
-      <x:c r="U20" s="14" t="n">
+      <x:c r="U20" s="14" t="str"/>
+      <x:c r="V20" s="14" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="V20" s="14" t="n">
+      <x:c r="W20" s="14" t="n">
         <x:v>1.02</x:v>
       </x:c>
-      <x:c r="W20" s="14" t="n">
+      <x:c r="X20" s="14" t="n">
         <x:v>7.84</x:v>
       </x:c>
-      <x:c r="X20" s="14" t="n">
+      <x:c r="Y20" s="14" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="Y20" s="14" t="n">
+      <x:c r="Z20" s="14" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="Z20" s="14" t="n">
+      <x:c r="AA20" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="AA20" s="14" t="n">
+      <x:c r="AB20" s="14" t="n">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="AB20" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC20" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD20" s="14" t="n">
         <x:v>0</x:v>
@@ -4118,53 +4164,53 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AN20" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AO20" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP20" s="14" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="AP20" s="14" t="n">
+      <x:c r="AQ20" s="14" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="AQ20" s="14" t="n">
+      <x:c r="AR20" s="14" t="n">
         <x:v>0.98</x:v>
       </x:c>
-      <x:c r="AR20" s="14" t="n">
+      <x:c r="AS20" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS20" s="14" t="n">
+      <x:c r="AT20" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT20" s="14" t="n">
+      <x:c r="AU20" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU20" s="14" t="n">
+      <x:c r="AV20" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV20" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AW20" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AX20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY20" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY20" s="14" t="n">
+      <x:c r="AZ20" s="14" t="n">
         <x:v>0.45</x:v>
       </x:c>
-      <x:c r="AZ20" s="14" t="n">
+      <x:c r="BA20" s="14" t="n">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="BA20" s="14" t="n">
+      <x:c r="BB20" s="14" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="BB20" s="14" t="n">
+      <x:c r="BC20" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC20" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD20" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4186,7 +4232,10 @@
       <x:c r="BJ20" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK20" s="15" t="str">
+      <x:c r="BK20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL20" s="15" t="str">
         <x:v>data/artifacts/iron_guard_puppet.tres</x:v>
       </x:c>
     </x:row>
@@ -4194,69 +4243,75 @@
       <x:c r="A21" s="13" t="str">
         <x:v>kick</x:v>
       </x:c>
-      <x:c r="B21" s="14" t="str">
+      <x:c r="B21" s="14" t="str"/>
+      <x:c r="C21" s="14" t="str">
         <x:v>腿</x:v>
       </x:c>
-      <x:c r="C21" s="14" t="str">
+      <x:c r="D21" s="14" t="str">
         <x:v>贴身旋身扫腿，对周围一圈敌人造成较高伤害并轻微击退。</x:v>
       </x:c>
-      <x:c r="D21" s="14" t="str"/>
-      <x:c r="E21" s="14" t="str"/>
+      <x:c r="E21" s="14" t="str">
+        <x:v>角色周围生成旋转腿罡横扫一圈，环形半径随体修范围加成同步放大。</x:v>
+      </x:c>
       <x:c r="F21" s="14" t="str"/>
       <x:c r="G21" s="14" t="str"/>
       <x:c r="H21" s="14" t="str"/>
       <x:c r="I21" s="14" t="str"/>
-      <x:c r="J21" s="14" t="str"/>
-      <x:c r="K21" s="14" t="str"/>
+      <x:c r="J21" s="14" t="str">
+        <x:v>第一圈后按secondary_delay反向再扫一圈，第二圈按secondary_damage_mult并用secondary_radius扩大范围。</x:v>
+      </x:c>
+      <x:c r="K21" s="14" t="str">
+        <x:v>2费贴身环形解围，高伤并轻微击退周围敌人。</x:v>
+      </x:c>
       <x:c r="L21" s="14" t="str">
+        <x:v>radius, knockback_force, secondary_damage_mult, secondary_radius, secondary_delay, sweep_rotation_speed</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="str">
         <x:v>体修</x:v>
       </x:c>
-      <x:c r="M21" s="14" t="str">
+      <x:c r="N21" s="14" t="str">
         <x:v>土</x:v>
       </x:c>
-      <x:c r="N21" s="14" t="str">
+      <x:c r="O21" s="14" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="O21" s="14" t="n">
+      <x:c r="P21" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="P21" s="14" t="str"/>
-      <x:c r="Q21" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R21" s="14" t="str">
+      <x:c r="Q21" s="14" t="str"/>
+      <x:c r="R21" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S21" s="14" t="str">
         <x:v>melee</x:v>
       </x:c>
-      <x:c r="S21" s="14" t="str">
+      <x:c r="T21" s="14" t="str">
         <x:v>circle</x:v>
       </x:c>
-      <x:c r="T21" s="14" t="str"/>
-      <x:c r="U21" s="14" t="n">
+      <x:c r="U21" s="14" t="str"/>
+      <x:c r="V21" s="14" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="V21" s="14" t="n">
+      <x:c r="W21" s="14" t="n">
         <x:v>0.71</x:v>
       </x:c>
-      <x:c r="W21" s="14" t="n">
+      <x:c r="X21" s="14" t="n">
         <x:v>33.8</x:v>
       </x:c>
-      <x:c r="X21" s="14" t="n">
+      <x:c r="Y21" s="14" t="n">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="Y21" s="14" t="n">
+      <x:c r="Z21" s="14" t="n">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="Z21" s="14" t="n">
+      <x:c r="AA21" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="AA21" s="14" t="n">
+      <x:c r="AB21" s="14" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="AB21" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC21" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD21" s="14" t="n">
         <x:v>0</x:v>
@@ -4265,11 +4320,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AF21" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG21" s="14" t="n">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="AG21" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AH21" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4298,44 +4353,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ21" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR21" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS21" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS21" s="14" t="n">
+      <x:c r="AT21" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT21" s="14" t="n">
+      <x:c r="AU21" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU21" s="14" t="n">
+      <x:c r="AV21" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV21" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AW21" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AX21" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY21" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY21" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AZ21" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.55</x:v>
       </x:c>
       <x:c r="BA21" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="BB21" s="14" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="BC21" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC21" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD21" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4355,9 +4410,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BJ21" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BK21" s="15" t="str">
+        <x:v>6.283</x:v>
+      </x:c>
+      <x:c r="BK21" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL21" s="15" t="str">
         <x:v>data/artifacts/kick.tres</x:v>
       </x:c>
     </x:row>
@@ -4365,77 +4423,75 @@
       <x:c r="A22" s="13" t="str">
         <x:v>long_spear</x:v>
       </x:c>
-      <x:c r="B22" s="14" t="str">
+      <x:c r="B22" s="14" t="str"/>
+      <x:c r="C22" s="14" t="str">
         <x:v>长枪</x:v>
       </x:c>
-      <x:c r="C22" s="14" t="str">
+      <x:c r="D22" s="14" t="str">
         <x:v>向最近敌人方向刺出长距离贯穿枪影，适合安全地穿透成排敌人。</x:v>
       </x:c>
-      <x:c r="D22" s="14" t="str">
+      <x:c r="E22" s="14" t="str">
         <x:v>枪尖光点蓄力，长枪影快速伸长并延伸枪罡直线贯穿。</x:v>
       </x:c>
-      <x:c r="E22" s="14" t="str"/>
       <x:c r="F22" s="14" t="str"/>
       <x:c r="G22" s="14" t="str"/>
       <x:c r="H22" s="14" t="str"/>
-      <x:c r="I22" s="14" t="str">
+      <x:c r="I22" s="14" t="str"/>
+      <x:c r="J22" s="14" t="str">
         <x:v>枪罡终点必定产生小范围冲击波。</x:v>
       </x:c>
-      <x:c r="J22" s="14" t="str">
+      <x:c r="K22" s="14" t="str">
         <x:v>3费极长距离窄直线贯穿。</x:v>
       </x:c>
-      <x:c r="K22" s="14" t="str">
+      <x:c r="L22" s="14" t="str">
         <x:v>windup_time, length, secondary_radius, secondary_damage_mult, trail_length</x:v>
       </x:c>
-      <x:c r="L22" s="14" t="str">
+      <x:c r="M22" s="14" t="str">
         <x:v>剑修</x:v>
       </x:c>
-      <x:c r="M22" s="14" t="str">
+      <x:c r="N22" s="14" t="str">
         <x:v>火</x:v>
       </x:c>
-      <x:c r="N22" s="14" t="str">
+      <x:c r="O22" s="14" t="str">
         <x:v>灵器</x:v>
       </x:c>
-      <x:c r="O22" s="14" t="n">
+      <x:c r="P22" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="P22" s="14" t="str"/>
-      <x:c r="Q22" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R22" s="14" t="str">
+      <x:c r="Q22" s="14" t="str"/>
+      <x:c r="R22" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S22" s="14" t="str">
         <x:v>melee</x:v>
       </x:c>
-      <x:c r="S22" s="14" t="str">
+      <x:c r="T22" s="14" t="str">
         <x:v>stab</x:v>
       </x:c>
-      <x:c r="T22" s="14" t="str"/>
-      <x:c r="U22" s="14" t="n">
+      <x:c r="U22" s="14" t="str"/>
+      <x:c r="V22" s="14" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="V22" s="14" t="n">
+      <x:c r="W22" s="14" t="n">
         <x:v>0.75</x:v>
       </x:c>
-      <x:c r="W22" s="14" t="n">
+      <x:c r="X22" s="14" t="n">
         <x:v>46.67</x:v>
       </x:c>
-      <x:c r="X22" s="14" t="n">
+      <x:c r="Y22" s="14" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="Y22" s="14" t="n">
+      <x:c r="Z22" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="Z22" s="14" t="n">
+      <x:c r="AA22" s="14" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="AA22" s="14" t="n">
+      <x:c r="AB22" s="14" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="AB22" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC22" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD22" s="14" t="n">
         <x:v>0</x:v>
@@ -4477,44 +4533,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ22" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR22" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS22" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS22" s="14" t="n">
+      <x:c r="AT22" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT22" s="14" t="n">
+      <x:c r="AU22" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU22" s="14" t="n">
+      <x:c r="AV22" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV22" s="14" t="n">
+      <x:c r="AW22" s="14" t="n">
         <x:v>0.14</x:v>
       </x:c>
-      <x:c r="AW22" s="14" t="n">
+      <x:c r="AX22" s="14" t="n">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="AX22" s="14" t="n">
+      <x:c r="AY22" s="14" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="AY22" s="14" t="n">
+      <x:c r="AZ22" s="14" t="n">
         <x:v>0.45</x:v>
       </x:c>
-      <x:c r="AZ22" s="14" t="n">
+      <x:c r="BA22" s="14" t="n">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="BA22" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BB22" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BC22" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC22" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD22" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4536,7 +4592,10 @@
       <x:c r="BJ22" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK22" s="15" t="str">
+      <x:c r="BK22" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL22" s="15" t="str">
         <x:v>data/artifacts/long_spear.tres</x:v>
       </x:c>
     </x:row>
@@ -4544,84 +4603,82 @@
       <x:c r="A23" s="13" t="str">
         <x:v>magic_ring</x:v>
       </x:c>
-      <x:c r="B23" s="14" t="str">
+      <x:c r="B23" s="14" t="str"/>
+      <x:c r="C23" s="14" t="str">
         <x:v>法环</x:v>
       </x:c>
-      <x:c r="C23" s="14" t="str">
+      <x:c r="D23" s="14" t="str">
         <x:v>宽大的法环沿直线缓慢穿透敌人，清线稳定但直伤偏低。</x:v>
       </x:c>
-      <x:c r="D23" s="14" t="str">
+      <x:c r="E23" s="14" t="str">
         <x:v>法环展开并蓄力，随后轰出短持续超长直线光束。</x:v>
       </x:c>
-      <x:c r="E23" s="14" t="str"/>
       <x:c r="F23" s="14" t="str"/>
       <x:c r="G23" s="14" t="str"/>
       <x:c r="H23" s="14" t="str"/>
-      <x:c r="I23" s="14" t="str">
+      <x:c r="I23" s="14" t="str"/>
+      <x:c r="J23" s="14" t="str">
         <x:v>主光束路径留下光痕，延迟后整条路径二次爆发。</x:v>
       </x:c>
-      <x:c r="J23" s="14" t="str">
+      <x:c r="K23" s="14" t="str">
         <x:v>2费短前摇、高爆发、贯穿光束。</x:v>
       </x:c>
-      <x:c r="K23" s="14" t="str">
+      <x:c r="L23" s="14" t="str">
         <x:v>windup_time, range, width, secondary_delay, secondary_radius, secondary_damage_mult</x:v>
       </x:c>
-      <x:c r="L23" s="14" t="str">
+      <x:c r="M23" s="14" t="str">
         <x:v>法修</x:v>
       </x:c>
-      <x:c r="M23" s="14" t="str">
+      <x:c r="N23" s="14" t="str">
         <x:v>水</x:v>
       </x:c>
-      <x:c r="N23" s="14" t="str">
+      <x:c r="O23" s="14" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="O23" s="14" t="n">
+      <x:c r="P23" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="P23" s="14" t="str"/>
-      <x:c r="Q23" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R23" s="14" t="str">
+      <x:c r="Q23" s="14" t="str"/>
+      <x:c r="R23" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S23" s="14" t="str">
         <x:v>projectile</x:v>
       </x:c>
-      <x:c r="S23" s="14" t="str">
+      <x:c r="T23" s="14" t="str">
         <x:v>circle</x:v>
       </x:c>
-      <x:c r="T23" s="14" t="str"/>
-      <x:c r="U23" s="14" t="n">
+      <x:c r="U23" s="14" t="str"/>
+      <x:c r="V23" s="14" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="V23" s="14" t="n">
+      <x:c r="W23" s="14" t="n">
         <x:v>1.15</x:v>
       </x:c>
-      <x:c r="W23" s="14" t="n">
+      <x:c r="X23" s="14" t="n">
         <x:v>36.52</x:v>
       </x:c>
-      <x:c r="X23" s="14" t="n">
+      <x:c r="Y23" s="14" t="n">
         <x:v>620</x:v>
       </x:c>
-      <x:c r="Y23" s="14" t="n">
+      <x:c r="Z23" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="Z23" s="14" t="n">
+      <x:c r="AA23" s="14" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="AA23" s="14" t="n">
+      <x:c r="AB23" s="14" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="AB23" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC23" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD23" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE23" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AE23" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AF23" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4656,44 +4713,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ23" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR23" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS23" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS23" s="14" t="n">
+      <x:c r="AT23" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT23" s="14" t="n">
+      <x:c r="AU23" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU23" s="14" t="n">
+      <x:c r="AV23" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV23" s="14" t="n">
+      <x:c r="AW23" s="14" t="n">
         <x:v>0.22</x:v>
       </x:c>
-      <x:c r="AW23" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AX23" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY23" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY23" s="14" t="n">
+      <x:c r="AZ23" s="14" t="n">
         <x:v>0.45</x:v>
       </x:c>
-      <x:c r="AZ23" s="14" t="n">
+      <x:c r="BA23" s="14" t="n">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="BA23" s="14" t="n">
+      <x:c r="BB23" s="14" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="BB23" s="14" t="n">
+      <x:c r="BC23" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC23" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD23" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4715,7 +4772,10 @@
       <x:c r="BJ23" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK23" s="15" t="str">
+      <x:c r="BK23" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL23" s="15" t="str">
         <x:v>data/artifacts/magic_ring.tres</x:v>
       </x:c>
     </x:row>
@@ -4723,77 +4783,75 @@
       <x:c r="A24" s="13" t="str">
         <x:v>one_handed_sword</x:v>
       </x:c>
-      <x:c r="B24" s="14" t="str">
+      <x:c r="B24" s="14" t="str"/>
+      <x:c r="C24" s="14" t="str">
         <x:v>单手剑</x:v>
       </x:c>
-      <x:c r="C24" s="14" t="str">
+      <x:c r="D24" s="14" t="str">
         <x:v>向最近敌人方向挥出近战剑光，伤害和范围都较稳定。</x:v>
       </x:c>
-      <x:c r="D24" s="14" t="str">
+      <x:c r="E24" s="14" t="str">
         <x:v>左右交替短剑光，命中生成短促十字闪光。</x:v>
       </x:c>
-      <x:c r="E24" s="14" t="str"/>
       <x:c r="F24" s="14" t="str"/>
       <x:c r="G24" s="14" t="str"/>
       <x:c r="H24" s="14" t="str"/>
-      <x:c r="I24" s="14" t="str">
+      <x:c r="I24" s="14" t="str"/>
+      <x:c r="J24" s="14" t="str">
         <x:v>每第三击变为X形双斩，额外剑光按secondary_damage_mult造成伤害。</x:v>
       </x:c>
-      <x:c r="J24" s="14" t="str">
+      <x:c r="K24" s="14" t="str">
         <x:v>1费基础剑修，正常范围、正常伤害、正常攻速。</x:v>
       </x:c>
-      <x:c r="K24" s="14" t="str">
+      <x:c r="L24" s="14" t="str">
         <x:v>trail_length, hit_flash_duration, secondary_damage_mult</x:v>
       </x:c>
-      <x:c r="L24" s="14" t="str">
+      <x:c r="M24" s="14" t="str">
         <x:v>剑修</x:v>
       </x:c>
-      <x:c r="M24" s="14" t="str">
+      <x:c r="N24" s="14" t="str">
         <x:v>金</x:v>
       </x:c>
-      <x:c r="N24" s="14" t="str">
+      <x:c r="O24" s="14" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="O24" s="14" t="n">
+      <x:c r="P24" s="14" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="P24" s="14" t="str"/>
-      <x:c r="Q24" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R24" s="14" t="str">
+      <x:c r="Q24" s="14" t="str"/>
+      <x:c r="R24" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S24" s="14" t="str">
         <x:v>melee</x:v>
       </x:c>
-      <x:c r="S24" s="14" t="str">
+      <x:c r="T24" s="14" t="str">
         <x:v>slash</x:v>
       </x:c>
-      <x:c r="T24" s="14" t="str"/>
-      <x:c r="U24" s="14" t="n">
+      <x:c r="U24" s="14" t="str"/>
+      <x:c r="V24" s="14" t="n">
         <x:v>19.5</x:v>
       </x:c>
-      <x:c r="V24" s="14" t="n">
+      <x:c r="W24" s="14" t="n">
         <x:v>0.54</x:v>
       </x:c>
-      <x:c r="W24" s="14" t="n">
+      <x:c r="X24" s="14" t="n">
         <x:v>36.11</x:v>
       </x:c>
-      <x:c r="X24" s="14" t="n">
+      <x:c r="Y24" s="14" t="n">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="Y24" s="14" t="n">
+      <x:c r="Z24" s="14" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="Z24" s="14" t="n">
+      <x:c r="AA24" s="14" t="n">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="AA24" s="14" t="n">
+      <x:c r="AB24" s="14" t="n">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="AB24" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC24" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD24" s="14" t="n">
         <x:v>0</x:v>
@@ -4835,44 +4893,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ24" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR24" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS24" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS24" s="14" t="n">
+      <x:c r="AT24" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT24" s="14" t="n">
+      <x:c r="AU24" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU24" s="14" t="n">
+      <x:c r="AV24" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV24" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AW24" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AX24" s="14" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="AX24" s="14" t="n">
+      <x:c r="AY24" s="14" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="AY24" s="14" t="n">
+      <x:c r="AZ24" s="14" t="n">
         <x:v>0.65</x:v>
       </x:c>
-      <x:c r="AZ24" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BA24" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="BB24" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BC24" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC24" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD24" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4894,7 +4952,10 @@
       <x:c r="BJ24" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK24" s="15" t="str">
+      <x:c r="BK24" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL24" s="15" t="str">
         <x:v>data/artifacts/one_handed_sword.tres</x:v>
       </x:c>
     </x:row>
@@ -4902,69 +4963,75 @@
       <x:c r="A25" s="13" t="str">
         <x:v>palm</x:v>
       </x:c>
-      <x:c r="B25" s="14" t="str">
+      <x:c r="B25" s="14" t="str"/>
+      <x:c r="C25" s="14" t="str">
         <x:v>掌</x:v>
       </x:c>
-      <x:c r="C25" s="14" t="str">
+      <x:c r="D25" s="14" t="str">
         <x:v>挥出掌劲打击前方扇形敌人，并将敌人击退。</x:v>
       </x:c>
-      <x:c r="D25" s="14" t="str"/>
-      <x:c r="E25" s="14" t="str"/>
+      <x:c r="E25" s="14" t="str">
+        <x:v>半透明大掌印短暂凝聚后向前推进，视觉扇形和伤害/击退判定保持一致。</x:v>
+      </x:c>
       <x:c r="F25" s="14" t="str"/>
       <x:c r="G25" s="14" t="str"/>
       <x:c r="H25" s="14" t="str"/>
       <x:c r="I25" s="14" t="str"/>
-      <x:c r="J25" s="14" t="str"/>
-      <x:c r="K25" s="14" t="str"/>
+      <x:c r="J25" s="14" t="str">
+        <x:v>主掌后按secondary_delay追加较淡余劲掌风，按secondary_damage_mult造成低伤并轻击退。</x:v>
+      </x:c>
+      <x:c r="K25" s="14" t="str">
+        <x:v>1费前方扇形控场，伤害中等，主打击退正面敌群。</x:v>
+      </x:c>
       <x:c r="L25" s="14" t="str">
+        <x:v>windup_time, length, width, knockback_force, secondary_delay, secondary_damage_mult, side_projectile_damage_mult</x:v>
+      </x:c>
+      <x:c r="M25" s="14" t="str">
         <x:v>体修</x:v>
       </x:c>
-      <x:c r="M25" s="14" t="str">
+      <x:c r="N25" s="14" t="str">
         <x:v>木</x:v>
       </x:c>
-      <x:c r="N25" s="14" t="str">
+      <x:c r="O25" s="14" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="O25" s="14" t="n">
+      <x:c r="P25" s="14" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="P25" s="14" t="str"/>
-      <x:c r="Q25" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R25" s="14" t="str">
+      <x:c r="Q25" s="14" t="str"/>
+      <x:c r="R25" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S25" s="14" t="str">
         <x:v>melee</x:v>
       </x:c>
-      <x:c r="S25" s="14" t="str">
+      <x:c r="T25" s="14" t="str">
         <x:v>cone</x:v>
       </x:c>
-      <x:c r="T25" s="14" t="str"/>
-      <x:c r="U25" s="14" t="n">
+      <x:c r="U25" s="14" t="str"/>
+      <x:c r="V25" s="14" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="V25" s="14" t="n">
+      <x:c r="W25" s="14" t="n">
         <x:v>0.61</x:v>
       </x:c>
-      <x:c r="W25" s="14" t="n">
+      <x:c r="X25" s="14" t="n">
         <x:v>27.87</x:v>
       </x:c>
-      <x:c r="X25" s="14" t="n">
+      <x:c r="Y25" s="14" t="n">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="Y25" s="14" t="n">
+      <x:c r="Z25" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="Z25" s="14" t="n">
+      <x:c r="AA25" s="14" t="n">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="AA25" s="14" t="n">
+      <x:c r="AB25" s="14" t="n">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="AB25" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC25" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD25" s="14" t="n">
         <x:v>0</x:v>
@@ -4973,11 +5040,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AF25" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG25" s="14" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="AG25" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AH25" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5006,43 +5073,43 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ25" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR25" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS25" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS25" s="14" t="n">
+      <x:c r="AT25" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT25" s="14" t="n">
+      <x:c r="AU25" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU25" s="14" t="n">
+      <x:c r="AV25" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV25" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AW25" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="AX25" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY25" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY25" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AZ25" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.42</x:v>
       </x:c>
       <x:c r="BA25" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="BB25" s="14" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="BC25" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="BD25" s="14" t="n">
         <x:v>0</x:v>
@@ -5065,7 +5132,10 @@
       <x:c r="BJ25" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK25" s="15" t="str">
+      <x:c r="BK25" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL25" s="15" t="str">
         <x:v>data/artifacts/palm.tres</x:v>
       </x:c>
     </x:row>
@@ -5073,85 +5143,83 @@
       <x:c r="A26" s="13" t="str">
         <x:v>poison_bug</x:v>
       </x:c>
-      <x:c r="B26" s="14" t="str">
+      <x:c r="B26" s="14" t="str"/>
+      <x:c r="C26" s="14" t="str">
         <x:v>毒虫</x:v>
       </x:c>
-      <x:c r="C26" s="14" t="str">
+      <x:c r="D26" s="14" t="str">
         <x:v>召唤没有仇恨值的毒虫群。毒虫不会被敌人主动攻击，但仍会被范围伤害波及。毒虫近战撕咬并附加中毒。</x:v>
       </x:c>
-      <x:c r="D26" s="14" t="str">
+      <x:c r="E26" s="14" t="str">
         <x:v>毒色召唤纹路中爬出虫群，低频批量索敌并按槽位分配目标，软分离围攻撕咬并附加不无限叠加中毒。</x:v>
       </x:c>
-      <x:c r="E26" s="14" t="str">
+      <x:c r="F26" s="14" t="str">
         <x:v>低频分批索敌；按槽位分配最近目标；软分离围攻，避免全员完全重叠。</x:v>
       </x:c>
-      <x:c r="F26" s="14" t="str">
+      <x:c r="G26" s="14" t="str">
         <x:v>无仇恨，敌人不会主动锁定。</x:v>
       </x:c>
-      <x:c r="G26" s="14" t="str">
+      <x:c r="H26" s="14" t="str">
         <x:v>可被范围伤害或非锁定伤害波及。</x:v>
       </x:c>
-      <x:c r="H26" s="14" t="str">
+      <x:c r="I26" s="14" t="str">
         <x:v>沿用现有毒虫补充逻辑；不为每只虫单独无限重生。</x:v>
       </x:c>
-      <x:c r="I26" s="14" t="str">
+      <x:c r="J26" s="14" t="str">
         <x:v>数量额外增加；中毒敌人死亡触发小型毒爆，范围=poison_explosion_radius，伤害=poison_explosion_damage_mult，并受delayed_strike_count连锁上限约束。</x:v>
       </x:c>
-      <x:c r="J26" s="14" t="str">
+      <x:c r="K26" s="14" t="str">
         <x:v>5费虫潮数量压制，无仇恨但可被范围伤害波及，沿用现有补充规则。</x:v>
       </x:c>
-      <x:c r="K26" s="14" t="str">
+      <x:c r="L26" s="14" t="str">
         <x:v>summon_base_count, summon_combat_radius, poison_can_stack, poison_explosion_radius, poison_explosion_damage_mult, delayed_strike_count</x:v>
       </x:c>
-      <x:c r="L26" s="14" t="str">
+      <x:c r="M26" s="14" t="str">
         <x:v>召唤</x:v>
       </x:c>
-      <x:c r="M26" s="14" t="str">
+      <x:c r="N26" s="14" t="str">
         <x:v>毒</x:v>
       </x:c>
-      <x:c r="N26" s="14" t="str">
+      <x:c r="O26" s="14" t="str">
         <x:v>仙宝</x:v>
       </x:c>
-      <x:c r="O26" s="14" t="n">
+      <x:c r="P26" s="14" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="P26" s="14" t="str"/>
-      <x:c r="Q26" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R26" s="14" t="str">
+      <x:c r="Q26" s="14" t="str"/>
+      <x:c r="R26" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S26" s="14" t="str">
         <x:v>summon</x:v>
       </x:c>
-      <x:c r="S26" s="14" t="str">
+      <x:c r="T26" s="14" t="str">
         <x:v>stab</x:v>
       </x:c>
-      <x:c r="T26" s="14" t="str"/>
-      <x:c r="U26" s="14" t="n">
+      <x:c r="U26" s="14" t="str"/>
+      <x:c r="V26" s="14" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="V26" s="14" t="n">
+      <x:c r="W26" s="14" t="n">
         <x:v>0.36</x:v>
       </x:c>
-      <x:c r="W26" s="14" t="n">
+      <x:c r="X26" s="14" t="n">
         <x:v>13.89</x:v>
       </x:c>
-      <x:c r="X26" s="14" t="n">
+      <x:c r="Y26" s="14" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="Y26" s="14" t="n">
+      <x:c r="Z26" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="Z26" s="14" t="n">
+      <x:c r="AA26" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="AA26" s="14" t="n">
+      <x:c r="AB26" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="AB26" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC26" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD26" s="14" t="n">
         <x:v>0</x:v>
@@ -5172,65 +5240,65 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AJ26" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK26" s="14" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AK26" s="14" t="n">
+      <x:c r="AL26" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AL26" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AM26" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AN26" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO26" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AO26" s="14" t="n">
+      <x:c r="AP26" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="AP26" s="14" t="n">
+      <x:c r="AQ26" s="14" t="n">
         <x:v>9.5</x:v>
       </x:c>
-      <x:c r="AQ26" s="14" t="n">
+      <x:c r="AR26" s="14" t="n">
         <x:v>2.8</x:v>
       </x:c>
-      <x:c r="AR26" s="14" t="n">
+      <x:c r="AS26" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS26" s="14" t="n">
+      <x:c r="AT26" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT26" s="14" t="n">
+      <x:c r="AU26" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU26" s="14" t="n">
+      <x:c r="AV26" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV26" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AW26" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AX26" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY26" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY26" s="14" t="n">
+      <x:c r="AZ26" s="14" t="n">
         <x:v>0.45</x:v>
       </x:c>
-      <x:c r="AZ26" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BA26" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="BB26" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BC26" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC26" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD26" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5252,7 +5320,10 @@
       <x:c r="BJ26" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK26" s="15" t="str">
+      <x:c r="BK26" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL26" s="15" t="str">
         <x:v>data/artifacts/poison_bug.tres</x:v>
       </x:c>
     </x:row>
@@ -5260,87 +5331,85 @@
       <x:c r="A27" s="13" t="str">
         <x:v>poison_needle</x:v>
       </x:c>
-      <x:c r="B27" s="14" t="str">
+      <x:c r="B27" s="14" t="str"/>
+      <x:c r="C27" s="14" t="str">
         <x:v>毒针</x:v>
       </x:c>
-      <x:c r="C27" s="14" t="str">
+      <x:c r="D27" s="14" t="str">
         <x:v>高速发射毒针，直接伤害较低，但会让敌人持续中毒。</x:v>
       </x:c>
-      <x:c r="D27" s="14" t="str">
+      <x:c r="E27" s="14" t="str">
         <x:v>身侧浮现数根细毒针，短暂停顿后以极短间隔连续射出，命中附加非无限叠加中毒标记。</x:v>
       </x:c>
-      <x:c r="E27" s="14" t="str"/>
       <x:c r="F27" s="14" t="str"/>
       <x:c r="G27" s="14" t="str"/>
       <x:c r="H27" s="14" t="str"/>
-      <x:c r="I27" s="14" t="str">
+      <x:c r="I27" s="14" t="str"/>
+      <x:c r="J27" s="14" t="str">
         <x:v>每delayed_strike_count次普通攻击追加一轮扇形针雨，数量=bounce_count，伤害按secondary_damage_mult。</x:v>
       </x:c>
-      <x:c r="J27" s="14" t="str">
+      <x:c r="K27" s="14" t="str">
         <x:v>2费高频低直伤，主要依靠中毒持续输出，不消耗生命。</x:v>
       </x:c>
-      <x:c r="K27" s="14" t="str">
+      <x:c r="L27" s="14" t="str">
         <x:v>count, delayed_strike_count, delayed_strike_interval, bounce_count, fan_angle, secondary_damage_mult, poison_can_stack</x:v>
       </x:c>
-      <x:c r="L27" s="14" t="str">
+      <x:c r="M27" s="14" t="str">
         <x:v>魔修</x:v>
       </x:c>
-      <x:c r="M27" s="14" t="str">
+      <x:c r="N27" s="14" t="str">
         <x:v>毒</x:v>
       </x:c>
-      <x:c r="N27" s="14" t="str">
+      <x:c r="O27" s="14" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="O27" s="14" t="n">
+      <x:c r="P27" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="P27" s="14" t="str"/>
-      <x:c r="Q27" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R27" s="14" t="str">
-        <x:v>projectile</x:v>
+      <x:c r="Q27" s="14" t="str"/>
+      <x:c r="R27" s="14" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="S27" s="14" t="str">
         <x:v>projectile</x:v>
       </x:c>
-      <x:c r="T27" s="14" t="str"/>
-      <x:c r="U27" s="14" t="n">
+      <x:c r="T27" s="14" t="str">
+        <x:v>projectile</x:v>
+      </x:c>
+      <x:c r="U27" s="14" t="str"/>
+      <x:c r="V27" s="14" t="n">
         <x:v>9.5</x:v>
       </x:c>
-      <x:c r="V27" s="14" t="n">
+      <x:c r="W27" s="14" t="n">
         <x:v>0.46</x:v>
       </x:c>
-      <x:c r="W27" s="14" t="n">
+      <x:c r="X27" s="14" t="n">
         <x:v>20.65</x:v>
       </x:c>
-      <x:c r="X27" s="14" t="n">
+      <x:c r="Y27" s="14" t="n">
         <x:v>500</x:v>
       </x:c>
-      <x:c r="Y27" s="14" t="n">
+      <x:c r="Z27" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="Z27" s="14" t="n">
+      <x:c r="AA27" s="14" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="AA27" s="14" t="n">
+      <x:c r="AB27" s="14" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="AB27" s="14" t="n">
+      <x:c r="AC27" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AC27" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AD27" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AE27" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF27" s="14" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="AF27" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AG27" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5351,13 +5420,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AJ27" s="14" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AK27" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="AL27" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AM27" s="14" t="n">
         <x:v>0</x:v>
@@ -5372,50 +5441,50 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ27" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR27" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS27" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS27" s="14" t="n">
+      <x:c r="AT27" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT27" s="14" t="n">
+      <x:c r="AU27" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU27" s="14" t="n">
+      <x:c r="AV27" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV27" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AW27" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AX27" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY27" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY27" s="14" t="n">
+      <x:c r="AZ27" s="14" t="n">
         <x:v>0.55</x:v>
       </x:c>
-      <x:c r="AZ27" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BA27" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BB27" s="14" t="n">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="BB27" s="14" t="n">
+      <x:c r="BC27" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC27" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD27" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE27" s="14" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="BE27" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BF27" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5431,7 +5500,10 @@
       <x:c r="BJ27" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK27" s="15" t="str">
+      <x:c r="BK27" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL27" s="15" t="str">
         <x:v>data/artifacts/poison_needle.tres</x:v>
       </x:c>
     </x:row>
@@ -5439,69 +5511,75 @@
       <x:c r="A28" s="13" t="str">
         <x:v>roar</x:v>
       </x:c>
-      <x:c r="B28" s="14" t="str">
+      <x:c r="B28" s="14" t="str"/>
+      <x:c r="C28" s="14" t="str">
         <x:v>吼</x:v>
       </x:c>
-      <x:c r="C28" s="14" t="str">
+      <x:c r="D28" s="14" t="str">
         <x:v>向目标方向发出锥形声浪，造成伤害并减速敌人。</x:v>
       </x:c>
-      <x:c r="D28" s="14" t="str"/>
-      <x:c r="E28" s="14" t="str"/>
+      <x:c r="E28" s="14" t="str">
+        <x:v>短蓄气后向目标方向释放多层锥形声浪，扫过敌人时造成伤害并刷新减速。</x:v>
+      </x:c>
       <x:c r="F28" s="14" t="str"/>
       <x:c r="G28" s="14" t="str"/>
       <x:c r="H28" s="14" t="str"/>
       <x:c r="I28" s="14" t="str"/>
-      <x:c r="J28" s="14" t="str"/>
-      <x:c r="K28" s="14" t="str"/>
+      <x:c r="J28" s="14" t="str">
+        <x:v>主声浪后在角色周围追加环形余吼，范围=secondary_radius，伤害按secondary_damage_mult。</x:v>
+      </x:c>
+      <x:c r="K28" s="14" t="str">
+        <x:v>2费中距离锥形控制，偏减速和阻止敌群接近。</x:v>
+      </x:c>
       <x:c r="L28" s="14" t="str">
+        <x:v>windup_time, length, width, fan_angle, slow_percent, debuff_duration, secondary_radius, secondary_damage_mult</x:v>
+      </x:c>
+      <x:c r="M28" s="14" t="str">
         <x:v>体修</x:v>
       </x:c>
-      <x:c r="M28" s="14" t="str">
+      <x:c r="N28" s="14" t="str">
         <x:v>雷</x:v>
       </x:c>
-      <x:c r="N28" s="14" t="str">
+      <x:c r="O28" s="14" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="O28" s="14" t="n">
+      <x:c r="P28" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="P28" s="14" t="str"/>
-      <x:c r="Q28" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R28" s="14" t="str">
+      <x:c r="Q28" s="14" t="str"/>
+      <x:c r="R28" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S28" s="14" t="str">
         <x:v>melee</x:v>
       </x:c>
-      <x:c r="S28" s="14" t="str">
+      <x:c r="T28" s="14" t="str">
         <x:v>cone</x:v>
       </x:c>
-      <x:c r="T28" s="14" t="str"/>
-      <x:c r="U28" s="14" t="n">
+      <x:c r="U28" s="14" t="str"/>
+      <x:c r="V28" s="14" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="V28" s="14" t="n">
+      <x:c r="W28" s="14" t="n">
         <x:v>1.11</x:v>
       </x:c>
-      <x:c r="W28" s="14" t="n">
+      <x:c r="X28" s="14" t="n">
         <x:v>29.73</x:v>
       </x:c>
-      <x:c r="X28" s="14" t="n">
+      <x:c r="Y28" s="14" t="n">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="Y28" s="14" t="n">
+      <x:c r="Z28" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="Z28" s="14" t="n">
+      <x:c r="AA28" s="14" t="n">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="AA28" s="14" t="n">
+      <x:c r="AB28" s="14" t="n">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="AB28" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC28" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD28" s="14" t="n">
         <x:v>0</x:v>
@@ -5510,14 +5588,14 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AF28" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG28" s="14" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="AG28" s="14" t="n">
+      <x:c r="AH28" s="14" t="n">
         <x:v>0.35</x:v>
       </x:c>
-      <x:c r="AH28" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AI28" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5543,49 +5621,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ28" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR28" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS28" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS28" s="14" t="n">
+      <x:c r="AT28" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT28" s="14" t="n">
+      <x:c r="AU28" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU28" s="14" t="n">
+      <x:c r="AV28" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV28" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AW28" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="AX28" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY28" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY28" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AZ28" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="BA28" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="BB28" s="14" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="BC28" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC28" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD28" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="BE28" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BF28" s="14" t="n">
         <x:v>0</x:v>
@@ -5602,7 +5680,10 @@
       <x:c r="BJ28" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK28" s="15" t="str">
+      <x:c r="BK28" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL28" s="15" t="str">
         <x:v>data/artifacts/roar.tres</x:v>
       </x:c>
     </x:row>
@@ -5610,77 +5691,75 @@
       <x:c r="A29" s="13" t="str">
         <x:v>scythe</x:v>
       </x:c>
-      <x:c r="B29" s="14" t="str">
+      <x:c r="B29" s="14" t="str"/>
+      <x:c r="C29" s="14" t="str">
         <x:v>镰刀</x:v>
       </x:c>
-      <x:c r="C29" s="14" t="str">
+      <x:c r="D29" s="14" t="str">
         <x:v>挥动镰刀造成伤害，只有镰刀头部有伤害。造成伤害的一部分会回复生命。</x:v>
       </x:c>
-      <x:c r="D29" s="14" t="str">
+      <x:c r="E29" s="14" t="str">
         <x:v>长柄镰刀后拉后大弧挥砍，仅外圈镰刃环带造成伤害，命中抽出生命丝线回血。</x:v>
       </x:c>
-      <x:c r="E29" s="14" t="str"/>
       <x:c r="F29" s="14" t="str"/>
       <x:c r="G29" s="14" t="str"/>
       <x:c r="H29" s="14" t="str"/>
-      <x:c r="I29" s="14" t="str">
+      <x:c r="I29" s="14" t="str"/>
+      <x:c r="J29" s="14" t="str">
         <x:v>第一轮结束后按secondary_delay反向再挥一轮，第二轮伤害按secondary_damage_mult。</x:v>
       </x:c>
-      <x:c r="J29" s="14" t="str">
+      <x:c r="K29" s="14" t="str">
         <x:v>4费中近距离外圈收割和续航，回血按实际伤害比例并受shield_max单轮上限限制。</x:v>
       </x:c>
-      <x:c r="K29" s="14" t="str">
+      <x:c r="L29" s="14" t="str">
         <x:v>fan_angle, length, width, heal_amount, shield_max, secondary_damage_mult, secondary_delay</x:v>
       </x:c>
-      <x:c r="L29" s="14" t="str">
+      <x:c r="M29" s="14" t="str">
         <x:v>魔修</x:v>
       </x:c>
-      <x:c r="M29" s="14" t="str">
+      <x:c r="N29" s="14" t="str">
         <x:v>水</x:v>
       </x:c>
-      <x:c r="N29" s="14" t="str">
+      <x:c r="O29" s="14" t="str">
         <x:v>灵宝</x:v>
       </x:c>
-      <x:c r="O29" s="14" t="n">
+      <x:c r="P29" s="14" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="P29" s="14" t="str"/>
-      <x:c r="Q29" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R29" s="14" t="str">
+      <x:c r="Q29" s="14" t="str"/>
+      <x:c r="R29" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S29" s="14" t="str">
         <x:v>melee</x:v>
       </x:c>
-      <x:c r="S29" s="14" t="str">
+      <x:c r="T29" s="14" t="str">
         <x:v>head_slash</x:v>
       </x:c>
-      <x:c r="T29" s="14" t="str"/>
-      <x:c r="U29" s="14" t="n">
+      <x:c r="U29" s="14" t="str"/>
+      <x:c r="V29" s="14" t="n">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="V29" s="14" t="n">
+      <x:c r="W29" s="14" t="n">
         <x:v>1.04</x:v>
       </x:c>
-      <x:c r="W29" s="14" t="n">
+      <x:c r="X29" s="14" t="n">
         <x:v>64.42</x:v>
       </x:c>
-      <x:c r="X29" s="14" t="n">
+      <x:c r="Y29" s="14" t="n">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="Y29" s="14" t="n">
+      <x:c r="Z29" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="Z29" s="14" t="n">
+      <x:c r="AA29" s="14" t="n">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="AA29" s="14" t="n">
+      <x:c r="AB29" s="14" t="n">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="AB29" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC29" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD29" s="14" t="n">
         <x:v>0</x:v>
@@ -5689,17 +5768,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AF29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG29" s="14" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="AG29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AH29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AI29" s="14" t="n">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="AI29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AJ29" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5710,11 +5789,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AN29" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AN29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AO29" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5722,50 +5801,50 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ29" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR29" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS29" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS29" s="14" t="n">
+      <x:c r="AT29" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT29" s="14" t="n">
+      <x:c r="AU29" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU29" s="14" t="n">
+      <x:c r="AV29" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AW29" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AX29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY29" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY29" s="14" t="n">
+      <x:c r="AZ29" s="14" t="n">
         <x:v>0.58</x:v>
       </x:c>
-      <x:c r="AZ29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BA29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BB29" s="14" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="BB29" s="14" t="n">
+      <x:c r="BC29" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE29" s="14" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="BE29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BF29" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5776,12 +5855,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BI29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ29" s="14" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="BJ29" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BK29" s="15" t="str">
+      <x:c r="BK29" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL29" s="15" t="str">
         <x:v>data/artifacts/scythe.tres</x:v>
       </x:c>
     </x:row>
@@ -5789,83 +5871,81 @@
       <x:c r="A30" s="13" t="str">
         <x:v>soul_banner</x:v>
       </x:c>
-      <x:c r="B30" s="14" t="str">
+      <x:c r="B30" s="14" t="str"/>
+      <x:c r="C30" s="14" t="str">
         <x:v>招魂幡</x:v>
       </x:c>
-      <x:c r="C30" s="14" t="str">
+      <x:c r="D30" s="14" t="str">
         <x:v>连接多名敌人并压制，持续造成伤害。敌人死亡后化为幽魂冲击其他敌人，接触后爆炸并消失。</x:v>
       </x:c>
-      <x:c r="D30" s="14" t="str">
+      <x:c r="E30" s="14" t="str">
         <x:v>招魂幡连接多名敌人，魂线按tick_interval固定脉冲压制和伤害；被本轮连接/伤害过的敌人死亡生成幽魂冲击。</x:v>
       </x:c>
-      <x:c r="E30" s="14" t="str"/>
       <x:c r="F30" s="14" t="str"/>
       <x:c r="G30" s="14" t="str"/>
       <x:c r="H30" s="14" t="str"/>
-      <x:c r="I30" s="14" t="str">
+      <x:c r="I30" s="14" t="str"/>
+      <x:c r="J30" s="14" t="str">
         <x:v>连接数提升到count，幽魂体积和爆炸范围按secondary_radius放大；累计delayed_strike_count只幽魂释放魂波。</x:v>
       </x:c>
-      <x:c r="J30" s="14" t="str">
+      <x:c r="K30" s="14" t="str">
         <x:v>5费多目标持续压制和拘魂清场，幽魂数量、寿命和搜索范围均有限制。</x:v>
       </x:c>
-      <x:c r="K30" s="14" t="str">
+      <x:c r="L30" s="14" t="str">
         <x:v>max_targets, count, summon_base_count, summon_respawn_time, summon_combat_radius, secondary_damage_mult, secondary_radius, delayed_strike_count, poison_explosion_damage_mult</x:v>
       </x:c>
-      <x:c r="L30" s="14" t="str">
+      <x:c r="M30" s="14" t="str">
         <x:v>魔修</x:v>
       </x:c>
-      <x:c r="M30" s="14" t="str">
+      <x:c r="N30" s="14" t="str">
         <x:v>木</x:v>
       </x:c>
-      <x:c r="N30" s="14" t="str">
+      <x:c r="O30" s="14" t="str">
         <x:v>仙宝</x:v>
       </x:c>
-      <x:c r="O30" s="14" t="n">
+      <x:c r="P30" s="14" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="P30" s="14" t="str"/>
-      <x:c r="Q30" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R30" s="14" t="str">
+      <x:c r="Q30" s="14" t="str"/>
+      <x:c r="R30" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S30" s="14" t="str">
         <x:v>soul_banner</x:v>
       </x:c>
-      <x:c r="S30" s="14" t="str">
+      <x:c r="T30" s="14" t="str">
         <x:v>beam</x:v>
       </x:c>
-      <x:c r="T30" s="14" t="str">
+      <x:c r="U30" s="14" t="str">
         <x:v>slow</x:v>
       </x:c>
-      <x:c r="U30" s="14" t="n">
+      <x:c r="V30" s="14" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="V30" s="14" t="n">
+      <x:c r="W30" s="14" t="n">
         <x:v>2.29</x:v>
       </x:c>
-      <x:c r="W30" s="14" t="n">
+      <x:c r="X30" s="14" t="n">
         <x:v>10.04</x:v>
       </x:c>
-      <x:c r="X30" s="14" t="n">
+      <x:c r="Y30" s="14" t="n">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="Y30" s="14" t="n">
+      <x:c r="Z30" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="Z30" s="14" t="n">
+      <x:c r="AA30" s="14" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="AA30" s="14" t="n">
+      <x:c r="AB30" s="14" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="AB30" s="14" t="n">
+      <x:c r="AC30" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="AC30" s="14" t="n">
+      <x:c r="AD30" s="14" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="AD30" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AE30" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5873,11 +5953,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG30" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH30" s="14" t="n">
         <x:v>0.45</x:v>
       </x:c>
-      <x:c r="AH30" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AI30" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5891,56 +5971,56 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AM30" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AN30" s="14" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="AN30" s="14" t="n">
+      <x:c r="AO30" s="14" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="AO30" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AP30" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ30" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR30" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS30" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS30" s="14" t="n">
+      <x:c r="AT30" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT30" s="14" t="n">
+      <x:c r="AU30" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU30" s="14" t="n">
+      <x:c r="AV30" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV30" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AW30" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AX30" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY30" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY30" s="14" t="n">
+      <x:c r="AZ30" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AZ30" s="14" t="n">
+      <x:c r="BA30" s="14" t="n">
         <x:v>1.35</x:v>
       </x:c>
-      <x:c r="BA30" s="14" t="n">
+      <x:c r="BB30" s="14" t="n">
         <x:v>0.22</x:v>
       </x:c>
-      <x:c r="BB30" s="14" t="n">
+      <x:c r="BC30" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC30" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD30" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5962,7 +6042,10 @@
       <x:c r="BJ30" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK30" s="15" t="str">
+      <x:c r="BK30" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL30" s="15" t="str">
         <x:v>data/artifacts/soul_banner.tres</x:v>
       </x:c>
     </x:row>
@@ -5970,85 +6053,83 @@
       <x:c r="A31" s="13" t="str">
         <x:v>sword_puppet</x:v>
       </x:c>
-      <x:c r="B31" s="14" t="str">
+      <x:c r="B31" s="14" t="str"/>
+      <x:c r="C31" s="14" t="str">
         <x:v>近战傀儡</x:v>
       </x:c>
-      <x:c r="C31" s="14" t="str">
+      <x:c r="D31" s="14" t="str">
         <x:v>召唤持续存在的近战傀儡，追击最近敌人并用近战挥砍。死亡后会在短时间后重生。</x:v>
       </x:c>
-      <x:c r="D31" s="14" t="str">
+      <x:c r="E31" s="14" t="str">
         <x:v>玩家身旁召唤阵显形，木质几何人形落地后追击近敌，近战挥砍产生短刀光和命中闪光。</x:v>
       </x:c>
-      <x:c r="E31" s="14" t="str">
+      <x:c r="F31" s="14" t="str">
         <x:v>主动追击近敌；超过summon_return_radius优先返回玩家附近；轻量软分离。</x:v>
       </x:c>
-      <x:c r="F31" s="14" t="str">
+      <x:c r="G31" s="14" t="str">
         <x:v>有仇恨，可被敌人主动选择。</x:v>
       </x:c>
-      <x:c r="G31" s="14" t="str">
+      <x:c r="H31" s="14" t="str">
         <x:v>可受伤。</x:v>
       </x:c>
-      <x:c r="H31" s="14" t="str">
+      <x:c r="I31" s="14" t="str">
         <x:v>死亡隐藏并禁用碰撞，显示重生印记，summon_respawn_time后在玩家附近满状态重生。</x:v>
       </x:c>
-      <x:c r="I31" s="14" t="str">
+      <x:c r="J31" s="14" t="str">
         <x:v>普通挥砍后按secondary_delay独立冷却触发短距离跃斩，落点按explosion_radius造成范围伤害。</x:v>
       </x:c>
-      <x:c r="J31" s="14" t="str">
+      <x:c r="K31" s="14" t="str">
         <x:v>1费基础前排近战输出，可被攻击，死亡后按summon_respawn_time重生。</x:v>
       </x:c>
-      <x:c r="K31" s="14" t="str">
+      <x:c r="L31" s="14" t="str">
         <x:v>summon_base_count, summon_hp, summon_attack, summon_attack_speed, summon_return_radius, secondary_damage_mult, secondary_radius, secondary_delay, explosion_radius</x:v>
       </x:c>
-      <x:c r="L31" s="14" t="str">
+      <x:c r="M31" s="14" t="str">
         <x:v>召唤</x:v>
       </x:c>
-      <x:c r="M31" s="14" t="str">
+      <x:c r="N31" s="14" t="str">
         <x:v>木</x:v>
       </x:c>
-      <x:c r="N31" s="14" t="str">
+      <x:c r="O31" s="14" t="str">
         <x:v>凡器</x:v>
       </x:c>
-      <x:c r="O31" s="14" t="n">
+      <x:c r="P31" s="14" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="P31" s="14" t="str"/>
-      <x:c r="Q31" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R31" s="14" t="str">
+      <x:c r="Q31" s="14" t="str"/>
+      <x:c r="R31" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S31" s="14" t="str">
         <x:v>summon</x:v>
       </x:c>
-      <x:c r="S31" s="14" t="str">
+      <x:c r="T31" s="14" t="str">
         <x:v>slash</x:v>
       </x:c>
-      <x:c r="T31" s="14" t="str"/>
-      <x:c r="U31" s="14" t="n">
+      <x:c r="U31" s="14" t="str"/>
+      <x:c r="V31" s="14" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="V31" s="14" t="n">
+      <x:c r="W31" s="14" t="n">
         <x:v>0.71</x:v>
       </x:c>
-      <x:c r="W31" s="14" t="n">
+      <x:c r="X31" s="14" t="n">
         <x:v>21.13</x:v>
       </x:c>
-      <x:c r="X31" s="14" t="n">
+      <x:c r="Y31" s="14" t="n">
         <x:v>500</x:v>
       </x:c>
-      <x:c r="Y31" s="14" t="n">
+      <x:c r="Z31" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="Z31" s="14" t="n">
+      <x:c r="AA31" s="14" t="n">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="AA31" s="14" t="n">
+      <x:c r="AB31" s="14" t="n">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="AB31" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC31" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD31" s="14" t="n">
         <x:v>0</x:v>
@@ -6081,53 +6162,53 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AN31" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AO31" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP31" s="14" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="AP31" s="14" t="n">
+      <x:c r="AQ31" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="AQ31" s="14" t="n">
+      <x:c r="AR31" s="14" t="n">
         <x:v>1.4</x:v>
       </x:c>
-      <x:c r="AR31" s="14" t="n">
+      <x:c r="AS31" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS31" s="14" t="n">
+      <x:c r="AT31" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT31" s="14" t="n">
+      <x:c r="AU31" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU31" s="14" t="n">
+      <x:c r="AV31" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV31" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AW31" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AX31" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY31" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY31" s="14" t="n">
+      <x:c r="AZ31" s="14" t="n">
         <x:v>0.55</x:v>
       </x:c>
-      <x:c r="AZ31" s="14" t="n">
+      <x:c r="BA31" s="14" t="n">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BA31" s="14" t="n">
+      <x:c r="BB31" s="14" t="n">
         <x:v>2.8</x:v>
       </x:c>
-      <x:c r="BB31" s="14" t="n">
+      <x:c r="BC31" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC31" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD31" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -6149,7 +6230,10 @@
       <x:c r="BJ31" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK31" s="15" t="str">
+      <x:c r="BK31" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL31" s="15" t="str">
         <x:v>data/artifacts/sword_puppet.tres</x:v>
       </x:c>
     </x:row>
@@ -6161,70 +6245,78 @@
         <x:v>反甲</x:v>
       </x:c>
       <x:c r="C32" s="14" t="str">
-        <x:v>受到伤害时触发，对角色周围敌人造成范围伤害。</x:v>
-      </x:c>
-      <x:c r="D32" s="14" t="str"/>
-      <x:c r="E32" s="14" t="str"/>
+        <x:v>擒龙手</x:v>
+      </x:c>
+      <x:c r="D32" s="14" t="str">
+        <x:v>主动凝出巨手抓向敌群，将普通敌人牵引到中心后握紧砸击，造成高额范围伤害。</x:v>
+      </x:c>
+      <x:c r="E32" s="14" t="str">
+        <x:v>主动凝出半透明巨手，锁定前方/附近密集区域，牵引普通敌人到中心后握紧砸击。</x:v>
+      </x:c>
       <x:c r="F32" s="14" t="str"/>
       <x:c r="G32" s="14" t="str"/>
       <x:c r="H32" s="14" t="str"/>
       <x:c r="I32" s="14" t="str"/>
-      <x:c r="J32" s="14" t="str"/>
-      <x:c r="K32" s="14" t="str"/>
+      <x:c r="J32" s="14" t="str">
+        <x:v>第一只巨手后生成第二只手合击中心，按secondary_damage_mult和secondary_radius造成额外范围伤害。</x:v>
+      </x:c>
+      <x:c r="K32" s="14" t="str">
+        <x:v>4费中距离聚怪与高额控制伤害核心；旧受伤反击机制已取消。</x:v>
+      </x:c>
       <x:c r="L32" s="14" t="str">
+        <x:v>range, radius, max_targets, tick_interval, windup_time, knockback_force, secondary_damage_mult, secondary_radius, secondary_delay</x:v>
+      </x:c>
+      <x:c r="M32" s="14" t="str">
         <x:v>体修</x:v>
       </x:c>
-      <x:c r="M32" s="14" t="str">
+      <x:c r="N32" s="14" t="str">
         <x:v>金</x:v>
       </x:c>
-      <x:c r="N32" s="14" t="str">
+      <x:c r="O32" s="14" t="str">
         <x:v>灵宝</x:v>
       </x:c>
-      <x:c r="O32" s="14" t="n">
+      <x:c r="P32" s="14" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="P32" s="14" t="str"/>
-      <x:c r="Q32" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R32" s="14" t="str">
+      <x:c r="Q32" s="14" t="str"/>
+      <x:c r="R32" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S32" s="14" t="str">
         <x:v>formation</x:v>
       </x:c>
-      <x:c r="S32" s="14" t="str">
+      <x:c r="T32" s="14" t="str">
         <x:v>aura</x:v>
       </x:c>
-      <x:c r="T32" s="14" t="str">
-        <x:v>counter_damage</x:v>
-      </x:c>
-      <x:c r="U32" s="14" t="n">
-        <x:v>55</x:v>
+      <x:c r="U32" s="14" t="str">
+        <x:v>damage</x:v>
       </x:c>
       <x:c r="V32" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="W32" s="14" t="n">
-        <x:v>55</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="X32" s="14" t="n">
-        <x:v>320</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="Y32" s="14" t="n">
-        <x:v>136</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="Z32" s="14" t="n">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="AA32" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="AA32" s="14" t="n">
+      <x:c r="AB32" s="14" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="AB32" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC32" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD32" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="AE32" s="14" t="n">
         <x:v>0</x:v>
@@ -6233,7 +6325,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG32" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="AH32" s="14" t="n">
         <x:v>0</x:v>
@@ -6263,44 +6355,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ32" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR32" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS32" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS32" s="14" t="n">
+      <x:c r="AT32" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT32" s="14" t="n">
+      <x:c r="AU32" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU32" s="14" t="n">
+      <x:c r="AV32" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV32" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AW32" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="AX32" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY32" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY32" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AZ32" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>0.55</x:v>
       </x:c>
       <x:c r="BA32" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="BB32" s="14" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="BC32" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC32" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD32" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -6322,7 +6414,10 @@
       <x:c r="BJ32" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK32" s="15" t="str">
+      <x:c r="BK32" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL32" s="15" t="str">
         <x:v>data/artifacts/thorn_armor.tres</x:v>
       </x:c>
     </x:row>
@@ -6330,85 +6425,83 @@
       <x:c r="A33" s="13" t="str">
         <x:v>turret</x:v>
       </x:c>
-      <x:c r="B33" s="14" t="str">
+      <x:c r="B33" s="14" t="str"/>
+      <x:c r="C33" s="14" t="str">
         <x:v>炮台</x:v>
       </x:c>
-      <x:c r="C33" s="14" t="str">
+      <x:c r="D33" s="14" t="str">
         <x:v>召唤固定炮台自动索敌并发射爆炸炮弹。玩家离开过远时，炮台会延迟重新部署到玩家附近。</x:v>
       </x:c>
-      <x:c r="D33" s="14" t="str">
+      <x:c r="E33" s="14" t="str">
         <x:v>地面部署阵后固定升起，炮管锁敌蓄能发射爆炸炮弹；离玩家超过summon_return_radius后按secondary_delay重新部署。</x:v>
       </x:c>
-      <x:c r="E33" s="14" t="str">
+      <x:c r="F33" s="14" t="str">
         <x:v>固定不移动；自动索敌；玩家离开过远后收起并延迟重新部署。</x:v>
       </x:c>
-      <x:c r="F33" s="14" t="str">
+      <x:c r="G33" s="14" t="str">
         <x:v>有仇恨，保持当前项目默认可被敌人选择。</x:v>
       </x:c>
-      <x:c r="G33" s="14" t="str">
+      <x:c r="H33" s="14" t="str">
         <x:v>可受伤。</x:v>
       </x:c>
-      <x:c r="H33" s="14" t="str">
+      <x:c r="I33" s="14" t="str">
         <x:v>沿用召唤物死亡/重生；另有过远重新部署逻辑。</x:v>
       </x:c>
-      <x:c r="I33" s="14" t="str">
+      <x:c r="J33" s="14" t="str">
         <x:v>增加副炮口，每次攻击极短间隔追加第二枚炮弹，副炮按secondary_damage_mult造成伤害并优先不同目标。</x:v>
       </x:c>
-      <x:c r="J33" s="14" t="str">
+      <x:c r="K33" s="14" t="str">
         <x:v>3费固定远程范围火力，默认可受伤，重新部署期间不攻击。</x:v>
       </x:c>
-      <x:c r="K33" s="14" t="str">
+      <x:c r="L33" s="14" t="str">
         <x:v>summon_return_radius, secondary_delay, explosion_radius, delayed_strike_interval, secondary_damage_mult</x:v>
       </x:c>
-      <x:c r="L33" s="14" t="str">
+      <x:c r="M33" s="14" t="str">
         <x:v>召唤</x:v>
       </x:c>
-      <x:c r="M33" s="14" t="str">
+      <x:c r="N33" s="14" t="str">
         <x:v>火</x:v>
       </x:c>
-      <x:c r="N33" s="14" t="str">
+      <x:c r="O33" s="14" t="str">
         <x:v>灵器</x:v>
       </x:c>
-      <x:c r="O33" s="14" t="n">
+      <x:c r="P33" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="P33" s="14" t="str"/>
-      <x:c r="Q33" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R33" s="14" t="str">
+      <x:c r="Q33" s="14" t="str"/>
+      <x:c r="R33" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S33" s="14" t="str">
         <x:v>summon</x:v>
       </x:c>
-      <x:c r="S33" s="14" t="str">
+      <x:c r="T33" s="14" t="str">
         <x:v>projectile</x:v>
       </x:c>
-      <x:c r="T33" s="14" t="str"/>
-      <x:c r="U33" s="14" t="n">
+      <x:c r="U33" s="14" t="str"/>
+      <x:c r="V33" s="14" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="V33" s="14" t="n">
+      <x:c r="W33" s="14" t="n">
         <x:v>0.89</x:v>
       </x:c>
-      <x:c r="W33" s="14" t="n">
+      <x:c r="X33" s="14" t="n">
         <x:v>20.22</x:v>
       </x:c>
-      <x:c r="X33" s="14" t="n">
+      <x:c r="Y33" s="14" t="n">
         <x:v>700</x:v>
       </x:c>
-      <x:c r="Y33" s="14" t="n">
+      <x:c r="Z33" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="Z33" s="14" t="n">
+      <x:c r="AA33" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="AA33" s="14" t="n">
+      <x:c r="AB33" s="14" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="AB33" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC33" s="14" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD33" s="14" t="n">
         <x:v>0</x:v>
@@ -6441,53 +6534,53 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AN33" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AO33" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP33" s="14" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="AP33" s="14" t="n">
+      <x:c r="AQ33" s="14" t="n">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="AQ33" s="14" t="n">
+      <x:c r="AR33" s="14" t="n">
         <x:v>1.12</x:v>
       </x:c>
-      <x:c r="AR33" s="14" t="n">
+      <x:c r="AS33" s="14" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS33" s="14" t="n">
+      <x:c r="AT33" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT33" s="14" t="n">
+      <x:c r="AU33" s="14" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU33" s="14" t="n">
+      <x:c r="AV33" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV33" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AW33" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AX33" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY33" s="14" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY33" s="14" t="n">
+      <x:c r="AZ33" s="14" t="n">
         <x:v>0.65</x:v>
       </x:c>
-      <x:c r="AZ33" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BA33" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BB33" s="14" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="BB33" s="14" t="n">
+      <x:c r="BC33" s="14" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="BC33" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="BD33" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -6509,7 +6602,10 @@
       <x:c r="BJ33" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK33" s="15" t="str">
+      <x:c r="BK33" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL33" s="15" t="str">
         <x:v>data/artifacts/turret.tres</x:v>
       </x:c>
     </x:row>
@@ -6517,77 +6613,75 @@
       <x:c r="A34" s="16" t="str">
         <x:v>two_handed_sword</x:v>
       </x:c>
-      <x:c r="B34" s="17" t="str">
+      <x:c r="B34" s="17" t="str"/>
+      <x:c r="C34" s="17" t="str">
         <x:v>双手剑</x:v>
       </x:c>
-      <x:c r="C34" s="17" t="str">
+      <x:c r="D34" s="17" t="str">
         <x:v>以较慢节奏挥出沉重剑光，造成高伤害的大范围扇形斩击。</x:v>
       </x:c>
-      <x:c r="D34" s="17" t="str">
+      <x:c r="E34" s="17" t="str">
         <x:v>半透明大剑影短蓄力后重劈，落点保留主剑痕和环形冲击痕。</x:v>
       </x:c>
-      <x:c r="E34" s="17" t="str"/>
       <x:c r="F34" s="17" t="str"/>
       <x:c r="G34" s="17" t="str"/>
       <x:c r="H34" s="17" t="str"/>
-      <x:c r="I34" s="17" t="str">
+      <x:c r="I34" s="17" t="str"/>
+      <x:c r="J34" s="17" t="str">
         <x:v>剑痕约0.5秒后亮起并二次爆裂。</x:v>
       </x:c>
-      <x:c r="J34" s="17" t="str">
+      <x:c r="K34" s="17" t="str">
         <x:v>2费低攻速高单次伤害，带前摇和厚重感。</x:v>
       </x:c>
-      <x:c r="K34" s="17" t="str">
+      <x:c r="L34" s="17" t="str">
         <x:v>windup_time, secondary_delay, secondary_radius, secondary_damage_mult, screen_shake_strength</x:v>
       </x:c>
-      <x:c r="L34" s="17" t="str">
+      <x:c r="M34" s="17" t="str">
         <x:v>剑修</x:v>
       </x:c>
-      <x:c r="M34" s="17" t="str">
+      <x:c r="N34" s="17" t="str">
         <x:v>土</x:v>
       </x:c>
-      <x:c r="N34" s="17" t="str">
+      <x:c r="O34" s="17" t="str">
         <x:v>法器</x:v>
       </x:c>
-      <x:c r="O34" s="17" t="n">
+      <x:c r="P34" s="17" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="P34" s="17" t="str"/>
-      <x:c r="Q34" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R34" s="17" t="str">
+      <x:c r="Q34" s="17" t="str"/>
+      <x:c r="R34" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S34" s="17" t="str">
         <x:v>melee</x:v>
       </x:c>
-      <x:c r="S34" s="17" t="str">
+      <x:c r="T34" s="17" t="str">
         <x:v>slash</x:v>
       </x:c>
-      <x:c r="T34" s="17" t="str"/>
-      <x:c r="U34" s="17" t="n">
+      <x:c r="U34" s="17" t="str"/>
+      <x:c r="V34" s="17" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="V34" s="17" t="n">
+      <x:c r="W34" s="17" t="n">
         <x:v>1.35</x:v>
       </x:c>
-      <x:c r="W34" s="17" t="n">
+      <x:c r="X34" s="17" t="n">
         <x:v>25.93</x:v>
       </x:c>
-      <x:c r="X34" s="17" t="n">
+      <x:c r="Y34" s="17" t="n">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="Y34" s="17" t="n">
+      <x:c r="Z34" s="17" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="Z34" s="17" t="n">
+      <x:c r="AA34" s="17" t="n">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="AA34" s="17" t="n">
+      <x:c r="AB34" s="17" t="n">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="AB34" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC34" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD34" s="17" t="n">
         <x:v>0</x:v>
@@ -6596,11 +6690,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AF34" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG34" s="17" t="n">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="AG34" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AH34" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -6629,43 +6723,43 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AQ34" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR34" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS34" s="17" t="n">
         <x:v>1.55</x:v>
       </x:c>
-      <x:c r="AS34" s="17" t="n">
+      <x:c r="AT34" s="17" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="AT34" s="17" t="n">
+      <x:c r="AU34" s="17" t="n">
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="AU34" s="17" t="n">
+      <x:c r="AV34" s="17" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="AV34" s="17" t="n">
+      <x:c r="AW34" s="17" t="n">
         <x:v>0.24</x:v>
       </x:c>
-      <x:c r="AW34" s="17" t="n">
+      <x:c r="AX34" s="17" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="AX34" s="17" t="n">
+      <x:c r="AY34" s="17" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="AY34" s="17" t="n">
+      <x:c r="AZ34" s="17" t="n">
         <x:v>0.55</x:v>
       </x:c>
-      <x:c r="AZ34" s="17" t="n">
+      <x:c r="BA34" s="17" t="n">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="BA34" s="17" t="n">
-        <x:v>0.5</x:v>
       </x:c>
       <x:c r="BB34" s="17" t="n">
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="BC34" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="BD34" s="17" t="n">
         <x:v>0</x:v>
@@ -6688,7 +6782,10 @@
       <x:c r="BJ34" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BK34" s="18" t="str">
+      <x:c r="BK34" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BL34" s="18" t="str">
         <x:v>data/artifacts/two_handed_sword.tres</x:v>
       </x:c>
     </x:row>
@@ -6950,7 +7047,7 @@
         <x:v>body_barrier</x:v>
       </x:c>
       <x:c r="B8" s="14" t="str">
-        <x:v>罩</x:v>
+        <x:v>气血护体</x:v>
       </x:c>
       <x:c r="C8" s="14" t="n">
         <x:v>1</x:v>
@@ -6982,7 +7079,7 @@
         <x:v>body_barrier</x:v>
       </x:c>
       <x:c r="B9" s="14" t="str">
-        <x:v>罩</x:v>
+        <x:v>气血护体</x:v>
       </x:c>
       <x:c r="C9" s="14" t="n">
         <x:v>2</x:v>
@@ -7014,7 +7111,7 @@
         <x:v>body_barrier</x:v>
       </x:c>
       <x:c r="B10" s="14" t="str">
-        <x:v>罩</x:v>
+        <x:v>气血护体</x:v>
       </x:c>
       <x:c r="C10" s="14" t="n">
         <x:v>3</x:v>
@@ -9674,7 +9771,7 @@
         <x:v>thorn_armor</x:v>
       </x:c>
       <x:c r="B92" s="14" t="str">
-        <x:v>反甲</x:v>
+        <x:v>擒龙手</x:v>
       </x:c>
       <x:c r="C92" s="14" t="n">
         <x:v>1</x:v>
@@ -9689,13 +9786,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G92" s="14" t="n">
-        <x:v>55</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H92" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I92" s="14" t="n">
-        <x:v>55</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J92" s="14" t="str"/>
       <x:c r="K92" s="14" t="str"/>
@@ -9706,7 +9803,7 @@
         <x:v>thorn_armor</x:v>
       </x:c>
       <x:c r="B93" s="14" t="str">
-        <x:v>反甲</x:v>
+        <x:v>擒龙手</x:v>
       </x:c>
       <x:c r="C93" s="14" t="n">
         <x:v>2</x:v>
@@ -9721,13 +9818,13 @@
         <x:v>0.85</x:v>
       </x:c>
       <x:c r="G93" s="14" t="n">
-        <x:v>85.25</x:v>
+        <x:v>108.5</x:v>
       </x:c>
       <x:c r="H93" s="14" t="n">
         <x:v>0.85</x:v>
       </x:c>
       <x:c r="I93" s="14" t="n">
-        <x:v>100.29</x:v>
+        <x:v>127.65</x:v>
       </x:c>
       <x:c r="J93" s="14" t="str"/>
       <x:c r="K93" s="14" t="str"/>
@@ -9738,7 +9835,7 @@
         <x:v>thorn_armor</x:v>
       </x:c>
       <x:c r="B94" s="14" t="str">
-        <x:v>反甲</x:v>
+        <x:v>擒龙手</x:v>
       </x:c>
       <x:c r="C94" s="14" t="n">
         <x:v>3</x:v>
@@ -9753,13 +9850,13 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="G94" s="14" t="n">
-        <x:v>123.75</x:v>
+        <x:v>157.5</x:v>
       </x:c>
       <x:c r="H94" s="14" t="n">
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="I94" s="14" t="n">
-        <x:v>176.79</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="J94" s="14" t="str"/>
       <x:c r="K94" s="14" t="str"/>

--- a/docs/GameBalance.xlsx
+++ b/docs/GameBalance.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="Rfd1e972ae2744fbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法宝总表" sheetId="2" r:id="Ra603700321c1460a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法宝星级预览" sheetId="3" r:id="Rf6dc18897d804e05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命" sheetId="4" r:id="Rde401093ea46448f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奇遇" sheetId="5" r:id="Ra0e6ea25f12b459c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊阈值" sheetId="6" r:id="Rb80342351d274a5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济与修为" sheetId="7" r:id="R925b6596af0b4c47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="Rf9bdc07e4e5b493a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法宝总表" sheetId="2" r:id="Rfe1ddae94fb24f53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法宝星级预览" sheetId="3" r:id="Rec5424fbe51d493f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命" sheetId="4" r:id="R7f486a8ea6ad4708"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奇遇" sheetId="5" r:id="R47d6d2365fe841d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊阈值" sheetId="6" r:id="R7ef2ffd4745e41c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济与修为" sheetId="7" r:id="Ra872cb3927284d3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战场环境" sheetId="8" r:id="R491274d6cf6244f3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,7 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="5">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="0.0%"/>
+  </x:numFmts>
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -47,8 +51,20 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF14532D"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -70,8 +86,18 @@
         <x:fgColor rgb="FF245366"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF14532D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCFCE7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="10">
+  <x:borders count="27">
     <x:border/>
     <x:border>
       <x:right style="thin">
@@ -163,11 +189,213 @@
         <x:color rgb="FFD8DEE8"/>
       </x:top>
     </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="medium">
+        <x:color rgb="FF86EFAC"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF86EFAC"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF86EFAC"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color rgb="FF86EFAC"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF86EFAC"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="medium">
+        <x:color rgb="FF86EFAC"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color rgb="FF86EFAC"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="medium">
+        <x:color rgb="FF86EFAC"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF86EFAC"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF86EFAC"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color rgb="FF86EFAC"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFBBF7D0"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF86EFAC"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="23">
+  <x:cellXfs count="53">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -242,6 +470,44 @@
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
         </x:ext>
       </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -13384,4 +13650,289 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="23.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="5.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="24" t="str">
+        <x:v>战场灵植回血系统配置</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="40" t="str">
+        <x:v>配置ID</x:v>
+      </x:c>
+      <x:c r="B3" s="41" t="str">
+        <x:v>字段</x:v>
+      </x:c>
+      <x:c r="C3" s="41" t="str">
+        <x:v>数值</x:v>
+      </x:c>
+      <x:c r="D3" s="41" t="str">
+        <x:v>单位</x:v>
+      </x:c>
+      <x:c r="E3" s="41" t="str">
+        <x:v>用途</x:v>
+      </x:c>
+      <x:c r="F3" s="42" t="str">
+        <x:v>备注</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="43" t="str">
+        <x:v>healing_plant</x:v>
+      </x:c>
+      <x:c r="B4" s="33" t="str">
+        <x:v>first_spawn_delay</x:v>
+      </x:c>
+      <x:c r="C4" s="33" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D4" s="33" t="str">
+        <x:v>秒</x:v>
+      </x:c>
+      <x:c r="E4" s="49" t="str">
+        <x:v>战斗开始后首次生成延迟</x:v>
+      </x:c>
+      <x:c r="F4" s="50" t="str">
+        <x:v>回春灵植</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="43" t="str">
+        <x:v>healing_plant</x:v>
+      </x:c>
+      <x:c r="B5" s="33" t="str">
+        <x:v>spawn_interval</x:v>
+      </x:c>
+      <x:c r="C5" s="33" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D5" s="33" t="str">
+        <x:v>秒</x:v>
+      </x:c>
+      <x:c r="E5" s="49" t="str">
+        <x:v>后续生成间隔</x:v>
+      </x:c>
+      <x:c r="F5" s="50" t="str">
+        <x:v>生成失败跳过本次</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="43" t="str">
+        <x:v>healing_plant</x:v>
+      </x:c>
+      <x:c r="B6" s="33" t="str">
+        <x:v>max_active</x:v>
+      </x:c>
+      <x:c r="C6" s="33" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="33" t="str">
+        <x:v>株</x:v>
+      </x:c>
+      <x:c r="E6" s="49" t="str">
+        <x:v>场上最多同时存在</x:v>
+      </x:c>
+      <x:c r="F6" s="50" t="str">
+        <x:v>不含已掉落草木精华</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="43" t="str">
+        <x:v>healing_plant</x:v>
+      </x:c>
+      <x:c r="B7" s="33" t="str">
+        <x:v>max_per_wave</x:v>
+      </x:c>
+      <x:c r="C7" s="33" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D7" s="33" t="str">
+        <x:v>株/关</x:v>
+      </x:c>
+      <x:c r="E7" s="49" t="str">
+        <x:v>每关总生成上限</x:v>
+      </x:c>
+      <x:c r="F7" s="50" t="str">
+        <x:v>每关开始重置</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="43" t="str">
+        <x:v>healing_plant</x:v>
+      </x:c>
+      <x:c r="B8" s="33" t="str">
+        <x:v>max_hp</x:v>
+      </x:c>
+      <x:c r="C8" s="33" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D8" s="33" t="str">
+        <x:v>生命值</x:v>
+      </x:c>
+      <x:c r="E8" s="49" t="str">
+        <x:v>灵植可破坏生命值</x:v>
+      </x:c>
+      <x:c r="F8" s="50" t="str">
+        <x:v>中立可破坏物</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="43" t="str">
+        <x:v>healing_plant</x:v>
+      </x:c>
+      <x:c r="B9" s="33" t="str">
+        <x:v>plant_radius</x:v>
+      </x:c>
+      <x:c r="C9" s="33" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D9" s="33" t="str">
+        <x:v>像素</x:v>
+      </x:c>
+      <x:c r="E9" s="49" t="str">
+        <x:v>碰撞和生成占位半径</x:v>
+      </x:c>
+      <x:c r="F9" s="50" t="str">
+        <x:v>不阻挡单位</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="43" t="str">
+        <x:v>healing_plant</x:v>
+      </x:c>
+      <x:c r="B10" s="33" t="str">
+        <x:v>spawn_clearance</x:v>
+      </x:c>
+      <x:c r="C10" s="33" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D10" s="33" t="str">
+        <x:v>像素</x:v>
+      </x:c>
+      <x:c r="E10" s="49" t="str">
+        <x:v>与敌人/其他灵植最小距离</x:v>
+      </x:c>
+      <x:c r="F10" s="50" t="str">
+        <x:v>避免明显重叠</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="43" t="str">
+        <x:v>healing_plant</x:v>
+      </x:c>
+      <x:c r="B11" s="33" t="str">
+        <x:v>player_clearance</x:v>
+      </x:c>
+      <x:c r="C11" s="33" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D11" s="33" t="str">
+        <x:v>像素</x:v>
+      </x:c>
+      <x:c r="E11" s="49" t="str">
+        <x:v>与玩家最小生成距离</x:v>
+      </x:c>
+      <x:c r="F11" s="50" t="str">
+        <x:v>避免贴脸生成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="43" t="str">
+        <x:v>healing_plant</x:v>
+      </x:c>
+      <x:c r="B12" s="33" t="str">
+        <x:v>edge_margin</x:v>
+      </x:c>
+      <x:c r="C12" s="33" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D12" s="33" t="str">
+        <x:v>像素</x:v>
+      </x:c>
+      <x:c r="E12" s="49" t="str">
+        <x:v>距离战场边缘最小距离</x:v>
+      </x:c>
+      <x:c r="F12" s="50" t="str">
+        <x:v>避开敌人出生边缘</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="43" t="str">
+        <x:v>healing_plant</x:v>
+      </x:c>
+      <x:c r="B13" s="33" t="str">
+        <x:v>spawn_attempts</x:v>
+      </x:c>
+      <x:c r="C13" s="33" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D13" s="33" t="str">
+        <x:v>次</x:v>
+      </x:c>
+      <x:c r="E13" s="49" t="str">
+        <x:v>每次生成位置尝试次数</x:v>
+      </x:c>
+      <x:c r="F13" s="50" t="str">
+        <x:v>失败不阻塞战斗</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="43" t="str">
+        <x:v>healing_essence</x:v>
+      </x:c>
+      <x:c r="B14" s="33" t="str">
+        <x:v>essence_heal_ratio</x:v>
+      </x:c>
+      <x:c r="C14" s="35" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="D14" s="33" t="str">
+        <x:v>最大生命百分比</x:v>
+      </x:c>
+      <x:c r="E14" s="49" t="str">
+        <x:v>草木精华单次回血</x:v>
+      </x:c>
+      <x:c r="F14" s="50" t="str">
+        <x:v>至少恢复1点</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="45" t="str">
+        <x:v>healing_essence</x:v>
+      </x:c>
+      <x:c r="B15" s="46" t="str">
+        <x:v>wave_heal_cap_ratio</x:v>
+      </x:c>
+      <x:c r="C15" s="47" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="D15" s="46" t="str">
+        <x:v>最大生命百分比/关</x:v>
+      </x:c>
+      <x:c r="E15" s="51" t="str">
+        <x:v>每关累计回血上限</x:v>
+      </x:c>
+      <x:c r="F15" s="52" t="str">
+        <x:v>每关开始重置</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:F1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>